--- a/11_付费课程/99.资料/文章信息备忘表.xlsx
+++ b/11_付费课程/99.资料/文章信息备忘表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Writing\11_付费课程\99.资料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0268E70-18C7-44E6-93C9-C2BC66D4F071}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6169BD84-7EF5-4A29-AFEC-6E75B89B17B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="870" yWindow="-120" windowWidth="19740" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1535" uniqueCount="1116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1538" uniqueCount="1118">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -4451,6 +4451,14 @@
   </si>
   <si>
     <t>wmic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>36579828</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>网管小贾的禄马生死掌诀</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -10788,9 +10796,18 @@
       </c>
     </row>
     <row r="217" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="C217" s="1" t="s">
+        <v>1117</v>
+      </c>
+      <c r="H217" s="1" t="s">
+        <v>654</v>
+      </c>
       <c r="J217" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
+      </c>
+      <c r="L217" s="2" t="s">
+        <v>1116</v>
       </c>
     </row>
     <row r="218" spans="2:12" x14ac:dyDescent="0.2">

--- a/11_付费课程/99.资料/文章信息备忘表.xlsx
+++ b/11_付费课程/99.资料/文章信息备忘表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Writing\11_付费课程\99.资料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6169BD84-7EF5-4A29-AFEC-6E75B89B17B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B61B2F1E-37ED-4678-BB28-AD1FCC663FB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="870" yWindow="-120" windowWidth="19740" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1538" uniqueCount="1118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1542" uniqueCount="1121">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -4434,10 +4434,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>scoop</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>2024-09-17 19:51:32</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -4459,6 +4455,22 @@
   </si>
   <si>
     <t>网管小贾的禄马生死掌诀</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>94649807</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>试用免费界面美化程序SeelenUI，让你的Windows变得更美</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1118</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一款全看个人造化的Windows命令行软件下载安装管理器：Scoop</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -10747,34 +10759,46 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="213" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="213" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B213" s="4" t="s">
         <v>1110</v>
       </c>
       <c r="C213" s="1" t="s">
-        <v>1111</v>
+        <v>1120</v>
       </c>
       <c r="H213" s="1" t="s">
         <v>21</v>
       </c>
       <c r="I213" s="4" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="J213" s="5" t="str">
         <f t="shared" si="5"/>
         <v>001117</v>
       </c>
       <c r="K213" s="3" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="L213" s="2" t="s">
         <v>1109</v>
       </c>
     </row>
-    <row r="214" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="214" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="B214" s="4" t="s">
+        <v>1119</v>
+      </c>
+      <c r="C214" s="1" t="s">
+        <v>1118</v>
+      </c>
+      <c r="H214" s="1" t="s">
+        <v>654</v>
+      </c>
       <c r="J214" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>00</v>
+        <v>001118</v>
+      </c>
+      <c r="L214" s="2" t="s">
+        <v>1117</v>
       </c>
     </row>
     <row r="215" spans="2:12" x14ac:dyDescent="0.2">
@@ -10785,19 +10809,19 @@
     </row>
     <row r="216" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C216" s="1" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="J216" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
       <c r="L216" s="2" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="217" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C217" s="1" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="H217" s="1" t="s">
         <v>654</v>
@@ -10807,7 +10831,7 @@
         <v>00</v>
       </c>
       <c r="L217" s="2" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="218" spans="2:12" x14ac:dyDescent="0.2">

--- a/11_付费课程/99.资料/文章信息备忘表.xlsx
+++ b/11_付费课程/99.资料/文章信息备忘表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Writing\11_付费课程\99.资料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B61B2F1E-37ED-4678-BB28-AD1FCC663FB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5EAAC45-D6D4-4F26-88DF-F6FE4E267DD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="870" yWindow="-120" windowWidth="19740" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1542" uniqueCount="1121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1545" uniqueCount="1124">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -4471,6 +4471,18 @@
   </si>
   <si>
     <t>一款全看个人造化的Windows命令行软件下载安装管理器：Scoop</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WindowsTerminal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>02474746</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1119</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4963,7 +4975,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:M318"/>
+  <dimension ref="A2:M317"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.25" style="8" customWidth="1"/>
@@ -10389,7 +10401,7 @@
         <v>1029</v>
       </c>
       <c r="J197" s="5" t="str">
-        <f t="shared" ref="J197:J260" si="5">"00"&amp;B197</f>
+        <f t="shared" ref="J197:J259" si="5">"00"&amp;B197</f>
         <v>001099</v>
       </c>
       <c r="K197" s="3" t="s">
@@ -10783,12 +10795,12 @@
         <v>1109</v>
       </c>
     </row>
-    <row r="214" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="214" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B214" s="4" t="s">
         <v>1119</v>
       </c>
       <c r="C214" s="1" t="s">
-        <v>1118</v>
+        <v>1116</v>
       </c>
       <c r="H214" s="1" t="s">
         <v>654</v>
@@ -10798,13 +10810,25 @@
         <v>001118</v>
       </c>
       <c r="L214" s="2" t="s">
-        <v>1117</v>
-      </c>
-    </row>
-    <row r="215" spans="2:12" x14ac:dyDescent="0.2">
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="215" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="B215" s="4" t="s">
+        <v>1123</v>
+      </c>
+      <c r="C215" s="1" t="s">
+        <v>1118</v>
+      </c>
+      <c r="H215" s="1" t="s">
+        <v>654</v>
+      </c>
       <c r="J215" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>00</v>
+        <v>001119</v>
+      </c>
+      <c r="L215" s="2" t="s">
+        <v>1117</v>
       </c>
     </row>
     <row r="216" spans="2:12" x14ac:dyDescent="0.2">
@@ -10821,17 +10845,14 @@
     </row>
     <row r="217" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C217" s="1" t="s">
-        <v>1116</v>
-      </c>
-      <c r="H217" s="1" t="s">
-        <v>654</v>
+        <v>1121</v>
       </c>
       <c r="J217" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
       <c r="L217" s="2" t="s">
-        <v>1115</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="218" spans="2:12" x14ac:dyDescent="0.2">
@@ -11088,13 +11109,13 @@
     </row>
     <row r="260" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J260" s="5" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="J260:J317" si="6">"00"&amp;B260</f>
         <v>00</v>
       </c>
     </row>
     <row r="261" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J261" s="5" t="str">
-        <f t="shared" ref="J261:J318" si="6">"00"&amp;B261</f>
+        <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
@@ -11430,12 +11451,6 @@
     </row>
     <row r="317" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J317" s="5" t="str">
-        <f t="shared" si="6"/>
-        <v>00</v>
-      </c>
-    </row>
-    <row r="318" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J318" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>

--- a/11_付费课程/99.资料/文章信息备忘表.xlsx
+++ b/11_付费课程/99.资料/文章信息备忘表.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Writing\11_付费课程\99.资料\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\writing\11_付费课程\99.资料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5EAAC45-D6D4-4F26-88DF-F6FE4E267DD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="870" yWindow="-120" windowWidth="19740" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1910" yWindow="-120" windowWidth="19740" windowHeight="11760"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$L$4</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -40,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1545" uniqueCount="1124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1547" uniqueCount="1126">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -4483,13 +4482,21 @@
   </si>
   <si>
     <t>1119</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-11-10 21:33:02</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>203312</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -4974,24 +4981,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A2:M317"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.25" style="8" customWidth="1"/>
-    <col min="2" max="2" width="6.625" style="4" customWidth="1"/>
-    <col min="3" max="3" width="30.875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="8.125" style="6" customWidth="1"/>
+    <col min="2" max="2" width="6.58203125" style="4" customWidth="1"/>
+    <col min="3" max="3" width="30.83203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="8.08203125" style="6" customWidth="1"/>
     <col min="5" max="7" width="8.75" style="6" customWidth="1"/>
-    <col min="8" max="8" width="9.125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="9.08203125" style="1" customWidth="1"/>
     <col min="9" max="9" width="19" style="4" customWidth="1"/>
-    <col min="10" max="10" width="14.625" style="5" customWidth="1"/>
-    <col min="11" max="11" width="10.875" style="3" customWidth="1"/>
+    <col min="10" max="10" width="14.58203125" style="5" customWidth="1"/>
+    <col min="11" max="11" width="10.83203125" style="3" customWidth="1"/>
     <col min="12" max="12" width="13.75" style="2" customWidth="1"/>
     <col min="13" max="13" width="16.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" ht="25" x14ac:dyDescent="0.3">
       <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
@@ -5007,8 +5014,8 @@
       <c r="K2" s="20"/>
       <c r="L2" s="20"/>
     </row>
-    <row r="3" spans="1:12" ht="6.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="4" spans="1:12" s="7" customFormat="1" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12" ht="6.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:12" s="7" customFormat="1" ht="28" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>0</v>
       </c>
@@ -5046,7 +5053,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
         <v>557</v>
       </c>
@@ -5073,7 +5080,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
         <v>559</v>
       </c>
@@ -5109,7 +5116,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
         <v>559</v>
       </c>
@@ -5145,25 +5152,25 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="J8" s="5" t="str">
         <f t="shared" si="0"/>
         <v>000</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="J9" s="5" t="str">
         <f t="shared" si="0"/>
         <v>000</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="J10" s="5" t="str">
         <f t="shared" si="0"/>
         <v>000</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
         <v>522</v>
       </c>
@@ -5196,7 +5203,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
         <v>558</v>
       </c>
@@ -5226,7 +5233,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A13" s="8" t="s">
         <v>558</v>
       </c>
@@ -5256,7 +5263,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A14" s="8" t="s">
         <v>640</v>
       </c>
@@ -5283,7 +5290,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="8" t="s">
         <v>557</v>
       </c>
@@ -5310,7 +5317,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="8" t="s">
         <v>557</v>
       </c>
@@ -5337,7 +5344,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="8" t="s">
         <v>557</v>
       </c>
@@ -5364,7 +5371,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="8" t="s">
         <v>767</v>
       </c>
@@ -5391,7 +5398,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
         <v>557</v>
       </c>
@@ -5418,7 +5425,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A20" s="8" t="s">
         <v>557</v>
       </c>
@@ -5445,7 +5452,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A21" s="8" t="s">
         <v>557</v>
       </c>
@@ -5472,7 +5479,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A22" s="8" t="s">
         <v>559</v>
       </c>
@@ -5508,7 +5515,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" s="8" t="s">
         <v>557</v>
       </c>
@@ -5535,7 +5542,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A24" s="8" t="s">
         <v>558</v>
       </c>
@@ -5565,7 +5572,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A25" s="8" t="s">
         <v>557</v>
       </c>
@@ -5592,7 +5599,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A26" s="8" t="s">
         <v>557</v>
       </c>
@@ -5619,7 +5626,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="27" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A27" s="8" t="s">
         <v>633</v>
       </c>
@@ -5646,7 +5653,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A28" s="8" t="s">
         <v>557</v>
       </c>
@@ -5673,7 +5680,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A29" s="8" t="s">
         <v>559</v>
       </c>
@@ -5709,7 +5716,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A30" s="8" t="s">
         <v>559</v>
       </c>
@@ -5745,7 +5752,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A31" s="8" t="s">
         <v>557</v>
       </c>
@@ -5772,7 +5779,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A32" s="8" t="s">
         <v>557</v>
       </c>
@@ -5799,7 +5806,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A33" s="8" t="s">
         <v>557</v>
       </c>
@@ -5826,7 +5833,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="34" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A34" s="8" t="s">
         <v>557</v>
       </c>
@@ -5853,7 +5860,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="35" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A35" s="8" t="s">
         <v>557</v>
       </c>
@@ -5880,7 +5887,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="36" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A36" s="8" t="s">
         <v>557</v>
       </c>
@@ -5907,7 +5914,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="37" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A37" s="8" t="s">
         <v>559</v>
       </c>
@@ -5943,7 +5950,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="38" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A38" s="8" t="s">
         <v>557</v>
       </c>
@@ -5970,7 +5977,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" s="8" t="s">
         <v>557</v>
       </c>
@@ -5997,7 +6004,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="40" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A40" s="8" t="s">
         <v>557</v>
       </c>
@@ -6024,7 +6031,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="41" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A41" s="8" t="s">
         <v>557</v>
       </c>
@@ -6051,7 +6058,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="42" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A42" s="8" t="s">
         <v>557</v>
       </c>
@@ -6078,7 +6085,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="43" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A43" s="8" t="s">
         <v>559</v>
       </c>
@@ -6111,7 +6118,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="44" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A44" s="8" t="s">
         <v>557</v>
       </c>
@@ -6138,7 +6145,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="45" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A45" s="8" t="s">
         <v>557</v>
       </c>
@@ -6165,7 +6172,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="46" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A46" s="8" t="s">
         <v>557</v>
       </c>
@@ -6192,7 +6199,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" s="8" t="s">
         <v>557</v>
       </c>
@@ -6219,7 +6226,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="48" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A48" s="8" t="s">
         <v>557</v>
       </c>
@@ -6246,7 +6253,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="49" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A49" s="8" t="s">
         <v>557</v>
       </c>
@@ -6273,7 +6280,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="50" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A50" s="8" t="s">
         <v>557</v>
       </c>
@@ -6300,7 +6307,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" s="8" t="s">
         <v>557</v>
       </c>
@@ -6327,7 +6334,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="52" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A52" s="8" t="s">
         <v>557</v>
       </c>
@@ -6354,7 +6361,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" s="8" t="s">
         <v>557</v>
       </c>
@@ -6381,7 +6388,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="54" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A54" s="8" t="s">
         <v>557</v>
       </c>
@@ -6408,7 +6415,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" s="8" t="s">
         <v>557</v>
       </c>
@@ -6435,7 +6442,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="56" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A56" s="8" t="s">
         <v>559</v>
       </c>
@@ -6471,7 +6478,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="57" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A57" s="8" t="s">
         <v>559</v>
       </c>
@@ -6507,7 +6514,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="58" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A58" s="8" t="s">
         <v>557</v>
       </c>
@@ -6534,7 +6541,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="59" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A59" s="8" t="s">
         <v>558</v>
       </c>
@@ -6564,7 +6571,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="60" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A60" s="8" t="s">
         <v>557</v>
       </c>
@@ -6591,7 +6598,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="61" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B61" s="4" t="s">
         <v>298</v>
       </c>
@@ -6624,7 +6631,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="62" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B62" s="4" t="s">
         <v>294</v>
       </c>
@@ -6657,7 +6664,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="63" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B63" s="4" t="s">
         <v>289</v>
       </c>
@@ -6690,7 +6697,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="64" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A64" s="8" t="s">
         <v>557</v>
       </c>
@@ -6717,7 +6724,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="65" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A65" s="8" t="s">
         <v>557</v>
       </c>
@@ -6744,7 +6751,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="66" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A66" s="8" t="s">
         <v>559</v>
       </c>
@@ -6780,7 +6787,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="67" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A67" s="8" t="s">
         <v>557</v>
       </c>
@@ -6807,7 +6814,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="68" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A68" s="8" t="s">
         <v>558</v>
       </c>
@@ -6837,7 +6844,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="69" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A69" s="8" t="s">
         <v>559</v>
       </c>
@@ -6864,7 +6871,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="70" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A70" s="8" t="s">
         <v>559</v>
       </c>
@@ -6891,7 +6898,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="71" spans="1:12" ht="57" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:12" ht="56" x14ac:dyDescent="0.3">
       <c r="A71" s="8" t="s">
         <v>558</v>
       </c>
@@ -6921,7 +6928,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="72" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A72" s="8" t="s">
         <v>558</v>
       </c>
@@ -6951,7 +6958,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="73" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A73" s="8" t="s">
         <v>558</v>
       </c>
@@ -6981,7 +6988,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="74" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A74" s="8" t="s">
         <v>557</v>
       </c>
@@ -7008,7 +7015,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="75" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A75" s="8" t="s">
         <v>557</v>
       </c>
@@ -7035,7 +7042,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="76" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A76" s="8" t="s">
         <v>558</v>
       </c>
@@ -7068,7 +7075,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="77" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A77" s="8" t="s">
         <v>557</v>
       </c>
@@ -7095,7 +7102,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="78" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A78" s="8" t="s">
         <v>558</v>
       </c>
@@ -7122,7 +7129,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="79" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A79" s="8" t="s">
         <v>557</v>
       </c>
@@ -7149,7 +7156,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="80" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A80" s="8" t="s">
         <v>558</v>
       </c>
@@ -7176,7 +7183,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="81" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A81" s="8" t="s">
         <v>557</v>
       </c>
@@ -7203,7 +7210,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="82" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A82" s="8" t="s">
         <v>557</v>
       </c>
@@ -7230,7 +7237,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="83" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A83" s="8" t="s">
         <v>557</v>
       </c>
@@ -7257,7 +7264,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="84" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A84" s="8" t="s">
         <v>557</v>
       </c>
@@ -7284,7 +7291,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="85" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A85" s="8" t="s">
         <v>558</v>
       </c>
@@ -7311,7 +7318,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="86" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A86" s="8" t="s">
         <v>557</v>
       </c>
@@ -7338,7 +7345,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="87" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A87" s="8" t="s">
         <v>559</v>
       </c>
@@ -7374,7 +7381,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="88" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A88" s="8" t="s">
         <v>559</v>
       </c>
@@ -7410,7 +7417,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="89" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A89" s="8" t="s">
         <v>559</v>
       </c>
@@ -7446,7 +7453,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="90" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A90" s="8" t="s">
         <v>557</v>
       </c>
@@ -7473,7 +7480,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="91" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B91" s="4" t="s">
         <v>151</v>
       </c>
@@ -7506,7 +7513,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="92" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B92" s="4" t="s">
         <v>146</v>
       </c>
@@ -7539,7 +7546,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="93" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B93" s="4" t="s">
         <v>140</v>
       </c>
@@ -7572,7 +7579,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="94" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B94" s="4" t="s">
         <v>135</v>
       </c>
@@ -7605,7 +7612,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="95" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A95" s="8" t="s">
         <v>558</v>
       </c>
@@ -7632,7 +7639,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="96" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="B96" s="4" t="s">
         <v>123</v>
       </c>
@@ -7665,7 +7672,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="97" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B97" s="4" t="s">
         <v>118</v>
       </c>
@@ -7698,7 +7705,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="98" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="B98" s="4" t="s">
         <v>112</v>
       </c>
@@ -7731,7 +7738,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="99" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B99" s="4" t="s">
         <v>109</v>
       </c>
@@ -7764,7 +7771,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="100" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B100" s="4" t="s">
         <v>104</v>
       </c>
@@ -7797,7 +7804,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="101" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="B101" s="4" t="s">
         <v>98</v>
       </c>
@@ -7830,7 +7837,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="102" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B102" s="4" t="s">
         <v>92</v>
       </c>
@@ -7863,7 +7870,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="103" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A103" s="8" t="s">
         <v>559</v>
       </c>
@@ -7899,7 +7906,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="104" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A104" s="8" t="s">
         <v>557</v>
       </c>
@@ -7926,7 +7933,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="105" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A105" s="8" t="s">
         <v>557</v>
       </c>
@@ -7953,7 +7960,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="106" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A106" s="8" t="s">
         <v>557</v>
       </c>
@@ -7980,7 +7987,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="107" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A107" s="8" t="s">
         <v>557</v>
       </c>
@@ -8007,7 +8014,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="108" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A108" s="8" t="s">
         <v>557</v>
       </c>
@@ -8034,7 +8041,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="109" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A109" s="8" t="s">
         <v>559</v>
       </c>
@@ -8070,7 +8077,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A110" s="8" t="s">
         <v>558</v>
       </c>
@@ -8097,7 +8104,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="111" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A111" s="8" t="s">
         <v>557</v>
       </c>
@@ -8124,7 +8131,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="112" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A112" s="8" t="s">
         <v>557</v>
       </c>
@@ -8151,7 +8158,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="113" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A113" s="8" t="s">
         <v>557</v>
       </c>
@@ -8178,7 +8185,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A114" s="8" t="s">
         <v>557</v>
       </c>
@@ -8205,7 +8212,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="115" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A115" s="8" t="s">
         <v>557</v>
       </c>
@@ -8232,7 +8239,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="116" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A116" s="8" t="s">
         <v>559</v>
       </c>
@@ -8268,7 +8275,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="117" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A117" s="8" t="s">
         <v>557</v>
       </c>
@@ -8295,7 +8302,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="118" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A118" s="8" t="s">
         <v>558</v>
       </c>
@@ -8325,7 +8332,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="119" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A119" s="8" t="s">
         <v>557</v>
       </c>
@@ -8352,7 +8359,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="120" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A120" s="8" t="s">
         <v>557</v>
       </c>
@@ -8379,7 +8386,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="121" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A121" s="8" t="s">
         <v>597</v>
       </c>
@@ -8406,7 +8413,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="122" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A122" s="8" t="s">
         <v>602</v>
       </c>
@@ -8433,7 +8440,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="123" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A123" s="8" t="s">
         <v>608</v>
       </c>
@@ -8460,7 +8467,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="124" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A124" s="8" t="s">
         <v>611</v>
       </c>
@@ -8487,7 +8494,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="125" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A125" s="8" t="s">
         <v>617</v>
       </c>
@@ -8514,7 +8521,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="126" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A126" s="8" t="s">
         <v>624</v>
       </c>
@@ -8541,7 +8548,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="127" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A127" s="8" t="s">
         <v>557</v>
       </c>
@@ -8568,7 +8575,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="128" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A128" s="8" t="s">
         <v>649</v>
       </c>
@@ -8595,7 +8602,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="129" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A129" s="8" t="s">
         <v>653</v>
       </c>
@@ -8622,7 +8629,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="130" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A130" s="8" t="s">
         <v>659</v>
       </c>
@@ -8649,7 +8656,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="131" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A131" s="8" t="s">
         <v>664</v>
       </c>
@@ -8676,7 +8683,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A132" s="8" t="s">
         <v>557</v>
       </c>
@@ -8703,7 +8710,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="133" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A133" s="8" t="s">
         <v>557</v>
       </c>
@@ -8730,7 +8737,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="134" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A134" s="8" t="s">
         <v>681</v>
       </c>
@@ -8757,7 +8764,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="135" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A135" s="8" t="s">
         <v>687</v>
       </c>
@@ -8784,7 +8791,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="136" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A136" s="8" t="s">
         <v>691</v>
       </c>
@@ -8811,7 +8818,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="137" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A137" s="8" t="s">
         <v>699</v>
       </c>
@@ -8838,7 +8845,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="138" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A138" s="8" t="s">
         <v>704</v>
       </c>
@@ -8865,7 +8872,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="139" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A139" s="8" t="s">
         <v>711</v>
       </c>
@@ -8892,7 +8899,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="140" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A140" s="8" t="s">
         <v>716</v>
       </c>
@@ -8919,7 +8926,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="141" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A141" s="8" t="s">
         <v>724</v>
       </c>
@@ -8946,7 +8953,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="142" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A142" s="8" t="s">
         <v>727</v>
       </c>
@@ -8973,7 +8980,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="143" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A143" s="8" t="s">
         <v>736</v>
       </c>
@@ -9000,7 +9007,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="144" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A144" s="8" t="s">
         <v>740</v>
       </c>
@@ -9027,7 +9034,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="145" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A145" s="8" t="s">
         <v>746</v>
       </c>
@@ -9054,7 +9061,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="146" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A146" s="8" t="s">
         <v>754</v>
       </c>
@@ -9081,7 +9088,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="147" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A147" s="8" t="s">
         <v>759</v>
       </c>
@@ -9108,7 +9115,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="148" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A148" s="8" t="s">
         <v>770</v>
       </c>
@@ -9135,7 +9142,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="149" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A149" s="8" t="s">
         <v>777</v>
       </c>
@@ -9162,7 +9169,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="150" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A150" s="8" t="s">
         <v>782</v>
       </c>
@@ -9189,7 +9196,7 @@
         <v>786</v>
       </c>
     </row>
-    <row r="151" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A151" s="8" t="s">
         <v>557</v>
       </c>
@@ -9216,7 +9223,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="152" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A152" s="8" t="s">
         <v>795</v>
       </c>
@@ -9243,7 +9250,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A153" s="8" t="s">
         <v>800</v>
       </c>
@@ -9270,7 +9277,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A154" s="8" t="s">
         <v>804</v>
       </c>
@@ -9297,7 +9304,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A155" s="8" t="s">
         <v>811</v>
       </c>
@@ -9324,7 +9331,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="156" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A156" s="8" t="s">
         <v>557</v>
       </c>
@@ -9351,7 +9358,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A157" s="8" t="s">
         <v>557</v>
       </c>
@@ -9378,7 +9385,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A158" s="8" t="s">
         <v>827</v>
       </c>
@@ -9405,7 +9412,7 @@
         <v>831</v>
       </c>
     </row>
-    <row r="159" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A159" s="8" t="s">
         <v>557</v>
       </c>
@@ -9432,7 +9439,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A160" s="8" t="s">
         <v>838</v>
       </c>
@@ -9459,7 +9466,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="161" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A161" s="8" t="s">
         <v>557</v>
       </c>
@@ -9486,7 +9493,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A162" s="8" t="s">
         <v>850</v>
       </c>
@@ -9513,7 +9520,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A163" s="8" t="s">
         <v>857</v>
       </c>
@@ -9540,7 +9547,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A164" s="8" t="s">
         <v>557</v>
       </c>
@@ -9567,7 +9574,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="165" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A165" s="8" t="s">
         <v>557</v>
       </c>
@@ -9594,7 +9601,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A166" s="8" t="s">
         <v>557</v>
       </c>
@@ -9621,7 +9628,7 @@
         <v>871</v>
       </c>
     </row>
-    <row r="167" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A167" s="8" t="s">
         <v>557</v>
       </c>
@@ -9648,7 +9655,7 @@
         <v>879</v>
       </c>
     </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A168" s="8" t="s">
         <v>557</v>
       </c>
@@ -9675,7 +9682,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A169" s="8" t="s">
         <v>557</v>
       </c>
@@ -9702,7 +9709,7 @@
         <v>889</v>
       </c>
     </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A170" s="8" t="s">
         <v>557</v>
       </c>
@@ -9729,7 +9736,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A171" s="8" t="s">
         <v>557</v>
       </c>
@@ -9756,7 +9763,7 @@
         <v>897</v>
       </c>
     </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A172" s="8" t="s">
         <v>902</v>
       </c>
@@ -9783,7 +9790,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A173" s="8" t="s">
         <v>902</v>
       </c>
@@ -9810,7 +9817,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A174" s="8" t="s">
         <v>557</v>
       </c>
@@ -9837,7 +9844,7 @@
         <v>915</v>
       </c>
     </row>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A175" s="8" t="s">
         <v>557</v>
       </c>
@@ -9864,7 +9871,7 @@
         <v>919</v>
       </c>
     </row>
-    <row r="176" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A176" s="8" t="s">
         <v>557</v>
       </c>
@@ -9891,7 +9898,7 @@
         <v>925</v>
       </c>
     </row>
-    <row r="177" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A177" s="8" t="s">
         <v>557</v>
       </c>
@@ -9918,7 +9925,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="178" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:13" ht="28" x14ac:dyDescent="0.3">
       <c r="A178" s="8" t="s">
         <v>557</v>
       </c>
@@ -9945,7 +9952,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="179" spans="1:13" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:13" ht="42" x14ac:dyDescent="0.3">
       <c r="A179" s="8" t="s">
         <v>938</v>
       </c>
@@ -9972,7 +9979,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="180" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B180" s="4" t="s">
         <v>942</v>
       </c>
@@ -9996,7 +10003,7 @@
         <v>946</v>
       </c>
     </row>
-    <row r="181" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:13" ht="28" x14ac:dyDescent="0.3">
       <c r="B181" s="4" t="s">
         <v>948</v>
       </c>
@@ -10020,7 +10027,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="182" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:13" ht="28" x14ac:dyDescent="0.3">
       <c r="B182" s="4" t="s">
         <v>954</v>
       </c>
@@ -10044,7 +10051,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="183" spans="1:13" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:13" ht="42" x14ac:dyDescent="0.3">
       <c r="B183" s="4" t="s">
         <v>959</v>
       </c>
@@ -10068,7 +10075,7 @@
         <v>960</v>
       </c>
     </row>
-    <row r="184" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:13" ht="28" x14ac:dyDescent="0.3">
       <c r="B184" s="4" t="s">
         <v>966</v>
       </c>
@@ -10092,7 +10099,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="185" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:13" ht="28" x14ac:dyDescent="0.3">
       <c r="B185" s="4" t="s">
         <v>971</v>
       </c>
@@ -10116,7 +10123,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="186" spans="1:13" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:13" ht="42" x14ac:dyDescent="0.3">
       <c r="B186" s="4" t="s">
         <v>976</v>
       </c>
@@ -10140,7 +10147,7 @@
         <v>963</v>
       </c>
     </row>
-    <row r="187" spans="1:13" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:13" ht="42" x14ac:dyDescent="0.3">
       <c r="B187" s="4" t="s">
         <v>979</v>
       </c>
@@ -10164,7 +10171,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="188" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:13" ht="28" x14ac:dyDescent="0.3">
       <c r="B188" s="4" t="s">
         <v>985</v>
       </c>
@@ -10191,7 +10198,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="189" spans="1:13" ht="15" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:13" ht="15.5" x14ac:dyDescent="0.3">
       <c r="B189" s="4" t="s">
         <v>988</v>
       </c>
@@ -10216,7 +10223,7 @@
       </c>
       <c r="M189" s="6"/>
     </row>
-    <row r="190" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:13" ht="28" x14ac:dyDescent="0.3">
       <c r="B190" s="4" t="s">
         <v>992</v>
       </c>
@@ -10240,7 +10247,7 @@
         <v>982</v>
       </c>
     </row>
-    <row r="191" spans="1:13" ht="45" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:13" ht="46.5" x14ac:dyDescent="0.3">
       <c r="B191" s="4" t="s">
         <v>1002</v>
       </c>
@@ -10264,7 +10271,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="192" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:13" ht="28" x14ac:dyDescent="0.3">
       <c r="B192" s="4" t="s">
         <v>1006</v>
       </c>
@@ -10288,7 +10295,7 @@
         <v>998</v>
       </c>
     </row>
-    <row r="193" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="193" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B193" s="4" t="s">
         <v>1010</v>
       </c>
@@ -10312,7 +10319,7 @@
         <v>1011</v>
       </c>
     </row>
-    <row r="194" spans="2:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="194" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B194" s="4" t="s">
         <v>1015</v>
       </c>
@@ -10339,7 +10346,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="195" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="195" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B195" s="4" t="s">
         <v>1021</v>
       </c>
@@ -10363,7 +10370,7 @@
         <v>1019</v>
       </c>
     </row>
-    <row r="196" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="196" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B196" s="4" t="s">
         <v>1025</v>
       </c>
@@ -10387,7 +10394,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="197" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="197" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B197" s="4" t="s">
         <v>1031</v>
       </c>
@@ -10411,7 +10418,7 @@
         <v>1033</v>
       </c>
     </row>
-    <row r="198" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="198" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B198" s="4" t="s">
         <v>1034</v>
       </c>
@@ -10435,7 +10442,7 @@
         <v>1035</v>
       </c>
     </row>
-    <row r="199" spans="2:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="199" spans="2:12" ht="42" x14ac:dyDescent="0.3">
       <c r="B199" s="4" t="s">
         <v>1040</v>
       </c>
@@ -10459,7 +10466,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="200" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="200" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B200" s="4" t="s">
         <v>1045</v>
       </c>
@@ -10483,7 +10490,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="201" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="201" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B201" s="4" t="s">
         <v>1051</v>
       </c>
@@ -10507,7 +10514,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="202" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="202" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B202" s="4" t="s">
         <v>1058</v>
       </c>
@@ -10531,7 +10538,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="203" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="203" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B203" s="4" t="s">
         <v>1062</v>
       </c>
@@ -10555,7 +10562,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="204" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="204" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B204" s="4" t="s">
         <v>1065</v>
       </c>
@@ -10579,7 +10586,7 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="205" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="205" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B205" s="4" t="s">
         <v>1071</v>
       </c>
@@ -10603,7 +10610,7 @@
         <v>1069</v>
       </c>
     </row>
-    <row r="206" spans="2:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="206" spans="2:12" ht="42" x14ac:dyDescent="0.3">
       <c r="B206" s="4" t="s">
         <v>1074</v>
       </c>
@@ -10627,7 +10634,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="207" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="207" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B207" s="4" t="s">
         <v>1080</v>
       </c>
@@ -10651,7 +10658,7 @@
         <v>1079</v>
       </c>
     </row>
-    <row r="208" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="208" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B208" s="4" t="s">
         <v>1082</v>
       </c>
@@ -10675,7 +10682,7 @@
         <v>1081</v>
       </c>
     </row>
-    <row r="209" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="209" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B209" s="4" t="s">
         <v>1091</v>
       </c>
@@ -10699,7 +10706,7 @@
         <v>1089</v>
       </c>
     </row>
-    <row r="210" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="210" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B210" s="4" t="s">
         <v>1093</v>
       </c>
@@ -10723,7 +10730,7 @@
         <v>1092</v>
       </c>
     </row>
-    <row r="211" spans="2:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="211" spans="2:12" ht="42" x14ac:dyDescent="0.3">
       <c r="B211" s="4" t="s">
         <v>1102</v>
       </c>
@@ -10747,7 +10754,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="212" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="212" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B212" s="4" t="s">
         <v>1105</v>
       </c>
@@ -10771,7 +10778,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="213" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="213" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B213" s="4" t="s">
         <v>1110</v>
       </c>
@@ -10795,7 +10802,7 @@
         <v>1109</v>
       </c>
     </row>
-    <row r="214" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="214" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B214" s="4" t="s">
         <v>1119</v>
       </c>
@@ -10813,7 +10820,7 @@
         <v>1115</v>
       </c>
     </row>
-    <row r="215" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="215" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B215" s="4" t="s">
         <v>1123</v>
       </c>
@@ -10822,16 +10829,22 @@
       </c>
       <c r="H215" s="1" t="s">
         <v>654</v>
+      </c>
+      <c r="I215" s="4" t="s">
+        <v>1124</v>
       </c>
       <c r="J215" s="5" t="str">
         <f t="shared" si="5"/>
         <v>001119</v>
       </c>
+      <c r="K215" s="3" t="s">
+        <v>1125</v>
+      </c>
       <c r="L215" s="2" t="s">
         <v>1117</v>
       </c>
     </row>
-    <row r="216" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="216" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C216" s="1" t="s">
         <v>1114</v>
       </c>
@@ -10843,7 +10856,7 @@
         <v>1113</v>
       </c>
     </row>
-    <row r="217" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="217" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C217" s="1" t="s">
         <v>1121</v>
       </c>
@@ -10855,608 +10868,608 @@
         <v>1122</v>
       </c>
     </row>
-    <row r="218" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="218" spans="2:12" x14ac:dyDescent="0.3">
       <c r="J218" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="219" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="219" spans="2:12" x14ac:dyDescent="0.3">
       <c r="J219" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="220" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="220" spans="2:12" x14ac:dyDescent="0.3">
       <c r="J220" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="221" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="221" spans="2:12" x14ac:dyDescent="0.3">
       <c r="J221" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="222" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="222" spans="2:12" x14ac:dyDescent="0.3">
       <c r="J222" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="223" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="223" spans="2:12" x14ac:dyDescent="0.3">
       <c r="J223" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="224" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="224" spans="2:12" x14ac:dyDescent="0.3">
       <c r="J224" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="225" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="225" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J225" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="226" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="226" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J226" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="227" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="227" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J227" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="228" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="228" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J228" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="229" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="229" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J229" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="230" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="230" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J230" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="231" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="231" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J231" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="232" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="232" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J232" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="233" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="233" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J233" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="234" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="234" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J234" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="235" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="235" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J235" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="236" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="236" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J236" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="237" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="237" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J237" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="238" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="238" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J238" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="239" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="239" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J239" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="240" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="240" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J240" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="241" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="241" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J241" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="242" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="242" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J242" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="243" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="243" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J243" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="244" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="244" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J244" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="245" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="245" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J245" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="246" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="246" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J246" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="247" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="247" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J247" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="248" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="248" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J248" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="249" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="249" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J249" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="250" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="250" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J250" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="251" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="251" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J251" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="252" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="252" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J252" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="253" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="253" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J253" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="254" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="254" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J254" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="255" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="255" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J255" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="256" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="256" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J256" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="257" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="257" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J257" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="258" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="258" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J258" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="259" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="259" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J259" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="260" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="260" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J260" s="5" t="str">
         <f t="shared" ref="J260:J317" si="6">"00"&amp;B260</f>
         <v>00</v>
       </c>
     </row>
-    <row r="261" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="261" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J261" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="262" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="262" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J262" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="263" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="263" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J263" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="264" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="264" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J264" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="265" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="265" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J265" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="266" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="266" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J266" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="267" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="267" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J267" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="268" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="268" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J268" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="269" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="269" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J269" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="270" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="270" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J270" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="271" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="271" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J271" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="272" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="272" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J272" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="273" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="273" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J273" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="274" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="274" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J274" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="275" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="275" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J275" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="276" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="276" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J276" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="277" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="277" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J277" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="278" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="278" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J278" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="279" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="279" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J279" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="280" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="280" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J280" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="281" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="281" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J281" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="282" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="282" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J282" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="283" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="283" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J283" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="284" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="284" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J284" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="285" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="285" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J285" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="286" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="286" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J286" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="287" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="287" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J287" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="288" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="288" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J288" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="289" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="289" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J289" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="290" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="290" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J290" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="291" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="291" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J291" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="292" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="292" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J292" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="293" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="293" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J293" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="294" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="294" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J294" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="295" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="295" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J295" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="296" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="296" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J296" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="297" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="297" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J297" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="298" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="298" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J298" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="299" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="299" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J299" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="300" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="300" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J300" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="301" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="301" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J301" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="302" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="302" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J302" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="303" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="303" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J303" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="304" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="304" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J304" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="305" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="305" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J305" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="306" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="306" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J306" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="307" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="307" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J307" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="308" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="308" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J308" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="309" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="309" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J309" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="310" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="310" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J310" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="311" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="311" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J311" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="312" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="312" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J312" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="313" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="313" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J313" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="314" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="314" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J314" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="315" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="315" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J315" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="316" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="316" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J316" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="317" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="317" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J317" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:L4" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A4:L4"/>
   <mergeCells count="1">
     <mergeCell ref="A2:L2"/>
   </mergeCells>
@@ -11465,10 +11478,10 @@
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1:E1 D3:E3 D6:E1048576" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1:E1 D3:E3 D6:E1048576">
       <formula1>"是,否"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H1 H3:H1048576" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H1 H3:H1048576">
       <formula1>"VB编程,系统运维,WEB学习,游戏碎片,日常随笔"</formula1>
     </dataValidation>
   </dataValidations>
@@ -11478,20 +11491,20 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A2:L34"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="6.375" customWidth="1"/>
+    <col min="2" max="2" width="6.33203125" customWidth="1"/>
     <col min="3" max="3" width="34" style="4" customWidth="1"/>
     <col min="4" max="4" width="4.75" customWidth="1"/>
-    <col min="8" max="8" width="6.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.83203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="19" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="7.125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="7.08203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.08203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:12" ht="23.25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
         <v>549</v>
       </c>
@@ -11507,7 +11520,7 @@
       <c r="K2" s="21"/>
       <c r="L2" s="21"/>
     </row>
-    <row r="4" spans="1:12" ht="57" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12" ht="56" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>0</v>
       </c>
@@ -11545,7 +11558,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>533</v>
       </c>
@@ -11568,7 +11581,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C8" s="15" t="s">
         <v>545</v>
       </c>
@@ -11577,7 +11590,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C9" s="4" t="s">
         <v>539</v>
       </c>
@@ -11585,7 +11598,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C10" t="s">
         <v>537</v>
       </c>
@@ -11593,7 +11606,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C11" t="s">
         <v>538</v>
       </c>
@@ -11601,7 +11614,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="23.25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A13" s="21" t="s">
         <v>543</v>
       </c>
@@ -11617,7 +11630,7 @@
       <c r="K13" s="21"/>
       <c r="L13" s="21"/>
     </row>
-    <row r="15" spans="1:12" ht="57" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:12" ht="56" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
         <v>0</v>
       </c>
@@ -11655,7 +11668,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>533</v>
       </c>
@@ -11681,7 +11694,7 @@
         <v>54837657</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C19" s="15" t="s">
         <v>545</v>
       </c>
@@ -11690,7 +11703,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C20" s="4" t="s">
         <v>539</v>
       </c>
@@ -11698,7 +11711,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C21" t="s">
         <v>537</v>
       </c>
@@ -11706,7 +11719,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C22" t="s">
         <v>538</v>
       </c>
@@ -11714,10 +11727,10 @@
         <v>541</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C23"/>
     </row>
-    <row r="25" spans="1:12" ht="23.25" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:12" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A25" s="21" t="s">
         <v>550</v>
       </c>
@@ -11733,7 +11746,7 @@
       <c r="K25" s="21"/>
       <c r="L25" s="21"/>
     </row>
-    <row r="27" spans="1:12" ht="57" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:12" ht="56" x14ac:dyDescent="0.3">
       <c r="A27" s="7" t="s">
         <v>0</v>
       </c>
@@ -11771,7 +11784,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
         <v>533</v>
       </c>
@@ -11797,7 +11810,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C31" s="15" t="s">
         <v>545</v>
       </c>
@@ -11806,7 +11819,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C32" s="4" t="s">
         <v>539</v>
       </c>
@@ -11814,7 +11827,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="33" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="33" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C33" t="s">
         <v>537</v>
       </c>
@@ -11822,7 +11835,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="34" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="34" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C34" t="s">
         <v>538</v>
       </c>
@@ -11838,7 +11851,7 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H15 H27 H4" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H15 H27 H4">
       <formula1>"VB编程,系统运维,WEB学习,游戏碎片,日常随笔"</formula1>
     </dataValidation>
   </dataValidations>

--- a/11_付费课程/99.资料/文章信息备忘表.xlsx
+++ b/11_付费课程/99.资料/文章信息备忘表.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\writing\11_付费课程\99.资料\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Writing\11_付费课程\99.资料\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3087A60-7B6A-4E66-8D23-E058714CCF7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1910" yWindow="-120" windowWidth="19740" windowHeight="11760"/>
+    <workbookView xWindow="870" yWindow="-120" windowWidth="19740" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,7 +19,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$L$4</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1547" uniqueCount="1126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1549" uniqueCount="1128">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -4490,13 +4491,21 @@
   </si>
   <si>
     <t>203312</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>85412593</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>浥尘伙伴社团独家密训课程：孩子成长必备之逻辑课</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -4981,24 +4990,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:M317"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.25" style="8" customWidth="1"/>
-    <col min="2" max="2" width="6.58203125" style="4" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="8.08203125" style="6" customWidth="1"/>
+    <col min="2" max="2" width="6.625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="30.875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="8.125" style="6" customWidth="1"/>
     <col min="5" max="7" width="8.75" style="6" customWidth="1"/>
-    <col min="8" max="8" width="9.08203125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="9.125" style="1" customWidth="1"/>
     <col min="9" max="9" width="19" style="4" customWidth="1"/>
-    <col min="10" max="10" width="14.58203125" style="5" customWidth="1"/>
-    <col min="11" max="11" width="10.83203125" style="3" customWidth="1"/>
+    <col min="10" max="10" width="14.625" style="5" customWidth="1"/>
+    <col min="11" max="11" width="10.875" style="3" customWidth="1"/>
     <col min="12" max="12" width="13.75" style="2" customWidth="1"/>
     <col min="13" max="13" width="16.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:12" ht="25" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
@@ -5014,8 +5023,8 @@
       <c r="K2" s="20"/>
       <c r="L2" s="20"/>
     </row>
-    <row r="3" spans="1:12" ht="6.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="4" spans="1:12" s="7" customFormat="1" ht="28" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" ht="6.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="4" spans="1:12" s="7" customFormat="1" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A4" s="7" t="s">
         <v>0</v>
       </c>
@@ -5053,7 +5062,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
         <v>557</v>
       </c>
@@ -5080,7 +5089,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
         <v>559</v>
       </c>
@@ -5116,7 +5125,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="8" t="s">
         <v>559</v>
       </c>
@@ -5152,25 +5161,25 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="J8" s="5" t="str">
         <f t="shared" si="0"/>
         <v>000</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="J9" s="5" t="str">
         <f t="shared" si="0"/>
         <v>000</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="J10" s="5" t="str">
         <f t="shared" si="0"/>
         <v>000</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B11" s="4" t="s">
         <v>522</v>
       </c>
@@ -5203,7 +5212,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A12" s="8" t="s">
         <v>558</v>
       </c>
@@ -5233,7 +5242,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A13" s="8" t="s">
         <v>558</v>
       </c>
@@ -5263,7 +5272,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A14" s="8" t="s">
         <v>640</v>
       </c>
@@ -5290,7 +5299,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" s="8" t="s">
         <v>557</v>
       </c>
@@ -5317,7 +5326,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" s="8" t="s">
         <v>557</v>
       </c>
@@ -5344,7 +5353,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" s="8" t="s">
         <v>557</v>
       </c>
@@ -5371,7 +5380,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" s="8" t="s">
         <v>767</v>
       </c>
@@ -5398,7 +5407,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A19" s="8" t="s">
         <v>557</v>
       </c>
@@ -5425,7 +5434,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A20" s="8" t="s">
         <v>557</v>
       </c>
@@ -5452,7 +5461,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A21" s="8" t="s">
         <v>557</v>
       </c>
@@ -5479,7 +5488,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A22" s="8" t="s">
         <v>559</v>
       </c>
@@ -5515,7 +5524,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23" s="8" t="s">
         <v>557</v>
       </c>
@@ -5542,7 +5551,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A24" s="8" t="s">
         <v>558</v>
       </c>
@@ -5572,7 +5581,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A25" s="8" t="s">
         <v>557</v>
       </c>
@@ -5599,7 +5608,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A26" s="8" t="s">
         <v>557</v>
       </c>
@@ -5626,7 +5635,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="27" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A27" s="8" t="s">
         <v>633</v>
       </c>
@@ -5653,7 +5662,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A28" s="8" t="s">
         <v>557</v>
       </c>
@@ -5680,7 +5689,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A29" s="8" t="s">
         <v>559</v>
       </c>
@@ -5716,7 +5725,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A30" s="8" t="s">
         <v>559</v>
       </c>
@@ -5752,7 +5761,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A31" s="8" t="s">
         <v>557</v>
       </c>
@@ -5779,7 +5788,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A32" s="8" t="s">
         <v>557</v>
       </c>
@@ -5806,7 +5815,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A33" s="8" t="s">
         <v>557</v>
       </c>
@@ -5833,7 +5842,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="34" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A34" s="8" t="s">
         <v>557</v>
       </c>
@@ -5860,7 +5869,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="35" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A35" s="8" t="s">
         <v>557</v>
       </c>
@@ -5887,7 +5896,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="36" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A36" s="8" t="s">
         <v>557</v>
       </c>
@@ -5914,7 +5923,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="37" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A37" s="8" t="s">
         <v>559</v>
       </c>
@@ -5950,7 +5959,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="38" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A38" s="8" t="s">
         <v>557</v>
       </c>
@@ -5977,7 +5986,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A39" s="8" t="s">
         <v>557</v>
       </c>
@@ -6004,7 +6013,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="40" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A40" s="8" t="s">
         <v>557</v>
       </c>
@@ -6031,7 +6040,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="41" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A41" s="8" t="s">
         <v>557</v>
       </c>
@@ -6058,7 +6067,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="42" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A42" s="8" t="s">
         <v>557</v>
       </c>
@@ -6085,7 +6094,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="43" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A43" s="8" t="s">
         <v>559</v>
       </c>
@@ -6118,7 +6127,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="44" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A44" s="8" t="s">
         <v>557</v>
       </c>
@@ -6145,7 +6154,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="45" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A45" s="8" t="s">
         <v>557</v>
       </c>
@@ -6172,7 +6181,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="46" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A46" s="8" t="s">
         <v>557</v>
       </c>
@@ -6199,7 +6208,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A47" s="8" t="s">
         <v>557</v>
       </c>
@@ -6226,7 +6235,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="48" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A48" s="8" t="s">
         <v>557</v>
       </c>
@@ -6253,7 +6262,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="49" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A49" s="8" t="s">
         <v>557</v>
       </c>
@@ -6280,7 +6289,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="50" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A50" s="8" t="s">
         <v>557</v>
       </c>
@@ -6307,7 +6316,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A51" s="8" t="s">
         <v>557</v>
       </c>
@@ -6334,7 +6343,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="52" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A52" s="8" t="s">
         <v>557</v>
       </c>
@@ -6361,7 +6370,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A53" s="8" t="s">
         <v>557</v>
       </c>
@@ -6388,7 +6397,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="54" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A54" s="8" t="s">
         <v>557</v>
       </c>
@@ -6415,7 +6424,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A55" s="8" t="s">
         <v>557</v>
       </c>
@@ -6442,7 +6451,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="56" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A56" s="8" t="s">
         <v>559</v>
       </c>
@@ -6478,7 +6487,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="57" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A57" s="8" t="s">
         <v>559</v>
       </c>
@@ -6514,7 +6523,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="58" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A58" s="8" t="s">
         <v>557</v>
       </c>
@@ -6541,7 +6550,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="59" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A59" s="8" t="s">
         <v>558</v>
       </c>
@@ -6571,7 +6580,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="60" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A60" s="8" t="s">
         <v>557</v>
       </c>
@@ -6598,7 +6607,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="61" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B61" s="4" t="s">
         <v>298</v>
       </c>
@@ -6631,7 +6640,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="62" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B62" s="4" t="s">
         <v>294</v>
       </c>
@@ -6664,7 +6673,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="63" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B63" s="4" t="s">
         <v>289</v>
       </c>
@@ -6697,7 +6706,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="64" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A64" s="8" t="s">
         <v>557</v>
       </c>
@@ -6724,7 +6733,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="65" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A65" s="8" t="s">
         <v>557</v>
       </c>
@@ -6751,7 +6760,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="66" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A66" s="8" t="s">
         <v>559</v>
       </c>
@@ -6787,7 +6796,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="67" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A67" s="8" t="s">
         <v>557</v>
       </c>
@@ -6814,7 +6823,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="68" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A68" s="8" t="s">
         <v>558</v>
       </c>
@@ -6844,7 +6853,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="69" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A69" s="8" t="s">
         <v>559</v>
       </c>
@@ -6871,7 +6880,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="70" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A70" s="8" t="s">
         <v>559</v>
       </c>
@@ -6898,7 +6907,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="71" spans="1:12" ht="56" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:12" ht="57" x14ac:dyDescent="0.2">
       <c r="A71" s="8" t="s">
         <v>558</v>
       </c>
@@ -6928,7 +6937,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="72" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A72" s="8" t="s">
         <v>558</v>
       </c>
@@ -6958,7 +6967,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="73" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A73" s="8" t="s">
         <v>558</v>
       </c>
@@ -6988,7 +6997,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="74" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A74" s="8" t="s">
         <v>557</v>
       </c>
@@ -7015,7 +7024,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="75" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A75" s="8" t="s">
         <v>557</v>
       </c>
@@ -7042,7 +7051,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="76" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A76" s="8" t="s">
         <v>558</v>
       </c>
@@ -7075,7 +7084,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="77" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A77" s="8" t="s">
         <v>557</v>
       </c>
@@ -7102,7 +7111,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="78" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A78" s="8" t="s">
         <v>558</v>
       </c>
@@ -7129,7 +7138,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="79" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A79" s="8" t="s">
         <v>557</v>
       </c>
@@ -7156,7 +7165,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="80" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A80" s="8" t="s">
         <v>558</v>
       </c>
@@ -7183,7 +7192,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="81" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A81" s="8" t="s">
         <v>557</v>
       </c>
@@ -7210,7 +7219,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="82" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A82" s="8" t="s">
         <v>557</v>
       </c>
@@ -7237,7 +7246,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="83" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A83" s="8" t="s">
         <v>557</v>
       </c>
@@ -7264,7 +7273,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="84" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A84" s="8" t="s">
         <v>557</v>
       </c>
@@ -7291,7 +7300,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="85" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A85" s="8" t="s">
         <v>558</v>
       </c>
@@ -7318,7 +7327,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="86" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A86" s="8" t="s">
         <v>557</v>
       </c>
@@ -7345,7 +7354,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="87" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A87" s="8" t="s">
         <v>559</v>
       </c>
@@ -7381,7 +7390,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="88" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A88" s="8" t="s">
         <v>559</v>
       </c>
@@ -7417,7 +7426,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="89" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A89" s="8" t="s">
         <v>559</v>
       </c>
@@ -7453,7 +7462,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="90" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A90" s="8" t="s">
         <v>557</v>
       </c>
@@ -7480,7 +7489,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="91" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B91" s="4" t="s">
         <v>151</v>
       </c>
@@ -7513,7 +7522,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="92" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B92" s="4" t="s">
         <v>146</v>
       </c>
@@ -7546,7 +7555,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="93" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B93" s="4" t="s">
         <v>140</v>
       </c>
@@ -7579,7 +7588,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="94" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B94" s="4" t="s">
         <v>135</v>
       </c>
@@ -7612,7 +7621,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="95" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A95" s="8" t="s">
         <v>558</v>
       </c>
@@ -7639,7 +7648,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="96" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B96" s="4" t="s">
         <v>123</v>
       </c>
@@ -7672,7 +7681,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="97" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B97" s="4" t="s">
         <v>118</v>
       </c>
@@ -7705,7 +7714,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="98" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B98" s="4" t="s">
         <v>112</v>
       </c>
@@ -7738,7 +7747,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="99" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B99" s="4" t="s">
         <v>109</v>
       </c>
@@ -7771,7 +7780,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="100" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B100" s="4" t="s">
         <v>104</v>
       </c>
@@ -7804,7 +7813,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="101" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B101" s="4" t="s">
         <v>98</v>
       </c>
@@ -7837,7 +7846,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="102" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B102" s="4" t="s">
         <v>92</v>
       </c>
@@ -7870,7 +7879,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="103" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A103" s="8" t="s">
         <v>559</v>
       </c>
@@ -7906,7 +7915,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="104" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A104" s="8" t="s">
         <v>557</v>
       </c>
@@ -7933,7 +7942,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="105" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A105" s="8" t="s">
         <v>557</v>
       </c>
@@ -7960,7 +7969,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="106" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A106" s="8" t="s">
         <v>557</v>
       </c>
@@ -7987,7 +7996,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="107" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A107" s="8" t="s">
         <v>557</v>
       </c>
@@ -8014,7 +8023,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="108" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A108" s="8" t="s">
         <v>557</v>
       </c>
@@ -8041,7 +8050,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="109" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A109" s="8" t="s">
         <v>559</v>
       </c>
@@ -8077,7 +8086,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A110" s="8" t="s">
         <v>558</v>
       </c>
@@ -8104,7 +8113,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="111" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A111" s="8" t="s">
         <v>557</v>
       </c>
@@ -8131,7 +8140,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A112" s="8" t="s">
         <v>557</v>
       </c>
@@ -8158,7 +8167,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="113" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A113" s="8" t="s">
         <v>557</v>
       </c>
@@ -8185,7 +8194,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A114" s="8" t="s">
         <v>557</v>
       </c>
@@ -8212,7 +8221,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="115" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A115" s="8" t="s">
         <v>557</v>
       </c>
@@ -8239,7 +8248,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="116" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A116" s="8" t="s">
         <v>559</v>
       </c>
@@ -8275,7 +8284,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="117" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A117" s="8" t="s">
         <v>557</v>
       </c>
@@ -8302,7 +8311,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="118" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A118" s="8" t="s">
         <v>558</v>
       </c>
@@ -8332,7 +8341,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="119" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A119" s="8" t="s">
         <v>557</v>
       </c>
@@ -8359,7 +8368,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="120" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A120" s="8" t="s">
         <v>557</v>
       </c>
@@ -8386,7 +8395,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="121" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A121" s="8" t="s">
         <v>597</v>
       </c>
@@ -8413,7 +8422,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="122" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A122" s="8" t="s">
         <v>602</v>
       </c>
@@ -8440,7 +8449,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="123" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A123" s="8" t="s">
         <v>608</v>
       </c>
@@ -8467,7 +8476,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="124" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A124" s="8" t="s">
         <v>611</v>
       </c>
@@ -8494,7 +8503,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="125" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A125" s="8" t="s">
         <v>617</v>
       </c>
@@ -8521,7 +8530,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="126" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A126" s="8" t="s">
         <v>624</v>
       </c>
@@ -8548,7 +8557,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="127" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A127" s="8" t="s">
         <v>557</v>
       </c>
@@ -8575,7 +8584,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="128" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A128" s="8" t="s">
         <v>649</v>
       </c>
@@ -8602,7 +8611,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="129" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A129" s="8" t="s">
         <v>653</v>
       </c>
@@ -8629,7 +8638,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="130" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A130" s="8" t="s">
         <v>659</v>
       </c>
@@ -8656,7 +8665,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="131" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A131" s="8" t="s">
         <v>664</v>
       </c>
@@ -8683,7 +8692,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A132" s="8" t="s">
         <v>557</v>
       </c>
@@ -8710,7 +8719,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="133" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A133" s="8" t="s">
         <v>557</v>
       </c>
@@ -8737,7 +8746,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="134" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A134" s="8" t="s">
         <v>681</v>
       </c>
@@ -8764,7 +8773,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="135" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A135" s="8" t="s">
         <v>687</v>
       </c>
@@ -8791,7 +8800,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="136" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A136" s="8" t="s">
         <v>691</v>
       </c>
@@ -8818,7 +8827,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="137" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A137" s="8" t="s">
         <v>699</v>
       </c>
@@ -8845,7 +8854,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="138" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A138" s="8" t="s">
         <v>704</v>
       </c>
@@ -8872,7 +8881,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="139" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A139" s="8" t="s">
         <v>711</v>
       </c>
@@ -8899,7 +8908,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="140" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A140" s="8" t="s">
         <v>716</v>
       </c>
@@ -8926,7 +8935,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="141" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A141" s="8" t="s">
         <v>724</v>
       </c>
@@ -8953,7 +8962,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="142" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A142" s="8" t="s">
         <v>727</v>
       </c>
@@ -8980,7 +8989,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="143" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A143" s="8" t="s">
         <v>736</v>
       </c>
@@ -9007,7 +9016,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="144" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A144" s="8" t="s">
         <v>740</v>
       </c>
@@ -9034,7 +9043,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="145" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A145" s="8" t="s">
         <v>746</v>
       </c>
@@ -9061,7 +9070,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="146" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A146" s="8" t="s">
         <v>754</v>
       </c>
@@ -9088,7 +9097,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="147" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A147" s="8" t="s">
         <v>759</v>
       </c>
@@ -9115,7 +9124,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="148" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A148" s="8" t="s">
         <v>770</v>
       </c>
@@ -9142,7 +9151,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="149" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A149" s="8" t="s">
         <v>777</v>
       </c>
@@ -9169,7 +9178,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="150" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A150" s="8" t="s">
         <v>782</v>
       </c>
@@ -9196,7 +9205,7 @@
         <v>786</v>
       </c>
     </row>
-    <row r="151" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A151" s="8" t="s">
         <v>557</v>
       </c>
@@ -9223,7 +9232,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="152" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A152" s="8" t="s">
         <v>795</v>
       </c>
@@ -9250,7 +9259,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A153" s="8" t="s">
         <v>800</v>
       </c>
@@ -9277,7 +9286,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A154" s="8" t="s">
         <v>804</v>
       </c>
@@ -9304,7 +9313,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A155" s="8" t="s">
         <v>811</v>
       </c>
@@ -9331,7 +9340,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="156" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A156" s="8" t="s">
         <v>557</v>
       </c>
@@ -9358,7 +9367,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A157" s="8" t="s">
         <v>557</v>
       </c>
@@ -9385,7 +9394,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A158" s="8" t="s">
         <v>827</v>
       </c>
@@ -9412,7 +9421,7 @@
         <v>831</v>
       </c>
     </row>
-    <row r="159" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A159" s="8" t="s">
         <v>557</v>
       </c>
@@ -9439,7 +9448,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A160" s="8" t="s">
         <v>838</v>
       </c>
@@ -9466,7 +9475,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="161" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A161" s="8" t="s">
         <v>557</v>
       </c>
@@ -9493,7 +9502,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A162" s="8" t="s">
         <v>850</v>
       </c>
@@ -9520,7 +9529,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A163" s="8" t="s">
         <v>857</v>
       </c>
@@ -9547,7 +9556,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A164" s="8" t="s">
         <v>557</v>
       </c>
@@ -9574,7 +9583,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="165" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A165" s="8" t="s">
         <v>557</v>
       </c>
@@ -9601,7 +9610,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A166" s="8" t="s">
         <v>557</v>
       </c>
@@ -9628,7 +9637,7 @@
         <v>871</v>
       </c>
     </row>
-    <row r="167" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A167" s="8" t="s">
         <v>557</v>
       </c>
@@ -9655,7 +9664,7 @@
         <v>879</v>
       </c>
     </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A168" s="8" t="s">
         <v>557</v>
       </c>
@@ -9682,7 +9691,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A169" s="8" t="s">
         <v>557</v>
       </c>
@@ -9709,7 +9718,7 @@
         <v>889</v>
       </c>
     </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A170" s="8" t="s">
         <v>557</v>
       </c>
@@ -9736,7 +9745,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A171" s="8" t="s">
         <v>557</v>
       </c>
@@ -9763,7 +9772,7 @@
         <v>897</v>
       </c>
     </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A172" s="8" t="s">
         <v>902</v>
       </c>
@@ -9790,7 +9799,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A173" s="8" t="s">
         <v>902</v>
       </c>
@@ -9817,7 +9826,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A174" s="8" t="s">
         <v>557</v>
       </c>
@@ -9844,7 +9853,7 @@
         <v>915</v>
       </c>
     </row>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A175" s="8" t="s">
         <v>557</v>
       </c>
@@ -9871,7 +9880,7 @@
         <v>919</v>
       </c>
     </row>
-    <row r="176" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A176" s="8" t="s">
         <v>557</v>
       </c>
@@ -9898,7 +9907,7 @@
         <v>925</v>
       </c>
     </row>
-    <row r="177" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A177" s="8" t="s">
         <v>557</v>
       </c>
@@ -9925,7 +9934,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="178" spans="1:13" ht="28" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A178" s="8" t="s">
         <v>557</v>
       </c>
@@ -9952,7 +9961,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="179" spans="1:13" ht="42" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:13" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A179" s="8" t="s">
         <v>938</v>
       </c>
@@ -9979,7 +9988,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="180" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B180" s="4" t="s">
         <v>942</v>
       </c>
@@ -10003,7 +10012,7 @@
         <v>946</v>
       </c>
     </row>
-    <row r="181" spans="1:13" ht="28" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B181" s="4" t="s">
         <v>948</v>
       </c>
@@ -10027,7 +10036,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="182" spans="1:13" ht="28" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B182" s="4" t="s">
         <v>954</v>
       </c>
@@ -10051,7 +10060,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="183" spans="1:13" ht="42" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:13" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B183" s="4" t="s">
         <v>959</v>
       </c>
@@ -10075,7 +10084,7 @@
         <v>960</v>
       </c>
     </row>
-    <row r="184" spans="1:13" ht="28" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B184" s="4" t="s">
         <v>966</v>
       </c>
@@ -10099,7 +10108,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="185" spans="1:13" ht="28" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B185" s="4" t="s">
         <v>971</v>
       </c>
@@ -10123,7 +10132,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="186" spans="1:13" ht="42" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:13" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B186" s="4" t="s">
         <v>976</v>
       </c>
@@ -10147,7 +10156,7 @@
         <v>963</v>
       </c>
     </row>
-    <row r="187" spans="1:13" ht="42" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:13" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B187" s="4" t="s">
         <v>979</v>
       </c>
@@ -10171,7 +10180,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="188" spans="1:13" ht="28" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B188" s="4" t="s">
         <v>985</v>
       </c>
@@ -10198,7 +10207,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="189" spans="1:13" ht="15.5" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:13" ht="15" x14ac:dyDescent="0.2">
       <c r="B189" s="4" t="s">
         <v>988</v>
       </c>
@@ -10223,7 +10232,7 @@
       </c>
       <c r="M189" s="6"/>
     </row>
-    <row r="190" spans="1:13" ht="28" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B190" s="4" t="s">
         <v>992</v>
       </c>
@@ -10247,7 +10256,7 @@
         <v>982</v>
       </c>
     </row>
-    <row r="191" spans="1:13" ht="46.5" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:13" ht="45" x14ac:dyDescent="0.2">
       <c r="B191" s="4" t="s">
         <v>1002</v>
       </c>
@@ -10271,7 +10280,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="192" spans="1:13" ht="28" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B192" s="4" t="s">
         <v>1006</v>
       </c>
@@ -10295,7 +10304,7 @@
         <v>998</v>
       </c>
     </row>
-    <row r="193" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="193" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B193" s="4" t="s">
         <v>1010</v>
       </c>
@@ -10319,7 +10328,7 @@
         <v>1011</v>
       </c>
     </row>
-    <row r="194" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="194" spans="2:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B194" s="4" t="s">
         <v>1015</v>
       </c>
@@ -10346,7 +10355,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="195" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="195" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B195" s="4" t="s">
         <v>1021</v>
       </c>
@@ -10370,7 +10379,7 @@
         <v>1019</v>
       </c>
     </row>
-    <row r="196" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="196" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B196" s="4" t="s">
         <v>1025</v>
       </c>
@@ -10394,7 +10403,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="197" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="197" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B197" s="4" t="s">
         <v>1031</v>
       </c>
@@ -10418,7 +10427,7 @@
         <v>1033</v>
       </c>
     </row>
-    <row r="198" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="198" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B198" s="4" t="s">
         <v>1034</v>
       </c>
@@ -10442,7 +10451,7 @@
         <v>1035</v>
       </c>
     </row>
-    <row r="199" spans="2:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="199" spans="2:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B199" s="4" t="s">
         <v>1040</v>
       </c>
@@ -10466,7 +10475,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="200" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="200" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B200" s="4" t="s">
         <v>1045</v>
       </c>
@@ -10490,7 +10499,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="201" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="201" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B201" s="4" t="s">
         <v>1051</v>
       </c>
@@ -10514,7 +10523,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="202" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="202" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B202" s="4" t="s">
         <v>1058</v>
       </c>
@@ -10538,7 +10547,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="203" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="203" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B203" s="4" t="s">
         <v>1062</v>
       </c>
@@ -10562,7 +10571,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="204" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="204" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B204" s="4" t="s">
         <v>1065</v>
       </c>
@@ -10586,7 +10595,7 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="205" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="205" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B205" s="4" t="s">
         <v>1071</v>
       </c>
@@ -10610,7 +10619,7 @@
         <v>1069</v>
       </c>
     </row>
-    <row r="206" spans="2:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="206" spans="2:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B206" s="4" t="s">
         <v>1074</v>
       </c>
@@ -10634,7 +10643,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="207" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="207" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B207" s="4" t="s">
         <v>1080</v>
       </c>
@@ -10658,7 +10667,7 @@
         <v>1079</v>
       </c>
     </row>
-    <row r="208" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="208" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B208" s="4" t="s">
         <v>1082</v>
       </c>
@@ -10682,7 +10691,7 @@
         <v>1081</v>
       </c>
     </row>
-    <row r="209" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="209" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B209" s="4" t="s">
         <v>1091</v>
       </c>
@@ -10706,7 +10715,7 @@
         <v>1089</v>
       </c>
     </row>
-    <row r="210" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="210" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B210" s="4" t="s">
         <v>1093</v>
       </c>
@@ -10730,7 +10739,7 @@
         <v>1092</v>
       </c>
     </row>
-    <row r="211" spans="2:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="211" spans="2:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B211" s="4" t="s">
         <v>1102</v>
       </c>
@@ -10754,7 +10763,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="212" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="212" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B212" s="4" t="s">
         <v>1105</v>
       </c>
@@ -10778,7 +10787,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="213" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="213" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B213" s="4" t="s">
         <v>1110</v>
       </c>
@@ -10802,7 +10811,7 @@
         <v>1109</v>
       </c>
     </row>
-    <row r="214" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="214" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B214" s="4" t="s">
         <v>1119</v>
       </c>
@@ -10820,7 +10829,7 @@
         <v>1115</v>
       </c>
     </row>
-    <row r="215" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="215" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B215" s="4" t="s">
         <v>1123</v>
       </c>
@@ -10844,7 +10853,7 @@
         <v>1117</v>
       </c>
     </row>
-    <row r="216" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="216" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C216" s="1" t="s">
         <v>1114</v>
       </c>
@@ -10856,7 +10865,7 @@
         <v>1113</v>
       </c>
     </row>
-    <row r="217" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="217" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C217" s="1" t="s">
         <v>1121</v>
       </c>
@@ -10868,608 +10877,614 @@
         <v>1122</v>
       </c>
     </row>
-    <row r="218" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="218" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J218" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="219" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="219" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="C219" s="1" t="s">
+        <v>1127</v>
+      </c>
       <c r="J219" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
-    </row>
-    <row r="220" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="L219" s="2" t="s">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="220" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J220" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="221" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="221" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J221" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="222" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="222" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J222" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="223" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="223" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J223" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="224" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="224" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J224" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="225" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="225" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J225" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="226" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="226" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J226" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="227" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="227" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J227" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="228" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="228" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J228" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="229" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="229" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J229" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="230" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="230" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J230" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="231" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="231" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J231" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="232" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="232" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J232" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="233" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="233" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J233" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="234" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="234" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J234" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="235" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="235" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J235" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="236" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="236" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J236" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="237" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="237" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J237" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="238" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="238" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J238" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="239" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="239" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J239" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="240" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="240" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J240" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="241" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="241" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J241" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="242" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="242" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J242" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="243" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="243" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J243" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="244" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="244" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J244" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="245" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="245" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J245" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="246" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="246" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J246" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="247" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="247" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J247" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="248" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="248" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J248" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="249" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="249" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J249" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="250" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="250" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J250" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="251" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="251" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J251" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="252" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="252" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J252" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="253" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="253" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J253" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="254" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="254" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J254" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="255" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="255" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J255" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="256" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="256" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J256" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="257" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="257" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J257" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="258" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="258" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J258" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="259" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="259" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J259" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="260" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="260" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J260" s="5" t="str">
         <f t="shared" ref="J260:J317" si="6">"00"&amp;B260</f>
         <v>00</v>
       </c>
     </row>
-    <row r="261" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="261" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J261" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="262" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="262" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J262" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="263" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="263" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J263" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="264" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="264" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J264" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="265" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="265" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J265" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="266" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="266" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J266" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="267" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="267" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J267" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="268" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="268" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J268" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="269" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="269" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J269" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="270" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="270" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J270" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="271" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="271" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J271" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="272" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="272" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J272" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="273" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="273" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J273" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="274" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="274" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J274" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="275" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="275" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J275" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="276" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="276" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J276" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="277" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="277" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J277" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="278" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="278" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J278" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="279" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="279" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J279" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="280" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="280" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J280" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="281" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="281" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J281" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="282" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="282" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J282" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="283" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="283" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J283" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="284" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="284" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J284" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="285" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="285" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J285" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="286" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="286" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J286" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="287" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="287" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J287" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="288" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="288" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J288" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="289" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="289" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J289" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="290" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="290" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J290" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="291" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="291" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J291" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="292" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="292" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J292" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="293" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="293" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J293" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="294" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="294" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J294" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="295" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="295" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J295" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="296" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="296" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J296" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="297" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="297" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J297" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="298" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="298" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J298" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="299" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="299" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J299" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="300" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="300" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J300" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="301" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="301" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J301" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="302" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="302" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J302" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="303" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="303" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J303" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="304" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="304" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J304" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="305" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="305" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J305" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="306" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="306" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J306" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="307" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="307" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J307" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="308" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="308" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J308" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="309" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="309" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J309" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="310" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="310" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J310" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="311" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="311" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J311" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="312" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="312" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J312" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="313" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="313" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J313" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="314" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="314" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J314" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="315" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="315" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J315" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="316" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="316" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J316" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="317" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="317" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J317" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:L4"/>
+  <autoFilter ref="A4:L4" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="1">
     <mergeCell ref="A2:L2"/>
   </mergeCells>
@@ -11478,10 +11493,10 @@
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1:E1 D3:E3 D6:E1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1:E1 D3:E3 D6:E1048576" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"是,否"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H1 H3:H1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H1 H3:H1048576" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"VB编程,系统运维,WEB学习,游戏碎片,日常随笔"</formula1>
     </dataValidation>
   </dataValidations>
@@ -11491,20 +11506,20 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A2:L34"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="6.33203125" customWidth="1"/>
+    <col min="2" max="2" width="6.375" customWidth="1"/>
     <col min="3" max="3" width="34" style="4" customWidth="1"/>
     <col min="4" max="4" width="4.75" customWidth="1"/>
-    <col min="8" max="8" width="6.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="19" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="7.08203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.08203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:12" ht="22.5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" ht="23.25" x14ac:dyDescent="0.2">
       <c r="A2" s="21" t="s">
         <v>549</v>
       </c>
@@ -11520,7 +11535,7 @@
       <c r="K2" s="21"/>
       <c r="L2" s="21"/>
     </row>
-    <row r="4" spans="1:12" ht="56" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" ht="57" x14ac:dyDescent="0.2">
       <c r="A4" s="7" t="s">
         <v>0</v>
       </c>
@@ -11558,7 +11573,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
         <v>533</v>
       </c>
@@ -11581,7 +11596,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C8" s="15" t="s">
         <v>545</v>
       </c>
@@ -11590,7 +11605,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C9" s="4" t="s">
         <v>539</v>
       </c>
@@ -11598,7 +11613,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C10" t="s">
         <v>537</v>
       </c>
@@ -11606,7 +11621,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C11" t="s">
         <v>538</v>
       </c>
@@ -11614,7 +11629,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="22.5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" ht="23.25" x14ac:dyDescent="0.2">
       <c r="A13" s="21" t="s">
         <v>543</v>
       </c>
@@ -11630,7 +11645,7 @@
       <c r="K13" s="21"/>
       <c r="L13" s="21"/>
     </row>
-    <row r="15" spans="1:12" ht="56" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" ht="57" x14ac:dyDescent="0.2">
       <c r="A15" s="7" t="s">
         <v>0</v>
       </c>
@@ -11668,7 +11683,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
         <v>533</v>
       </c>
@@ -11694,7 +11709,7 @@
         <v>54837657</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C19" s="15" t="s">
         <v>545</v>
       </c>
@@ -11703,7 +11718,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C20" s="4" t="s">
         <v>539</v>
       </c>
@@ -11711,7 +11726,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C21" t="s">
         <v>537</v>
       </c>
@@ -11719,7 +11734,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C22" t="s">
         <v>538</v>
       </c>
@@ -11727,10 +11742,10 @@
         <v>541</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C23"/>
     </row>
-    <row r="25" spans="1:12" ht="22.5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" ht="23.25" x14ac:dyDescent="0.2">
       <c r="A25" s="21" t="s">
         <v>550</v>
       </c>
@@ -11746,7 +11761,7 @@
       <c r="K25" s="21"/>
       <c r="L25" s="21"/>
     </row>
-    <row r="27" spans="1:12" ht="56" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" ht="57" x14ac:dyDescent="0.2">
       <c r="A27" s="7" t="s">
         <v>0</v>
       </c>
@@ -11784,7 +11799,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B28" t="s">
         <v>533</v>
       </c>
@@ -11810,7 +11825,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C31" s="15" t="s">
         <v>545</v>
       </c>
@@ -11819,7 +11834,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C32" s="4" t="s">
         <v>539</v>
       </c>
@@ -11827,7 +11842,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="33" spans="3:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="3:5" x14ac:dyDescent="0.2">
       <c r="C33" t="s">
         <v>537</v>
       </c>
@@ -11835,7 +11850,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="34" spans="3:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="3:5" x14ac:dyDescent="0.2">
       <c r="C34" t="s">
         <v>538</v>
       </c>
@@ -11851,7 +11866,7 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H15 H27 H4">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H15 H27 H4" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"VB编程,系统运维,WEB学习,游戏碎片,日常随笔"</formula1>
     </dataValidation>
   </dataValidations>

--- a/11_付费课程/99.资料/文章信息备忘表.xlsx
+++ b/11_付费课程/99.资料/文章信息备忘表.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="1910" yWindow="-120" windowWidth="19740" windowHeight="11760"/>
+    <workbookView xWindow="2950" yWindow="-120" windowWidth="19740" windowHeight="11760"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1547" uniqueCount="1126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1549" uniqueCount="1128">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -4490,6 +4490,14 @@
   </si>
   <si>
     <t>203312</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-11-13 20:45:17</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>715402</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -10812,9 +10820,15 @@
       <c r="H214" s="1" t="s">
         <v>654</v>
       </c>
+      <c r="I214" s="4" t="s">
+        <v>1126</v>
+      </c>
       <c r="J214" s="5" t="str">
         <f t="shared" si="5"/>
         <v>001118</v>
+      </c>
+      <c r="K214" s="3" t="s">
+        <v>1127</v>
       </c>
       <c r="L214" s="2" t="s">
         <v>1115</v>

--- a/11_付费课程/99.资料/文章信息备忘表.xlsx
+++ b/11_付费课程/99.资料/文章信息备忘表.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="2950" yWindow="-120" windowWidth="19740" windowHeight="11760"/>
+    <workbookView xWindow="3990" yWindow="-120" windowWidth="19740" windowHeight="11760"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1549" uniqueCount="1128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1555" uniqueCount="1134">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -4498,6 +4498,29 @@
   </si>
   <si>
     <t>715402</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1120</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>浥尘伙伴社团独家密训课程：孩子成长必备之逻辑课</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>浥尘伙伴社团</t>
+  </si>
+  <si>
+    <t>2024-11-17 19:23:47</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>743291</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>85412593</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4990,19 +5013,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:M317"/>
+  <dimension ref="A2:M318"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.25" style="8" customWidth="1"/>
-    <col min="2" max="2" width="6.58203125" style="4" customWidth="1"/>
+    <col min="2" max="2" width="5.58203125" style="4" customWidth="1"/>
     <col min="3" max="3" width="30.83203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="8.08203125" style="6" customWidth="1"/>
-    <col min="5" max="7" width="8.75" style="6" customWidth="1"/>
-    <col min="8" max="8" width="9.08203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="5.4140625" style="6" customWidth="1"/>
+    <col min="5" max="5" width="5.08203125" style="6" customWidth="1"/>
+    <col min="6" max="6" width="5.1640625" style="6" customWidth="1"/>
+    <col min="7" max="7" width="5.25" style="6" customWidth="1"/>
+    <col min="8" max="8" width="11.75" style="1" customWidth="1"/>
     <col min="9" max="9" width="19" style="4" customWidth="1"/>
-    <col min="10" max="10" width="14.58203125" style="5" customWidth="1"/>
-    <col min="11" max="11" width="10.83203125" style="3" customWidth="1"/>
-    <col min="12" max="12" width="13.75" style="2" customWidth="1"/>
+    <col min="10" max="10" width="8.58203125" style="5" customWidth="1"/>
+    <col min="11" max="11" width="7.5" style="3" customWidth="1"/>
+    <col min="12" max="12" width="9.25" style="2" customWidth="1"/>
     <col min="13" max="13" width="16.25" customWidth="1"/>
   </cols>
   <sheetData>
@@ -10416,7 +10441,7 @@
         <v>1029</v>
       </c>
       <c r="J197" s="5" t="str">
-        <f t="shared" ref="J197:J259" si="5">"00"&amp;B197</f>
+        <f t="shared" ref="J197:J260" si="5">"00"&amp;B197</f>
         <v>001099</v>
       </c>
       <c r="K197" s="3" t="s">
@@ -10858,34 +10883,52 @@
         <v>1117</v>
       </c>
     </row>
-    <row r="216" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="216" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+      <c r="B216" s="4" t="s">
+        <v>1128</v>
+      </c>
       <c r="C216" s="1" t="s">
-        <v>1114</v>
+        <v>1129</v>
+      </c>
+      <c r="H216" s="1" t="s">
+        <v>1130</v>
+      </c>
+      <c r="I216" s="4" t="s">
+        <v>1131</v>
       </c>
       <c r="J216" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>00</v>
+        <v>001120</v>
+      </c>
+      <c r="K216" s="3" t="s">
+        <v>1132</v>
       </c>
       <c r="L216" s="2" t="s">
-        <v>1113</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="217" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C217" s="1" t="s">
-        <v>1121</v>
+        <v>1114</v>
       </c>
       <c r="J217" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
       <c r="L217" s="2" t="s">
-        <v>1122</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="218" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="C218" s="1" t="s">
+        <v>1121</v>
+      </c>
       <c r="J218" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
+      </c>
+      <c r="L218" s="2" t="s">
+        <v>1122</v>
       </c>
     </row>
     <row r="219" spans="2:12" x14ac:dyDescent="0.3">
@@ -11136,13 +11179,13 @@
     </row>
     <row r="260" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J260" s="5" t="str">
-        <f t="shared" ref="J260:J317" si="6">"00"&amp;B260</f>
+        <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
     <row r="261" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J261" s="5" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="J261:J318" si="6">"00"&amp;B261</f>
         <v>00</v>
       </c>
     </row>
@@ -11478,6 +11521,12 @@
     </row>
     <row r="317" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J317" s="5" t="str">
+        <f t="shared" si="6"/>
+        <v>00</v>
+      </c>
+    </row>
+    <row r="318" spans="10:10" x14ac:dyDescent="0.3">
+      <c r="J318" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
@@ -11496,7 +11545,7 @@
       <formula1>"是,否"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H1 H3:H1048576">
-      <formula1>"VB编程,系统运维,WEB学习,游戏碎片,日常随笔"</formula1>
+      <formula1>"VB编程,系统运维,WEB学习,游戏碎片,日常随笔,浥尘伙伴社团"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/11_付费课程/99.资料/文章信息备忘表.xlsx
+++ b/11_付费课程/99.资料/文章信息备忘表.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\writing\11_付费课程\99.资料\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Writing\11_付费课程\99.资料\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41DE26BC-C20C-475E-ACBA-71B2ACB0B3F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3990" yWindow="-120" windowWidth="19740" windowHeight="11760"/>
+    <workbookView xWindow="870" yWindow="-120" windowWidth="19740" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,7 +19,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$L$4</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -4527,7 +4528,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -5012,26 +5013,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:M318"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.25" style="8" customWidth="1"/>
-    <col min="2" max="2" width="5.58203125" style="4" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="5.4140625" style="6" customWidth="1"/>
-    <col min="5" max="5" width="5.08203125" style="6" customWidth="1"/>
-    <col min="6" max="6" width="5.1640625" style="6" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="30.875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="5.375" style="6" customWidth="1"/>
+    <col min="5" max="6" width="5.125" style="6" customWidth="1"/>
     <col min="7" max="7" width="5.25" style="6" customWidth="1"/>
-    <col min="8" max="8" width="11.75" style="1" customWidth="1"/>
+    <col min="8" max="8" width="13.5" style="1" customWidth="1"/>
     <col min="9" max="9" width="19" style="4" customWidth="1"/>
-    <col min="10" max="10" width="8.58203125" style="5" customWidth="1"/>
+    <col min="10" max="10" width="8.625" style="5" customWidth="1"/>
     <col min="11" max="11" width="7.5" style="3" customWidth="1"/>
     <col min="12" max="12" width="9.25" style="2" customWidth="1"/>
     <col min="13" max="13" width="16.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:12" ht="25" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
@@ -5047,8 +5047,8 @@
       <c r="K2" s="20"/>
       <c r="L2" s="20"/>
     </row>
-    <row r="3" spans="1:12" ht="6.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="4" spans="1:12" s="7" customFormat="1" ht="28" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" ht="6.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="4" spans="1:12" s="7" customFormat="1" ht="57" x14ac:dyDescent="0.2">
       <c r="A4" s="7" t="s">
         <v>0</v>
       </c>
@@ -5086,7 +5086,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
         <v>557</v>
       </c>
@@ -5113,7 +5113,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
         <v>559</v>
       </c>
@@ -5149,7 +5149,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="8" t="s">
         <v>559</v>
       </c>
@@ -5185,25 +5185,25 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="J8" s="5" t="str">
         <f t="shared" si="0"/>
         <v>000</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="J9" s="5" t="str">
         <f t="shared" si="0"/>
         <v>000</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="J10" s="5" t="str">
         <f t="shared" si="0"/>
         <v>000</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B11" s="4" t="s">
         <v>522</v>
       </c>
@@ -5236,7 +5236,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A12" s="8" t="s">
         <v>558</v>
       </c>
@@ -5266,7 +5266,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A13" s="8" t="s">
         <v>558</v>
       </c>
@@ -5296,7 +5296,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A14" s="8" t="s">
         <v>640</v>
       </c>
@@ -5323,7 +5323,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" s="8" t="s">
         <v>557</v>
       </c>
@@ -5350,7 +5350,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" s="8" t="s">
         <v>557</v>
       </c>
@@ -5377,7 +5377,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" s="8" t="s">
         <v>557</v>
       </c>
@@ -5404,7 +5404,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" s="8" t="s">
         <v>767</v>
       </c>
@@ -5431,7 +5431,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A19" s="8" t="s">
         <v>557</v>
       </c>
@@ -5458,7 +5458,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A20" s="8" t="s">
         <v>557</v>
       </c>
@@ -5485,7 +5485,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A21" s="8" t="s">
         <v>557</v>
       </c>
@@ -5512,7 +5512,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A22" s="8" t="s">
         <v>559</v>
       </c>
@@ -5548,7 +5548,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23" s="8" t="s">
         <v>557</v>
       </c>
@@ -5575,7 +5575,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A24" s="8" t="s">
         <v>558</v>
       </c>
@@ -5605,7 +5605,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A25" s="8" t="s">
         <v>557</v>
       </c>
@@ -5632,7 +5632,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A26" s="8" t="s">
         <v>557</v>
       </c>
@@ -5659,7 +5659,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="27" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A27" s="8" t="s">
         <v>633</v>
       </c>
@@ -5686,7 +5686,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A28" s="8" t="s">
         <v>557</v>
       </c>
@@ -5713,7 +5713,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A29" s="8" t="s">
         <v>559</v>
       </c>
@@ -5749,7 +5749,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A30" s="8" t="s">
         <v>559</v>
       </c>
@@ -5785,7 +5785,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A31" s="8" t="s">
         <v>557</v>
       </c>
@@ -5812,7 +5812,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A32" s="8" t="s">
         <v>557</v>
       </c>
@@ -5839,7 +5839,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A33" s="8" t="s">
         <v>557</v>
       </c>
@@ -5866,7 +5866,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="34" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A34" s="8" t="s">
         <v>557</v>
       </c>
@@ -5893,7 +5893,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="35" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A35" s="8" t="s">
         <v>557</v>
       </c>
@@ -5920,7 +5920,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="36" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A36" s="8" t="s">
         <v>557</v>
       </c>
@@ -5947,7 +5947,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="37" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A37" s="8" t="s">
         <v>559</v>
       </c>
@@ -5983,7 +5983,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="38" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A38" s="8" t="s">
         <v>557</v>
       </c>
@@ -6010,7 +6010,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A39" s="8" t="s">
         <v>557</v>
       </c>
@@ -6037,7 +6037,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="40" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A40" s="8" t="s">
         <v>557</v>
       </c>
@@ -6064,7 +6064,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="41" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A41" s="8" t="s">
         <v>557</v>
       </c>
@@ -6091,7 +6091,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="42" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A42" s="8" t="s">
         <v>557</v>
       </c>
@@ -6118,7 +6118,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="43" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A43" s="8" t="s">
         <v>559</v>
       </c>
@@ -6151,7 +6151,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="44" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A44" s="8" t="s">
         <v>557</v>
       </c>
@@ -6178,7 +6178,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="45" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A45" s="8" t="s">
         <v>557</v>
       </c>
@@ -6205,7 +6205,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="46" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A46" s="8" t="s">
         <v>557</v>
       </c>
@@ -6232,7 +6232,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A47" s="8" t="s">
         <v>557</v>
       </c>
@@ -6259,7 +6259,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="48" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A48" s="8" t="s">
         <v>557</v>
       </c>
@@ -6286,7 +6286,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="49" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A49" s="8" t="s">
         <v>557</v>
       </c>
@@ -6313,7 +6313,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="50" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A50" s="8" t="s">
         <v>557</v>
       </c>
@@ -6340,7 +6340,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A51" s="8" t="s">
         <v>557</v>
       </c>
@@ -6367,7 +6367,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="52" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A52" s="8" t="s">
         <v>557</v>
       </c>
@@ -6394,7 +6394,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A53" s="8" t="s">
         <v>557</v>
       </c>
@@ -6421,7 +6421,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="54" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A54" s="8" t="s">
         <v>557</v>
       </c>
@@ -6448,7 +6448,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A55" s="8" t="s">
         <v>557</v>
       </c>
@@ -6475,7 +6475,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="56" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A56" s="8" t="s">
         <v>559</v>
       </c>
@@ -6511,7 +6511,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="57" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A57" s="8" t="s">
         <v>559</v>
       </c>
@@ -6547,7 +6547,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="58" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A58" s="8" t="s">
         <v>557</v>
       </c>
@@ -6574,7 +6574,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="59" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A59" s="8" t="s">
         <v>558</v>
       </c>
@@ -6604,7 +6604,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="60" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A60" s="8" t="s">
         <v>557</v>
       </c>
@@ -6631,7 +6631,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="61" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B61" s="4" t="s">
         <v>298</v>
       </c>
@@ -6664,7 +6664,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="62" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B62" s="4" t="s">
         <v>294</v>
       </c>
@@ -6697,7 +6697,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="63" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B63" s="4" t="s">
         <v>289</v>
       </c>
@@ -6730,7 +6730,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="64" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A64" s="8" t="s">
         <v>557</v>
       </c>
@@ -6757,7 +6757,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="65" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A65" s="8" t="s">
         <v>557</v>
       </c>
@@ -6784,7 +6784,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="66" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A66" s="8" t="s">
         <v>559</v>
       </c>
@@ -6820,7 +6820,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="67" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A67" s="8" t="s">
         <v>557</v>
       </c>
@@ -6847,7 +6847,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="68" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A68" s="8" t="s">
         <v>558</v>
       </c>
@@ -6877,7 +6877,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="69" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A69" s="8" t="s">
         <v>559</v>
       </c>
@@ -6904,7 +6904,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="70" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A70" s="8" t="s">
         <v>559</v>
       </c>
@@ -6931,7 +6931,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="71" spans="1:12" ht="56" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:12" ht="57" x14ac:dyDescent="0.2">
       <c r="A71" s="8" t="s">
         <v>558</v>
       </c>
@@ -6961,7 +6961,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="72" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A72" s="8" t="s">
         <v>558</v>
       </c>
@@ -6991,7 +6991,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="73" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A73" s="8" t="s">
         <v>558</v>
       </c>
@@ -7021,7 +7021,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="74" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A74" s="8" t="s">
         <v>557</v>
       </c>
@@ -7048,7 +7048,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="75" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A75" s="8" t="s">
         <v>557</v>
       </c>
@@ -7075,7 +7075,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="76" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A76" s="8" t="s">
         <v>558</v>
       </c>
@@ -7108,7 +7108,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="77" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A77" s="8" t="s">
         <v>557</v>
       </c>
@@ -7135,7 +7135,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="78" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A78" s="8" t="s">
         <v>558</v>
       </c>
@@ -7162,7 +7162,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="79" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A79" s="8" t="s">
         <v>557</v>
       </c>
@@ -7189,7 +7189,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="80" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A80" s="8" t="s">
         <v>558</v>
       </c>
@@ -7216,7 +7216,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="81" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A81" s="8" t="s">
         <v>557</v>
       </c>
@@ -7243,7 +7243,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="82" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A82" s="8" t="s">
         <v>557</v>
       </c>
@@ -7270,7 +7270,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="83" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A83" s="8" t="s">
         <v>557</v>
       </c>
@@ -7297,7 +7297,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="84" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A84" s="8" t="s">
         <v>557</v>
       </c>
@@ -7324,7 +7324,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="85" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A85" s="8" t="s">
         <v>558</v>
       </c>
@@ -7351,7 +7351,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="86" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A86" s="8" t="s">
         <v>557</v>
       </c>
@@ -7378,7 +7378,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="87" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A87" s="8" t="s">
         <v>559</v>
       </c>
@@ -7414,7 +7414,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="88" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A88" s="8" t="s">
         <v>559</v>
       </c>
@@ -7450,7 +7450,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="89" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A89" s="8" t="s">
         <v>559</v>
       </c>
@@ -7486,7 +7486,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="90" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A90" s="8" t="s">
         <v>557</v>
       </c>
@@ -7513,7 +7513,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="91" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B91" s="4" t="s">
         <v>151</v>
       </c>
@@ -7546,7 +7546,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="92" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B92" s="4" t="s">
         <v>146</v>
       </c>
@@ -7579,7 +7579,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="93" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B93" s="4" t="s">
         <v>140</v>
       </c>
@@ -7612,7 +7612,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="94" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B94" s="4" t="s">
         <v>135</v>
       </c>
@@ -7645,7 +7645,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="95" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A95" s="8" t="s">
         <v>558</v>
       </c>
@@ -7672,7 +7672,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="96" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B96" s="4" t="s">
         <v>123</v>
       </c>
@@ -7705,7 +7705,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="97" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B97" s="4" t="s">
         <v>118</v>
       </c>
@@ -7738,7 +7738,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="98" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B98" s="4" t="s">
         <v>112</v>
       </c>
@@ -7771,7 +7771,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="99" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B99" s="4" t="s">
         <v>109</v>
       </c>
@@ -7804,7 +7804,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="100" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B100" s="4" t="s">
         <v>104</v>
       </c>
@@ -7837,7 +7837,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="101" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B101" s="4" t="s">
         <v>98</v>
       </c>
@@ -7870,7 +7870,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="102" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B102" s="4" t="s">
         <v>92</v>
       </c>
@@ -7903,7 +7903,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="103" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A103" s="8" t="s">
         <v>559</v>
       </c>
@@ -7939,7 +7939,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="104" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A104" s="8" t="s">
         <v>557</v>
       </c>
@@ -7966,7 +7966,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="105" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A105" s="8" t="s">
         <v>557</v>
       </c>
@@ -7993,7 +7993,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="106" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A106" s="8" t="s">
         <v>557</v>
       </c>
@@ -8020,7 +8020,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="107" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A107" s="8" t="s">
         <v>557</v>
       </c>
@@ -8047,7 +8047,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="108" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A108" s="8" t="s">
         <v>557</v>
       </c>
@@ -8074,7 +8074,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="109" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A109" s="8" t="s">
         <v>559</v>
       </c>
@@ -8110,7 +8110,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A110" s="8" t="s">
         <v>558</v>
       </c>
@@ -8137,7 +8137,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="111" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A111" s="8" t="s">
         <v>557</v>
       </c>
@@ -8164,7 +8164,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A112" s="8" t="s">
         <v>557</v>
       </c>
@@ -8191,7 +8191,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="113" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A113" s="8" t="s">
         <v>557</v>
       </c>
@@ -8218,7 +8218,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A114" s="8" t="s">
         <v>557</v>
       </c>
@@ -8245,7 +8245,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="115" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A115" s="8" t="s">
         <v>557</v>
       </c>
@@ -8272,7 +8272,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="116" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A116" s="8" t="s">
         <v>559</v>
       </c>
@@ -8308,7 +8308,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="117" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A117" s="8" t="s">
         <v>557</v>
       </c>
@@ -8335,7 +8335,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="118" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A118" s="8" t="s">
         <v>558</v>
       </c>
@@ -8365,7 +8365,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="119" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A119" s="8" t="s">
         <v>557</v>
       </c>
@@ -8392,7 +8392,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="120" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A120" s="8" t="s">
         <v>557</v>
       </c>
@@ -8419,7 +8419,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="121" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A121" s="8" t="s">
         <v>597</v>
       </c>
@@ -8446,7 +8446,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="122" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A122" s="8" t="s">
         <v>602</v>
       </c>
@@ -8473,7 +8473,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="123" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A123" s="8" t="s">
         <v>608</v>
       </c>
@@ -8500,7 +8500,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="124" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A124" s="8" t="s">
         <v>611</v>
       </c>
@@ -8527,7 +8527,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="125" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A125" s="8" t="s">
         <v>617</v>
       </c>
@@ -8554,7 +8554,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="126" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A126" s="8" t="s">
         <v>624</v>
       </c>
@@ -8581,7 +8581,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="127" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A127" s="8" t="s">
         <v>557</v>
       </c>
@@ -8608,7 +8608,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="128" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A128" s="8" t="s">
         <v>649</v>
       </c>
@@ -8635,7 +8635,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="129" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A129" s="8" t="s">
         <v>653</v>
       </c>
@@ -8662,7 +8662,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="130" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A130" s="8" t="s">
         <v>659</v>
       </c>
@@ -8689,7 +8689,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="131" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A131" s="8" t="s">
         <v>664</v>
       </c>
@@ -8716,7 +8716,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A132" s="8" t="s">
         <v>557</v>
       </c>
@@ -8743,7 +8743,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="133" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A133" s="8" t="s">
         <v>557</v>
       </c>
@@ -8770,7 +8770,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="134" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A134" s="8" t="s">
         <v>681</v>
       </c>
@@ -8797,7 +8797,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="135" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A135" s="8" t="s">
         <v>687</v>
       </c>
@@ -8824,7 +8824,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="136" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A136" s="8" t="s">
         <v>691</v>
       </c>
@@ -8851,7 +8851,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="137" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A137" s="8" t="s">
         <v>699</v>
       </c>
@@ -8878,7 +8878,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="138" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A138" s="8" t="s">
         <v>704</v>
       </c>
@@ -8905,7 +8905,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="139" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A139" s="8" t="s">
         <v>711</v>
       </c>
@@ -8932,7 +8932,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="140" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A140" s="8" t="s">
         <v>716</v>
       </c>
@@ -8959,7 +8959,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="141" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A141" s="8" t="s">
         <v>724</v>
       </c>
@@ -8986,7 +8986,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="142" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A142" s="8" t="s">
         <v>727</v>
       </c>
@@ -9013,7 +9013,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="143" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A143" s="8" t="s">
         <v>736</v>
       </c>
@@ -9040,7 +9040,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="144" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A144" s="8" t="s">
         <v>740</v>
       </c>
@@ -9067,7 +9067,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="145" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A145" s="8" t="s">
         <v>746</v>
       </c>
@@ -9094,7 +9094,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="146" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A146" s="8" t="s">
         <v>754</v>
       </c>
@@ -9121,7 +9121,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="147" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A147" s="8" t="s">
         <v>759</v>
       </c>
@@ -9148,7 +9148,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="148" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A148" s="8" t="s">
         <v>770</v>
       </c>
@@ -9175,7 +9175,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="149" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A149" s="8" t="s">
         <v>777</v>
       </c>
@@ -9202,7 +9202,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="150" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A150" s="8" t="s">
         <v>782</v>
       </c>
@@ -9229,7 +9229,7 @@
         <v>786</v>
       </c>
     </row>
-    <row r="151" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A151" s="8" t="s">
         <v>557</v>
       </c>
@@ -9256,7 +9256,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="152" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A152" s="8" t="s">
         <v>795</v>
       </c>
@@ -9283,7 +9283,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A153" s="8" t="s">
         <v>800</v>
       </c>
@@ -9310,7 +9310,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A154" s="8" t="s">
         <v>804</v>
       </c>
@@ -9337,7 +9337,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A155" s="8" t="s">
         <v>811</v>
       </c>
@@ -9364,7 +9364,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="156" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A156" s="8" t="s">
         <v>557</v>
       </c>
@@ -9391,7 +9391,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A157" s="8" t="s">
         <v>557</v>
       </c>
@@ -9418,7 +9418,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A158" s="8" t="s">
         <v>827</v>
       </c>
@@ -9445,7 +9445,7 @@
         <v>831</v>
       </c>
     </row>
-    <row r="159" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A159" s="8" t="s">
         <v>557</v>
       </c>
@@ -9472,7 +9472,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A160" s="8" t="s">
         <v>838</v>
       </c>
@@ -9499,7 +9499,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="161" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A161" s="8" t="s">
         <v>557</v>
       </c>
@@ -9526,7 +9526,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A162" s="8" t="s">
         <v>850</v>
       </c>
@@ -9553,7 +9553,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A163" s="8" t="s">
         <v>857</v>
       </c>
@@ -9580,7 +9580,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A164" s="8" t="s">
         <v>557</v>
       </c>
@@ -9607,7 +9607,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="165" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A165" s="8" t="s">
         <v>557</v>
       </c>
@@ -9634,7 +9634,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A166" s="8" t="s">
         <v>557</v>
       </c>
@@ -9661,7 +9661,7 @@
         <v>871</v>
       </c>
     </row>
-    <row r="167" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A167" s="8" t="s">
         <v>557</v>
       </c>
@@ -9688,7 +9688,7 @@
         <v>879</v>
       </c>
     </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A168" s="8" t="s">
         <v>557</v>
       </c>
@@ -9715,7 +9715,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A169" s="8" t="s">
         <v>557</v>
       </c>
@@ -9742,7 +9742,7 @@
         <v>889</v>
       </c>
     </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A170" s="8" t="s">
         <v>557</v>
       </c>
@@ -9769,7 +9769,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A171" s="8" t="s">
         <v>557</v>
       </c>
@@ -9796,7 +9796,7 @@
         <v>897</v>
       </c>
     </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A172" s="8" t="s">
         <v>902</v>
       </c>
@@ -9823,7 +9823,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A173" s="8" t="s">
         <v>902</v>
       </c>
@@ -9850,7 +9850,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A174" s="8" t="s">
         <v>557</v>
       </c>
@@ -9877,7 +9877,7 @@
         <v>915</v>
       </c>
     </row>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A175" s="8" t="s">
         <v>557</v>
       </c>
@@ -9904,7 +9904,7 @@
         <v>919</v>
       </c>
     </row>
-    <row r="176" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A176" s="8" t="s">
         <v>557</v>
       </c>
@@ -9931,7 +9931,7 @@
         <v>925</v>
       </c>
     </row>
-    <row r="177" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A177" s="8" t="s">
         <v>557</v>
       </c>
@@ -9958,7 +9958,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="178" spans="1:13" ht="28" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A178" s="8" t="s">
         <v>557</v>
       </c>
@@ -9985,7 +9985,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="179" spans="1:13" ht="42" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:13" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A179" s="8" t="s">
         <v>938</v>
       </c>
@@ -10012,7 +10012,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="180" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B180" s="4" t="s">
         <v>942</v>
       </c>
@@ -10036,7 +10036,7 @@
         <v>946</v>
       </c>
     </row>
-    <row r="181" spans="1:13" ht="28" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B181" s="4" t="s">
         <v>948</v>
       </c>
@@ -10060,7 +10060,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="182" spans="1:13" ht="28" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B182" s="4" t="s">
         <v>954</v>
       </c>
@@ -10084,7 +10084,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="183" spans="1:13" ht="42" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:13" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B183" s="4" t="s">
         <v>959</v>
       </c>
@@ -10108,7 +10108,7 @@
         <v>960</v>
       </c>
     </row>
-    <row r="184" spans="1:13" ht="28" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B184" s="4" t="s">
         <v>966</v>
       </c>
@@ -10132,7 +10132,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="185" spans="1:13" ht="28" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B185" s="4" t="s">
         <v>971</v>
       </c>
@@ -10156,7 +10156,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="186" spans="1:13" ht="42" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:13" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B186" s="4" t="s">
         <v>976</v>
       </c>
@@ -10180,7 +10180,7 @@
         <v>963</v>
       </c>
     </row>
-    <row r="187" spans="1:13" ht="42" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:13" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B187" s="4" t="s">
         <v>979</v>
       </c>
@@ -10204,7 +10204,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="188" spans="1:13" ht="28" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B188" s="4" t="s">
         <v>985</v>
       </c>
@@ -10231,7 +10231,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="189" spans="1:13" ht="15.5" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:13" ht="15" x14ac:dyDescent="0.2">
       <c r="B189" s="4" t="s">
         <v>988</v>
       </c>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="M189" s="6"/>
     </row>
-    <row r="190" spans="1:13" ht="28" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B190" s="4" t="s">
         <v>992</v>
       </c>
@@ -10280,7 +10280,7 @@
         <v>982</v>
       </c>
     </row>
-    <row r="191" spans="1:13" ht="46.5" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:13" ht="45" x14ac:dyDescent="0.2">
       <c r="B191" s="4" t="s">
         <v>1002</v>
       </c>
@@ -10304,7 +10304,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="192" spans="1:13" ht="28" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B192" s="4" t="s">
         <v>1006</v>
       </c>
@@ -10328,7 +10328,7 @@
         <v>998</v>
       </c>
     </row>
-    <row r="193" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="193" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B193" s="4" t="s">
         <v>1010</v>
       </c>
@@ -10352,7 +10352,7 @@
         <v>1011</v>
       </c>
     </row>
-    <row r="194" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="194" spans="2:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B194" s="4" t="s">
         <v>1015</v>
       </c>
@@ -10379,7 +10379,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="195" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="195" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B195" s="4" t="s">
         <v>1021</v>
       </c>
@@ -10403,7 +10403,7 @@
         <v>1019</v>
       </c>
     </row>
-    <row r="196" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="196" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B196" s="4" t="s">
         <v>1025</v>
       </c>
@@ -10427,7 +10427,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="197" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="197" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B197" s="4" t="s">
         <v>1031</v>
       </c>
@@ -10451,7 +10451,7 @@
         <v>1033</v>
       </c>
     </row>
-    <row r="198" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="198" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B198" s="4" t="s">
         <v>1034</v>
       </c>
@@ -10475,7 +10475,7 @@
         <v>1035</v>
       </c>
     </row>
-    <row r="199" spans="2:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="199" spans="2:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B199" s="4" t="s">
         <v>1040</v>
       </c>
@@ -10499,7 +10499,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="200" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="200" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B200" s="4" t="s">
         <v>1045</v>
       </c>
@@ -10523,7 +10523,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="201" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="201" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B201" s="4" t="s">
         <v>1051</v>
       </c>
@@ -10547,7 +10547,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="202" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="202" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B202" s="4" t="s">
         <v>1058</v>
       </c>
@@ -10571,7 +10571,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="203" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="203" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B203" s="4" t="s">
         <v>1062</v>
       </c>
@@ -10595,7 +10595,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="204" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="204" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B204" s="4" t="s">
         <v>1065</v>
       </c>
@@ -10619,7 +10619,7 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="205" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="205" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B205" s="4" t="s">
         <v>1071</v>
       </c>
@@ -10643,7 +10643,7 @@
         <v>1069</v>
       </c>
     </row>
-    <row r="206" spans="2:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="206" spans="2:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B206" s="4" t="s">
         <v>1074</v>
       </c>
@@ -10667,7 +10667,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="207" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="207" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B207" s="4" t="s">
         <v>1080</v>
       </c>
@@ -10691,7 +10691,7 @@
         <v>1079</v>
       </c>
     </row>
-    <row r="208" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="208" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B208" s="4" t="s">
         <v>1082</v>
       </c>
@@ -10715,7 +10715,7 @@
         <v>1081</v>
       </c>
     </row>
-    <row r="209" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="209" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B209" s="4" t="s">
         <v>1091</v>
       </c>
@@ -10739,7 +10739,7 @@
         <v>1089</v>
       </c>
     </row>
-    <row r="210" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="210" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B210" s="4" t="s">
         <v>1093</v>
       </c>
@@ -10763,7 +10763,7 @@
         <v>1092</v>
       </c>
     </row>
-    <row r="211" spans="2:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="211" spans="2:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B211" s="4" t="s">
         <v>1102</v>
       </c>
@@ -10787,7 +10787,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="212" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="212" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B212" s="4" t="s">
         <v>1105</v>
       </c>
@@ -10811,7 +10811,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="213" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="213" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B213" s="4" t="s">
         <v>1110</v>
       </c>
@@ -10835,7 +10835,7 @@
         <v>1109</v>
       </c>
     </row>
-    <row r="214" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="214" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B214" s="4" t="s">
         <v>1119</v>
       </c>
@@ -10859,7 +10859,7 @@
         <v>1115</v>
       </c>
     </row>
-    <row r="215" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="215" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B215" s="4" t="s">
         <v>1123</v>
       </c>
@@ -10883,7 +10883,7 @@
         <v>1117</v>
       </c>
     </row>
-    <row r="216" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="216" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B216" s="4" t="s">
         <v>1128</v>
       </c>
@@ -10907,7 +10907,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="217" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="217" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C217" s="1" t="s">
         <v>1114</v>
       </c>
@@ -10919,7 +10919,7 @@
         <v>1113</v>
       </c>
     </row>
-    <row r="218" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="218" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C218" s="1" t="s">
         <v>1121</v>
       </c>
@@ -10931,608 +10931,608 @@
         <v>1122</v>
       </c>
     </row>
-    <row r="219" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="219" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J219" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="220" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="220" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J220" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="221" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="221" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J221" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="222" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="222" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J222" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="223" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="223" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J223" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="224" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="224" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J224" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="225" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="225" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J225" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="226" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="226" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J226" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="227" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="227" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J227" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="228" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="228" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J228" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="229" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="229" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J229" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="230" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="230" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J230" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="231" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="231" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J231" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="232" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="232" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J232" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="233" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="233" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J233" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="234" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="234" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J234" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="235" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="235" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J235" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="236" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="236" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J236" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="237" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="237" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J237" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="238" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="238" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J238" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="239" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="239" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J239" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="240" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="240" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J240" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="241" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="241" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J241" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="242" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="242" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J242" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="243" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="243" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J243" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="244" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="244" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J244" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="245" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="245" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J245" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="246" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="246" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J246" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="247" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="247" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J247" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="248" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="248" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J248" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="249" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="249" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J249" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="250" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="250" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J250" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="251" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="251" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J251" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="252" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="252" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J252" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="253" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="253" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J253" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="254" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="254" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J254" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="255" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="255" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J255" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="256" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="256" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J256" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="257" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="257" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J257" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="258" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="258" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J258" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="259" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="259" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J259" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="260" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="260" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J260" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="261" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="261" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J261" s="5" t="str">
         <f t="shared" ref="J261:J318" si="6">"00"&amp;B261</f>
         <v>00</v>
       </c>
     </row>
-    <row r="262" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="262" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J262" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="263" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="263" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J263" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="264" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="264" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J264" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="265" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="265" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J265" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="266" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="266" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J266" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="267" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="267" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J267" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="268" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="268" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J268" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="269" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="269" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J269" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="270" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="270" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J270" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="271" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="271" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J271" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="272" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="272" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J272" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="273" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="273" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J273" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="274" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="274" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J274" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="275" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="275" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J275" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="276" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="276" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J276" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="277" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="277" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J277" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="278" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="278" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J278" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="279" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="279" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J279" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="280" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="280" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J280" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="281" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="281" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J281" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="282" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="282" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J282" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="283" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="283" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J283" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="284" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="284" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J284" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="285" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="285" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J285" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="286" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="286" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J286" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="287" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="287" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J287" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="288" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="288" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J288" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="289" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="289" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J289" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="290" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="290" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J290" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="291" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="291" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J291" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="292" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="292" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J292" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="293" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="293" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J293" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="294" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="294" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J294" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="295" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="295" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J295" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="296" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="296" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J296" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="297" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="297" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J297" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="298" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="298" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J298" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="299" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="299" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J299" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="300" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="300" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J300" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="301" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="301" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J301" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="302" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="302" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J302" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="303" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="303" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J303" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="304" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="304" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J304" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="305" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="305" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J305" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="306" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="306" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J306" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="307" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="307" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J307" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="308" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="308" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J308" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="309" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="309" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J309" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="310" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="310" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J310" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="311" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="311" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J311" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="312" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="312" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J312" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="313" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="313" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J313" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="314" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="314" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J314" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="315" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="315" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J315" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="316" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="316" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J316" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="317" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="317" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J317" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
-    <row r="318" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="318" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J318" s="5" t="str">
         <f t="shared" si="6"/>
         <v>00</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:L4"/>
+  <autoFilter ref="A4:L4" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="1">
     <mergeCell ref="A2:L2"/>
   </mergeCells>
@@ -11541,10 +11541,10 @@
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1:E1 D3:E3 D6:E1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1:E1 D3:E3 D6:E1048576" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"是,否"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H1 H3:H1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H1 H3:H1048576" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"VB编程,系统运维,WEB学习,游戏碎片,日常随笔,浥尘伙伴社团"</formula1>
     </dataValidation>
   </dataValidations>
@@ -11554,20 +11554,20 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A2:L34"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="6.33203125" customWidth="1"/>
+    <col min="2" max="2" width="6.375" customWidth="1"/>
     <col min="3" max="3" width="34" style="4" customWidth="1"/>
     <col min="4" max="4" width="4.75" customWidth="1"/>
-    <col min="8" max="8" width="6.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="19" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="7.08203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.08203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:12" ht="22.5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" ht="23.25" x14ac:dyDescent="0.2">
       <c r="A2" s="21" t="s">
         <v>549</v>
       </c>
@@ -11583,7 +11583,7 @@
       <c r="K2" s="21"/>
       <c r="L2" s="21"/>
     </row>
-    <row r="4" spans="1:12" ht="56" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" ht="57" x14ac:dyDescent="0.2">
       <c r="A4" s="7" t="s">
         <v>0</v>
       </c>
@@ -11621,7 +11621,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
         <v>533</v>
       </c>
@@ -11644,7 +11644,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C8" s="15" t="s">
         <v>545</v>
       </c>
@@ -11653,7 +11653,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C9" s="4" t="s">
         <v>539</v>
       </c>
@@ -11661,7 +11661,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C10" t="s">
         <v>537</v>
       </c>
@@ -11669,7 +11669,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C11" t="s">
         <v>538</v>
       </c>
@@ -11677,7 +11677,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="22.5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" ht="23.25" x14ac:dyDescent="0.2">
       <c r="A13" s="21" t="s">
         <v>543</v>
       </c>
@@ -11693,7 +11693,7 @@
       <c r="K13" s="21"/>
       <c r="L13" s="21"/>
     </row>
-    <row r="15" spans="1:12" ht="56" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" ht="57" x14ac:dyDescent="0.2">
       <c r="A15" s="7" t="s">
         <v>0</v>
       </c>
@@ -11731,7 +11731,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
         <v>533</v>
       </c>
@@ -11757,7 +11757,7 @@
         <v>54837657</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C19" s="15" t="s">
         <v>545</v>
       </c>
@@ -11766,7 +11766,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C20" s="4" t="s">
         <v>539</v>
       </c>
@@ -11774,7 +11774,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C21" t="s">
         <v>537</v>
       </c>
@@ -11782,7 +11782,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C22" t="s">
         <v>538</v>
       </c>
@@ -11790,10 +11790,10 @@
         <v>541</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C23"/>
     </row>
-    <row r="25" spans="1:12" ht="22.5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" ht="23.25" x14ac:dyDescent="0.2">
       <c r="A25" s="21" t="s">
         <v>550</v>
       </c>
@@ -11809,7 +11809,7 @@
       <c r="K25" s="21"/>
       <c r="L25" s="21"/>
     </row>
-    <row r="27" spans="1:12" ht="56" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" ht="57" x14ac:dyDescent="0.2">
       <c r="A27" s="7" t="s">
         <v>0</v>
       </c>
@@ -11847,7 +11847,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B28" t="s">
         <v>533</v>
       </c>
@@ -11873,7 +11873,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C31" s="15" t="s">
         <v>545</v>
       </c>
@@ -11882,7 +11882,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C32" s="4" t="s">
         <v>539</v>
       </c>
@@ -11890,7 +11890,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="33" spans="3:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="3:5" x14ac:dyDescent="0.2">
       <c r="C33" t="s">
         <v>537</v>
       </c>
@@ -11898,7 +11898,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="34" spans="3:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="3:5" x14ac:dyDescent="0.2">
       <c r="C34" t="s">
         <v>538</v>
       </c>
@@ -11914,7 +11914,7 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H15 H27 H4">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H15 H27 H4" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"VB编程,系统运维,WEB学习,游戏碎片,日常随笔"</formula1>
     </dataValidation>
   </dataValidations>

--- a/11_付费课程/99.资料/文章信息备忘表.xlsx
+++ b/11_付费课程/99.资料/文章信息备忘表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Writing\11_付费课程\99.资料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41DE26BC-C20C-475E-ACBA-71B2ACB0B3F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8335E681-0471-44C4-87BF-43F71DB70B52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="870" yWindow="-120" windowWidth="19740" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6060" yWindow="195" windowWidth="13725" windowHeight="10605" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1555" uniqueCount="1134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1558" uniqueCount="1136">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -4446,10 +4446,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>wmic</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>36579828</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -4522,6 +4518,18 @@
   </si>
   <si>
     <t>85412593</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>30707479</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>阴阳历转换</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>奇哉怪也，Windows11不支持WMIC？（附离线安装方法及安装包）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -10816,7 +10824,7 @@
         <v>1110</v>
       </c>
       <c r="C213" s="1" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="H213" s="1" t="s">
         <v>21</v>
@@ -10837,79 +10845,79 @@
     </row>
     <row r="214" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B214" s="4" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="C214" s="1" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="H214" s="1" t="s">
         <v>654</v>
       </c>
       <c r="I214" s="4" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="J214" s="5" t="str">
         <f t="shared" si="5"/>
         <v>001118</v>
       </c>
       <c r="K214" s="3" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="L214" s="2" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="215" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B215" s="4" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="C215" s="1" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="H215" s="1" t="s">
         <v>654</v>
       </c>
       <c r="I215" s="4" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="J215" s="5" t="str">
         <f t="shared" si="5"/>
         <v>001119</v>
       </c>
       <c r="K215" s="3" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="L215" s="2" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="216" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B216" s="4" t="s">
+        <v>1127</v>
+      </c>
+      <c r="C216" s="1" t="s">
         <v>1128</v>
       </c>
-      <c r="C216" s="1" t="s">
+      <c r="H216" s="1" t="s">
         <v>1129</v>
       </c>
-      <c r="H216" s="1" t="s">
+      <c r="I216" s="4" t="s">
         <v>1130</v>
-      </c>
-      <c r="I216" s="4" t="s">
-        <v>1131</v>
       </c>
       <c r="J216" s="5" t="str">
         <f t="shared" si="5"/>
         <v>001120</v>
       </c>
       <c r="K216" s="3" t="s">
+        <v>1131</v>
+      </c>
+      <c r="L216" s="2" t="s">
         <v>1132</v>
       </c>
-      <c r="L216" s="2" t="s">
-        <v>1133</v>
-      </c>
-    </row>
-    <row r="217" spans="2:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="217" spans="2:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="C217" s="1" t="s">
-        <v>1114</v>
+        <v>1135</v>
       </c>
       <c r="J217" s="5" t="str">
         <f t="shared" si="5"/>
@@ -10921,20 +10929,29 @@
     </row>
     <row r="218" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C218" s="1" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="J218" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
       <c r="L218" s="2" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="219" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="C219" s="1" t="s">
+        <v>1134</v>
+      </c>
+      <c r="H219" s="1" t="s">
+        <v>11</v>
+      </c>
       <c r="J219" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
+      </c>
+      <c r="L219" s="2" t="s">
+        <v>1133</v>
       </c>
     </row>
     <row r="220" spans="2:12" x14ac:dyDescent="0.2">

--- a/11_付费课程/99.资料/文章信息备忘表.xlsx
+++ b/11_付费课程/99.资料/文章信息备忘表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Writing\11_付费课程\99.资料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8335E681-0471-44C4-87BF-43F71DB70B52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{698575F0-2737-493B-AFC9-99F4E63FE161}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6060" yWindow="195" windowWidth="13725" windowHeight="10605" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="870" yWindow="-120" windowWidth="19740" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1558" uniqueCount="1136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1562" uniqueCount="1139">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -4530,6 +4530,18 @@
   </si>
   <si>
     <t>奇哉怪也，Windows11不支持WMIC？（附离线安装方法及安装包）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1122</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-12-01 09:26:15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>516290</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -10916,12 +10928,24 @@
       </c>
     </row>
     <row r="217" spans="2:12" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="B217" s="4" t="s">
+        <v>1136</v>
+      </c>
       <c r="C217" s="1" t="s">
         <v>1135</v>
       </c>
+      <c r="H217" s="1" t="s">
+        <v>654</v>
+      </c>
+      <c r="I217" s="4" t="s">
+        <v>1137</v>
+      </c>
       <c r="J217" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>00</v>
+        <v>001122</v>
+      </c>
+      <c r="K217" s="3" t="s">
+        <v>1138</v>
       </c>
       <c r="L217" s="2" t="s">
         <v>1113</v>

--- a/11_付费课程/99.资料/文章信息备忘表.xlsx
+++ b/11_付费课程/99.资料/文章信息备忘表.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Writing\11_付费课程\99.资料\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\writing\11_付费课程\99.资料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{698575F0-2737-493B-AFC9-99F4E63FE161}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="870" yWindow="-120" windowWidth="19740" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1910" yWindow="-120" windowWidth="19740" windowHeight="11760"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$L$4</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -40,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1562" uniqueCount="1139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1563" uniqueCount="1140">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -4542,13 +4541,17 @@
   </si>
   <si>
     <t>516290</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1123</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -4716,7 +4719,14 @@
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -5033,25 +5043,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:M318"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A2:M317"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.25" style="8" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="4" customWidth="1"/>
-    <col min="3" max="3" width="30.875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="5.375" style="6" customWidth="1"/>
-    <col min="5" max="6" width="5.125" style="6" customWidth="1"/>
+    <col min="2" max="2" width="5.58203125" style="4" customWidth="1"/>
+    <col min="3" max="3" width="30.83203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="5.33203125" style="6" customWidth="1"/>
+    <col min="5" max="6" width="5.08203125" style="6" customWidth="1"/>
     <col min="7" max="7" width="5.25" style="6" customWidth="1"/>
     <col min="8" max="8" width="13.5" style="1" customWidth="1"/>
     <col min="9" max="9" width="19" style="4" customWidth="1"/>
-    <col min="10" max="10" width="8.625" style="5" customWidth="1"/>
+    <col min="10" max="10" width="8.58203125" style="5" customWidth="1"/>
     <col min="11" max="11" width="7.5" style="3" customWidth="1"/>
     <col min="12" max="12" width="9.25" style="2" customWidth="1"/>
     <col min="13" max="13" width="16.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" ht="25" x14ac:dyDescent="0.3">
       <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
@@ -5067,8 +5077,8 @@
       <c r="K2" s="20"/>
       <c r="L2" s="20"/>
     </row>
-    <row r="3" spans="1:12" ht="6.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="4" spans="1:12" s="7" customFormat="1" ht="57" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12" ht="6.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:12" s="7" customFormat="1" ht="56" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>0</v>
       </c>
@@ -5106,7 +5116,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
         <v>557</v>
       </c>
@@ -5133,7 +5143,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
         <v>559</v>
       </c>
@@ -5169,7 +5179,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
         <v>559</v>
       </c>
@@ -5205,25 +5215,25 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="J8" s="5" t="str">
         <f t="shared" si="0"/>
         <v>000</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="J9" s="5" t="str">
         <f t="shared" si="0"/>
         <v>000</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="J10" s="5" t="str">
         <f t="shared" si="0"/>
         <v>000</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
         <v>522</v>
       </c>
@@ -5256,7 +5266,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
         <v>558</v>
       </c>
@@ -5286,7 +5296,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A13" s="8" t="s">
         <v>558</v>
       </c>
@@ -5316,7 +5326,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A14" s="8" t="s">
         <v>640</v>
       </c>
@@ -5343,7 +5353,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="8" t="s">
         <v>557</v>
       </c>
@@ -5370,7 +5380,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="8" t="s">
         <v>557</v>
       </c>
@@ -5397,7 +5407,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="8" t="s">
         <v>557</v>
       </c>
@@ -5424,7 +5434,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="8" t="s">
         <v>767</v>
       </c>
@@ -5451,7 +5461,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
         <v>557</v>
       </c>
@@ -5478,7 +5488,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A20" s="8" t="s">
         <v>557</v>
       </c>
@@ -5505,7 +5515,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A21" s="8" t="s">
         <v>557</v>
       </c>
@@ -5532,7 +5542,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A22" s="8" t="s">
         <v>559</v>
       </c>
@@ -5568,7 +5578,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" s="8" t="s">
         <v>557</v>
       </c>
@@ -5595,7 +5605,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A24" s="8" t="s">
         <v>558</v>
       </c>
@@ -5625,7 +5635,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A25" s="8" t="s">
         <v>557</v>
       </c>
@@ -5652,7 +5662,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A26" s="8" t="s">
         <v>557</v>
       </c>
@@ -5679,7 +5689,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="27" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A27" s="8" t="s">
         <v>633</v>
       </c>
@@ -5706,7 +5716,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A28" s="8" t="s">
         <v>557</v>
       </c>
@@ -5733,7 +5743,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A29" s="8" t="s">
         <v>559</v>
       </c>
@@ -5769,7 +5779,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A30" s="8" t="s">
         <v>559</v>
       </c>
@@ -5805,7 +5815,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A31" s="8" t="s">
         <v>557</v>
       </c>
@@ -5832,7 +5842,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A32" s="8" t="s">
         <v>557</v>
       </c>
@@ -5859,7 +5869,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A33" s="8" t="s">
         <v>557</v>
       </c>
@@ -5886,7 +5896,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="34" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A34" s="8" t="s">
         <v>557</v>
       </c>
@@ -5913,7 +5923,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="35" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A35" s="8" t="s">
         <v>557</v>
       </c>
@@ -5940,7 +5950,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="36" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A36" s="8" t="s">
         <v>557</v>
       </c>
@@ -5967,7 +5977,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="37" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A37" s="8" t="s">
         <v>559</v>
       </c>
@@ -6003,7 +6013,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="38" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A38" s="8" t="s">
         <v>557</v>
       </c>
@@ -6030,7 +6040,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" s="8" t="s">
         <v>557</v>
       </c>
@@ -6057,7 +6067,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="40" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A40" s="8" t="s">
         <v>557</v>
       </c>
@@ -6084,7 +6094,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="41" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A41" s="8" t="s">
         <v>557</v>
       </c>
@@ -6111,7 +6121,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="42" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A42" s="8" t="s">
         <v>557</v>
       </c>
@@ -6138,7 +6148,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="43" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A43" s="8" t="s">
         <v>559</v>
       </c>
@@ -6171,7 +6181,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="44" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A44" s="8" t="s">
         <v>557</v>
       </c>
@@ -6198,7 +6208,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="45" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A45" s="8" t="s">
         <v>557</v>
       </c>
@@ -6225,7 +6235,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="46" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A46" s="8" t="s">
         <v>557</v>
       </c>
@@ -6252,7 +6262,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" s="8" t="s">
         <v>557</v>
       </c>
@@ -6279,7 +6289,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="48" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A48" s="8" t="s">
         <v>557</v>
       </c>
@@ -6306,7 +6316,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="49" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A49" s="8" t="s">
         <v>557</v>
       </c>
@@ -6333,7 +6343,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="50" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A50" s="8" t="s">
         <v>557</v>
       </c>
@@ -6360,7 +6370,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" s="8" t="s">
         <v>557</v>
       </c>
@@ -6387,7 +6397,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="52" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A52" s="8" t="s">
         <v>557</v>
       </c>
@@ -6414,7 +6424,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" s="8" t="s">
         <v>557</v>
       </c>
@@ -6441,7 +6451,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="54" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A54" s="8" t="s">
         <v>557</v>
       </c>
@@ -6468,7 +6478,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" s="8" t="s">
         <v>557</v>
       </c>
@@ -6495,7 +6505,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="56" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A56" s="8" t="s">
         <v>559</v>
       </c>
@@ -6531,7 +6541,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="57" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A57" s="8" t="s">
         <v>559</v>
       </c>
@@ -6567,7 +6577,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="58" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A58" s="8" t="s">
         <v>557</v>
       </c>
@@ -6594,7 +6604,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="59" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A59" s="8" t="s">
         <v>558</v>
       </c>
@@ -6624,7 +6634,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="60" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A60" s="8" t="s">
         <v>557</v>
       </c>
@@ -6651,7 +6661,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="61" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B61" s="4" t="s">
         <v>298</v>
       </c>
@@ -6684,7 +6694,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="62" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B62" s="4" t="s">
         <v>294</v>
       </c>
@@ -6717,7 +6727,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="63" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B63" s="4" t="s">
         <v>289</v>
       </c>
@@ -6750,7 +6760,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="64" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A64" s="8" t="s">
         <v>557</v>
       </c>
@@ -6777,7 +6787,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="65" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A65" s="8" t="s">
         <v>557</v>
       </c>
@@ -6804,7 +6814,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="66" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A66" s="8" t="s">
         <v>559</v>
       </c>
@@ -6840,7 +6850,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="67" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A67" s="8" t="s">
         <v>557</v>
       </c>
@@ -6867,7 +6877,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="68" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A68" s="8" t="s">
         <v>558</v>
       </c>
@@ -6897,7 +6907,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="69" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A69" s="8" t="s">
         <v>559</v>
       </c>
@@ -6924,7 +6934,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="70" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A70" s="8" t="s">
         <v>559</v>
       </c>
@@ -6951,7 +6961,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="71" spans="1:12" ht="57" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:12" ht="56" x14ac:dyDescent="0.3">
       <c r="A71" s="8" t="s">
         <v>558</v>
       </c>
@@ -6981,7 +6991,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="72" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A72" s="8" t="s">
         <v>558</v>
       </c>
@@ -7011,7 +7021,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="73" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A73" s="8" t="s">
         <v>558</v>
       </c>
@@ -7041,7 +7051,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="74" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A74" s="8" t="s">
         <v>557</v>
       </c>
@@ -7068,7 +7078,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="75" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A75" s="8" t="s">
         <v>557</v>
       </c>
@@ -7095,7 +7105,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="76" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A76" s="8" t="s">
         <v>558</v>
       </c>
@@ -7128,7 +7138,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="77" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A77" s="8" t="s">
         <v>557</v>
       </c>
@@ -7155,7 +7165,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="78" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A78" s="8" t="s">
         <v>558</v>
       </c>
@@ -7182,7 +7192,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="79" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A79" s="8" t="s">
         <v>557</v>
       </c>
@@ -7209,7 +7219,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="80" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A80" s="8" t="s">
         <v>558</v>
       </c>
@@ -7236,7 +7246,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="81" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A81" s="8" t="s">
         <v>557</v>
       </c>
@@ -7263,7 +7273,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="82" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A82" s="8" t="s">
         <v>557</v>
       </c>
@@ -7290,7 +7300,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="83" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A83" s="8" t="s">
         <v>557</v>
       </c>
@@ -7317,7 +7327,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="84" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A84" s="8" t="s">
         <v>557</v>
       </c>
@@ -7344,7 +7354,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="85" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A85" s="8" t="s">
         <v>558</v>
       </c>
@@ -7371,7 +7381,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="86" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A86" s="8" t="s">
         <v>557</v>
       </c>
@@ -7398,7 +7408,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="87" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A87" s="8" t="s">
         <v>559</v>
       </c>
@@ -7434,7 +7444,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="88" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A88" s="8" t="s">
         <v>559</v>
       </c>
@@ -7470,7 +7480,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="89" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A89" s="8" t="s">
         <v>559</v>
       </c>
@@ -7506,7 +7516,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="90" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A90" s="8" t="s">
         <v>557</v>
       </c>
@@ -7533,7 +7543,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="91" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B91" s="4" t="s">
         <v>151</v>
       </c>
@@ -7566,7 +7576,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="92" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B92" s="4" t="s">
         <v>146</v>
       </c>
@@ -7599,7 +7609,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="93" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B93" s="4" t="s">
         <v>140</v>
       </c>
@@ -7632,7 +7642,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="94" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B94" s="4" t="s">
         <v>135</v>
       </c>
@@ -7665,7 +7675,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="95" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A95" s="8" t="s">
         <v>558</v>
       </c>
@@ -7692,7 +7702,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="96" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="B96" s="4" t="s">
         <v>123</v>
       </c>
@@ -7725,7 +7735,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="97" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B97" s="4" t="s">
         <v>118</v>
       </c>
@@ -7758,7 +7768,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="98" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="B98" s="4" t="s">
         <v>112</v>
       </c>
@@ -7791,7 +7801,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="99" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B99" s="4" t="s">
         <v>109</v>
       </c>
@@ -7824,7 +7834,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="100" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B100" s="4" t="s">
         <v>104</v>
       </c>
@@ -7857,7 +7867,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="101" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="B101" s="4" t="s">
         <v>98</v>
       </c>
@@ -7890,7 +7900,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="102" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B102" s="4" t="s">
         <v>92</v>
       </c>
@@ -7923,7 +7933,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="103" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A103" s="8" t="s">
         <v>559</v>
       </c>
@@ -7959,7 +7969,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="104" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A104" s="8" t="s">
         <v>557</v>
       </c>
@@ -7986,7 +7996,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="105" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A105" s="8" t="s">
         <v>557</v>
       </c>
@@ -8013,7 +8023,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="106" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A106" s="8" t="s">
         <v>557</v>
       </c>
@@ -8040,7 +8050,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="107" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A107" s="8" t="s">
         <v>557</v>
       </c>
@@ -8067,7 +8077,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="108" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A108" s="8" t="s">
         <v>557</v>
       </c>
@@ -8094,7 +8104,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="109" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A109" s="8" t="s">
         <v>559</v>
       </c>
@@ -8130,7 +8140,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A110" s="8" t="s">
         <v>558</v>
       </c>
@@ -8157,7 +8167,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="111" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A111" s="8" t="s">
         <v>557</v>
       </c>
@@ -8184,7 +8194,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="112" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A112" s="8" t="s">
         <v>557</v>
       </c>
@@ -8211,7 +8221,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="113" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A113" s="8" t="s">
         <v>557</v>
       </c>
@@ -8238,7 +8248,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A114" s="8" t="s">
         <v>557</v>
       </c>
@@ -8265,7 +8275,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="115" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A115" s="8" t="s">
         <v>557</v>
       </c>
@@ -8292,7 +8302,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="116" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A116" s="8" t="s">
         <v>559</v>
       </c>
@@ -8328,7 +8338,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="117" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A117" s="8" t="s">
         <v>557</v>
       </c>
@@ -8355,7 +8365,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="118" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A118" s="8" t="s">
         <v>558</v>
       </c>
@@ -8385,7 +8395,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="119" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A119" s="8" t="s">
         <v>557</v>
       </c>
@@ -8412,7 +8422,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="120" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A120" s="8" t="s">
         <v>557</v>
       </c>
@@ -8439,7 +8449,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="121" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A121" s="8" t="s">
         <v>597</v>
       </c>
@@ -8466,7 +8476,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="122" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A122" s="8" t="s">
         <v>602</v>
       </c>
@@ -8493,7 +8503,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="123" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A123" s="8" t="s">
         <v>608</v>
       </c>
@@ -8520,7 +8530,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="124" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A124" s="8" t="s">
         <v>611</v>
       </c>
@@ -8547,7 +8557,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="125" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A125" s="8" t="s">
         <v>617</v>
       </c>
@@ -8574,7 +8584,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="126" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A126" s="8" t="s">
         <v>624</v>
       </c>
@@ -8601,7 +8611,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="127" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A127" s="8" t="s">
         <v>557</v>
       </c>
@@ -8628,7 +8638,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="128" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A128" s="8" t="s">
         <v>649</v>
       </c>
@@ -8655,7 +8665,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="129" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A129" s="8" t="s">
         <v>653</v>
       </c>
@@ -8682,7 +8692,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="130" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A130" s="8" t="s">
         <v>659</v>
       </c>
@@ -8709,7 +8719,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="131" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A131" s="8" t="s">
         <v>664</v>
       </c>
@@ -8736,7 +8746,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A132" s="8" t="s">
         <v>557</v>
       </c>
@@ -8763,7 +8773,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="133" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A133" s="8" t="s">
         <v>557</v>
       </c>
@@ -8790,7 +8800,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="134" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A134" s="8" t="s">
         <v>681</v>
       </c>
@@ -8817,7 +8827,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="135" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A135" s="8" t="s">
         <v>687</v>
       </c>
@@ -8844,7 +8854,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="136" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A136" s="8" t="s">
         <v>691</v>
       </c>
@@ -8871,7 +8881,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="137" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A137" s="8" t="s">
         <v>699</v>
       </c>
@@ -8898,7 +8908,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="138" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A138" s="8" t="s">
         <v>704</v>
       </c>
@@ -8925,7 +8935,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="139" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A139" s="8" t="s">
         <v>711</v>
       </c>
@@ -8952,7 +8962,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="140" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A140" s="8" t="s">
         <v>716</v>
       </c>
@@ -8979,7 +8989,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="141" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A141" s="8" t="s">
         <v>724</v>
       </c>
@@ -9006,7 +9016,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="142" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A142" s="8" t="s">
         <v>727</v>
       </c>
@@ -9033,7 +9043,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="143" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A143" s="8" t="s">
         <v>736</v>
       </c>
@@ -9060,7 +9070,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="144" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A144" s="8" t="s">
         <v>740</v>
       </c>
@@ -9087,7 +9097,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="145" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A145" s="8" t="s">
         <v>746</v>
       </c>
@@ -9114,7 +9124,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="146" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A146" s="8" t="s">
         <v>754</v>
       </c>
@@ -9141,7 +9151,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="147" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A147" s="8" t="s">
         <v>759</v>
       </c>
@@ -9168,7 +9178,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="148" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A148" s="8" t="s">
         <v>770</v>
       </c>
@@ -9195,7 +9205,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="149" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A149" s="8" t="s">
         <v>777</v>
       </c>
@@ -9222,7 +9232,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="150" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A150" s="8" t="s">
         <v>782</v>
       </c>
@@ -9249,7 +9259,7 @@
         <v>786</v>
       </c>
     </row>
-    <row r="151" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A151" s="8" t="s">
         <v>557</v>
       </c>
@@ -9276,7 +9286,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="152" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A152" s="8" t="s">
         <v>795</v>
       </c>
@@ -9303,7 +9313,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A153" s="8" t="s">
         <v>800</v>
       </c>
@@ -9330,7 +9340,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A154" s="8" t="s">
         <v>804</v>
       </c>
@@ -9357,7 +9367,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A155" s="8" t="s">
         <v>811</v>
       </c>
@@ -9384,7 +9394,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="156" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A156" s="8" t="s">
         <v>557</v>
       </c>
@@ -9411,7 +9421,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A157" s="8" t="s">
         <v>557</v>
       </c>
@@ -9438,7 +9448,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A158" s="8" t="s">
         <v>827</v>
       </c>
@@ -9465,7 +9475,7 @@
         <v>831</v>
       </c>
     </row>
-    <row r="159" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A159" s="8" t="s">
         <v>557</v>
       </c>
@@ -9492,7 +9502,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A160" s="8" t="s">
         <v>838</v>
       </c>
@@ -9519,7 +9529,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="161" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A161" s="8" t="s">
         <v>557</v>
       </c>
@@ -9546,7 +9556,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A162" s="8" t="s">
         <v>850</v>
       </c>
@@ -9573,7 +9583,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A163" s="8" t="s">
         <v>857</v>
       </c>
@@ -9600,7 +9610,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A164" s="8" t="s">
         <v>557</v>
       </c>
@@ -9627,7 +9637,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="165" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A165" s="8" t="s">
         <v>557</v>
       </c>
@@ -9654,7 +9664,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A166" s="8" t="s">
         <v>557</v>
       </c>
@@ -9681,7 +9691,7 @@
         <v>871</v>
       </c>
     </row>
-    <row r="167" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A167" s="8" t="s">
         <v>557</v>
       </c>
@@ -9708,7 +9718,7 @@
         <v>879</v>
       </c>
     </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A168" s="8" t="s">
         <v>557</v>
       </c>
@@ -9735,7 +9745,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A169" s="8" t="s">
         <v>557</v>
       </c>
@@ -9762,7 +9772,7 @@
         <v>889</v>
       </c>
     </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A170" s="8" t="s">
         <v>557</v>
       </c>
@@ -9789,7 +9799,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A171" s="8" t="s">
         <v>557</v>
       </c>
@@ -9816,7 +9826,7 @@
         <v>897</v>
       </c>
     </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A172" s="8" t="s">
         <v>902</v>
       </c>
@@ -9843,7 +9853,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A173" s="8" t="s">
         <v>902</v>
       </c>
@@ -9870,7 +9880,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A174" s="8" t="s">
         <v>557</v>
       </c>
@@ -9897,7 +9907,7 @@
         <v>915</v>
       </c>
     </row>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A175" s="8" t="s">
         <v>557</v>
       </c>
@@ -9924,7 +9934,7 @@
         <v>919</v>
       </c>
     </row>
-    <row r="176" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A176" s="8" t="s">
         <v>557</v>
       </c>
@@ -9951,7 +9961,7 @@
         <v>925</v>
       </c>
     </row>
-    <row r="177" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A177" s="8" t="s">
         <v>557</v>
       </c>
@@ -9978,7 +9988,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="178" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:13" ht="28" x14ac:dyDescent="0.3">
       <c r="A178" s="8" t="s">
         <v>557</v>
       </c>
@@ -10005,7 +10015,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="179" spans="1:13" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:13" ht="42" x14ac:dyDescent="0.3">
       <c r="A179" s="8" t="s">
         <v>938</v>
       </c>
@@ -10032,7 +10042,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="180" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B180" s="4" t="s">
         <v>942</v>
       </c>
@@ -10056,7 +10066,7 @@
         <v>946</v>
       </c>
     </row>
-    <row r="181" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:13" ht="28" x14ac:dyDescent="0.3">
       <c r="B181" s="4" t="s">
         <v>948</v>
       </c>
@@ -10080,7 +10090,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="182" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:13" ht="28" x14ac:dyDescent="0.3">
       <c r="B182" s="4" t="s">
         <v>954</v>
       </c>
@@ -10104,7 +10114,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="183" spans="1:13" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:13" ht="42" x14ac:dyDescent="0.3">
       <c r="B183" s="4" t="s">
         <v>959</v>
       </c>
@@ -10128,7 +10138,7 @@
         <v>960</v>
       </c>
     </row>
-    <row r="184" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:13" ht="28" x14ac:dyDescent="0.3">
       <c r="B184" s="4" t="s">
         <v>966</v>
       </c>
@@ -10152,7 +10162,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="185" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:13" ht="28" x14ac:dyDescent="0.3">
       <c r="B185" s="4" t="s">
         <v>971</v>
       </c>
@@ -10176,7 +10186,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="186" spans="1:13" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:13" ht="42" x14ac:dyDescent="0.3">
       <c r="B186" s="4" t="s">
         <v>976</v>
       </c>
@@ -10200,7 +10210,7 @@
         <v>963</v>
       </c>
     </row>
-    <row r="187" spans="1:13" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:13" ht="42" x14ac:dyDescent="0.3">
       <c r="B187" s="4" t="s">
         <v>979</v>
       </c>
@@ -10224,7 +10234,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="188" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:13" ht="28" x14ac:dyDescent="0.3">
       <c r="B188" s="4" t="s">
         <v>985</v>
       </c>
@@ -10251,7 +10261,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="189" spans="1:13" ht="15" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:13" ht="15.5" x14ac:dyDescent="0.3">
       <c r="B189" s="4" t="s">
         <v>988</v>
       </c>
@@ -10276,7 +10286,7 @@
       </c>
       <c r="M189" s="6"/>
     </row>
-    <row r="190" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:13" ht="28" x14ac:dyDescent="0.3">
       <c r="B190" s="4" t="s">
         <v>992</v>
       </c>
@@ -10300,7 +10310,7 @@
         <v>982</v>
       </c>
     </row>
-    <row r="191" spans="1:13" ht="45" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:13" ht="46.5" x14ac:dyDescent="0.3">
       <c r="B191" s="4" t="s">
         <v>1002</v>
       </c>
@@ -10324,7 +10334,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="192" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:13" ht="28" x14ac:dyDescent="0.3">
       <c r="B192" s="4" t="s">
         <v>1006</v>
       </c>
@@ -10348,7 +10358,7 @@
         <v>998</v>
       </c>
     </row>
-    <row r="193" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="193" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B193" s="4" t="s">
         <v>1010</v>
       </c>
@@ -10372,7 +10382,7 @@
         <v>1011</v>
       </c>
     </row>
-    <row r="194" spans="2:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="194" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B194" s="4" t="s">
         <v>1015</v>
       </c>
@@ -10399,7 +10409,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="195" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="195" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B195" s="4" t="s">
         <v>1021</v>
       </c>
@@ -10423,7 +10433,7 @@
         <v>1019</v>
       </c>
     </row>
-    <row r="196" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="196" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B196" s="4" t="s">
         <v>1025</v>
       </c>
@@ -10447,7 +10457,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="197" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="197" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B197" s="4" t="s">
         <v>1031</v>
       </c>
@@ -10461,7 +10471,7 @@
         <v>1029</v>
       </c>
       <c r="J197" s="5" t="str">
-        <f t="shared" ref="J197:J260" si="5">"00"&amp;B197</f>
+        <f t="shared" ref="J197:J259" si="5">"00"&amp;B197</f>
         <v>001099</v>
       </c>
       <c r="K197" s="3" t="s">
@@ -10471,7 +10481,7 @@
         <v>1033</v>
       </c>
     </row>
-    <row r="198" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="198" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B198" s="4" t="s">
         <v>1034</v>
       </c>
@@ -10495,7 +10505,7 @@
         <v>1035</v>
       </c>
     </row>
-    <row r="199" spans="2:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="199" spans="2:12" ht="42" x14ac:dyDescent="0.3">
       <c r="B199" s="4" t="s">
         <v>1040</v>
       </c>
@@ -10519,7 +10529,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="200" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="200" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B200" s="4" t="s">
         <v>1045</v>
       </c>
@@ -10543,7 +10553,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="201" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="201" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B201" s="4" t="s">
         <v>1051</v>
       </c>
@@ -10567,7 +10577,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="202" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="202" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B202" s="4" t="s">
         <v>1058</v>
       </c>
@@ -10591,7 +10601,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="203" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="203" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B203" s="4" t="s">
         <v>1062</v>
       </c>
@@ -10615,7 +10625,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="204" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="204" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B204" s="4" t="s">
         <v>1065</v>
       </c>
@@ -10639,7 +10649,7 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="205" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="205" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B205" s="4" t="s">
         <v>1071</v>
       </c>
@@ -10663,7 +10673,7 @@
         <v>1069</v>
       </c>
     </row>
-    <row r="206" spans="2:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="206" spans="2:12" ht="42" x14ac:dyDescent="0.3">
       <c r="B206" s="4" t="s">
         <v>1074</v>
       </c>
@@ -10687,7 +10697,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="207" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="207" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B207" s="4" t="s">
         <v>1080</v>
       </c>
@@ -10711,7 +10721,7 @@
         <v>1079</v>
       </c>
     </row>
-    <row r="208" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="208" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B208" s="4" t="s">
         <v>1082</v>
       </c>
@@ -10735,7 +10745,7 @@
         <v>1081</v>
       </c>
     </row>
-    <row r="209" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="209" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B209" s="4" t="s">
         <v>1091</v>
       </c>
@@ -10759,7 +10769,7 @@
         <v>1089</v>
       </c>
     </row>
-    <row r="210" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="210" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B210" s="4" t="s">
         <v>1093</v>
       </c>
@@ -10783,7 +10793,7 @@
         <v>1092</v>
       </c>
     </row>
-    <row r="211" spans="2:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="211" spans="2:12" ht="42" x14ac:dyDescent="0.3">
       <c r="B211" s="4" t="s">
         <v>1102</v>
       </c>
@@ -10807,7 +10817,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="212" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="212" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B212" s="4" t="s">
         <v>1105</v>
       </c>
@@ -10831,7 +10841,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="213" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="213" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B213" s="4" t="s">
         <v>1110</v>
       </c>
@@ -10855,7 +10865,7 @@
         <v>1109</v>
       </c>
     </row>
-    <row r="214" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="214" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B214" s="4" t="s">
         <v>1118</v>
       </c>
@@ -10879,7 +10889,7 @@
         <v>1114</v>
       </c>
     </row>
-    <row r="215" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="215" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B215" s="4" t="s">
         <v>1122</v>
       </c>
@@ -10903,7 +10913,7 @@
         <v>1116</v>
       </c>
     </row>
-    <row r="216" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="216" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B216" s="4" t="s">
         <v>1127</v>
       </c>
@@ -10927,7 +10937,7 @@
         <v>1132</v>
       </c>
     </row>
-    <row r="217" spans="2:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="217" spans="2:12" ht="42" x14ac:dyDescent="0.3">
       <c r="B217" s="4" t="s">
         <v>1136</v>
       </c>
@@ -10951,641 +10961,641 @@
         <v>1113</v>
       </c>
     </row>
-    <row r="218" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="218" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B218" s="4" t="s">
+        <v>1139</v>
+      </c>
       <c r="C218" s="1" t="s">
-        <v>1120</v>
+        <v>1134</v>
+      </c>
+      <c r="H218" s="1" t="s">
+        <v>11</v>
       </c>
       <c r="J218" s="5" t="str">
         <f t="shared" si="5"/>
+        <v>001123</v>
+      </c>
+      <c r="L218" s="2" t="s">
+        <v>1133</v>
+      </c>
+    </row>
+    <row r="219" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="C219" s="1" t="s">
+        <v>1120</v>
+      </c>
+      <c r="J219" s="5" t="str">
+        <f t="shared" ref="J219" si="6">"00"&amp;B219</f>
         <v>00</v>
       </c>
-      <c r="L218" s="2" t="s">
+      <c r="L219" s="2" t="s">
         <v>1121</v>
       </c>
     </row>
-    <row r="219" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C219" s="1" t="s">
-        <v>1134</v>
-      </c>
-      <c r="H219" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="J219" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>00</v>
-      </c>
-      <c r="L219" s="2" t="s">
-        <v>1133</v>
-      </c>
-    </row>
-    <row r="220" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="220" spans="2:12" x14ac:dyDescent="0.3">
       <c r="J220" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="221" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="221" spans="2:12" x14ac:dyDescent="0.3">
       <c r="J221" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="222" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="222" spans="2:12" x14ac:dyDescent="0.3">
       <c r="J222" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="223" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="223" spans="2:12" x14ac:dyDescent="0.3">
       <c r="J223" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="224" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="224" spans="2:12" x14ac:dyDescent="0.3">
       <c r="J224" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="225" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="225" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J225" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="226" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="226" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J226" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="227" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="227" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J227" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="228" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="228" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J228" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="229" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="229" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J229" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="230" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="230" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J230" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="231" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="231" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J231" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="232" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="232" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J232" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="233" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="233" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J233" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="234" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="234" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J234" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="235" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="235" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J235" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="236" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="236" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J236" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="237" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="237" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J237" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="238" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="238" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J238" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="239" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="239" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J239" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="240" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="240" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J240" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="241" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="241" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J241" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="242" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="242" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J242" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="243" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="243" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J243" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="244" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="244" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J244" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="245" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="245" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J245" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="246" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="246" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J246" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="247" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="247" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J247" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="248" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="248" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J248" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="249" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="249" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J249" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="250" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="250" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J250" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="251" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="251" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J251" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="252" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="252" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J252" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="253" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="253" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J253" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="254" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="254" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J254" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="255" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="255" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J255" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="256" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="256" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J256" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="257" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="257" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J257" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="258" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="258" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J258" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="259" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="259" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J259" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="260" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="260" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J260" s="5" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="J260:J317" si="7">"00"&amp;B260</f>
         <v>00</v>
       </c>
     </row>
-    <row r="261" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="261" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J261" s="5" t="str">
-        <f t="shared" ref="J261:J318" si="6">"00"&amp;B261</f>
+        <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="262" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="262" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J262" s="5" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="263" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="263" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J263" s="5" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="264" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="264" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J264" s="5" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="265" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="265" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J265" s="5" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="266" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="266" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J266" s="5" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="267" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="267" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J267" s="5" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="268" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="268" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J268" s="5" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="269" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="269" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J269" s="5" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="270" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="270" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J270" s="5" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="271" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="271" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J271" s="5" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="272" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="272" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J272" s="5" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="273" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="273" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J273" s="5" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="274" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="274" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J274" s="5" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="275" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="275" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J275" s="5" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="276" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="276" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J276" s="5" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="277" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="277" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J277" s="5" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="278" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="278" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J278" s="5" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="279" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="279" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J279" s="5" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="280" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="280" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J280" s="5" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="281" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="281" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J281" s="5" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="282" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="282" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J282" s="5" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="283" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="283" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J283" s="5" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="284" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="284" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J284" s="5" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="285" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="285" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J285" s="5" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="286" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="286" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J286" s="5" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="287" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="287" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J287" s="5" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="288" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="288" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J288" s="5" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="289" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="289" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J289" s="5" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="290" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="290" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J290" s="5" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="291" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="291" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J291" s="5" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="292" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="292" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J292" s="5" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="293" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="293" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J293" s="5" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="294" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="294" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J294" s="5" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="295" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="295" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J295" s="5" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="296" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="296" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J296" s="5" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="297" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="297" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J297" s="5" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="298" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="298" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J298" s="5" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="299" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="299" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J299" s="5" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="300" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="300" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J300" s="5" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="301" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="301" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J301" s="5" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="302" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="302" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J302" s="5" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="303" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="303" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J303" s="5" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="304" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="304" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J304" s="5" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="305" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="305" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J305" s="5" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="306" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="306" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J306" s="5" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="307" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="307" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J307" s="5" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="308" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="308" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J308" s="5" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="309" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="309" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J309" s="5" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="310" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="310" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J310" s="5" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="311" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="311" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J311" s="5" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="312" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="312" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J312" s="5" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="313" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="313" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J313" s="5" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="314" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="314" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J314" s="5" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="315" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="315" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J315" s="5" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="316" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="316" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J316" s="5" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="317" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="317" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J317" s="5" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="318" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J318" s="5" t="str">
-        <f t="shared" si="6"/>
-        <v>00</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A4:L4" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A4:L4"/>
   <mergeCells count="1">
     <mergeCell ref="A2:L2"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="J1:L1048576">
+  <conditionalFormatting sqref="J220:L1048576 J1:L218">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J219:L219">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1:E1 D3:E3 D6:E1048576" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1:E1 D3:E3 D6:E1048576">
       <formula1>"是,否"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H1 H3:H1048576" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H1 H3:H1048576">
       <formula1>"VB编程,系统运维,WEB学习,游戏碎片,日常随笔,浥尘伙伴社团"</formula1>
     </dataValidation>
   </dataValidations>
@@ -11595,20 +11605,20 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A2:L34"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="6.375" customWidth="1"/>
+    <col min="2" max="2" width="6.33203125" customWidth="1"/>
     <col min="3" max="3" width="34" style="4" customWidth="1"/>
     <col min="4" max="4" width="4.75" customWidth="1"/>
-    <col min="8" max="8" width="6.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.83203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="19" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="7.125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="7.08203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.08203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:12" ht="23.25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
         <v>549</v>
       </c>
@@ -11624,7 +11634,7 @@
       <c r="K2" s="21"/>
       <c r="L2" s="21"/>
     </row>
-    <row r="4" spans="1:12" ht="57" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12" ht="56" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>0</v>
       </c>
@@ -11662,7 +11672,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>533</v>
       </c>
@@ -11685,7 +11695,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C8" s="15" t="s">
         <v>545</v>
       </c>
@@ -11694,7 +11704,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C9" s="4" t="s">
         <v>539</v>
       </c>
@@ -11702,7 +11712,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C10" t="s">
         <v>537</v>
       </c>
@@ -11710,7 +11720,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C11" t="s">
         <v>538</v>
       </c>
@@ -11718,7 +11728,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="23.25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A13" s="21" t="s">
         <v>543</v>
       </c>
@@ -11734,7 +11744,7 @@
       <c r="K13" s="21"/>
       <c r="L13" s="21"/>
     </row>
-    <row r="15" spans="1:12" ht="57" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:12" ht="56" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
         <v>0</v>
       </c>
@@ -11772,7 +11782,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>533</v>
       </c>
@@ -11798,7 +11808,7 @@
         <v>54837657</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C19" s="15" t="s">
         <v>545</v>
       </c>
@@ -11807,7 +11817,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C20" s="4" t="s">
         <v>539</v>
       </c>
@@ -11815,7 +11825,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C21" t="s">
         <v>537</v>
       </c>
@@ -11823,7 +11833,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C22" t="s">
         <v>538</v>
       </c>
@@ -11831,10 +11841,10 @@
         <v>541</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C23"/>
     </row>
-    <row r="25" spans="1:12" ht="23.25" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:12" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A25" s="21" t="s">
         <v>550</v>
       </c>
@@ -11850,7 +11860,7 @@
       <c r="K25" s="21"/>
       <c r="L25" s="21"/>
     </row>
-    <row r="27" spans="1:12" ht="57" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:12" ht="56" x14ac:dyDescent="0.3">
       <c r="A27" s="7" t="s">
         <v>0</v>
       </c>
@@ -11888,7 +11898,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
         <v>533</v>
       </c>
@@ -11914,7 +11924,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C31" s="15" t="s">
         <v>545</v>
       </c>
@@ -11923,7 +11933,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C32" s="4" t="s">
         <v>539</v>
       </c>
@@ -11931,7 +11941,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="33" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="33" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C33" t="s">
         <v>537</v>
       </c>
@@ -11939,7 +11949,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="34" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="34" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C34" t="s">
         <v>538</v>
       </c>
@@ -11955,7 +11965,7 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H15 H27 H4" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H15 H27 H4">
       <formula1>"VB编程,系统运维,WEB学习,游戏碎片,日常随笔"</formula1>
     </dataValidation>
   </dataValidations>

--- a/11_付费课程/99.资料/文章信息备忘表.xlsx
+++ b/11_付费课程/99.资料/文章信息备忘表.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\writing\11_付费课程\99.资料\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Writing\11_付费课程\99.资料\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28CDD98F-2773-4E3C-8726-E9F5F374447A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1910" yWindow="-120" windowWidth="19740" windowHeight="11760"/>
+    <workbookView xWindow="870" yWindow="-120" windowWidth="19740" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,7 +19,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$L$4</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1563" uniqueCount="1140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1568" uniqueCount="1142">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -4524,10 +4525,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>阴阳历转换</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>奇哉怪也，Windows11不支持WMIC？（附离线安装方法及安装包）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -4545,13 +4542,25 @@
   </si>
   <si>
     <t>1123</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-12-09 08:09:47</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>749080</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>另辟蹊径的阴阳历转换方法（含程序下载）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -5043,25 +5052,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:M317"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.25" style="8" customWidth="1"/>
-    <col min="2" max="2" width="5.58203125" style="4" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="5.33203125" style="6" customWidth="1"/>
-    <col min="5" max="6" width="5.08203125" style="6" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="30.875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="5.375" style="6" customWidth="1"/>
+    <col min="5" max="6" width="5.125" style="6" customWidth="1"/>
     <col min="7" max="7" width="5.25" style="6" customWidth="1"/>
     <col min="8" max="8" width="13.5" style="1" customWidth="1"/>
     <col min="9" max="9" width="19" style="4" customWidth="1"/>
-    <col min="10" max="10" width="8.58203125" style="5" customWidth="1"/>
+    <col min="10" max="10" width="8.625" style="5" customWidth="1"/>
     <col min="11" max="11" width="7.5" style="3" customWidth="1"/>
     <col min="12" max="12" width="9.25" style="2" customWidth="1"/>
     <col min="13" max="13" width="16.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:12" ht="25" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
@@ -5077,8 +5086,8 @@
       <c r="K2" s="20"/>
       <c r="L2" s="20"/>
     </row>
-    <row r="3" spans="1:12" ht="6.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="4" spans="1:12" s="7" customFormat="1" ht="56" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" ht="6.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="4" spans="1:12" s="7" customFormat="1" ht="57" x14ac:dyDescent="0.2">
       <c r="A4" s="7" t="s">
         <v>0</v>
       </c>
@@ -5116,7 +5125,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
         <v>557</v>
       </c>
@@ -5143,7 +5152,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
         <v>559</v>
       </c>
@@ -5179,7 +5188,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="8" t="s">
         <v>559</v>
       </c>
@@ -5215,25 +5224,25 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="J8" s="5" t="str">
         <f t="shared" si="0"/>
         <v>000</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="J9" s="5" t="str">
         <f t="shared" si="0"/>
         <v>000</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="J10" s="5" t="str">
         <f t="shared" si="0"/>
         <v>000</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B11" s="4" t="s">
         <v>522</v>
       </c>
@@ -5266,7 +5275,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A12" s="8" t="s">
         <v>558</v>
       </c>
@@ -5296,7 +5305,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A13" s="8" t="s">
         <v>558</v>
       </c>
@@ -5326,7 +5335,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A14" s="8" t="s">
         <v>640</v>
       </c>
@@ -5353,7 +5362,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" s="8" t="s">
         <v>557</v>
       </c>
@@ -5380,7 +5389,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" s="8" t="s">
         <v>557</v>
       </c>
@@ -5407,7 +5416,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" s="8" t="s">
         <v>557</v>
       </c>
@@ -5434,7 +5443,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" s="8" t="s">
         <v>767</v>
       </c>
@@ -5461,7 +5470,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A19" s="8" t="s">
         <v>557</v>
       </c>
@@ -5488,7 +5497,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A20" s="8" t="s">
         <v>557</v>
       </c>
@@ -5515,7 +5524,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A21" s="8" t="s">
         <v>557</v>
       </c>
@@ -5542,7 +5551,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A22" s="8" t="s">
         <v>559</v>
       </c>
@@ -5578,7 +5587,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23" s="8" t="s">
         <v>557</v>
       </c>
@@ -5605,7 +5614,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A24" s="8" t="s">
         <v>558</v>
       </c>
@@ -5635,7 +5644,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A25" s="8" t="s">
         <v>557</v>
       </c>
@@ -5662,7 +5671,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A26" s="8" t="s">
         <v>557</v>
       </c>
@@ -5689,7 +5698,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="27" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A27" s="8" t="s">
         <v>633</v>
       </c>
@@ -5716,7 +5725,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A28" s="8" t="s">
         <v>557</v>
       </c>
@@ -5743,7 +5752,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A29" s="8" t="s">
         <v>559</v>
       </c>
@@ -5779,7 +5788,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A30" s="8" t="s">
         <v>559</v>
       </c>
@@ -5815,7 +5824,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A31" s="8" t="s">
         <v>557</v>
       </c>
@@ -5842,7 +5851,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A32" s="8" t="s">
         <v>557</v>
       </c>
@@ -5869,7 +5878,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A33" s="8" t="s">
         <v>557</v>
       </c>
@@ -5896,7 +5905,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="34" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A34" s="8" t="s">
         <v>557</v>
       </c>
@@ -5923,7 +5932,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="35" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A35" s="8" t="s">
         <v>557</v>
       </c>
@@ -5950,7 +5959,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="36" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A36" s="8" t="s">
         <v>557</v>
       </c>
@@ -5977,7 +5986,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="37" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A37" s="8" t="s">
         <v>559</v>
       </c>
@@ -6013,7 +6022,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="38" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A38" s="8" t="s">
         <v>557</v>
       </c>
@@ -6040,7 +6049,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A39" s="8" t="s">
         <v>557</v>
       </c>
@@ -6067,7 +6076,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="40" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A40" s="8" t="s">
         <v>557</v>
       </c>
@@ -6094,7 +6103,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="41" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A41" s="8" t="s">
         <v>557</v>
       </c>
@@ -6121,7 +6130,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="42" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A42" s="8" t="s">
         <v>557</v>
       </c>
@@ -6148,7 +6157,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="43" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A43" s="8" t="s">
         <v>559</v>
       </c>
@@ -6181,7 +6190,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="44" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A44" s="8" t="s">
         <v>557</v>
       </c>
@@ -6208,7 +6217,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="45" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A45" s="8" t="s">
         <v>557</v>
       </c>
@@ -6235,7 +6244,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="46" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A46" s="8" t="s">
         <v>557</v>
       </c>
@@ -6262,7 +6271,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A47" s="8" t="s">
         <v>557</v>
       </c>
@@ -6289,7 +6298,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="48" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A48" s="8" t="s">
         <v>557</v>
       </c>
@@ -6316,7 +6325,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="49" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A49" s="8" t="s">
         <v>557</v>
       </c>
@@ -6343,7 +6352,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="50" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A50" s="8" t="s">
         <v>557</v>
       </c>
@@ -6370,7 +6379,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A51" s="8" t="s">
         <v>557</v>
       </c>
@@ -6397,7 +6406,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="52" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A52" s="8" t="s">
         <v>557</v>
       </c>
@@ -6424,7 +6433,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A53" s="8" t="s">
         <v>557</v>
       </c>
@@ -6451,7 +6460,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="54" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A54" s="8" t="s">
         <v>557</v>
       </c>
@@ -6478,7 +6487,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A55" s="8" t="s">
         <v>557</v>
       </c>
@@ -6505,7 +6514,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="56" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A56" s="8" t="s">
         <v>559</v>
       </c>
@@ -6541,7 +6550,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="57" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A57" s="8" t="s">
         <v>559</v>
       </c>
@@ -6577,7 +6586,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="58" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A58" s="8" t="s">
         <v>557</v>
       </c>
@@ -6604,7 +6613,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="59" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A59" s="8" t="s">
         <v>558</v>
       </c>
@@ -6634,7 +6643,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="60" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A60" s="8" t="s">
         <v>557</v>
       </c>
@@ -6661,7 +6670,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="61" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B61" s="4" t="s">
         <v>298</v>
       </c>
@@ -6694,7 +6703,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="62" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B62" s="4" t="s">
         <v>294</v>
       </c>
@@ -6727,7 +6736,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="63" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B63" s="4" t="s">
         <v>289</v>
       </c>
@@ -6760,7 +6769,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="64" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A64" s="8" t="s">
         <v>557</v>
       </c>
@@ -6787,7 +6796,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="65" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A65" s="8" t="s">
         <v>557</v>
       </c>
@@ -6814,7 +6823,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="66" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A66" s="8" t="s">
         <v>559</v>
       </c>
@@ -6850,7 +6859,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="67" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A67" s="8" t="s">
         <v>557</v>
       </c>
@@ -6877,7 +6886,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="68" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A68" s="8" t="s">
         <v>558</v>
       </c>
@@ -6907,7 +6916,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="69" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A69" s="8" t="s">
         <v>559</v>
       </c>
@@ -6934,7 +6943,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="70" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A70" s="8" t="s">
         <v>559</v>
       </c>
@@ -6961,7 +6970,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="71" spans="1:12" ht="56" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:12" ht="57" x14ac:dyDescent="0.2">
       <c r="A71" s="8" t="s">
         <v>558</v>
       </c>
@@ -6991,7 +7000,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="72" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A72" s="8" t="s">
         <v>558</v>
       </c>
@@ -7021,7 +7030,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="73" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A73" s="8" t="s">
         <v>558</v>
       </c>
@@ -7051,7 +7060,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="74" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A74" s="8" t="s">
         <v>557</v>
       </c>
@@ -7078,7 +7087,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="75" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A75" s="8" t="s">
         <v>557</v>
       </c>
@@ -7105,7 +7114,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="76" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A76" s="8" t="s">
         <v>558</v>
       </c>
@@ -7138,7 +7147,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="77" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A77" s="8" t="s">
         <v>557</v>
       </c>
@@ -7165,7 +7174,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="78" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A78" s="8" t="s">
         <v>558</v>
       </c>
@@ -7192,7 +7201,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="79" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A79" s="8" t="s">
         <v>557</v>
       </c>
@@ -7219,7 +7228,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="80" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A80" s="8" t="s">
         <v>558</v>
       </c>
@@ -7246,7 +7255,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="81" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A81" s="8" t="s">
         <v>557</v>
       </c>
@@ -7273,7 +7282,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="82" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A82" s="8" t="s">
         <v>557</v>
       </c>
@@ -7300,7 +7309,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="83" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A83" s="8" t="s">
         <v>557</v>
       </c>
@@ -7327,7 +7336,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="84" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A84" s="8" t="s">
         <v>557</v>
       </c>
@@ -7354,7 +7363,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="85" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A85" s="8" t="s">
         <v>558</v>
       </c>
@@ -7381,7 +7390,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="86" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A86" s="8" t="s">
         <v>557</v>
       </c>
@@ -7408,7 +7417,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="87" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A87" s="8" t="s">
         <v>559</v>
       </c>
@@ -7444,7 +7453,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="88" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A88" s="8" t="s">
         <v>559</v>
       </c>
@@ -7480,7 +7489,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="89" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A89" s="8" t="s">
         <v>559</v>
       </c>
@@ -7516,7 +7525,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="90" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A90" s="8" t="s">
         <v>557</v>
       </c>
@@ -7543,7 +7552,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="91" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B91" s="4" t="s">
         <v>151</v>
       </c>
@@ -7576,7 +7585,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="92" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B92" s="4" t="s">
         <v>146</v>
       </c>
@@ -7609,7 +7618,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="93" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B93" s="4" t="s">
         <v>140</v>
       </c>
@@ -7642,7 +7651,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="94" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B94" s="4" t="s">
         <v>135</v>
       </c>
@@ -7675,7 +7684,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="95" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A95" s="8" t="s">
         <v>558</v>
       </c>
@@ -7702,7 +7711,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="96" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B96" s="4" t="s">
         <v>123</v>
       </c>
@@ -7735,7 +7744,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="97" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B97" s="4" t="s">
         <v>118</v>
       </c>
@@ -7768,7 +7777,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="98" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B98" s="4" t="s">
         <v>112</v>
       </c>
@@ -7801,7 +7810,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="99" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B99" s="4" t="s">
         <v>109</v>
       </c>
@@ -7834,7 +7843,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="100" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B100" s="4" t="s">
         <v>104</v>
       </c>
@@ -7867,7 +7876,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="101" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B101" s="4" t="s">
         <v>98</v>
       </c>
@@ -7900,7 +7909,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="102" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B102" s="4" t="s">
         <v>92</v>
       </c>
@@ -7933,7 +7942,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="103" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A103" s="8" t="s">
         <v>559</v>
       </c>
@@ -7969,7 +7978,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="104" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A104" s="8" t="s">
         <v>557</v>
       </c>
@@ -7996,7 +8005,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="105" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A105" s="8" t="s">
         <v>557</v>
       </c>
@@ -8023,7 +8032,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="106" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A106" s="8" t="s">
         <v>557</v>
       </c>
@@ -8050,7 +8059,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="107" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A107" s="8" t="s">
         <v>557</v>
       </c>
@@ -8077,7 +8086,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="108" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A108" s="8" t="s">
         <v>557</v>
       </c>
@@ -8104,7 +8113,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="109" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A109" s="8" t="s">
         <v>559</v>
       </c>
@@ -8140,7 +8149,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A110" s="8" t="s">
         <v>558</v>
       </c>
@@ -8167,7 +8176,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="111" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A111" s="8" t="s">
         <v>557</v>
       </c>
@@ -8194,7 +8203,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A112" s="8" t="s">
         <v>557</v>
       </c>
@@ -8221,7 +8230,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="113" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A113" s="8" t="s">
         <v>557</v>
       </c>
@@ -8248,7 +8257,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A114" s="8" t="s">
         <v>557</v>
       </c>
@@ -8275,7 +8284,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="115" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A115" s="8" t="s">
         <v>557</v>
       </c>
@@ -8302,7 +8311,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="116" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A116" s="8" t="s">
         <v>559</v>
       </c>
@@ -8338,7 +8347,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="117" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A117" s="8" t="s">
         <v>557</v>
       </c>
@@ -8365,7 +8374,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="118" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A118" s="8" t="s">
         <v>558</v>
       </c>
@@ -8395,7 +8404,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="119" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A119" s="8" t="s">
         <v>557</v>
       </c>
@@ -8422,7 +8431,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="120" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A120" s="8" t="s">
         <v>557</v>
       </c>
@@ -8449,7 +8458,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="121" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A121" s="8" t="s">
         <v>597</v>
       </c>
@@ -8476,7 +8485,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="122" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A122" s="8" t="s">
         <v>602</v>
       </c>
@@ -8503,7 +8512,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="123" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A123" s="8" t="s">
         <v>608</v>
       </c>
@@ -8530,7 +8539,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="124" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A124" s="8" t="s">
         <v>611</v>
       </c>
@@ -8557,7 +8566,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="125" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A125" s="8" t="s">
         <v>617</v>
       </c>
@@ -8584,7 +8593,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="126" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A126" s="8" t="s">
         <v>624</v>
       </c>
@@ -8611,7 +8620,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="127" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A127" s="8" t="s">
         <v>557</v>
       </c>
@@ -8638,7 +8647,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="128" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A128" s="8" t="s">
         <v>649</v>
       </c>
@@ -8665,7 +8674,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="129" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A129" s="8" t="s">
         <v>653</v>
       </c>
@@ -8692,7 +8701,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="130" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A130" s="8" t="s">
         <v>659</v>
       </c>
@@ -8719,7 +8728,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="131" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A131" s="8" t="s">
         <v>664</v>
       </c>
@@ -8746,7 +8755,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A132" s="8" t="s">
         <v>557</v>
       </c>
@@ -8773,7 +8782,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="133" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A133" s="8" t="s">
         <v>557</v>
       </c>
@@ -8800,7 +8809,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="134" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A134" s="8" t="s">
         <v>681</v>
       </c>
@@ -8827,7 +8836,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="135" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A135" s="8" t="s">
         <v>687</v>
       </c>
@@ -8854,7 +8863,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="136" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A136" s="8" t="s">
         <v>691</v>
       </c>
@@ -8881,7 +8890,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="137" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A137" s="8" t="s">
         <v>699</v>
       </c>
@@ -8908,7 +8917,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="138" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A138" s="8" t="s">
         <v>704</v>
       </c>
@@ -8935,7 +8944,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="139" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A139" s="8" t="s">
         <v>711</v>
       </c>
@@ -8962,7 +8971,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="140" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A140" s="8" t="s">
         <v>716</v>
       </c>
@@ -8989,7 +8998,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="141" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A141" s="8" t="s">
         <v>724</v>
       </c>
@@ -9016,7 +9025,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="142" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A142" s="8" t="s">
         <v>727</v>
       </c>
@@ -9043,7 +9052,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="143" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A143" s="8" t="s">
         <v>736</v>
       </c>
@@ -9070,7 +9079,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="144" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A144" s="8" t="s">
         <v>740</v>
       </c>
@@ -9097,7 +9106,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="145" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A145" s="8" t="s">
         <v>746</v>
       </c>
@@ -9124,7 +9133,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="146" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A146" s="8" t="s">
         <v>754</v>
       </c>
@@ -9151,7 +9160,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="147" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A147" s="8" t="s">
         <v>759</v>
       </c>
@@ -9178,7 +9187,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="148" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A148" s="8" t="s">
         <v>770</v>
       </c>
@@ -9205,7 +9214,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="149" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A149" s="8" t="s">
         <v>777</v>
       </c>
@@ -9232,7 +9241,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="150" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A150" s="8" t="s">
         <v>782</v>
       </c>
@@ -9259,7 +9268,7 @@
         <v>786</v>
       </c>
     </row>
-    <row r="151" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A151" s="8" t="s">
         <v>557</v>
       </c>
@@ -9286,7 +9295,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="152" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A152" s="8" t="s">
         <v>795</v>
       </c>
@@ -9313,7 +9322,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A153" s="8" t="s">
         <v>800</v>
       </c>
@@ -9340,7 +9349,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A154" s="8" t="s">
         <v>804</v>
       </c>
@@ -9367,7 +9376,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A155" s="8" t="s">
         <v>811</v>
       </c>
@@ -9394,7 +9403,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="156" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A156" s="8" t="s">
         <v>557</v>
       </c>
@@ -9421,7 +9430,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A157" s="8" t="s">
         <v>557</v>
       </c>
@@ -9448,7 +9457,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A158" s="8" t="s">
         <v>827</v>
       </c>
@@ -9475,7 +9484,7 @@
         <v>831</v>
       </c>
     </row>
-    <row r="159" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A159" s="8" t="s">
         <v>557</v>
       </c>
@@ -9502,7 +9511,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A160" s="8" t="s">
         <v>838</v>
       </c>
@@ -9529,7 +9538,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="161" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A161" s="8" t="s">
         <v>557</v>
       </c>
@@ -9556,7 +9565,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A162" s="8" t="s">
         <v>850</v>
       </c>
@@ -9583,7 +9592,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A163" s="8" t="s">
         <v>857</v>
       </c>
@@ -9610,7 +9619,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A164" s="8" t="s">
         <v>557</v>
       </c>
@@ -9637,7 +9646,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="165" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A165" s="8" t="s">
         <v>557</v>
       </c>
@@ -9664,7 +9673,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A166" s="8" t="s">
         <v>557</v>
       </c>
@@ -9691,7 +9700,7 @@
         <v>871</v>
       </c>
     </row>
-    <row r="167" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A167" s="8" t="s">
         <v>557</v>
       </c>
@@ -9718,7 +9727,7 @@
         <v>879</v>
       </c>
     </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A168" s="8" t="s">
         <v>557</v>
       </c>
@@ -9745,7 +9754,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A169" s="8" t="s">
         <v>557</v>
       </c>
@@ -9772,7 +9781,7 @@
         <v>889</v>
       </c>
     </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A170" s="8" t="s">
         <v>557</v>
       </c>
@@ -9799,7 +9808,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A171" s="8" t="s">
         <v>557</v>
       </c>
@@ -9826,7 +9835,7 @@
         <v>897</v>
       </c>
     </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A172" s="8" t="s">
         <v>902</v>
       </c>
@@ -9853,7 +9862,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A173" s="8" t="s">
         <v>902</v>
       </c>
@@ -9880,7 +9889,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A174" s="8" t="s">
         <v>557</v>
       </c>
@@ -9907,7 +9916,7 @@
         <v>915</v>
       </c>
     </row>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A175" s="8" t="s">
         <v>557</v>
       </c>
@@ -9934,7 +9943,7 @@
         <v>919</v>
       </c>
     </row>
-    <row r="176" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A176" s="8" t="s">
         <v>557</v>
       </c>
@@ -9961,7 +9970,7 @@
         <v>925</v>
       </c>
     </row>
-    <row r="177" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A177" s="8" t="s">
         <v>557</v>
       </c>
@@ -9988,7 +9997,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="178" spans="1:13" ht="28" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A178" s="8" t="s">
         <v>557</v>
       </c>
@@ -10015,7 +10024,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="179" spans="1:13" ht="42" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:13" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A179" s="8" t="s">
         <v>938</v>
       </c>
@@ -10042,7 +10051,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="180" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B180" s="4" t="s">
         <v>942</v>
       </c>
@@ -10066,7 +10075,7 @@
         <v>946</v>
       </c>
     </row>
-    <row r="181" spans="1:13" ht="28" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B181" s="4" t="s">
         <v>948</v>
       </c>
@@ -10090,7 +10099,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="182" spans="1:13" ht="28" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B182" s="4" t="s">
         <v>954</v>
       </c>
@@ -10114,7 +10123,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="183" spans="1:13" ht="42" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:13" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B183" s="4" t="s">
         <v>959</v>
       </c>
@@ -10138,7 +10147,7 @@
         <v>960</v>
       </c>
     </row>
-    <row r="184" spans="1:13" ht="28" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B184" s="4" t="s">
         <v>966</v>
       </c>
@@ -10162,7 +10171,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="185" spans="1:13" ht="28" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B185" s="4" t="s">
         <v>971</v>
       </c>
@@ -10186,7 +10195,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="186" spans="1:13" ht="42" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:13" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B186" s="4" t="s">
         <v>976</v>
       </c>
@@ -10210,7 +10219,7 @@
         <v>963</v>
       </c>
     </row>
-    <row r="187" spans="1:13" ht="42" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:13" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B187" s="4" t="s">
         <v>979</v>
       </c>
@@ -10234,7 +10243,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="188" spans="1:13" ht="28" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B188" s="4" t="s">
         <v>985</v>
       </c>
@@ -10261,7 +10270,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="189" spans="1:13" ht="15.5" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:13" ht="15" x14ac:dyDescent="0.2">
       <c r="B189" s="4" t="s">
         <v>988</v>
       </c>
@@ -10286,7 +10295,7 @@
       </c>
       <c r="M189" s="6"/>
     </row>
-    <row r="190" spans="1:13" ht="28" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B190" s="4" t="s">
         <v>992</v>
       </c>
@@ -10310,7 +10319,7 @@
         <v>982</v>
       </c>
     </row>
-    <row r="191" spans="1:13" ht="46.5" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:13" ht="45" x14ac:dyDescent="0.2">
       <c r="B191" s="4" t="s">
         <v>1002</v>
       </c>
@@ -10334,7 +10343,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="192" spans="1:13" ht="28" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B192" s="4" t="s">
         <v>1006</v>
       </c>
@@ -10358,7 +10367,7 @@
         <v>998</v>
       </c>
     </row>
-    <row r="193" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="193" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B193" s="4" t="s">
         <v>1010</v>
       </c>
@@ -10382,7 +10391,7 @@
         <v>1011</v>
       </c>
     </row>
-    <row r="194" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="194" spans="2:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B194" s="4" t="s">
         <v>1015</v>
       </c>
@@ -10409,7 +10418,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="195" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="195" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B195" s="4" t="s">
         <v>1021</v>
       </c>
@@ -10433,7 +10442,7 @@
         <v>1019</v>
       </c>
     </row>
-    <row r="196" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="196" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B196" s="4" t="s">
         <v>1025</v>
       </c>
@@ -10457,7 +10466,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="197" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="197" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B197" s="4" t="s">
         <v>1031</v>
       </c>
@@ -10481,7 +10490,7 @@
         <v>1033</v>
       </c>
     </row>
-    <row r="198" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="198" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B198" s="4" t="s">
         <v>1034</v>
       </c>
@@ -10505,7 +10514,7 @@
         <v>1035</v>
       </c>
     </row>
-    <row r="199" spans="2:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="199" spans="2:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B199" s="4" t="s">
         <v>1040</v>
       </c>
@@ -10529,7 +10538,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="200" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="200" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B200" s="4" t="s">
         <v>1045</v>
       </c>
@@ -10553,7 +10562,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="201" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="201" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B201" s="4" t="s">
         <v>1051</v>
       </c>
@@ -10577,7 +10586,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="202" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="202" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B202" s="4" t="s">
         <v>1058</v>
       </c>
@@ -10601,7 +10610,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="203" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="203" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B203" s="4" t="s">
         <v>1062</v>
       </c>
@@ -10625,7 +10634,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="204" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="204" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B204" s="4" t="s">
         <v>1065</v>
       </c>
@@ -10649,7 +10658,7 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="205" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="205" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B205" s="4" t="s">
         <v>1071</v>
       </c>
@@ -10673,7 +10682,7 @@
         <v>1069</v>
       </c>
     </row>
-    <row r="206" spans="2:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="206" spans="2:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B206" s="4" t="s">
         <v>1074</v>
       </c>
@@ -10697,7 +10706,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="207" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="207" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B207" s="4" t="s">
         <v>1080</v>
       </c>
@@ -10721,7 +10730,7 @@
         <v>1079</v>
       </c>
     </row>
-    <row r="208" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="208" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B208" s="4" t="s">
         <v>1082</v>
       </c>
@@ -10745,7 +10754,7 @@
         <v>1081</v>
       </c>
     </row>
-    <row r="209" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="209" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B209" s="4" t="s">
         <v>1091</v>
       </c>
@@ -10769,7 +10778,7 @@
         <v>1089</v>
       </c>
     </row>
-    <row r="210" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="210" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B210" s="4" t="s">
         <v>1093</v>
       </c>
@@ -10793,7 +10802,7 @@
         <v>1092</v>
       </c>
     </row>
-    <row r="211" spans="2:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="211" spans="2:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B211" s="4" t="s">
         <v>1102</v>
       </c>
@@ -10817,7 +10826,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="212" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="212" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B212" s="4" t="s">
         <v>1105</v>
       </c>
@@ -10841,7 +10850,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="213" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="213" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B213" s="4" t="s">
         <v>1110</v>
       </c>
@@ -10865,12 +10874,15 @@
         <v>1109</v>
       </c>
     </row>
-    <row r="214" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="214" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B214" s="4" t="s">
         <v>1118</v>
       </c>
       <c r="C214" s="1" t="s">
         <v>1115</v>
+      </c>
+      <c r="E214" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="H214" s="1" t="s">
         <v>654</v>
@@ -10889,7 +10901,7 @@
         <v>1114</v>
       </c>
     </row>
-    <row r="215" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="215" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B215" s="4" t="s">
         <v>1122</v>
       </c>
@@ -10913,12 +10925,15 @@
         <v>1116</v>
       </c>
     </row>
-    <row r="216" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="216" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B216" s="4" t="s">
         <v>1127</v>
       </c>
       <c r="C216" s="1" t="s">
         <v>1128</v>
+      </c>
+      <c r="E216" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="H216" s="1" t="s">
         <v>1129</v>
@@ -10937,49 +10952,58 @@
         <v>1132</v>
       </c>
     </row>
-    <row r="217" spans="2:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="217" spans="2:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B217" s="4" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="C217" s="1" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="H217" s="1" t="s">
         <v>654</v>
       </c>
       <c r="I217" s="4" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="J217" s="5" t="str">
         <f t="shared" si="5"/>
         <v>001122</v>
       </c>
       <c r="K217" s="3" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="L217" s="2" t="s">
         <v>1113</v>
       </c>
     </row>
-    <row r="218" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="218" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B218" s="4" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="C218" s="1" t="s">
-        <v>1134</v>
+        <v>1141</v>
+      </c>
+      <c r="E218" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="H218" s="1" t="s">
         <v>11</v>
+      </c>
+      <c r="I218" s="4" t="s">
+        <v>1139</v>
       </c>
       <c r="J218" s="5" t="str">
         <f t="shared" si="5"/>
         <v>001123</v>
       </c>
+      <c r="K218" s="3" t="s">
+        <v>1140</v>
+      </c>
       <c r="L218" s="2" t="s">
         <v>1133</v>
       </c>
     </row>
-    <row r="219" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="219" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C219" s="1" t="s">
         <v>1120</v>
       </c>
@@ -10991,611 +11015,611 @@
         <v>1121</v>
       </c>
     </row>
-    <row r="220" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="220" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J220" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="221" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="221" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J221" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="222" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="222" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J222" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="223" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="223" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J223" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="224" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="224" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J224" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="225" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="225" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J225" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="226" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="226" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J226" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="227" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="227" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J227" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="228" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="228" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J228" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="229" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="229" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J229" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="230" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="230" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J230" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="231" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="231" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J231" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="232" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="232" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J232" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="233" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="233" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J233" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="234" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="234" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J234" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="235" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="235" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J235" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="236" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="236" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J236" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="237" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="237" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J237" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="238" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="238" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J238" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="239" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="239" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J239" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="240" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="240" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J240" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="241" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="241" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J241" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="242" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="242" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J242" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="243" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="243" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J243" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="244" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="244" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J244" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="245" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="245" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J245" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="246" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="246" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J246" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="247" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="247" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J247" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="248" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="248" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J248" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="249" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="249" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J249" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="250" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="250" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J250" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="251" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="251" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J251" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="252" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="252" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J252" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="253" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="253" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J253" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="254" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="254" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J254" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="255" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="255" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J255" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="256" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="256" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J256" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="257" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="257" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J257" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="258" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="258" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J258" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="259" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="259" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J259" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="260" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="260" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J260" s="5" t="str">
         <f t="shared" ref="J260:J317" si="7">"00"&amp;B260</f>
         <v>00</v>
       </c>
     </row>
-    <row r="261" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="261" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J261" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="262" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="262" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J262" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="263" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="263" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J263" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="264" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="264" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J264" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="265" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="265" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J265" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="266" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="266" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J266" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="267" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="267" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J267" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="268" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="268" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J268" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="269" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="269" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J269" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="270" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="270" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J270" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="271" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="271" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J271" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="272" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="272" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J272" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="273" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="273" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J273" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="274" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="274" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J274" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="275" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="275" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J275" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="276" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="276" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J276" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="277" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="277" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J277" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="278" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="278" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J278" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="279" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="279" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J279" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="280" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="280" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J280" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="281" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="281" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J281" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="282" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="282" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J282" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="283" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="283" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J283" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="284" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="284" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J284" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="285" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="285" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J285" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="286" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="286" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J286" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="287" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="287" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J287" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="288" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="288" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J288" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="289" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="289" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J289" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="290" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="290" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J290" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="291" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="291" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J291" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="292" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="292" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J292" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="293" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="293" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J293" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="294" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="294" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J294" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="295" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="295" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J295" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="296" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="296" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J296" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="297" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="297" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J297" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="298" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="298" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J298" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="299" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="299" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J299" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="300" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="300" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J300" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="301" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="301" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J301" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="302" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="302" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J302" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="303" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="303" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J303" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="304" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="304" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J304" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="305" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="305" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J305" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="306" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="306" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J306" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="307" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="307" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J307" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="308" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="308" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J308" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="309" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="309" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J309" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="310" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="310" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J310" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="311" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="311" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J311" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="312" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="312" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J312" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="313" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="313" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J313" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="314" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="314" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J314" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="315" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="315" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J315" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="316" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="316" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J316" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="317" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="317" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J317" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:L4"/>
+  <autoFilter ref="A4:L4" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="1">
     <mergeCell ref="A2:L2"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="J219:L219">
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="J220:L1048576 J1:L218">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J219:L219">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1:E1 D3:E3 D6:E1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1:E1 D3:E3 D6:E1048576" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"是,否"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H1 H3:H1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H1 H3:H1048576" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"VB编程,系统运维,WEB学习,游戏碎片,日常随笔,浥尘伙伴社团"</formula1>
     </dataValidation>
   </dataValidations>
@@ -11605,20 +11629,20 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A2:L34"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="6.33203125" customWidth="1"/>
+    <col min="2" max="2" width="6.375" customWidth="1"/>
     <col min="3" max="3" width="34" style="4" customWidth="1"/>
     <col min="4" max="4" width="4.75" customWidth="1"/>
-    <col min="8" max="8" width="6.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="19" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="7.08203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.08203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:12" ht="22.5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" ht="23.25" x14ac:dyDescent="0.2">
       <c r="A2" s="21" t="s">
         <v>549</v>
       </c>
@@ -11634,7 +11658,7 @@
       <c r="K2" s="21"/>
       <c r="L2" s="21"/>
     </row>
-    <row r="4" spans="1:12" ht="56" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" ht="57" x14ac:dyDescent="0.2">
       <c r="A4" s="7" t="s">
         <v>0</v>
       </c>
@@ -11672,7 +11696,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
         <v>533</v>
       </c>
@@ -11695,7 +11719,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C8" s="15" t="s">
         <v>545</v>
       </c>
@@ -11704,7 +11728,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C9" s="4" t="s">
         <v>539</v>
       </c>
@@ -11712,7 +11736,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C10" t="s">
         <v>537</v>
       </c>
@@ -11720,7 +11744,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C11" t="s">
         <v>538</v>
       </c>
@@ -11728,7 +11752,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="22.5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" ht="23.25" x14ac:dyDescent="0.2">
       <c r="A13" s="21" t="s">
         <v>543</v>
       </c>
@@ -11744,7 +11768,7 @@
       <c r="K13" s="21"/>
       <c r="L13" s="21"/>
     </row>
-    <row r="15" spans="1:12" ht="56" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" ht="57" x14ac:dyDescent="0.2">
       <c r="A15" s="7" t="s">
         <v>0</v>
       </c>
@@ -11782,7 +11806,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
         <v>533</v>
       </c>
@@ -11808,7 +11832,7 @@
         <v>54837657</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C19" s="15" t="s">
         <v>545</v>
       </c>
@@ -11817,7 +11841,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C20" s="4" t="s">
         <v>539</v>
       </c>
@@ -11825,7 +11849,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C21" t="s">
         <v>537</v>
       </c>
@@ -11833,7 +11857,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C22" t="s">
         <v>538</v>
       </c>
@@ -11841,10 +11865,10 @@
         <v>541</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C23"/>
     </row>
-    <row r="25" spans="1:12" ht="22.5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" ht="23.25" x14ac:dyDescent="0.2">
       <c r="A25" s="21" t="s">
         <v>550</v>
       </c>
@@ -11860,7 +11884,7 @@
       <c r="K25" s="21"/>
       <c r="L25" s="21"/>
     </row>
-    <row r="27" spans="1:12" ht="56" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" ht="57" x14ac:dyDescent="0.2">
       <c r="A27" s="7" t="s">
         <v>0</v>
       </c>
@@ -11898,7 +11922,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B28" t="s">
         <v>533</v>
       </c>
@@ -11924,7 +11948,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C31" s="15" t="s">
         <v>545</v>
       </c>
@@ -11933,7 +11957,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C32" s="4" t="s">
         <v>539</v>
       </c>
@@ -11941,7 +11965,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="33" spans="3:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="3:5" x14ac:dyDescent="0.2">
       <c r="C33" t="s">
         <v>537</v>
       </c>
@@ -11949,7 +11973,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="34" spans="3:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="3:5" x14ac:dyDescent="0.2">
       <c r="C34" t="s">
         <v>538</v>
       </c>
@@ -11965,7 +11989,7 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H15 H27 H4">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H15 H27 H4" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"VB编程,系统运维,WEB学习,游戏碎片,日常随笔"</formula1>
     </dataValidation>
   </dataValidations>

--- a/11_付费课程/99.资料/文章信息备忘表.xlsx
+++ b/11_付费课程/99.资料/文章信息备忘表.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Writing\11_付费课程\99.资料\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\writing\11_付费课程\99.资料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28CDD98F-2773-4E3C-8726-E9F5F374447A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="870" yWindow="-120" windowWidth="19740" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1910" yWindow="-120" windowWidth="19740" windowHeight="11760"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$L$4</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -40,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1568" uniqueCount="1142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1572" uniqueCount="1145">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -4470,10 +4469,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>WindowsTerminal</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>02474746</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -4554,13 +4549,29 @@
   </si>
   <si>
     <t>另辟蹊径的阴阳历转换方法（含程序下载）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-12-15 20:32:20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1124</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>022302</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>如何在 Windows 11 LTSC 上快速离线安装 Windows 终端</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -5052,25 +5063,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A2:M317"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.25" style="8" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="4" customWidth="1"/>
-    <col min="3" max="3" width="30.875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="5.375" style="6" customWidth="1"/>
-    <col min="5" max="6" width="5.125" style="6" customWidth="1"/>
+    <col min="2" max="2" width="5.58203125" style="4" customWidth="1"/>
+    <col min="3" max="3" width="30.83203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="5.33203125" style="6" customWidth="1"/>
+    <col min="5" max="6" width="5.08203125" style="6" customWidth="1"/>
     <col min="7" max="7" width="5.25" style="6" customWidth="1"/>
     <col min="8" max="8" width="13.5" style="1" customWidth="1"/>
     <col min="9" max="9" width="19" style="4" customWidth="1"/>
-    <col min="10" max="10" width="8.625" style="5" customWidth="1"/>
+    <col min="10" max="10" width="8.58203125" style="5" customWidth="1"/>
     <col min="11" max="11" width="7.5" style="3" customWidth="1"/>
     <col min="12" max="12" width="9.25" style="2" customWidth="1"/>
     <col min="13" max="13" width="16.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" ht="25" x14ac:dyDescent="0.3">
       <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
@@ -5086,8 +5097,8 @@
       <c r="K2" s="20"/>
       <c r="L2" s="20"/>
     </row>
-    <row r="3" spans="1:12" ht="6.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="4" spans="1:12" s="7" customFormat="1" ht="57" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12" ht="6.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:12" s="7" customFormat="1" ht="56" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>0</v>
       </c>
@@ -5125,7 +5136,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
         <v>557</v>
       </c>
@@ -5152,7 +5163,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
         <v>559</v>
       </c>
@@ -5188,7 +5199,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
         <v>559</v>
       </c>
@@ -5224,25 +5235,25 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="J8" s="5" t="str">
         <f t="shared" si="0"/>
         <v>000</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="J9" s="5" t="str">
         <f t="shared" si="0"/>
         <v>000</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="J10" s="5" t="str">
         <f t="shared" si="0"/>
         <v>000</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
         <v>522</v>
       </c>
@@ -5275,7 +5286,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
         <v>558</v>
       </c>
@@ -5305,7 +5316,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A13" s="8" t="s">
         <v>558</v>
       </c>
@@ -5335,7 +5346,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A14" s="8" t="s">
         <v>640</v>
       </c>
@@ -5362,7 +5373,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="8" t="s">
         <v>557</v>
       </c>
@@ -5389,7 +5400,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="8" t="s">
         <v>557</v>
       </c>
@@ -5416,7 +5427,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="8" t="s">
         <v>557</v>
       </c>
@@ -5443,7 +5454,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="8" t="s">
         <v>767</v>
       </c>
@@ -5470,7 +5481,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
         <v>557</v>
       </c>
@@ -5497,7 +5508,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A20" s="8" t="s">
         <v>557</v>
       </c>
@@ -5524,7 +5535,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A21" s="8" t="s">
         <v>557</v>
       </c>
@@ -5551,7 +5562,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A22" s="8" t="s">
         <v>559</v>
       </c>
@@ -5587,7 +5598,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" s="8" t="s">
         <v>557</v>
       </c>
@@ -5614,7 +5625,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A24" s="8" t="s">
         <v>558</v>
       </c>
@@ -5644,7 +5655,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A25" s="8" t="s">
         <v>557</v>
       </c>
@@ -5671,7 +5682,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A26" s="8" t="s">
         <v>557</v>
       </c>
@@ -5698,7 +5709,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="27" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A27" s="8" t="s">
         <v>633</v>
       </c>
@@ -5725,7 +5736,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A28" s="8" t="s">
         <v>557</v>
       </c>
@@ -5752,7 +5763,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A29" s="8" t="s">
         <v>559</v>
       </c>
@@ -5788,7 +5799,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A30" s="8" t="s">
         <v>559</v>
       </c>
@@ -5824,7 +5835,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A31" s="8" t="s">
         <v>557</v>
       </c>
@@ -5851,7 +5862,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A32" s="8" t="s">
         <v>557</v>
       </c>
@@ -5878,7 +5889,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A33" s="8" t="s">
         <v>557</v>
       </c>
@@ -5905,7 +5916,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="34" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A34" s="8" t="s">
         <v>557</v>
       </c>
@@ -5932,7 +5943,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="35" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A35" s="8" t="s">
         <v>557</v>
       </c>
@@ -5959,7 +5970,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="36" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A36" s="8" t="s">
         <v>557</v>
       </c>
@@ -5986,7 +5997,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="37" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A37" s="8" t="s">
         <v>559</v>
       </c>
@@ -6022,7 +6033,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="38" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A38" s="8" t="s">
         <v>557</v>
       </c>
@@ -6049,7 +6060,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" s="8" t="s">
         <v>557</v>
       </c>
@@ -6076,7 +6087,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="40" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A40" s="8" t="s">
         <v>557</v>
       </c>
@@ -6103,7 +6114,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="41" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A41" s="8" t="s">
         <v>557</v>
       </c>
@@ -6130,7 +6141,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="42" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A42" s="8" t="s">
         <v>557</v>
       </c>
@@ -6157,7 +6168,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="43" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A43" s="8" t="s">
         <v>559</v>
       </c>
@@ -6190,7 +6201,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="44" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A44" s="8" t="s">
         <v>557</v>
       </c>
@@ -6217,7 +6228,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="45" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A45" s="8" t="s">
         <v>557</v>
       </c>
@@ -6244,7 +6255,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="46" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A46" s="8" t="s">
         <v>557</v>
       </c>
@@ -6271,7 +6282,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" s="8" t="s">
         <v>557</v>
       </c>
@@ -6298,7 +6309,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="48" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A48" s="8" t="s">
         <v>557</v>
       </c>
@@ -6325,7 +6336,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="49" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A49" s="8" t="s">
         <v>557</v>
       </c>
@@ -6352,7 +6363,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="50" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A50" s="8" t="s">
         <v>557</v>
       </c>
@@ -6379,7 +6390,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" s="8" t="s">
         <v>557</v>
       </c>
@@ -6406,7 +6417,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="52" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A52" s="8" t="s">
         <v>557</v>
       </c>
@@ -6433,7 +6444,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" s="8" t="s">
         <v>557</v>
       </c>
@@ -6460,7 +6471,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="54" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A54" s="8" t="s">
         <v>557</v>
       </c>
@@ -6487,7 +6498,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" s="8" t="s">
         <v>557</v>
       </c>
@@ -6514,7 +6525,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="56" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A56" s="8" t="s">
         <v>559</v>
       </c>
@@ -6550,7 +6561,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="57" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A57" s="8" t="s">
         <v>559</v>
       </c>
@@ -6586,7 +6597,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="58" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A58" s="8" t="s">
         <v>557</v>
       </c>
@@ -6613,7 +6624,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="59" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A59" s="8" t="s">
         <v>558</v>
       </c>
@@ -6643,7 +6654,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="60" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A60" s="8" t="s">
         <v>557</v>
       </c>
@@ -6670,7 +6681,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="61" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B61" s="4" t="s">
         <v>298</v>
       </c>
@@ -6703,7 +6714,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="62" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B62" s="4" t="s">
         <v>294</v>
       </c>
@@ -6736,7 +6747,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="63" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B63" s="4" t="s">
         <v>289</v>
       </c>
@@ -6769,7 +6780,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="64" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A64" s="8" t="s">
         <v>557</v>
       </c>
@@ -6796,7 +6807,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="65" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A65" s="8" t="s">
         <v>557</v>
       </c>
@@ -6823,7 +6834,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="66" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A66" s="8" t="s">
         <v>559</v>
       </c>
@@ -6859,7 +6870,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="67" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A67" s="8" t="s">
         <v>557</v>
       </c>
@@ -6886,7 +6897,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="68" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A68" s="8" t="s">
         <v>558</v>
       </c>
@@ -6916,7 +6927,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="69" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A69" s="8" t="s">
         <v>559</v>
       </c>
@@ -6943,7 +6954,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="70" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A70" s="8" t="s">
         <v>559</v>
       </c>
@@ -6970,7 +6981,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="71" spans="1:12" ht="57" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:12" ht="56" x14ac:dyDescent="0.3">
       <c r="A71" s="8" t="s">
         <v>558</v>
       </c>
@@ -7000,7 +7011,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="72" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A72" s="8" t="s">
         <v>558</v>
       </c>
@@ -7030,7 +7041,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="73" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A73" s="8" t="s">
         <v>558</v>
       </c>
@@ -7060,7 +7071,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="74" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A74" s="8" t="s">
         <v>557</v>
       </c>
@@ -7087,7 +7098,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="75" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A75" s="8" t="s">
         <v>557</v>
       </c>
@@ -7114,7 +7125,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="76" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A76" s="8" t="s">
         <v>558</v>
       </c>
@@ -7147,7 +7158,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="77" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A77" s="8" t="s">
         <v>557</v>
       </c>
@@ -7174,7 +7185,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="78" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A78" s="8" t="s">
         <v>558</v>
       </c>
@@ -7201,7 +7212,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="79" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A79" s="8" t="s">
         <v>557</v>
       </c>
@@ -7228,7 +7239,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="80" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A80" s="8" t="s">
         <v>558</v>
       </c>
@@ -7255,7 +7266,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="81" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A81" s="8" t="s">
         <v>557</v>
       </c>
@@ -7282,7 +7293,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="82" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A82" s="8" t="s">
         <v>557</v>
       </c>
@@ -7309,7 +7320,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="83" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A83" s="8" t="s">
         <v>557</v>
       </c>
@@ -7336,7 +7347,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="84" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A84" s="8" t="s">
         <v>557</v>
       </c>
@@ -7363,7 +7374,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="85" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A85" s="8" t="s">
         <v>558</v>
       </c>
@@ -7390,7 +7401,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="86" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A86" s="8" t="s">
         <v>557</v>
       </c>
@@ -7417,7 +7428,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="87" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A87" s="8" t="s">
         <v>559</v>
       </c>
@@ -7453,7 +7464,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="88" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A88" s="8" t="s">
         <v>559</v>
       </c>
@@ -7489,7 +7500,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="89" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A89" s="8" t="s">
         <v>559</v>
       </c>
@@ -7525,7 +7536,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="90" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A90" s="8" t="s">
         <v>557</v>
       </c>
@@ -7552,7 +7563,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="91" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B91" s="4" t="s">
         <v>151</v>
       </c>
@@ -7585,7 +7596,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="92" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B92" s="4" t="s">
         <v>146</v>
       </c>
@@ -7618,7 +7629,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="93" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B93" s="4" t="s">
         <v>140</v>
       </c>
@@ -7651,7 +7662,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="94" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B94" s="4" t="s">
         <v>135</v>
       </c>
@@ -7684,7 +7695,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="95" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A95" s="8" t="s">
         <v>558</v>
       </c>
@@ -7711,7 +7722,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="96" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="B96" s="4" t="s">
         <v>123</v>
       </c>
@@ -7744,7 +7755,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="97" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B97" s="4" t="s">
         <v>118</v>
       </c>
@@ -7777,7 +7788,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="98" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="B98" s="4" t="s">
         <v>112</v>
       </c>
@@ -7810,7 +7821,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="99" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B99" s="4" t="s">
         <v>109</v>
       </c>
@@ -7843,7 +7854,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="100" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B100" s="4" t="s">
         <v>104</v>
       </c>
@@ -7876,7 +7887,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="101" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="B101" s="4" t="s">
         <v>98</v>
       </c>
@@ -7909,7 +7920,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="102" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B102" s="4" t="s">
         <v>92</v>
       </c>
@@ -7942,7 +7953,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="103" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A103" s="8" t="s">
         <v>559</v>
       </c>
@@ -7978,7 +7989,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="104" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A104" s="8" t="s">
         <v>557</v>
       </c>
@@ -8005,7 +8016,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="105" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A105" s="8" t="s">
         <v>557</v>
       </c>
@@ -8032,7 +8043,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="106" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A106" s="8" t="s">
         <v>557</v>
       </c>
@@ -8059,7 +8070,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="107" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A107" s="8" t="s">
         <v>557</v>
       </c>
@@ -8086,7 +8097,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="108" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A108" s="8" t="s">
         <v>557</v>
       </c>
@@ -8113,7 +8124,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="109" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A109" s="8" t="s">
         <v>559</v>
       </c>
@@ -8149,7 +8160,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A110" s="8" t="s">
         <v>558</v>
       </c>
@@ -8176,7 +8187,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="111" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A111" s="8" t="s">
         <v>557</v>
       </c>
@@ -8203,7 +8214,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="112" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A112" s="8" t="s">
         <v>557</v>
       </c>
@@ -8230,7 +8241,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="113" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A113" s="8" t="s">
         <v>557</v>
       </c>
@@ -8257,7 +8268,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A114" s="8" t="s">
         <v>557</v>
       </c>
@@ -8284,7 +8295,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="115" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A115" s="8" t="s">
         <v>557</v>
       </c>
@@ -8311,7 +8322,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="116" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A116" s="8" t="s">
         <v>559</v>
       </c>
@@ -8347,7 +8358,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="117" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A117" s="8" t="s">
         <v>557</v>
       </c>
@@ -8374,7 +8385,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="118" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A118" s="8" t="s">
         <v>558</v>
       </c>
@@ -8404,7 +8415,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="119" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A119" s="8" t="s">
         <v>557</v>
       </c>
@@ -8431,7 +8442,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="120" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A120" s="8" t="s">
         <v>557</v>
       </c>
@@ -8458,7 +8469,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="121" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A121" s="8" t="s">
         <v>597</v>
       </c>
@@ -8485,7 +8496,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="122" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A122" s="8" t="s">
         <v>602</v>
       </c>
@@ -8512,7 +8523,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="123" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A123" s="8" t="s">
         <v>608</v>
       </c>
@@ -8539,7 +8550,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="124" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A124" s="8" t="s">
         <v>611</v>
       </c>
@@ -8566,7 +8577,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="125" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A125" s="8" t="s">
         <v>617</v>
       </c>
@@ -8593,7 +8604,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="126" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A126" s="8" t="s">
         <v>624</v>
       </c>
@@ -8620,7 +8631,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="127" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A127" s="8" t="s">
         <v>557</v>
       </c>
@@ -8647,7 +8658,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="128" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A128" s="8" t="s">
         <v>649</v>
       </c>
@@ -8674,7 +8685,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="129" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A129" s="8" t="s">
         <v>653</v>
       </c>
@@ -8701,7 +8712,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="130" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A130" s="8" t="s">
         <v>659</v>
       </c>
@@ -8728,7 +8739,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="131" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A131" s="8" t="s">
         <v>664</v>
       </c>
@@ -8755,7 +8766,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A132" s="8" t="s">
         <v>557</v>
       </c>
@@ -8782,7 +8793,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="133" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A133" s="8" t="s">
         <v>557</v>
       </c>
@@ -8809,7 +8820,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="134" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A134" s="8" t="s">
         <v>681</v>
       </c>
@@ -8836,7 +8847,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="135" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A135" s="8" t="s">
         <v>687</v>
       </c>
@@ -8863,7 +8874,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="136" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A136" s="8" t="s">
         <v>691</v>
       </c>
@@ -8890,7 +8901,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="137" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A137" s="8" t="s">
         <v>699</v>
       </c>
@@ -8917,7 +8928,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="138" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A138" s="8" t="s">
         <v>704</v>
       </c>
@@ -8944,7 +8955,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="139" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A139" s="8" t="s">
         <v>711</v>
       </c>
@@ -8971,7 +8982,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="140" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A140" s="8" t="s">
         <v>716</v>
       </c>
@@ -8998,7 +9009,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="141" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A141" s="8" t="s">
         <v>724</v>
       </c>
@@ -9025,7 +9036,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="142" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A142" s="8" t="s">
         <v>727</v>
       </c>
@@ -9052,7 +9063,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="143" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A143" s="8" t="s">
         <v>736</v>
       </c>
@@ -9079,7 +9090,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="144" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A144" s="8" t="s">
         <v>740</v>
       </c>
@@ -9106,7 +9117,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="145" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A145" s="8" t="s">
         <v>746</v>
       </c>
@@ -9133,7 +9144,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="146" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A146" s="8" t="s">
         <v>754</v>
       </c>
@@ -9160,7 +9171,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="147" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A147" s="8" t="s">
         <v>759</v>
       </c>
@@ -9187,7 +9198,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="148" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A148" s="8" t="s">
         <v>770</v>
       </c>
@@ -9214,7 +9225,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="149" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A149" s="8" t="s">
         <v>777</v>
       </c>
@@ -9241,7 +9252,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="150" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A150" s="8" t="s">
         <v>782</v>
       </c>
@@ -9268,7 +9279,7 @@
         <v>786</v>
       </c>
     </row>
-    <row r="151" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A151" s="8" t="s">
         <v>557</v>
       </c>
@@ -9295,7 +9306,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="152" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A152" s="8" t="s">
         <v>795</v>
       </c>
@@ -9322,7 +9333,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A153" s="8" t="s">
         <v>800</v>
       </c>
@@ -9349,7 +9360,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A154" s="8" t="s">
         <v>804</v>
       </c>
@@ -9376,7 +9387,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A155" s="8" t="s">
         <v>811</v>
       </c>
@@ -9403,7 +9414,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="156" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A156" s="8" t="s">
         <v>557</v>
       </c>
@@ -9430,7 +9441,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A157" s="8" t="s">
         <v>557</v>
       </c>
@@ -9457,7 +9468,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A158" s="8" t="s">
         <v>827</v>
       </c>
@@ -9484,7 +9495,7 @@
         <v>831</v>
       </c>
     </row>
-    <row r="159" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A159" s="8" t="s">
         <v>557</v>
       </c>
@@ -9511,7 +9522,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A160" s="8" t="s">
         <v>838</v>
       </c>
@@ -9538,7 +9549,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="161" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A161" s="8" t="s">
         <v>557</v>
       </c>
@@ -9565,7 +9576,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A162" s="8" t="s">
         <v>850</v>
       </c>
@@ -9592,7 +9603,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A163" s="8" t="s">
         <v>857</v>
       </c>
@@ -9619,7 +9630,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A164" s="8" t="s">
         <v>557</v>
       </c>
@@ -9646,7 +9657,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="165" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A165" s="8" t="s">
         <v>557</v>
       </c>
@@ -9673,7 +9684,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A166" s="8" t="s">
         <v>557</v>
       </c>
@@ -9700,7 +9711,7 @@
         <v>871</v>
       </c>
     </row>
-    <row r="167" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A167" s="8" t="s">
         <v>557</v>
       </c>
@@ -9727,7 +9738,7 @@
         <v>879</v>
       </c>
     </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A168" s="8" t="s">
         <v>557</v>
       </c>
@@ -9754,7 +9765,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A169" s="8" t="s">
         <v>557</v>
       </c>
@@ -9781,7 +9792,7 @@
         <v>889</v>
       </c>
     </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A170" s="8" t="s">
         <v>557</v>
       </c>
@@ -9808,7 +9819,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A171" s="8" t="s">
         <v>557</v>
       </c>
@@ -9835,7 +9846,7 @@
         <v>897</v>
       </c>
     </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A172" s="8" t="s">
         <v>902</v>
       </c>
@@ -9862,7 +9873,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A173" s="8" t="s">
         <v>902</v>
       </c>
@@ -9889,7 +9900,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A174" s="8" t="s">
         <v>557</v>
       </c>
@@ -9916,7 +9927,7 @@
         <v>915</v>
       </c>
     </row>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A175" s="8" t="s">
         <v>557</v>
       </c>
@@ -9943,7 +9954,7 @@
         <v>919</v>
       </c>
     </row>
-    <row r="176" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A176" s="8" t="s">
         <v>557</v>
       </c>
@@ -9970,7 +9981,7 @@
         <v>925</v>
       </c>
     </row>
-    <row r="177" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A177" s="8" t="s">
         <v>557</v>
       </c>
@@ -9997,7 +10008,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="178" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:13" ht="28" x14ac:dyDescent="0.3">
       <c r="A178" s="8" t="s">
         <v>557</v>
       </c>
@@ -10024,7 +10035,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="179" spans="1:13" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:13" ht="42" x14ac:dyDescent="0.3">
       <c r="A179" s="8" t="s">
         <v>938</v>
       </c>
@@ -10051,7 +10062,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="180" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B180" s="4" t="s">
         <v>942</v>
       </c>
@@ -10075,7 +10086,7 @@
         <v>946</v>
       </c>
     </row>
-    <row r="181" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:13" ht="28" x14ac:dyDescent="0.3">
       <c r="B181" s="4" t="s">
         <v>948</v>
       </c>
@@ -10099,7 +10110,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="182" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:13" ht="28" x14ac:dyDescent="0.3">
       <c r="B182" s="4" t="s">
         <v>954</v>
       </c>
@@ -10123,7 +10134,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="183" spans="1:13" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:13" ht="42" x14ac:dyDescent="0.3">
       <c r="B183" s="4" t="s">
         <v>959</v>
       </c>
@@ -10147,7 +10158,7 @@
         <v>960</v>
       </c>
     </row>
-    <row r="184" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:13" ht="28" x14ac:dyDescent="0.3">
       <c r="B184" s="4" t="s">
         <v>966</v>
       </c>
@@ -10171,7 +10182,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="185" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:13" ht="28" x14ac:dyDescent="0.3">
       <c r="B185" s="4" t="s">
         <v>971</v>
       </c>
@@ -10195,7 +10206,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="186" spans="1:13" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:13" ht="42" x14ac:dyDescent="0.3">
       <c r="B186" s="4" t="s">
         <v>976</v>
       </c>
@@ -10219,7 +10230,7 @@
         <v>963</v>
       </c>
     </row>
-    <row r="187" spans="1:13" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:13" ht="42" x14ac:dyDescent="0.3">
       <c r="B187" s="4" t="s">
         <v>979</v>
       </c>
@@ -10243,7 +10254,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="188" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:13" ht="28" x14ac:dyDescent="0.3">
       <c r="B188" s="4" t="s">
         <v>985</v>
       </c>
@@ -10270,7 +10281,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="189" spans="1:13" ht="15" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:13" ht="15.5" x14ac:dyDescent="0.3">
       <c r="B189" s="4" t="s">
         <v>988</v>
       </c>
@@ -10295,7 +10306,7 @@
       </c>
       <c r="M189" s="6"/>
     </row>
-    <row r="190" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:13" ht="28" x14ac:dyDescent="0.3">
       <c r="B190" s="4" t="s">
         <v>992</v>
       </c>
@@ -10319,7 +10330,7 @@
         <v>982</v>
       </c>
     </row>
-    <row r="191" spans="1:13" ht="45" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:13" ht="46.5" x14ac:dyDescent="0.3">
       <c r="B191" s="4" t="s">
         <v>1002</v>
       </c>
@@ -10343,7 +10354,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="192" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:13" ht="28" x14ac:dyDescent="0.3">
       <c r="B192" s="4" t="s">
         <v>1006</v>
       </c>
@@ -10367,7 +10378,7 @@
         <v>998</v>
       </c>
     </row>
-    <row r="193" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="193" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B193" s="4" t="s">
         <v>1010</v>
       </c>
@@ -10391,7 +10402,7 @@
         <v>1011</v>
       </c>
     </row>
-    <row r="194" spans="2:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="194" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B194" s="4" t="s">
         <v>1015</v>
       </c>
@@ -10418,7 +10429,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="195" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="195" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B195" s="4" t="s">
         <v>1021</v>
       </c>
@@ -10442,7 +10453,7 @@
         <v>1019</v>
       </c>
     </row>
-    <row r="196" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="196" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B196" s="4" t="s">
         <v>1025</v>
       </c>
@@ -10466,7 +10477,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="197" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="197" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B197" s="4" t="s">
         <v>1031</v>
       </c>
@@ -10490,7 +10501,7 @@
         <v>1033</v>
       </c>
     </row>
-    <row r="198" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="198" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B198" s="4" t="s">
         <v>1034</v>
       </c>
@@ -10514,7 +10525,7 @@
         <v>1035</v>
       </c>
     </row>
-    <row r="199" spans="2:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="199" spans="2:12" ht="42" x14ac:dyDescent="0.3">
       <c r="B199" s="4" t="s">
         <v>1040</v>
       </c>
@@ -10538,7 +10549,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="200" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="200" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B200" s="4" t="s">
         <v>1045</v>
       </c>
@@ -10562,7 +10573,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="201" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="201" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B201" s="4" t="s">
         <v>1051</v>
       </c>
@@ -10586,7 +10597,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="202" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="202" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B202" s="4" t="s">
         <v>1058</v>
       </c>
@@ -10610,7 +10621,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="203" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="203" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B203" s="4" t="s">
         <v>1062</v>
       </c>
@@ -10634,7 +10645,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="204" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="204" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B204" s="4" t="s">
         <v>1065</v>
       </c>
@@ -10658,7 +10669,7 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="205" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="205" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B205" s="4" t="s">
         <v>1071</v>
       </c>
@@ -10682,7 +10693,7 @@
         <v>1069</v>
       </c>
     </row>
-    <row r="206" spans="2:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="206" spans="2:12" ht="42" x14ac:dyDescent="0.3">
       <c r="B206" s="4" t="s">
         <v>1074</v>
       </c>
@@ -10706,7 +10717,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="207" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="207" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B207" s="4" t="s">
         <v>1080</v>
       </c>
@@ -10730,7 +10741,7 @@
         <v>1079</v>
       </c>
     </row>
-    <row r="208" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="208" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B208" s="4" t="s">
         <v>1082</v>
       </c>
@@ -10754,7 +10765,7 @@
         <v>1081</v>
       </c>
     </row>
-    <row r="209" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="209" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B209" s="4" t="s">
         <v>1091</v>
       </c>
@@ -10778,7 +10789,7 @@
         <v>1089</v>
       </c>
     </row>
-    <row r="210" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="210" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B210" s="4" t="s">
         <v>1093</v>
       </c>
@@ -10802,7 +10813,7 @@
         <v>1092</v>
       </c>
     </row>
-    <row r="211" spans="2:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="211" spans="2:12" ht="42" x14ac:dyDescent="0.3">
       <c r="B211" s="4" t="s">
         <v>1102</v>
       </c>
@@ -10826,7 +10837,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="212" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="212" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B212" s="4" t="s">
         <v>1105</v>
       </c>
@@ -10850,7 +10861,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="213" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="213" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B213" s="4" t="s">
         <v>1110</v>
       </c>
@@ -10874,7 +10885,7 @@
         <v>1109</v>
       </c>
     </row>
-    <row r="214" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="214" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B214" s="4" t="s">
         <v>1118</v>
       </c>
@@ -10888,22 +10899,22 @@
         <v>654</v>
       </c>
       <c r="I214" s="4" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="J214" s="5" t="str">
         <f t="shared" si="5"/>
         <v>001118</v>
       </c>
       <c r="K214" s="3" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="L214" s="2" t="s">
         <v>1114</v>
       </c>
     </row>
-    <row r="215" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="215" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B215" s="4" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>1117</v>
@@ -10912,76 +10923,76 @@
         <v>654</v>
       </c>
       <c r="I215" s="4" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="J215" s="5" t="str">
         <f t="shared" si="5"/>
         <v>001119</v>
       </c>
       <c r="K215" s="3" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="L215" s="2" t="s">
         <v>1116</v>
       </c>
     </row>
-    <row r="216" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="216" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B216" s="4" t="s">
+        <v>1126</v>
+      </c>
+      <c r="C216" s="1" t="s">
         <v>1127</v>
-      </c>
-      <c r="C216" s="1" t="s">
-        <v>1128</v>
       </c>
       <c r="E216" s="6" t="s">
         <v>32</v>
       </c>
       <c r="H216" s="1" t="s">
+        <v>1128</v>
+      </c>
+      <c r="I216" s="4" t="s">
         <v>1129</v>
-      </c>
-      <c r="I216" s="4" t="s">
-        <v>1130</v>
       </c>
       <c r="J216" s="5" t="str">
         <f t="shared" si="5"/>
         <v>001120</v>
       </c>
       <c r="K216" s="3" t="s">
+        <v>1130</v>
+      </c>
+      <c r="L216" s="2" t="s">
         <v>1131</v>
       </c>
-      <c r="L216" s="2" t="s">
-        <v>1132</v>
-      </c>
-    </row>
-    <row r="217" spans="2:12" ht="42.75" x14ac:dyDescent="0.2">
+    </row>
+    <row r="217" spans="2:12" ht="42" x14ac:dyDescent="0.3">
       <c r="B217" s="4" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="C217" s="1" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="H217" s="1" t="s">
         <v>654</v>
       </c>
       <c r="I217" s="4" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="J217" s="5" t="str">
         <f t="shared" si="5"/>
         <v>001122</v>
       </c>
       <c r="K217" s="3" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="L217" s="2" t="s">
         <v>1113</v>
       </c>
     </row>
-    <row r="218" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="218" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B218" s="4" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="C218" s="1" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E218" s="6" t="s">
         <v>32</v>
@@ -10990,621 +11001,633 @@
         <v>11</v>
       </c>
       <c r="I218" s="4" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="J218" s="5" t="str">
         <f t="shared" si="5"/>
         <v>001123</v>
       </c>
       <c r="K218" s="3" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="L218" s="2" t="s">
-        <v>1133</v>
-      </c>
-    </row>
-    <row r="219" spans="2:12" x14ac:dyDescent="0.2">
+        <v>1132</v>
+      </c>
+    </row>
+    <row r="219" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+      <c r="B219" s="4" t="s">
+        <v>1142</v>
+      </c>
       <c r="C219" s="1" t="s">
-        <v>1120</v>
+        <v>1144</v>
+      </c>
+      <c r="H219" s="1" t="s">
+        <v>654</v>
+      </c>
+      <c r="I219" s="4" t="s">
+        <v>1141</v>
       </c>
       <c r="J219" s="5" t="str">
         <f t="shared" ref="J219" si="6">"00"&amp;B219</f>
-        <v>00</v>
+        <v>001124</v>
+      </c>
+      <c r="K219" s="3" t="s">
+        <v>1143</v>
       </c>
       <c r="L219" s="2" t="s">
-        <v>1121</v>
-      </c>
-    </row>
-    <row r="220" spans="2:12" x14ac:dyDescent="0.2">
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="220" spans="2:12" x14ac:dyDescent="0.3">
       <c r="J220" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="221" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="221" spans="2:12" x14ac:dyDescent="0.3">
       <c r="J221" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="222" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="222" spans="2:12" x14ac:dyDescent="0.3">
       <c r="J222" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="223" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="223" spans="2:12" x14ac:dyDescent="0.3">
       <c r="J223" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="224" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="224" spans="2:12" x14ac:dyDescent="0.3">
       <c r="J224" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="225" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="225" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J225" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="226" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="226" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J226" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="227" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="227" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J227" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="228" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="228" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J228" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="229" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="229" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J229" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="230" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="230" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J230" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="231" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="231" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J231" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="232" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="232" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J232" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="233" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="233" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J233" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="234" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="234" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J234" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="235" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="235" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J235" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="236" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="236" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J236" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="237" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="237" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J237" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="238" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="238" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J238" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="239" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="239" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J239" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="240" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="240" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J240" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="241" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="241" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J241" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="242" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="242" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J242" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="243" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="243" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J243" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="244" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="244" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J244" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="245" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="245" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J245" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="246" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="246" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J246" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="247" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="247" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J247" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="248" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="248" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J248" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="249" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="249" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J249" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="250" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="250" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J250" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="251" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="251" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J251" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="252" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="252" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J252" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="253" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="253" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J253" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="254" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="254" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J254" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="255" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="255" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J255" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="256" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="256" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J256" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="257" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="257" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J257" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="258" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="258" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J258" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="259" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="259" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J259" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="260" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="260" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J260" s="5" t="str">
         <f t="shared" ref="J260:J317" si="7">"00"&amp;B260</f>
         <v>00</v>
       </c>
     </row>
-    <row r="261" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="261" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J261" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="262" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="262" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J262" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="263" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="263" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J263" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="264" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="264" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J264" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="265" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="265" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J265" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="266" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="266" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J266" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="267" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="267" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J267" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="268" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="268" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J268" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="269" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="269" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J269" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="270" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="270" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J270" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="271" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="271" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J271" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="272" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="272" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J272" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="273" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="273" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J273" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="274" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="274" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J274" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="275" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="275" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J275" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="276" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="276" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J276" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="277" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="277" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J277" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="278" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="278" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J278" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="279" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="279" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J279" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="280" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="280" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J280" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="281" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="281" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J281" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="282" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="282" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J282" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="283" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="283" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J283" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="284" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="284" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J284" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="285" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="285" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J285" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="286" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="286" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J286" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="287" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="287" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J287" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="288" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="288" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J288" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="289" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="289" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J289" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="290" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="290" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J290" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="291" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="291" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J291" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="292" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="292" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J292" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="293" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="293" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J293" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="294" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="294" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J294" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="295" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="295" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J295" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="296" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="296" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J296" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="297" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="297" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J297" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="298" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="298" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J298" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="299" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="299" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J299" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="300" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="300" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J300" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="301" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="301" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J301" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="302" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="302" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J302" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="303" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="303" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J303" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="304" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="304" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J304" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="305" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="305" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J305" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="306" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="306" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J306" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="307" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="307" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J307" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="308" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="308" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J308" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="309" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="309" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J309" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="310" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="310" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J310" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="311" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="311" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J311" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="312" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="312" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J312" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="313" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="313" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J313" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="314" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="314" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J314" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="315" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="315" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J315" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="316" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="316" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J316" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="317" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="317" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J317" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:L4" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A4:L4"/>
   <mergeCells count="1">
     <mergeCell ref="A2:L2"/>
   </mergeCells>
@@ -11616,10 +11639,10 @@
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1:E1 D3:E3 D6:E1048576" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1:E1 D3:E3 D6:E1048576">
       <formula1>"是,否"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H1 H3:H1048576" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H1 H3:H1048576">
       <formula1>"VB编程,系统运维,WEB学习,游戏碎片,日常随笔,浥尘伙伴社团"</formula1>
     </dataValidation>
   </dataValidations>
@@ -11629,20 +11652,20 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A2:L34"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="6.375" customWidth="1"/>
+    <col min="2" max="2" width="6.33203125" customWidth="1"/>
     <col min="3" max="3" width="34" style="4" customWidth="1"/>
     <col min="4" max="4" width="4.75" customWidth="1"/>
-    <col min="8" max="8" width="6.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.83203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="19" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="7.125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="7.08203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.08203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:12" ht="23.25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
         <v>549</v>
       </c>
@@ -11658,7 +11681,7 @@
       <c r="K2" s="21"/>
       <c r="L2" s="21"/>
     </row>
-    <row r="4" spans="1:12" ht="57" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12" ht="56" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>0</v>
       </c>
@@ -11696,7 +11719,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>533</v>
       </c>
@@ -11719,7 +11742,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C8" s="15" t="s">
         <v>545</v>
       </c>
@@ -11728,7 +11751,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C9" s="4" t="s">
         <v>539</v>
       </c>
@@ -11736,7 +11759,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C10" t="s">
         <v>537</v>
       </c>
@@ -11744,7 +11767,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C11" t="s">
         <v>538</v>
       </c>
@@ -11752,7 +11775,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="23.25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A13" s="21" t="s">
         <v>543</v>
       </c>
@@ -11768,7 +11791,7 @@
       <c r="K13" s="21"/>
       <c r="L13" s="21"/>
     </row>
-    <row r="15" spans="1:12" ht="57" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:12" ht="56" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
         <v>0</v>
       </c>
@@ -11806,7 +11829,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>533</v>
       </c>
@@ -11832,7 +11855,7 @@
         <v>54837657</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C19" s="15" t="s">
         <v>545</v>
       </c>
@@ -11841,7 +11864,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C20" s="4" t="s">
         <v>539</v>
       </c>
@@ -11849,7 +11872,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C21" t="s">
         <v>537</v>
       </c>
@@ -11857,7 +11880,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C22" t="s">
         <v>538</v>
       </c>
@@ -11865,10 +11888,10 @@
         <v>541</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C23"/>
     </row>
-    <row r="25" spans="1:12" ht="23.25" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:12" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A25" s="21" t="s">
         <v>550</v>
       </c>
@@ -11884,7 +11907,7 @@
       <c r="K25" s="21"/>
       <c r="L25" s="21"/>
     </row>
-    <row r="27" spans="1:12" ht="57" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:12" ht="56" x14ac:dyDescent="0.3">
       <c r="A27" s="7" t="s">
         <v>0</v>
       </c>
@@ -11922,7 +11945,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
         <v>533</v>
       </c>
@@ -11948,7 +11971,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C31" s="15" t="s">
         <v>545</v>
       </c>
@@ -11957,7 +11980,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C32" s="4" t="s">
         <v>539</v>
       </c>
@@ -11965,7 +11988,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="33" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="33" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C33" t="s">
         <v>537</v>
       </c>
@@ -11973,7 +11996,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="34" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="34" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C34" t="s">
         <v>538</v>
       </c>
@@ -11989,7 +12012,7 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H15 H27 H4" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H15 H27 H4">
       <formula1>"VB编程,系统运维,WEB学习,游戏碎片,日常随笔"</formula1>
     </dataValidation>
   </dataValidations>

--- a/11_付费课程/99.资料/文章信息备忘表.xlsx
+++ b/11_付费课程/99.资料/文章信息备忘表.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\writing\11_付费课程\99.资料\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Writing\11_付费课程\99.资料\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{650F0901-E4C6-4FCC-950F-BC7EB8E9289D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1910" yWindow="-120" windowWidth="19740" windowHeight="11760"/>
+    <workbookView xWindow="870" yWindow="-120" windowWidth="19740" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,7 +19,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$L$4</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1572" uniqueCount="1145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1578" uniqueCount="1150">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -4565,13 +4566,33 @@
   </si>
   <si>
     <t>如何在 Windows 11 LTSC 上快速离线安装 Windows 终端</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1125</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>神秘代码绕开限制，手机没有SIM卡照样可以连接USB</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-01-06 08:11:34</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>431180</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>85749508</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -5063,25 +5084,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:M317"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.25" style="8" customWidth="1"/>
-    <col min="2" max="2" width="5.58203125" style="4" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="5.33203125" style="6" customWidth="1"/>
-    <col min="5" max="6" width="5.08203125" style="6" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="30.875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="5.375" style="6" customWidth="1"/>
+    <col min="5" max="6" width="5.125" style="6" customWidth="1"/>
     <col min="7" max="7" width="5.25" style="6" customWidth="1"/>
     <col min="8" max="8" width="13.5" style="1" customWidth="1"/>
     <col min="9" max="9" width="19" style="4" customWidth="1"/>
-    <col min="10" max="10" width="8.58203125" style="5" customWidth="1"/>
+    <col min="10" max="10" width="8.625" style="5" customWidth="1"/>
     <col min="11" max="11" width="7.5" style="3" customWidth="1"/>
     <col min="12" max="12" width="9.25" style="2" customWidth="1"/>
     <col min="13" max="13" width="16.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:12" ht="25" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
@@ -5097,8 +5118,8 @@
       <c r="K2" s="20"/>
       <c r="L2" s="20"/>
     </row>
-    <row r="3" spans="1:12" ht="6.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="4" spans="1:12" s="7" customFormat="1" ht="56" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" ht="6.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="4" spans="1:12" s="7" customFormat="1" ht="57" x14ac:dyDescent="0.2">
       <c r="A4" s="7" t="s">
         <v>0</v>
       </c>
@@ -5136,7 +5157,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
         <v>557</v>
       </c>
@@ -5163,7 +5184,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
         <v>559</v>
       </c>
@@ -5199,7 +5220,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="8" t="s">
         <v>559</v>
       </c>
@@ -5235,25 +5256,25 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="J8" s="5" t="str">
         <f t="shared" si="0"/>
         <v>000</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="J9" s="5" t="str">
         <f t="shared" si="0"/>
         <v>000</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="J10" s="5" t="str">
         <f t="shared" si="0"/>
         <v>000</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B11" s="4" t="s">
         <v>522</v>
       </c>
@@ -5286,7 +5307,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A12" s="8" t="s">
         <v>558</v>
       </c>
@@ -5316,7 +5337,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A13" s="8" t="s">
         <v>558</v>
       </c>
@@ -5346,7 +5367,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A14" s="8" t="s">
         <v>640</v>
       </c>
@@ -5373,7 +5394,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" s="8" t="s">
         <v>557</v>
       </c>
@@ -5400,7 +5421,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" s="8" t="s">
         <v>557</v>
       </c>
@@ -5427,7 +5448,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" s="8" t="s">
         <v>557</v>
       </c>
@@ -5454,7 +5475,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" s="8" t="s">
         <v>767</v>
       </c>
@@ -5481,7 +5502,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A19" s="8" t="s">
         <v>557</v>
       </c>
@@ -5508,7 +5529,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A20" s="8" t="s">
         <v>557</v>
       </c>
@@ -5535,7 +5556,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A21" s="8" t="s">
         <v>557</v>
       </c>
@@ -5562,7 +5583,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A22" s="8" t="s">
         <v>559</v>
       </c>
@@ -5598,7 +5619,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23" s="8" t="s">
         <v>557</v>
       </c>
@@ -5625,7 +5646,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A24" s="8" t="s">
         <v>558</v>
       </c>
@@ -5655,7 +5676,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A25" s="8" t="s">
         <v>557</v>
       </c>
@@ -5682,7 +5703,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A26" s="8" t="s">
         <v>557</v>
       </c>
@@ -5709,7 +5730,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="27" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A27" s="8" t="s">
         <v>633</v>
       </c>
@@ -5736,7 +5757,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A28" s="8" t="s">
         <v>557</v>
       </c>
@@ -5763,7 +5784,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A29" s="8" t="s">
         <v>559</v>
       </c>
@@ -5799,7 +5820,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A30" s="8" t="s">
         <v>559</v>
       </c>
@@ -5835,7 +5856,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A31" s="8" t="s">
         <v>557</v>
       </c>
@@ -5862,7 +5883,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A32" s="8" t="s">
         <v>557</v>
       </c>
@@ -5889,7 +5910,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A33" s="8" t="s">
         <v>557</v>
       </c>
@@ -5916,7 +5937,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="34" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A34" s="8" t="s">
         <v>557</v>
       </c>
@@ -5943,7 +5964,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="35" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A35" s="8" t="s">
         <v>557</v>
       </c>
@@ -5970,7 +5991,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="36" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A36" s="8" t="s">
         <v>557</v>
       </c>
@@ -5997,7 +6018,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="37" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A37" s="8" t="s">
         <v>559</v>
       </c>
@@ -6033,7 +6054,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="38" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A38" s="8" t="s">
         <v>557</v>
       </c>
@@ -6060,7 +6081,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A39" s="8" t="s">
         <v>557</v>
       </c>
@@ -6087,7 +6108,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="40" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A40" s="8" t="s">
         <v>557</v>
       </c>
@@ -6114,7 +6135,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="41" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A41" s="8" t="s">
         <v>557</v>
       </c>
@@ -6141,7 +6162,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="42" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A42" s="8" t="s">
         <v>557</v>
       </c>
@@ -6168,7 +6189,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="43" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A43" s="8" t="s">
         <v>559</v>
       </c>
@@ -6201,7 +6222,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="44" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A44" s="8" t="s">
         <v>557</v>
       </c>
@@ -6228,7 +6249,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="45" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A45" s="8" t="s">
         <v>557</v>
       </c>
@@ -6255,7 +6276,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="46" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A46" s="8" t="s">
         <v>557</v>
       </c>
@@ -6282,7 +6303,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A47" s="8" t="s">
         <v>557</v>
       </c>
@@ -6309,7 +6330,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="48" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A48" s="8" t="s">
         <v>557</v>
       </c>
@@ -6336,7 +6357,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="49" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A49" s="8" t="s">
         <v>557</v>
       </c>
@@ -6363,7 +6384,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="50" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A50" s="8" t="s">
         <v>557</v>
       </c>
@@ -6390,7 +6411,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A51" s="8" t="s">
         <v>557</v>
       </c>
@@ -6417,7 +6438,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="52" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A52" s="8" t="s">
         <v>557</v>
       </c>
@@ -6444,7 +6465,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A53" s="8" t="s">
         <v>557</v>
       </c>
@@ -6471,7 +6492,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="54" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A54" s="8" t="s">
         <v>557</v>
       </c>
@@ -6498,7 +6519,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A55" s="8" t="s">
         <v>557</v>
       </c>
@@ -6525,7 +6546,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="56" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A56" s="8" t="s">
         <v>559</v>
       </c>
@@ -6561,7 +6582,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="57" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A57" s="8" t="s">
         <v>559</v>
       </c>
@@ -6597,7 +6618,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="58" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A58" s="8" t="s">
         <v>557</v>
       </c>
@@ -6624,7 +6645,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="59" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A59" s="8" t="s">
         <v>558</v>
       </c>
@@ -6654,7 +6675,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="60" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A60" s="8" t="s">
         <v>557</v>
       </c>
@@ -6681,7 +6702,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="61" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B61" s="4" t="s">
         <v>298</v>
       </c>
@@ -6714,7 +6735,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="62" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B62" s="4" t="s">
         <v>294</v>
       </c>
@@ -6747,7 +6768,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="63" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B63" s="4" t="s">
         <v>289</v>
       </c>
@@ -6780,7 +6801,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="64" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A64" s="8" t="s">
         <v>557</v>
       </c>
@@ -6807,7 +6828,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="65" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A65" s="8" t="s">
         <v>557</v>
       </c>
@@ -6834,7 +6855,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="66" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A66" s="8" t="s">
         <v>559</v>
       </c>
@@ -6870,7 +6891,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="67" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A67" s="8" t="s">
         <v>557</v>
       </c>
@@ -6897,7 +6918,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="68" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A68" s="8" t="s">
         <v>558</v>
       </c>
@@ -6927,7 +6948,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="69" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A69" s="8" t="s">
         <v>559</v>
       </c>
@@ -6954,7 +6975,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="70" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A70" s="8" t="s">
         <v>559</v>
       </c>
@@ -6981,7 +7002,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="71" spans="1:12" ht="56" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:12" ht="57" x14ac:dyDescent="0.2">
       <c r="A71" s="8" t="s">
         <v>558</v>
       </c>
@@ -7011,7 +7032,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="72" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A72" s="8" t="s">
         <v>558</v>
       </c>
@@ -7041,7 +7062,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="73" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A73" s="8" t="s">
         <v>558</v>
       </c>
@@ -7071,7 +7092,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="74" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A74" s="8" t="s">
         <v>557</v>
       </c>
@@ -7098,7 +7119,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="75" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A75" s="8" t="s">
         <v>557</v>
       </c>
@@ -7125,7 +7146,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="76" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A76" s="8" t="s">
         <v>558</v>
       </c>
@@ -7158,7 +7179,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="77" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A77" s="8" t="s">
         <v>557</v>
       </c>
@@ -7185,7 +7206,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="78" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A78" s="8" t="s">
         <v>558</v>
       </c>
@@ -7212,7 +7233,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="79" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A79" s="8" t="s">
         <v>557</v>
       </c>
@@ -7239,7 +7260,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="80" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A80" s="8" t="s">
         <v>558</v>
       </c>
@@ -7266,7 +7287,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="81" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A81" s="8" t="s">
         <v>557</v>
       </c>
@@ -7293,7 +7314,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="82" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A82" s="8" t="s">
         <v>557</v>
       </c>
@@ -7320,7 +7341,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="83" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A83" s="8" t="s">
         <v>557</v>
       </c>
@@ -7347,7 +7368,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="84" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A84" s="8" t="s">
         <v>557</v>
       </c>
@@ -7374,7 +7395,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="85" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A85" s="8" t="s">
         <v>558</v>
       </c>
@@ -7401,7 +7422,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="86" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A86" s="8" t="s">
         <v>557</v>
       </c>
@@ -7428,7 +7449,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="87" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A87" s="8" t="s">
         <v>559</v>
       </c>
@@ -7464,7 +7485,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="88" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A88" s="8" t="s">
         <v>559</v>
       </c>
@@ -7500,7 +7521,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="89" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A89" s="8" t="s">
         <v>559</v>
       </c>
@@ -7536,7 +7557,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="90" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A90" s="8" t="s">
         <v>557</v>
       </c>
@@ -7563,7 +7584,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="91" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B91" s="4" t="s">
         <v>151</v>
       </c>
@@ -7596,7 +7617,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="92" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B92" s="4" t="s">
         <v>146</v>
       </c>
@@ -7629,7 +7650,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="93" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B93" s="4" t="s">
         <v>140</v>
       </c>
@@ -7662,7 +7683,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="94" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B94" s="4" t="s">
         <v>135</v>
       </c>
@@ -7695,7 +7716,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="95" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A95" s="8" t="s">
         <v>558</v>
       </c>
@@ -7722,7 +7743,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="96" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B96" s="4" t="s">
         <v>123</v>
       </c>
@@ -7755,7 +7776,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="97" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B97" s="4" t="s">
         <v>118</v>
       </c>
@@ -7788,7 +7809,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="98" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B98" s="4" t="s">
         <v>112</v>
       </c>
@@ -7821,7 +7842,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="99" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B99" s="4" t="s">
         <v>109</v>
       </c>
@@ -7854,7 +7875,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="100" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B100" s="4" t="s">
         <v>104</v>
       </c>
@@ -7887,7 +7908,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="101" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B101" s="4" t="s">
         <v>98</v>
       </c>
@@ -7920,7 +7941,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="102" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B102" s="4" t="s">
         <v>92</v>
       </c>
@@ -7953,7 +7974,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="103" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A103" s="8" t="s">
         <v>559</v>
       </c>
@@ -7989,7 +8010,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="104" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A104" s="8" t="s">
         <v>557</v>
       </c>
@@ -8016,7 +8037,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="105" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A105" s="8" t="s">
         <v>557</v>
       </c>
@@ -8043,7 +8064,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="106" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A106" s="8" t="s">
         <v>557</v>
       </c>
@@ -8070,7 +8091,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="107" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A107" s="8" t="s">
         <v>557</v>
       </c>
@@ -8097,7 +8118,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="108" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A108" s="8" t="s">
         <v>557</v>
       </c>
@@ -8124,7 +8145,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="109" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A109" s="8" t="s">
         <v>559</v>
       </c>
@@ -8160,7 +8181,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A110" s="8" t="s">
         <v>558</v>
       </c>
@@ -8187,7 +8208,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="111" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A111" s="8" t="s">
         <v>557</v>
       </c>
@@ -8214,7 +8235,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A112" s="8" t="s">
         <v>557</v>
       </c>
@@ -8241,7 +8262,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="113" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A113" s="8" t="s">
         <v>557</v>
       </c>
@@ -8268,7 +8289,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A114" s="8" t="s">
         <v>557</v>
       </c>
@@ -8295,7 +8316,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="115" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A115" s="8" t="s">
         <v>557</v>
       </c>
@@ -8322,7 +8343,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="116" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A116" s="8" t="s">
         <v>559</v>
       </c>
@@ -8358,7 +8379,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="117" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A117" s="8" t="s">
         <v>557</v>
       </c>
@@ -8385,7 +8406,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="118" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A118" s="8" t="s">
         <v>558</v>
       </c>
@@ -8415,7 +8436,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="119" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A119" s="8" t="s">
         <v>557</v>
       </c>
@@ -8442,7 +8463,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="120" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A120" s="8" t="s">
         <v>557</v>
       </c>
@@ -8469,7 +8490,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="121" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A121" s="8" t="s">
         <v>597</v>
       </c>
@@ -8496,7 +8517,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="122" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A122" s="8" t="s">
         <v>602</v>
       </c>
@@ -8523,7 +8544,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="123" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A123" s="8" t="s">
         <v>608</v>
       </c>
@@ -8550,7 +8571,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="124" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A124" s="8" t="s">
         <v>611</v>
       </c>
@@ -8577,7 +8598,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="125" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A125" s="8" t="s">
         <v>617</v>
       </c>
@@ -8604,7 +8625,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="126" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A126" s="8" t="s">
         <v>624</v>
       </c>
@@ -8631,7 +8652,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="127" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A127" s="8" t="s">
         <v>557</v>
       </c>
@@ -8658,7 +8679,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="128" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A128" s="8" t="s">
         <v>649</v>
       </c>
@@ -8685,7 +8706,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="129" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A129" s="8" t="s">
         <v>653</v>
       </c>
@@ -8712,7 +8733,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="130" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A130" s="8" t="s">
         <v>659</v>
       </c>
@@ -8739,7 +8760,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="131" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A131" s="8" t="s">
         <v>664</v>
       </c>
@@ -8766,7 +8787,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A132" s="8" t="s">
         <v>557</v>
       </c>
@@ -8793,7 +8814,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="133" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A133" s="8" t="s">
         <v>557</v>
       </c>
@@ -8820,7 +8841,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="134" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A134" s="8" t="s">
         <v>681</v>
       </c>
@@ -8847,7 +8868,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="135" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A135" s="8" t="s">
         <v>687</v>
       </c>
@@ -8874,7 +8895,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="136" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A136" s="8" t="s">
         <v>691</v>
       </c>
@@ -8901,7 +8922,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="137" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A137" s="8" t="s">
         <v>699</v>
       </c>
@@ -8928,7 +8949,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="138" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A138" s="8" t="s">
         <v>704</v>
       </c>
@@ -8955,7 +8976,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="139" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A139" s="8" t="s">
         <v>711</v>
       </c>
@@ -8982,7 +9003,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="140" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A140" s="8" t="s">
         <v>716</v>
       </c>
@@ -9009,7 +9030,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="141" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A141" s="8" t="s">
         <v>724</v>
       </c>
@@ -9036,7 +9057,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="142" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A142" s="8" t="s">
         <v>727</v>
       </c>
@@ -9063,7 +9084,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="143" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A143" s="8" t="s">
         <v>736</v>
       </c>
@@ -9090,7 +9111,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="144" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A144" s="8" t="s">
         <v>740</v>
       </c>
@@ -9117,7 +9138,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="145" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A145" s="8" t="s">
         <v>746</v>
       </c>
@@ -9144,7 +9165,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="146" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A146" s="8" t="s">
         <v>754</v>
       </c>
@@ -9171,7 +9192,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="147" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A147" s="8" t="s">
         <v>759</v>
       </c>
@@ -9198,7 +9219,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="148" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A148" s="8" t="s">
         <v>770</v>
       </c>
@@ -9225,7 +9246,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="149" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A149" s="8" t="s">
         <v>777</v>
       </c>
@@ -9252,7 +9273,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="150" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A150" s="8" t="s">
         <v>782</v>
       </c>
@@ -9279,7 +9300,7 @@
         <v>786</v>
       </c>
     </row>
-    <row r="151" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A151" s="8" t="s">
         <v>557</v>
       </c>
@@ -9306,7 +9327,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="152" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A152" s="8" t="s">
         <v>795</v>
       </c>
@@ -9333,7 +9354,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A153" s="8" t="s">
         <v>800</v>
       </c>
@@ -9360,7 +9381,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A154" s="8" t="s">
         <v>804</v>
       </c>
@@ -9387,7 +9408,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A155" s="8" t="s">
         <v>811</v>
       </c>
@@ -9414,7 +9435,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="156" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A156" s="8" t="s">
         <v>557</v>
       </c>
@@ -9441,7 +9462,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A157" s="8" t="s">
         <v>557</v>
       </c>
@@ -9468,7 +9489,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A158" s="8" t="s">
         <v>827</v>
       </c>
@@ -9495,7 +9516,7 @@
         <v>831</v>
       </c>
     </row>
-    <row r="159" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A159" s="8" t="s">
         <v>557</v>
       </c>
@@ -9522,7 +9543,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A160" s="8" t="s">
         <v>838</v>
       </c>
@@ -9549,7 +9570,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="161" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A161" s="8" t="s">
         <v>557</v>
       </c>
@@ -9576,7 +9597,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A162" s="8" t="s">
         <v>850</v>
       </c>
@@ -9603,7 +9624,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A163" s="8" t="s">
         <v>857</v>
       </c>
@@ -9630,7 +9651,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A164" s="8" t="s">
         <v>557</v>
       </c>
@@ -9657,7 +9678,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="165" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A165" s="8" t="s">
         <v>557</v>
       </c>
@@ -9684,7 +9705,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A166" s="8" t="s">
         <v>557</v>
       </c>
@@ -9711,7 +9732,7 @@
         <v>871</v>
       </c>
     </row>
-    <row r="167" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A167" s="8" t="s">
         <v>557</v>
       </c>
@@ -9738,7 +9759,7 @@
         <v>879</v>
       </c>
     </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A168" s="8" t="s">
         <v>557</v>
       </c>
@@ -9765,7 +9786,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A169" s="8" t="s">
         <v>557</v>
       </c>
@@ -9792,7 +9813,7 @@
         <v>889</v>
       </c>
     </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A170" s="8" t="s">
         <v>557</v>
       </c>
@@ -9819,7 +9840,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A171" s="8" t="s">
         <v>557</v>
       </c>
@@ -9846,7 +9867,7 @@
         <v>897</v>
       </c>
     </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A172" s="8" t="s">
         <v>902</v>
       </c>
@@ -9873,7 +9894,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A173" s="8" t="s">
         <v>902</v>
       </c>
@@ -9900,7 +9921,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A174" s="8" t="s">
         <v>557</v>
       </c>
@@ -9927,7 +9948,7 @@
         <v>915</v>
       </c>
     </row>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A175" s="8" t="s">
         <v>557</v>
       </c>
@@ -9954,7 +9975,7 @@
         <v>919</v>
       </c>
     </row>
-    <row r="176" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A176" s="8" t="s">
         <v>557</v>
       </c>
@@ -9981,7 +10002,7 @@
         <v>925</v>
       </c>
     </row>
-    <row r="177" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A177" s="8" t="s">
         <v>557</v>
       </c>
@@ -10008,7 +10029,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="178" spans="1:13" ht="28" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A178" s="8" t="s">
         <v>557</v>
       </c>
@@ -10035,7 +10056,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="179" spans="1:13" ht="42" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:13" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A179" s="8" t="s">
         <v>938</v>
       </c>
@@ -10062,7 +10083,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="180" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B180" s="4" t="s">
         <v>942</v>
       </c>
@@ -10086,7 +10107,7 @@
         <v>946</v>
       </c>
     </row>
-    <row r="181" spans="1:13" ht="28" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B181" s="4" t="s">
         <v>948</v>
       </c>
@@ -10110,7 +10131,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="182" spans="1:13" ht="28" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B182" s="4" t="s">
         <v>954</v>
       </c>
@@ -10134,7 +10155,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="183" spans="1:13" ht="42" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:13" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B183" s="4" t="s">
         <v>959</v>
       </c>
@@ -10158,7 +10179,7 @@
         <v>960</v>
       </c>
     </row>
-    <row r="184" spans="1:13" ht="28" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B184" s="4" t="s">
         <v>966</v>
       </c>
@@ -10182,7 +10203,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="185" spans="1:13" ht="28" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B185" s="4" t="s">
         <v>971</v>
       </c>
@@ -10206,7 +10227,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="186" spans="1:13" ht="42" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:13" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B186" s="4" t="s">
         <v>976</v>
       </c>
@@ -10230,7 +10251,7 @@
         <v>963</v>
       </c>
     </row>
-    <row r="187" spans="1:13" ht="42" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:13" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B187" s="4" t="s">
         <v>979</v>
       </c>
@@ -10254,7 +10275,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="188" spans="1:13" ht="28" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B188" s="4" t="s">
         <v>985</v>
       </c>
@@ -10281,7 +10302,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="189" spans="1:13" ht="15.5" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:13" ht="15" x14ac:dyDescent="0.2">
       <c r="B189" s="4" t="s">
         <v>988</v>
       </c>
@@ -10306,7 +10327,7 @@
       </c>
       <c r="M189" s="6"/>
     </row>
-    <row r="190" spans="1:13" ht="28" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B190" s="4" t="s">
         <v>992</v>
       </c>
@@ -10330,7 +10351,7 @@
         <v>982</v>
       </c>
     </row>
-    <row r="191" spans="1:13" ht="46.5" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:13" ht="45" x14ac:dyDescent="0.2">
       <c r="B191" s="4" t="s">
         <v>1002</v>
       </c>
@@ -10354,7 +10375,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="192" spans="1:13" ht="28" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B192" s="4" t="s">
         <v>1006</v>
       </c>
@@ -10378,7 +10399,7 @@
         <v>998</v>
       </c>
     </row>
-    <row r="193" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="193" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B193" s="4" t="s">
         <v>1010</v>
       </c>
@@ -10402,7 +10423,7 @@
         <v>1011</v>
       </c>
     </row>
-    <row r="194" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="194" spans="2:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B194" s="4" t="s">
         <v>1015</v>
       </c>
@@ -10429,7 +10450,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="195" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="195" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B195" s="4" t="s">
         <v>1021</v>
       </c>
@@ -10453,7 +10474,7 @@
         <v>1019</v>
       </c>
     </row>
-    <row r="196" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="196" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B196" s="4" t="s">
         <v>1025</v>
       </c>
@@ -10477,7 +10498,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="197" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="197" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B197" s="4" t="s">
         <v>1031</v>
       </c>
@@ -10501,7 +10522,7 @@
         <v>1033</v>
       </c>
     </row>
-    <row r="198" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="198" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B198" s="4" t="s">
         <v>1034</v>
       </c>
@@ -10525,7 +10546,7 @@
         <v>1035</v>
       </c>
     </row>
-    <row r="199" spans="2:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="199" spans="2:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B199" s="4" t="s">
         <v>1040</v>
       </c>
@@ -10549,7 +10570,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="200" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="200" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B200" s="4" t="s">
         <v>1045</v>
       </c>
@@ -10573,7 +10594,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="201" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="201" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B201" s="4" t="s">
         <v>1051</v>
       </c>
@@ -10597,7 +10618,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="202" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="202" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B202" s="4" t="s">
         <v>1058</v>
       </c>
@@ -10621,7 +10642,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="203" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="203" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B203" s="4" t="s">
         <v>1062</v>
       </c>
@@ -10645,7 +10666,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="204" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="204" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B204" s="4" t="s">
         <v>1065</v>
       </c>
@@ -10669,7 +10690,7 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="205" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="205" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B205" s="4" t="s">
         <v>1071</v>
       </c>
@@ -10693,7 +10714,7 @@
         <v>1069</v>
       </c>
     </row>
-    <row r="206" spans="2:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="206" spans="2:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B206" s="4" t="s">
         <v>1074</v>
       </c>
@@ -10717,7 +10738,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="207" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="207" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B207" s="4" t="s">
         <v>1080</v>
       </c>
@@ -10741,7 +10762,7 @@
         <v>1079</v>
       </c>
     </row>
-    <row r="208" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="208" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B208" s="4" t="s">
         <v>1082</v>
       </c>
@@ -10765,7 +10786,7 @@
         <v>1081</v>
       </c>
     </row>
-    <row r="209" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="209" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B209" s="4" t="s">
         <v>1091</v>
       </c>
@@ -10789,7 +10810,7 @@
         <v>1089</v>
       </c>
     </row>
-    <row r="210" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="210" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B210" s="4" t="s">
         <v>1093</v>
       </c>
@@ -10813,7 +10834,7 @@
         <v>1092</v>
       </c>
     </row>
-    <row r="211" spans="2:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="211" spans="2:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B211" s="4" t="s">
         <v>1102</v>
       </c>
@@ -10837,7 +10858,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="212" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="212" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B212" s="4" t="s">
         <v>1105</v>
       </c>
@@ -10861,7 +10882,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="213" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="213" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B213" s="4" t="s">
         <v>1110</v>
       </c>
@@ -10885,7 +10906,7 @@
         <v>1109</v>
       </c>
     </row>
-    <row r="214" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="214" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B214" s="4" t="s">
         <v>1118</v>
       </c>
@@ -10912,7 +10933,7 @@
         <v>1114</v>
       </c>
     </row>
-    <row r="215" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="215" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B215" s="4" t="s">
         <v>1121</v>
       </c>
@@ -10936,7 +10957,7 @@
         <v>1116</v>
       </c>
     </row>
-    <row r="216" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="216" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B216" s="4" t="s">
         <v>1126</v>
       </c>
@@ -10963,7 +10984,7 @@
         <v>1131</v>
       </c>
     </row>
-    <row r="217" spans="2:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="217" spans="2:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B217" s="4" t="s">
         <v>1134</v>
       </c>
@@ -10987,7 +11008,7 @@
         <v>1113</v>
       </c>
     </row>
-    <row r="218" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="218" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B218" s="4" t="s">
         <v>1137</v>
       </c>
@@ -11014,7 +11035,7 @@
         <v>1132</v>
       </c>
     </row>
-    <row r="219" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="219" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B219" s="4" t="s">
         <v>1142</v>
       </c>
@@ -11038,596 +11059,614 @@
         <v>1120</v>
       </c>
     </row>
-    <row r="220" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="220" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="B220" s="4" t="s">
+        <v>1145</v>
+      </c>
+      <c r="C220" s="1" t="s">
+        <v>1146</v>
+      </c>
+      <c r="H220" s="1" t="s">
+        <v>654</v>
+      </c>
+      <c r="I220" s="4" t="s">
+        <v>1147</v>
+      </c>
       <c r="J220" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>00</v>
-      </c>
-    </row>
-    <row r="221" spans="2:12" x14ac:dyDescent="0.3">
+        <v>001125</v>
+      </c>
+      <c r="K220" s="3" t="s">
+        <v>1148</v>
+      </c>
+      <c r="L220" s="2" t="s">
+        <v>1149</v>
+      </c>
+    </row>
+    <row r="221" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J221" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="222" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="222" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J222" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="223" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="223" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J223" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="224" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="224" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J224" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="225" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="225" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J225" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="226" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="226" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J226" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="227" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="227" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J227" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="228" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="228" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J228" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="229" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="229" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J229" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="230" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="230" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J230" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="231" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="231" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J231" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="232" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="232" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J232" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="233" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="233" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J233" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="234" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="234" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J234" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="235" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="235" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J235" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="236" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="236" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J236" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="237" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="237" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J237" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="238" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="238" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J238" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="239" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="239" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J239" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="240" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="240" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J240" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="241" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="241" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J241" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="242" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="242" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J242" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="243" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="243" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J243" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="244" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="244" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J244" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="245" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="245" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J245" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="246" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="246" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J246" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="247" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="247" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J247" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="248" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="248" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J248" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="249" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="249" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J249" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="250" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="250" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J250" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="251" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="251" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J251" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="252" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="252" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J252" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="253" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="253" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J253" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="254" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="254" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J254" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="255" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="255" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J255" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="256" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="256" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J256" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="257" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="257" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J257" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="258" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="258" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J258" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="259" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="259" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J259" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="260" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="260" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J260" s="5" t="str">
         <f t="shared" ref="J260:J317" si="7">"00"&amp;B260</f>
         <v>00</v>
       </c>
     </row>
-    <row r="261" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="261" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J261" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="262" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="262" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J262" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="263" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="263" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J263" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="264" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="264" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J264" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="265" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="265" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J265" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="266" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="266" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J266" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="267" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="267" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J267" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="268" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="268" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J268" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="269" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="269" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J269" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="270" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="270" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J270" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="271" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="271" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J271" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="272" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="272" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J272" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="273" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="273" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J273" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="274" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="274" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J274" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="275" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="275" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J275" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="276" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="276" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J276" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="277" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="277" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J277" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="278" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="278" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J278" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="279" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="279" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J279" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="280" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="280" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J280" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="281" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="281" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J281" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="282" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="282" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J282" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="283" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="283" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J283" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="284" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="284" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J284" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="285" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="285" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J285" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="286" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="286" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J286" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="287" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="287" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J287" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="288" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="288" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J288" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="289" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="289" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J289" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="290" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="290" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J290" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="291" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="291" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J291" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="292" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="292" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J292" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="293" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="293" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J293" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="294" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="294" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J294" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="295" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="295" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J295" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="296" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="296" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J296" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="297" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="297" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J297" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="298" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="298" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J298" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="299" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="299" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J299" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="300" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="300" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J300" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="301" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="301" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J301" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="302" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="302" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J302" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="303" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="303" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J303" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="304" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="304" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J304" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="305" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="305" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J305" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="306" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="306" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J306" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="307" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="307" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J307" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="308" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="308" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J308" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="309" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="309" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J309" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="310" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="310" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J310" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="311" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="311" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J311" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="312" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="312" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J312" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="313" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="313" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J313" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="314" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="314" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J314" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="315" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="315" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J315" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="316" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="316" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J316" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="317" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="317" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J317" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:L4"/>
+  <autoFilter ref="A4:L4" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="1">
     <mergeCell ref="A2:L2"/>
   </mergeCells>
@@ -11639,10 +11678,10 @@
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1:E1 D3:E3 D6:E1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1:E1 D3:E3 D6:E1048576" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"是,否"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H1 H3:H1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H1 H3:H1048576" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"VB编程,系统运维,WEB学习,游戏碎片,日常随笔,浥尘伙伴社团"</formula1>
     </dataValidation>
   </dataValidations>
@@ -11652,20 +11691,20 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A2:L34"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="6.33203125" customWidth="1"/>
+    <col min="2" max="2" width="6.375" customWidth="1"/>
     <col min="3" max="3" width="34" style="4" customWidth="1"/>
     <col min="4" max="4" width="4.75" customWidth="1"/>
-    <col min="8" max="8" width="6.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="19" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="7.08203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.08203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:12" ht="22.5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" ht="23.25" x14ac:dyDescent="0.2">
       <c r="A2" s="21" t="s">
         <v>549</v>
       </c>
@@ -11681,7 +11720,7 @@
       <c r="K2" s="21"/>
       <c r="L2" s="21"/>
     </row>
-    <row r="4" spans="1:12" ht="56" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" ht="57" x14ac:dyDescent="0.2">
       <c r="A4" s="7" t="s">
         <v>0</v>
       </c>
@@ -11719,7 +11758,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
         <v>533</v>
       </c>
@@ -11742,7 +11781,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C8" s="15" t="s">
         <v>545</v>
       </c>
@@ -11751,7 +11790,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C9" s="4" t="s">
         <v>539</v>
       </c>
@@ -11759,7 +11798,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C10" t="s">
         <v>537</v>
       </c>
@@ -11767,7 +11806,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C11" t="s">
         <v>538</v>
       </c>
@@ -11775,7 +11814,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="22.5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" ht="23.25" x14ac:dyDescent="0.2">
       <c r="A13" s="21" t="s">
         <v>543</v>
       </c>
@@ -11791,7 +11830,7 @@
       <c r="K13" s="21"/>
       <c r="L13" s="21"/>
     </row>
-    <row r="15" spans="1:12" ht="56" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" ht="57" x14ac:dyDescent="0.2">
       <c r="A15" s="7" t="s">
         <v>0</v>
       </c>
@@ -11829,7 +11868,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
         <v>533</v>
       </c>
@@ -11855,7 +11894,7 @@
         <v>54837657</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C19" s="15" t="s">
         <v>545</v>
       </c>
@@ -11864,7 +11903,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C20" s="4" t="s">
         <v>539</v>
       </c>
@@ -11872,7 +11911,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C21" t="s">
         <v>537</v>
       </c>
@@ -11880,7 +11919,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C22" t="s">
         <v>538</v>
       </c>
@@ -11888,10 +11927,10 @@
         <v>541</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C23"/>
     </row>
-    <row r="25" spans="1:12" ht="22.5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" ht="23.25" x14ac:dyDescent="0.2">
       <c r="A25" s="21" t="s">
         <v>550</v>
       </c>
@@ -11907,7 +11946,7 @@
       <c r="K25" s="21"/>
       <c r="L25" s="21"/>
     </row>
-    <row r="27" spans="1:12" ht="56" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" ht="57" x14ac:dyDescent="0.2">
       <c r="A27" s="7" t="s">
         <v>0</v>
       </c>
@@ -11945,7 +11984,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B28" t="s">
         <v>533</v>
       </c>
@@ -11971,7 +12010,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C31" s="15" t="s">
         <v>545</v>
       </c>
@@ -11980,7 +12019,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C32" s="4" t="s">
         <v>539</v>
       </c>
@@ -11988,7 +12027,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="33" spans="3:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="3:5" x14ac:dyDescent="0.2">
       <c r="C33" t="s">
         <v>537</v>
       </c>
@@ -11996,7 +12035,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="34" spans="3:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="3:5" x14ac:dyDescent="0.2">
       <c r="C34" t="s">
         <v>538</v>
       </c>
@@ -12012,7 +12051,7 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H15 H27 H4">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H15 H27 H4" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"VB编程,系统运维,WEB学习,游戏碎片,日常随笔"</formula1>
     </dataValidation>
   </dataValidations>

--- a/11_付费课程/99.资料/文章信息备忘表.xlsx
+++ b/11_付费课程/99.资料/文章信息备忘表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Writing\11_付费课程\99.资料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{650F0901-E4C6-4FCC-950F-BC7EB8E9289D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBE7341E-8142-4610-8489-0E916DF27E84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="870" yWindow="-120" windowWidth="19740" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1578" uniqueCount="1150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1581" uniqueCount="1152">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -4586,6 +4586,14 @@
   </si>
   <si>
     <t>85749508</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1126</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>64214780</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -11084,9 +11092,18 @@
       </c>
     </row>
     <row r="221" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B221" s="4" t="s">
+        <v>1150</v>
+      </c>
+      <c r="H221" s="1" t="s">
+        <v>21</v>
+      </c>
       <c r="J221" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>00</v>
+        <v>001126</v>
+      </c>
+      <c r="L221" s="2" t="s">
+        <v>1151</v>
       </c>
     </row>
     <row r="222" spans="2:12" x14ac:dyDescent="0.2">

--- a/11_付费课程/99.资料/文章信息备忘表.xlsx
+++ b/11_付费课程/99.资料/文章信息备忘表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Writing\11_付费课程\99.资料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBE7341E-8142-4610-8489-0E916DF27E84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B6F78E6-A3F8-4C6C-A6C7-577E31090883}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="870" yWindow="-120" windowWidth="19740" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1581" uniqueCount="1152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1582" uniqueCount="1153">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -4594,6 +4594,10 @@
   </si>
   <si>
     <t>64214780</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>免费开源的虚拟机系统 XCP-ng ，没听说过就对了！</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -11091,9 +11095,12 @@
         <v>1149</v>
       </c>
     </row>
-    <row r="221" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="221" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B221" s="4" t="s">
         <v>1150</v>
+      </c>
+      <c r="C221" s="1" t="s">
+        <v>1152</v>
       </c>
       <c r="H221" s="1" t="s">
         <v>21</v>

--- a/11_付费课程/99.资料/文章信息备忘表.xlsx
+++ b/11_付费课程/99.资料/文章信息备忘表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Writing\11_付费课程\99.资料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B6F78E6-A3F8-4C6C-A6C7-577E31090883}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEFD7D38-B207-4A86-BCA3-E087F2025308}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="870" yWindow="-120" windowWidth="19740" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1582" uniqueCount="1153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1585" uniqueCount="1155">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -4598,6 +4598,14 @@
   </si>
   <si>
     <t>免费开源的虚拟机系统 XCP-ng ，没听说过就对了！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1127</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>18248068</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -11110,13 +11118,22 @@
         <v>001126</v>
       </c>
       <c r="L221" s="2" t="s">
-        <v>1151</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="222" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B222" s="4" t="s">
+        <v>1153</v>
+      </c>
+      <c r="H222" s="1" t="s">
+        <v>58</v>
+      </c>
       <c r="J222" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>00</v>
+        <v>001127</v>
+      </c>
+      <c r="L222" s="2" t="s">
+        <v>1151</v>
       </c>
     </row>
     <row r="223" spans="2:12" x14ac:dyDescent="0.2">

--- a/11_付费课程/99.资料/文章信息备忘表.xlsx
+++ b/11_付费课程/99.资料/文章信息备忘表.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Writing\11_付费课程\99.资料\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\writing\11_付费课程\99.资料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEFD7D38-B207-4A86-BCA3-E087F2025308}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="870" yWindow="-120" windowWidth="19740" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1910" yWindow="-120" windowWidth="19740" windowHeight="11760"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$L$4</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -40,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1585" uniqueCount="1155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1587" uniqueCount="1157">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -4606,13 +4605,21 @@
   </si>
   <si>
     <t>18248068</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-01-27 09:23:45</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>543290</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -5104,25 +5111,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A2:M317"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.25" style="8" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="4" customWidth="1"/>
-    <col min="3" max="3" width="30.875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="5.375" style="6" customWidth="1"/>
-    <col min="5" max="6" width="5.125" style="6" customWidth="1"/>
+    <col min="2" max="2" width="5.58203125" style="4" customWidth="1"/>
+    <col min="3" max="3" width="30.83203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="5.33203125" style="6" customWidth="1"/>
+    <col min="5" max="6" width="5.08203125" style="6" customWidth="1"/>
     <col min="7" max="7" width="5.25" style="6" customWidth="1"/>
     <col min="8" max="8" width="13.5" style="1" customWidth="1"/>
     <col min="9" max="9" width="19" style="4" customWidth="1"/>
-    <col min="10" max="10" width="8.625" style="5" customWidth="1"/>
+    <col min="10" max="10" width="8.58203125" style="5" customWidth="1"/>
     <col min="11" max="11" width="7.5" style="3" customWidth="1"/>
     <col min="12" max="12" width="9.25" style="2" customWidth="1"/>
     <col min="13" max="13" width="16.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" ht="25" x14ac:dyDescent="0.3">
       <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
@@ -5138,8 +5145,8 @@
       <c r="K2" s="20"/>
       <c r="L2" s="20"/>
     </row>
-    <row r="3" spans="1:12" ht="6.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="4" spans="1:12" s="7" customFormat="1" ht="57" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12" ht="6.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:12" s="7" customFormat="1" ht="56" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>0</v>
       </c>
@@ -5177,7 +5184,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
         <v>557</v>
       </c>
@@ -5204,7 +5211,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
         <v>559</v>
       </c>
@@ -5240,7 +5247,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
         <v>559</v>
       </c>
@@ -5276,25 +5283,25 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="J8" s="5" t="str">
         <f t="shared" si="0"/>
         <v>000</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="J9" s="5" t="str">
         <f t="shared" si="0"/>
         <v>000</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="J10" s="5" t="str">
         <f t="shared" si="0"/>
         <v>000</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
         <v>522</v>
       </c>
@@ -5327,7 +5334,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
         <v>558</v>
       </c>
@@ -5357,7 +5364,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A13" s="8" t="s">
         <v>558</v>
       </c>
@@ -5387,7 +5394,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A14" s="8" t="s">
         <v>640</v>
       </c>
@@ -5414,7 +5421,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="8" t="s">
         <v>557</v>
       </c>
@@ -5441,7 +5448,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="8" t="s">
         <v>557</v>
       </c>
@@ -5468,7 +5475,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="8" t="s">
         <v>557</v>
       </c>
@@ -5495,7 +5502,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="8" t="s">
         <v>767</v>
       </c>
@@ -5522,7 +5529,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
         <v>557</v>
       </c>
@@ -5549,7 +5556,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A20" s="8" t="s">
         <v>557</v>
       </c>
@@ -5576,7 +5583,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A21" s="8" t="s">
         <v>557</v>
       </c>
@@ -5603,7 +5610,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A22" s="8" t="s">
         <v>559</v>
       </c>
@@ -5639,7 +5646,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" s="8" t="s">
         <v>557</v>
       </c>
@@ -5666,7 +5673,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A24" s="8" t="s">
         <v>558</v>
       </c>
@@ -5696,7 +5703,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A25" s="8" t="s">
         <v>557</v>
       </c>
@@ -5723,7 +5730,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A26" s="8" t="s">
         <v>557</v>
       </c>
@@ -5750,7 +5757,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="27" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A27" s="8" t="s">
         <v>633</v>
       </c>
@@ -5777,7 +5784,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A28" s="8" t="s">
         <v>557</v>
       </c>
@@ -5804,7 +5811,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A29" s="8" t="s">
         <v>559</v>
       </c>
@@ -5840,7 +5847,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A30" s="8" t="s">
         <v>559</v>
       </c>
@@ -5876,7 +5883,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A31" s="8" t="s">
         <v>557</v>
       </c>
@@ -5903,7 +5910,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A32" s="8" t="s">
         <v>557</v>
       </c>
@@ -5930,7 +5937,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A33" s="8" t="s">
         <v>557</v>
       </c>
@@ -5957,7 +5964,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="34" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A34" s="8" t="s">
         <v>557</v>
       </c>
@@ -5984,7 +5991,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="35" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A35" s="8" t="s">
         <v>557</v>
       </c>
@@ -6011,7 +6018,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="36" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A36" s="8" t="s">
         <v>557</v>
       </c>
@@ -6038,7 +6045,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="37" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A37" s="8" t="s">
         <v>559</v>
       </c>
@@ -6074,7 +6081,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="38" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A38" s="8" t="s">
         <v>557</v>
       </c>
@@ -6101,7 +6108,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" s="8" t="s">
         <v>557</v>
       </c>
@@ -6128,7 +6135,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="40" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A40" s="8" t="s">
         <v>557</v>
       </c>
@@ -6155,7 +6162,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="41" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A41" s="8" t="s">
         <v>557</v>
       </c>
@@ -6182,7 +6189,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="42" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A42" s="8" t="s">
         <v>557</v>
       </c>
@@ -6209,7 +6216,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="43" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A43" s="8" t="s">
         <v>559</v>
       </c>
@@ -6242,7 +6249,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="44" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A44" s="8" t="s">
         <v>557</v>
       </c>
@@ -6269,7 +6276,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="45" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A45" s="8" t="s">
         <v>557</v>
       </c>
@@ -6296,7 +6303,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="46" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A46" s="8" t="s">
         <v>557</v>
       </c>
@@ -6323,7 +6330,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" s="8" t="s">
         <v>557</v>
       </c>
@@ -6350,7 +6357,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="48" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A48" s="8" t="s">
         <v>557</v>
       </c>
@@ -6377,7 +6384,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="49" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A49" s="8" t="s">
         <v>557</v>
       </c>
@@ -6404,7 +6411,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="50" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A50" s="8" t="s">
         <v>557</v>
       </c>
@@ -6431,7 +6438,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" s="8" t="s">
         <v>557</v>
       </c>
@@ -6458,7 +6465,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="52" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A52" s="8" t="s">
         <v>557</v>
       </c>
@@ -6485,7 +6492,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" s="8" t="s">
         <v>557</v>
       </c>
@@ -6512,7 +6519,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="54" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A54" s="8" t="s">
         <v>557</v>
       </c>
@@ -6539,7 +6546,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" s="8" t="s">
         <v>557</v>
       </c>
@@ -6566,7 +6573,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="56" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A56" s="8" t="s">
         <v>559</v>
       </c>
@@ -6602,7 +6609,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="57" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A57" s="8" t="s">
         <v>559</v>
       </c>
@@ -6638,7 +6645,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="58" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A58" s="8" t="s">
         <v>557</v>
       </c>
@@ -6665,7 +6672,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="59" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A59" s="8" t="s">
         <v>558</v>
       </c>
@@ -6695,7 +6702,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="60" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A60" s="8" t="s">
         <v>557</v>
       </c>
@@ -6722,7 +6729,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="61" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B61" s="4" t="s">
         <v>298</v>
       </c>
@@ -6755,7 +6762,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="62" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B62" s="4" t="s">
         <v>294</v>
       </c>
@@ -6788,7 +6795,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="63" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B63" s="4" t="s">
         <v>289</v>
       </c>
@@ -6821,7 +6828,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="64" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A64" s="8" t="s">
         <v>557</v>
       </c>
@@ -6848,7 +6855,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="65" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A65" s="8" t="s">
         <v>557</v>
       </c>
@@ -6875,7 +6882,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="66" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A66" s="8" t="s">
         <v>559</v>
       </c>
@@ -6911,7 +6918,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="67" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A67" s="8" t="s">
         <v>557</v>
       </c>
@@ -6938,7 +6945,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="68" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A68" s="8" t="s">
         <v>558</v>
       </c>
@@ -6968,7 +6975,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="69" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A69" s="8" t="s">
         <v>559</v>
       </c>
@@ -6995,7 +7002,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="70" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A70" s="8" t="s">
         <v>559</v>
       </c>
@@ -7022,7 +7029,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="71" spans="1:12" ht="57" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:12" ht="56" x14ac:dyDescent="0.3">
       <c r="A71" s="8" t="s">
         <v>558</v>
       </c>
@@ -7052,7 +7059,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="72" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A72" s="8" t="s">
         <v>558</v>
       </c>
@@ -7082,7 +7089,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="73" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A73" s="8" t="s">
         <v>558</v>
       </c>
@@ -7112,7 +7119,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="74" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A74" s="8" t="s">
         <v>557</v>
       </c>
@@ -7139,7 +7146,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="75" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A75" s="8" t="s">
         <v>557</v>
       </c>
@@ -7166,7 +7173,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="76" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A76" s="8" t="s">
         <v>558</v>
       </c>
@@ -7199,7 +7206,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="77" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A77" s="8" t="s">
         <v>557</v>
       </c>
@@ -7226,7 +7233,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="78" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A78" s="8" t="s">
         <v>558</v>
       </c>
@@ -7253,7 +7260,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="79" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A79" s="8" t="s">
         <v>557</v>
       </c>
@@ -7280,7 +7287,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="80" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A80" s="8" t="s">
         <v>558</v>
       </c>
@@ -7307,7 +7314,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="81" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A81" s="8" t="s">
         <v>557</v>
       </c>
@@ -7334,7 +7341,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="82" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A82" s="8" t="s">
         <v>557</v>
       </c>
@@ -7361,7 +7368,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="83" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A83" s="8" t="s">
         <v>557</v>
       </c>
@@ -7388,7 +7395,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="84" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A84" s="8" t="s">
         <v>557</v>
       </c>
@@ -7415,7 +7422,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="85" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A85" s="8" t="s">
         <v>558</v>
       </c>
@@ -7442,7 +7449,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="86" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A86" s="8" t="s">
         <v>557</v>
       </c>
@@ -7469,7 +7476,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="87" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A87" s="8" t="s">
         <v>559</v>
       </c>
@@ -7505,7 +7512,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="88" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A88" s="8" t="s">
         <v>559</v>
       </c>
@@ -7541,7 +7548,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="89" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A89" s="8" t="s">
         <v>559</v>
       </c>
@@ -7577,7 +7584,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="90" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A90" s="8" t="s">
         <v>557</v>
       </c>
@@ -7604,7 +7611,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="91" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B91" s="4" t="s">
         <v>151</v>
       </c>
@@ -7637,7 +7644,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="92" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B92" s="4" t="s">
         <v>146</v>
       </c>
@@ -7670,7 +7677,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="93" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B93" s="4" t="s">
         <v>140</v>
       </c>
@@ -7703,7 +7710,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="94" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B94" s="4" t="s">
         <v>135</v>
       </c>
@@ -7736,7 +7743,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="95" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A95" s="8" t="s">
         <v>558</v>
       </c>
@@ -7763,7 +7770,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="96" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="B96" s="4" t="s">
         <v>123</v>
       </c>
@@ -7796,7 +7803,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="97" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B97" s="4" t="s">
         <v>118</v>
       </c>
@@ -7829,7 +7836,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="98" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="B98" s="4" t="s">
         <v>112</v>
       </c>
@@ -7862,7 +7869,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="99" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B99" s="4" t="s">
         <v>109</v>
       </c>
@@ -7895,7 +7902,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="100" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B100" s="4" t="s">
         <v>104</v>
       </c>
@@ -7928,7 +7935,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="101" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="B101" s="4" t="s">
         <v>98</v>
       </c>
@@ -7961,7 +7968,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="102" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B102" s="4" t="s">
         <v>92</v>
       </c>
@@ -7994,7 +8001,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="103" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A103" s="8" t="s">
         <v>559</v>
       </c>
@@ -8030,7 +8037,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="104" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A104" s="8" t="s">
         <v>557</v>
       </c>
@@ -8057,7 +8064,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="105" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A105" s="8" t="s">
         <v>557</v>
       </c>
@@ -8084,7 +8091,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="106" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A106" s="8" t="s">
         <v>557</v>
       </c>
@@ -8111,7 +8118,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="107" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A107" s="8" t="s">
         <v>557</v>
       </c>
@@ -8138,7 +8145,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="108" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A108" s="8" t="s">
         <v>557</v>
       </c>
@@ -8165,7 +8172,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="109" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A109" s="8" t="s">
         <v>559</v>
       </c>
@@ -8201,7 +8208,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A110" s="8" t="s">
         <v>558</v>
       </c>
@@ -8228,7 +8235,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="111" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A111" s="8" t="s">
         <v>557</v>
       </c>
@@ -8255,7 +8262,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="112" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A112" s="8" t="s">
         <v>557</v>
       </c>
@@ -8282,7 +8289,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="113" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A113" s="8" t="s">
         <v>557</v>
       </c>
@@ -8309,7 +8316,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A114" s="8" t="s">
         <v>557</v>
       </c>
@@ -8336,7 +8343,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="115" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A115" s="8" t="s">
         <v>557</v>
       </c>
@@ -8363,7 +8370,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="116" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A116" s="8" t="s">
         <v>559</v>
       </c>
@@ -8399,7 +8406,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="117" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A117" s="8" t="s">
         <v>557</v>
       </c>
@@ -8426,7 +8433,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="118" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A118" s="8" t="s">
         <v>558</v>
       </c>
@@ -8456,7 +8463,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="119" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A119" s="8" t="s">
         <v>557</v>
       </c>
@@ -8483,7 +8490,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="120" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A120" s="8" t="s">
         <v>557</v>
       </c>
@@ -8510,7 +8517,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="121" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A121" s="8" t="s">
         <v>597</v>
       </c>
@@ -8537,7 +8544,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="122" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A122" s="8" t="s">
         <v>602</v>
       </c>
@@ -8564,7 +8571,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="123" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A123" s="8" t="s">
         <v>608</v>
       </c>
@@ -8591,7 +8598,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="124" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A124" s="8" t="s">
         <v>611</v>
       </c>
@@ -8618,7 +8625,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="125" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A125" s="8" t="s">
         <v>617</v>
       </c>
@@ -8645,7 +8652,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="126" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A126" s="8" t="s">
         <v>624</v>
       </c>
@@ -8672,7 +8679,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="127" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A127" s="8" t="s">
         <v>557</v>
       </c>
@@ -8699,7 +8706,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="128" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A128" s="8" t="s">
         <v>649</v>
       </c>
@@ -8726,7 +8733,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="129" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A129" s="8" t="s">
         <v>653</v>
       </c>
@@ -8753,7 +8760,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="130" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A130" s="8" t="s">
         <v>659</v>
       </c>
@@ -8780,7 +8787,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="131" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A131" s="8" t="s">
         <v>664</v>
       </c>
@@ -8807,7 +8814,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A132" s="8" t="s">
         <v>557</v>
       </c>
@@ -8834,7 +8841,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="133" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A133" s="8" t="s">
         <v>557</v>
       </c>
@@ -8861,7 +8868,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="134" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A134" s="8" t="s">
         <v>681</v>
       </c>
@@ -8888,7 +8895,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="135" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A135" s="8" t="s">
         <v>687</v>
       </c>
@@ -8915,7 +8922,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="136" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A136" s="8" t="s">
         <v>691</v>
       </c>
@@ -8942,7 +8949,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="137" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A137" s="8" t="s">
         <v>699</v>
       </c>
@@ -8969,7 +8976,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="138" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A138" s="8" t="s">
         <v>704</v>
       </c>
@@ -8996,7 +9003,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="139" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A139" s="8" t="s">
         <v>711</v>
       </c>
@@ -9023,7 +9030,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="140" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A140" s="8" t="s">
         <v>716</v>
       </c>
@@ -9050,7 +9057,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="141" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A141" s="8" t="s">
         <v>724</v>
       </c>
@@ -9077,7 +9084,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="142" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A142" s="8" t="s">
         <v>727</v>
       </c>
@@ -9104,7 +9111,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="143" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A143" s="8" t="s">
         <v>736</v>
       </c>
@@ -9131,7 +9138,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="144" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A144" s="8" t="s">
         <v>740</v>
       </c>
@@ -9158,7 +9165,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="145" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A145" s="8" t="s">
         <v>746</v>
       </c>
@@ -9185,7 +9192,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="146" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A146" s="8" t="s">
         <v>754</v>
       </c>
@@ -9212,7 +9219,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="147" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A147" s="8" t="s">
         <v>759</v>
       </c>
@@ -9239,7 +9246,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="148" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A148" s="8" t="s">
         <v>770</v>
       </c>
@@ -9266,7 +9273,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="149" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A149" s="8" t="s">
         <v>777</v>
       </c>
@@ -9293,7 +9300,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="150" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A150" s="8" t="s">
         <v>782</v>
       </c>
@@ -9320,7 +9327,7 @@
         <v>786</v>
       </c>
     </row>
-    <row r="151" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A151" s="8" t="s">
         <v>557</v>
       </c>
@@ -9347,7 +9354,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="152" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A152" s="8" t="s">
         <v>795</v>
       </c>
@@ -9374,7 +9381,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A153" s="8" t="s">
         <v>800</v>
       </c>
@@ -9401,7 +9408,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A154" s="8" t="s">
         <v>804</v>
       </c>
@@ -9428,7 +9435,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A155" s="8" t="s">
         <v>811</v>
       </c>
@@ -9455,7 +9462,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="156" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A156" s="8" t="s">
         <v>557</v>
       </c>
@@ -9482,7 +9489,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A157" s="8" t="s">
         <v>557</v>
       </c>
@@ -9509,7 +9516,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A158" s="8" t="s">
         <v>827</v>
       </c>
@@ -9536,7 +9543,7 @@
         <v>831</v>
       </c>
     </row>
-    <row r="159" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A159" s="8" t="s">
         <v>557</v>
       </c>
@@ -9563,7 +9570,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A160" s="8" t="s">
         <v>838</v>
       </c>
@@ -9590,7 +9597,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="161" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A161" s="8" t="s">
         <v>557</v>
       </c>
@@ -9617,7 +9624,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A162" s="8" t="s">
         <v>850</v>
       </c>
@@ -9644,7 +9651,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A163" s="8" t="s">
         <v>857</v>
       </c>
@@ -9671,7 +9678,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A164" s="8" t="s">
         <v>557</v>
       </c>
@@ -9698,7 +9705,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="165" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A165" s="8" t="s">
         <v>557</v>
       </c>
@@ -9725,7 +9732,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A166" s="8" t="s">
         <v>557</v>
       </c>
@@ -9752,7 +9759,7 @@
         <v>871</v>
       </c>
     </row>
-    <row r="167" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A167" s="8" t="s">
         <v>557</v>
       </c>
@@ -9779,7 +9786,7 @@
         <v>879</v>
       </c>
     </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A168" s="8" t="s">
         <v>557</v>
       </c>
@@ -9806,7 +9813,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A169" s="8" t="s">
         <v>557</v>
       </c>
@@ -9833,7 +9840,7 @@
         <v>889</v>
       </c>
     </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A170" s="8" t="s">
         <v>557</v>
       </c>
@@ -9860,7 +9867,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A171" s="8" t="s">
         <v>557</v>
       </c>
@@ -9887,7 +9894,7 @@
         <v>897</v>
       </c>
     </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A172" s="8" t="s">
         <v>902</v>
       </c>
@@ -9914,7 +9921,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A173" s="8" t="s">
         <v>902</v>
       </c>
@@ -9941,7 +9948,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A174" s="8" t="s">
         <v>557</v>
       </c>
@@ -9968,7 +9975,7 @@
         <v>915</v>
       </c>
     </row>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A175" s="8" t="s">
         <v>557</v>
       </c>
@@ -9995,7 +10002,7 @@
         <v>919</v>
       </c>
     </row>
-    <row r="176" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A176" s="8" t="s">
         <v>557</v>
       </c>
@@ -10022,7 +10029,7 @@
         <v>925</v>
       </c>
     </row>
-    <row r="177" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A177" s="8" t="s">
         <v>557</v>
       </c>
@@ -10049,7 +10056,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="178" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:13" ht="28" x14ac:dyDescent="0.3">
       <c r="A178" s="8" t="s">
         <v>557</v>
       </c>
@@ -10076,7 +10083,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="179" spans="1:13" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:13" ht="42" x14ac:dyDescent="0.3">
       <c r="A179" s="8" t="s">
         <v>938</v>
       </c>
@@ -10103,7 +10110,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="180" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B180" s="4" t="s">
         <v>942</v>
       </c>
@@ -10127,7 +10134,7 @@
         <v>946</v>
       </c>
     </row>
-    <row r="181" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:13" ht="28" x14ac:dyDescent="0.3">
       <c r="B181" s="4" t="s">
         <v>948</v>
       </c>
@@ -10151,7 +10158,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="182" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:13" ht="28" x14ac:dyDescent="0.3">
       <c r="B182" s="4" t="s">
         <v>954</v>
       </c>
@@ -10175,7 +10182,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="183" spans="1:13" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:13" ht="42" x14ac:dyDescent="0.3">
       <c r="B183" s="4" t="s">
         <v>959</v>
       </c>
@@ -10199,7 +10206,7 @@
         <v>960</v>
       </c>
     </row>
-    <row r="184" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:13" ht="28" x14ac:dyDescent="0.3">
       <c r="B184" s="4" t="s">
         <v>966</v>
       </c>
@@ -10223,7 +10230,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="185" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:13" ht="28" x14ac:dyDescent="0.3">
       <c r="B185" s="4" t="s">
         <v>971</v>
       </c>
@@ -10247,7 +10254,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="186" spans="1:13" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:13" ht="42" x14ac:dyDescent="0.3">
       <c r="B186" s="4" t="s">
         <v>976</v>
       </c>
@@ -10271,7 +10278,7 @@
         <v>963</v>
       </c>
     </row>
-    <row r="187" spans="1:13" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:13" ht="42" x14ac:dyDescent="0.3">
       <c r="B187" s="4" t="s">
         <v>979</v>
       </c>
@@ -10295,7 +10302,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="188" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:13" ht="28" x14ac:dyDescent="0.3">
       <c r="B188" s="4" t="s">
         <v>985</v>
       </c>
@@ -10322,7 +10329,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="189" spans="1:13" ht="15" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:13" ht="15.5" x14ac:dyDescent="0.3">
       <c r="B189" s="4" t="s">
         <v>988</v>
       </c>
@@ -10347,7 +10354,7 @@
       </c>
       <c r="M189" s="6"/>
     </row>
-    <row r="190" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:13" ht="28" x14ac:dyDescent="0.3">
       <c r="B190" s="4" t="s">
         <v>992</v>
       </c>
@@ -10371,7 +10378,7 @@
         <v>982</v>
       </c>
     </row>
-    <row r="191" spans="1:13" ht="45" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:13" ht="46.5" x14ac:dyDescent="0.3">
       <c r="B191" s="4" t="s">
         <v>1002</v>
       </c>
@@ -10395,7 +10402,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="192" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:13" ht="28" x14ac:dyDescent="0.3">
       <c r="B192" s="4" t="s">
         <v>1006</v>
       </c>
@@ -10419,7 +10426,7 @@
         <v>998</v>
       </c>
     </row>
-    <row r="193" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="193" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B193" s="4" t="s">
         <v>1010</v>
       </c>
@@ -10443,7 +10450,7 @@
         <v>1011</v>
       </c>
     </row>
-    <row r="194" spans="2:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="194" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B194" s="4" t="s">
         <v>1015</v>
       </c>
@@ -10470,7 +10477,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="195" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="195" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B195" s="4" t="s">
         <v>1021</v>
       </c>
@@ -10494,7 +10501,7 @@
         <v>1019</v>
       </c>
     </row>
-    <row r="196" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="196" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B196" s="4" t="s">
         <v>1025</v>
       </c>
@@ -10518,7 +10525,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="197" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="197" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B197" s="4" t="s">
         <v>1031</v>
       </c>
@@ -10542,7 +10549,7 @@
         <v>1033</v>
       </c>
     </row>
-    <row r="198" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="198" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B198" s="4" t="s">
         <v>1034</v>
       </c>
@@ -10566,7 +10573,7 @@
         <v>1035</v>
       </c>
     </row>
-    <row r="199" spans="2:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="199" spans="2:12" ht="42" x14ac:dyDescent="0.3">
       <c r="B199" s="4" t="s">
         <v>1040</v>
       </c>
@@ -10590,7 +10597,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="200" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="200" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B200" s="4" t="s">
         <v>1045</v>
       </c>
@@ -10614,7 +10621,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="201" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="201" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B201" s="4" t="s">
         <v>1051</v>
       </c>
@@ -10638,7 +10645,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="202" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="202" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B202" s="4" t="s">
         <v>1058</v>
       </c>
@@ -10662,7 +10669,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="203" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="203" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B203" s="4" t="s">
         <v>1062</v>
       </c>
@@ -10686,7 +10693,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="204" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="204" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B204" s="4" t="s">
         <v>1065</v>
       </c>
@@ -10710,7 +10717,7 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="205" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="205" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B205" s="4" t="s">
         <v>1071</v>
       </c>
@@ -10734,7 +10741,7 @@
         <v>1069</v>
       </c>
     </row>
-    <row r="206" spans="2:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="206" spans="2:12" ht="42" x14ac:dyDescent="0.3">
       <c r="B206" s="4" t="s">
         <v>1074</v>
       </c>
@@ -10758,7 +10765,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="207" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="207" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B207" s="4" t="s">
         <v>1080</v>
       </c>
@@ -10782,7 +10789,7 @@
         <v>1079</v>
       </c>
     </row>
-    <row r="208" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="208" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B208" s="4" t="s">
         <v>1082</v>
       </c>
@@ -10806,7 +10813,7 @@
         <v>1081</v>
       </c>
     </row>
-    <row r="209" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="209" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B209" s="4" t="s">
         <v>1091</v>
       </c>
@@ -10830,7 +10837,7 @@
         <v>1089</v>
       </c>
     </row>
-    <row r="210" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="210" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B210" s="4" t="s">
         <v>1093</v>
       </c>
@@ -10854,7 +10861,7 @@
         <v>1092</v>
       </c>
     </row>
-    <row r="211" spans="2:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="211" spans="2:12" ht="42" x14ac:dyDescent="0.3">
       <c r="B211" s="4" t="s">
         <v>1102</v>
       </c>
@@ -10878,7 +10885,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="212" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="212" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B212" s="4" t="s">
         <v>1105</v>
       </c>
@@ -10902,7 +10909,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="213" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="213" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B213" s="4" t="s">
         <v>1110</v>
       </c>
@@ -10926,7 +10933,7 @@
         <v>1109</v>
       </c>
     </row>
-    <row r="214" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="214" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B214" s="4" t="s">
         <v>1118</v>
       </c>
@@ -10953,7 +10960,7 @@
         <v>1114</v>
       </c>
     </row>
-    <row r="215" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="215" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B215" s="4" t="s">
         <v>1121</v>
       </c>
@@ -10977,7 +10984,7 @@
         <v>1116</v>
       </c>
     </row>
-    <row r="216" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="216" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B216" s="4" t="s">
         <v>1126</v>
       </c>
@@ -11004,7 +11011,7 @@
         <v>1131</v>
       </c>
     </row>
-    <row r="217" spans="2:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="217" spans="2:12" ht="42" x14ac:dyDescent="0.3">
       <c r="B217" s="4" t="s">
         <v>1134</v>
       </c>
@@ -11028,7 +11035,7 @@
         <v>1113</v>
       </c>
     </row>
-    <row r="218" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="218" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B218" s="4" t="s">
         <v>1137</v>
       </c>
@@ -11055,7 +11062,7 @@
         <v>1132</v>
       </c>
     </row>
-    <row r="219" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="219" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B219" s="4" t="s">
         <v>1142</v>
       </c>
@@ -11079,7 +11086,7 @@
         <v>1120</v>
       </c>
     </row>
-    <row r="220" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="220" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B220" s="4" t="s">
         <v>1145</v>
       </c>
@@ -11103,7 +11110,7 @@
         <v>1149</v>
       </c>
     </row>
-    <row r="221" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="221" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B221" s="4" t="s">
         <v>1150</v>
       </c>
@@ -11112,16 +11119,22 @@
       </c>
       <c r="H221" s="1" t="s">
         <v>21</v>
+      </c>
+      <c r="I221" s="4" t="s">
+        <v>1155</v>
       </c>
       <c r="J221" s="5" t="str">
         <f t="shared" si="5"/>
         <v>001126</v>
       </c>
+      <c r="K221" s="3" t="s">
+        <v>1156</v>
+      </c>
       <c r="L221" s="2" t="s">
         <v>1154</v>
       </c>
     </row>
-    <row r="222" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="222" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B222" s="4" t="s">
         <v>1153</v>
       </c>
@@ -11136,578 +11149,578 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="223" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="223" spans="2:12" x14ac:dyDescent="0.3">
       <c r="J223" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="224" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="224" spans="2:12" x14ac:dyDescent="0.3">
       <c r="J224" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="225" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="225" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J225" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="226" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="226" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J226" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="227" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="227" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J227" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="228" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="228" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J228" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="229" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="229" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J229" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="230" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="230" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J230" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="231" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="231" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J231" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="232" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="232" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J232" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="233" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="233" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J233" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="234" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="234" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J234" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="235" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="235" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J235" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="236" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="236" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J236" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="237" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="237" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J237" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="238" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="238" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J238" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="239" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="239" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J239" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="240" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="240" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J240" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="241" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="241" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J241" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="242" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="242" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J242" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="243" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="243" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J243" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="244" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="244" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J244" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="245" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="245" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J245" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="246" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="246" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J246" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="247" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="247" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J247" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="248" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="248" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J248" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="249" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="249" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J249" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="250" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="250" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J250" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="251" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="251" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J251" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="252" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="252" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J252" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="253" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="253" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J253" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="254" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="254" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J254" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="255" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="255" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J255" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="256" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="256" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J256" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="257" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="257" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J257" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="258" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="258" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J258" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="259" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="259" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J259" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="260" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="260" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J260" s="5" t="str">
         <f t="shared" ref="J260:J317" si="7">"00"&amp;B260</f>
         <v>00</v>
       </c>
     </row>
-    <row r="261" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="261" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J261" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="262" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="262" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J262" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="263" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="263" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J263" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="264" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="264" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J264" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="265" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="265" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J265" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="266" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="266" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J266" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="267" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="267" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J267" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="268" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="268" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J268" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="269" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="269" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J269" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="270" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="270" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J270" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="271" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="271" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J271" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="272" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="272" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J272" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="273" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="273" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J273" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="274" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="274" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J274" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="275" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="275" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J275" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="276" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="276" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J276" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="277" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="277" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J277" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="278" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="278" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J278" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="279" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="279" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J279" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="280" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="280" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J280" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="281" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="281" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J281" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="282" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="282" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J282" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="283" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="283" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J283" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="284" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="284" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J284" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="285" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="285" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J285" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="286" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="286" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J286" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="287" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="287" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J287" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="288" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="288" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J288" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="289" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="289" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J289" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="290" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="290" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J290" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="291" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="291" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J291" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="292" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="292" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J292" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="293" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="293" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J293" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="294" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="294" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J294" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="295" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="295" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J295" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="296" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="296" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J296" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="297" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="297" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J297" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="298" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="298" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J298" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="299" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="299" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J299" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="300" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="300" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J300" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="301" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="301" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J301" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="302" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="302" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J302" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="303" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="303" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J303" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="304" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="304" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J304" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="305" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="305" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J305" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="306" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="306" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J306" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="307" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="307" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J307" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="308" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="308" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J308" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="309" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="309" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J309" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="310" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="310" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J310" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="311" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="311" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J311" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="312" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="312" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J312" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="313" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="313" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J313" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="314" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="314" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J314" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="315" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="315" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J315" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="316" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="316" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J316" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="317" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="317" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J317" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:L4" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A4:L4"/>
   <mergeCells count="1">
     <mergeCell ref="A2:L2"/>
   </mergeCells>
@@ -11719,10 +11732,10 @@
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1:E1 D3:E3 D6:E1048576" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1:E1 D3:E3 D6:E1048576">
       <formula1>"是,否"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H1 H3:H1048576" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H1 H3:H1048576">
       <formula1>"VB编程,系统运维,WEB学习,游戏碎片,日常随笔,浥尘伙伴社团"</formula1>
     </dataValidation>
   </dataValidations>
@@ -11732,20 +11745,20 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A2:L34"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="6.375" customWidth="1"/>
+    <col min="2" max="2" width="6.33203125" customWidth="1"/>
     <col min="3" max="3" width="34" style="4" customWidth="1"/>
     <col min="4" max="4" width="4.75" customWidth="1"/>
-    <col min="8" max="8" width="6.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.83203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="19" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="7.125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="7.08203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.08203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:12" ht="23.25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
         <v>549</v>
       </c>
@@ -11761,7 +11774,7 @@
       <c r="K2" s="21"/>
       <c r="L2" s="21"/>
     </row>
-    <row r="4" spans="1:12" ht="57" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12" ht="56" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>0</v>
       </c>
@@ -11799,7 +11812,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>533</v>
       </c>
@@ -11822,7 +11835,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C8" s="15" t="s">
         <v>545</v>
       </c>
@@ -11831,7 +11844,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C9" s="4" t="s">
         <v>539</v>
       </c>
@@ -11839,7 +11852,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C10" t="s">
         <v>537</v>
       </c>
@@ -11847,7 +11860,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C11" t="s">
         <v>538</v>
       </c>
@@ -11855,7 +11868,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="23.25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A13" s="21" t="s">
         <v>543</v>
       </c>
@@ -11871,7 +11884,7 @@
       <c r="K13" s="21"/>
       <c r="L13" s="21"/>
     </row>
-    <row r="15" spans="1:12" ht="57" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:12" ht="56" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
         <v>0</v>
       </c>
@@ -11909,7 +11922,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>533</v>
       </c>
@@ -11935,7 +11948,7 @@
         <v>54837657</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C19" s="15" t="s">
         <v>545</v>
       </c>
@@ -11944,7 +11957,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C20" s="4" t="s">
         <v>539</v>
       </c>
@@ -11952,7 +11965,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C21" t="s">
         <v>537</v>
       </c>
@@ -11960,7 +11973,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C22" t="s">
         <v>538</v>
       </c>
@@ -11968,10 +11981,10 @@
         <v>541</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C23"/>
     </row>
-    <row r="25" spans="1:12" ht="23.25" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:12" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A25" s="21" t="s">
         <v>550</v>
       </c>
@@ -11987,7 +12000,7 @@
       <c r="K25" s="21"/>
       <c r="L25" s="21"/>
     </row>
-    <row r="27" spans="1:12" ht="57" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:12" ht="56" x14ac:dyDescent="0.3">
       <c r="A27" s="7" t="s">
         <v>0</v>
       </c>
@@ -12025,7 +12038,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
         <v>533</v>
       </c>
@@ -12051,7 +12064,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C31" s="15" t="s">
         <v>545</v>
       </c>
@@ -12060,7 +12073,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C32" s="4" t="s">
         <v>539</v>
       </c>
@@ -12068,7 +12081,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="33" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="33" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C33" t="s">
         <v>537</v>
       </c>
@@ -12076,7 +12089,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="34" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="34" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C34" t="s">
         <v>538</v>
       </c>
@@ -12092,7 +12105,7 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H15 H27 H4" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H15 H27 H4">
       <formula1>"VB编程,系统运维,WEB学习,游戏碎片,日常随笔"</formula1>
     </dataValidation>
   </dataValidations>

--- a/11_付费课程/99.资料/文章信息备忘表.xlsx
+++ b/11_付费课程/99.资料/文章信息备忘表.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\writing\11_付费课程\99.资料\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Writing\11_付费课程\99.资料\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{637F0D3D-D8EB-4E92-B101-CD50C1844BEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1910" yWindow="-120" windowWidth="19740" windowHeight="11760"/>
+    <workbookView xWindow="870" yWindow="-120" windowWidth="19740" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,7 +19,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$L$4</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1587" uniqueCount="1157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1590" uniqueCount="1160">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -4613,13 +4614,25 @@
   </si>
   <si>
     <t>543290</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-02-10 08:26:10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>拔网线也挡不住玩游戏的热情，PDF文档里边都能玩游戏？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>016280</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -5111,25 +5124,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:M317"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.25" style="8" customWidth="1"/>
-    <col min="2" max="2" width="5.58203125" style="4" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="5.33203125" style="6" customWidth="1"/>
-    <col min="5" max="6" width="5.08203125" style="6" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="30.875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="5.375" style="6" customWidth="1"/>
+    <col min="5" max="6" width="5.125" style="6" customWidth="1"/>
     <col min="7" max="7" width="5.25" style="6" customWidth="1"/>
     <col min="8" max="8" width="13.5" style="1" customWidth="1"/>
     <col min="9" max="9" width="19" style="4" customWidth="1"/>
-    <col min="10" max="10" width="8.58203125" style="5" customWidth="1"/>
+    <col min="10" max="10" width="8.625" style="5" customWidth="1"/>
     <col min="11" max="11" width="7.5" style="3" customWidth="1"/>
     <col min="12" max="12" width="9.25" style="2" customWidth="1"/>
     <col min="13" max="13" width="16.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:12" ht="25" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
@@ -5145,8 +5158,8 @@
       <c r="K2" s="20"/>
       <c r="L2" s="20"/>
     </row>
-    <row r="3" spans="1:12" ht="6.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="4" spans="1:12" s="7" customFormat="1" ht="56" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" ht="6.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="4" spans="1:12" s="7" customFormat="1" ht="57" x14ac:dyDescent="0.2">
       <c r="A4" s="7" t="s">
         <v>0</v>
       </c>
@@ -5184,7 +5197,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
         <v>557</v>
       </c>
@@ -5211,7 +5224,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
         <v>559</v>
       </c>
@@ -5247,7 +5260,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="8" t="s">
         <v>559</v>
       </c>
@@ -5283,25 +5296,25 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="J8" s="5" t="str">
         <f t="shared" si="0"/>
         <v>000</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="J9" s="5" t="str">
         <f t="shared" si="0"/>
         <v>000</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="J10" s="5" t="str">
         <f t="shared" si="0"/>
         <v>000</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B11" s="4" t="s">
         <v>522</v>
       </c>
@@ -5334,7 +5347,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A12" s="8" t="s">
         <v>558</v>
       </c>
@@ -5364,7 +5377,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A13" s="8" t="s">
         <v>558</v>
       </c>
@@ -5394,7 +5407,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A14" s="8" t="s">
         <v>640</v>
       </c>
@@ -5421,7 +5434,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" s="8" t="s">
         <v>557</v>
       </c>
@@ -5448,7 +5461,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" s="8" t="s">
         <v>557</v>
       </c>
@@ -5475,7 +5488,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" s="8" t="s">
         <v>557</v>
       </c>
@@ -5502,7 +5515,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" s="8" t="s">
         <v>767</v>
       </c>
@@ -5529,7 +5542,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A19" s="8" t="s">
         <v>557</v>
       </c>
@@ -5556,7 +5569,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A20" s="8" t="s">
         <v>557</v>
       </c>
@@ -5583,7 +5596,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A21" s="8" t="s">
         <v>557</v>
       </c>
@@ -5610,7 +5623,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A22" s="8" t="s">
         <v>559</v>
       </c>
@@ -5646,7 +5659,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23" s="8" t="s">
         <v>557</v>
       </c>
@@ -5673,7 +5686,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A24" s="8" t="s">
         <v>558</v>
       </c>
@@ -5703,7 +5716,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A25" s="8" t="s">
         <v>557</v>
       </c>
@@ -5730,7 +5743,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A26" s="8" t="s">
         <v>557</v>
       </c>
@@ -5757,7 +5770,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="27" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A27" s="8" t="s">
         <v>633</v>
       </c>
@@ -5784,7 +5797,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A28" s="8" t="s">
         <v>557</v>
       </c>
@@ -5811,7 +5824,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A29" s="8" t="s">
         <v>559</v>
       </c>
@@ -5847,7 +5860,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A30" s="8" t="s">
         <v>559</v>
       </c>
@@ -5883,7 +5896,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A31" s="8" t="s">
         <v>557</v>
       </c>
@@ -5910,7 +5923,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A32" s="8" t="s">
         <v>557</v>
       </c>
@@ -5937,7 +5950,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A33" s="8" t="s">
         <v>557</v>
       </c>
@@ -5964,7 +5977,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="34" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A34" s="8" t="s">
         <v>557</v>
       </c>
@@ -5991,7 +6004,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="35" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A35" s="8" t="s">
         <v>557</v>
       </c>
@@ -6018,7 +6031,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="36" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A36" s="8" t="s">
         <v>557</v>
       </c>
@@ -6045,7 +6058,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="37" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A37" s="8" t="s">
         <v>559</v>
       </c>
@@ -6081,7 +6094,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="38" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A38" s="8" t="s">
         <v>557</v>
       </c>
@@ -6108,7 +6121,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A39" s="8" t="s">
         <v>557</v>
       </c>
@@ -6135,7 +6148,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="40" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A40" s="8" t="s">
         <v>557</v>
       </c>
@@ -6162,7 +6175,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="41" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A41" s="8" t="s">
         <v>557</v>
       </c>
@@ -6189,7 +6202,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="42" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A42" s="8" t="s">
         <v>557</v>
       </c>
@@ -6216,7 +6229,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="43" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A43" s="8" t="s">
         <v>559</v>
       </c>
@@ -6249,7 +6262,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="44" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A44" s="8" t="s">
         <v>557</v>
       </c>
@@ -6276,7 +6289,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="45" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A45" s="8" t="s">
         <v>557</v>
       </c>
@@ -6303,7 +6316,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="46" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A46" s="8" t="s">
         <v>557</v>
       </c>
@@ -6330,7 +6343,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A47" s="8" t="s">
         <v>557</v>
       </c>
@@ -6357,7 +6370,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="48" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A48" s="8" t="s">
         <v>557</v>
       </c>
@@ -6384,7 +6397,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="49" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A49" s="8" t="s">
         <v>557</v>
       </c>
@@ -6411,7 +6424,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="50" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A50" s="8" t="s">
         <v>557</v>
       </c>
@@ -6438,7 +6451,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A51" s="8" t="s">
         <v>557</v>
       </c>
@@ -6465,7 +6478,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="52" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A52" s="8" t="s">
         <v>557</v>
       </c>
@@ -6492,7 +6505,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A53" s="8" t="s">
         <v>557</v>
       </c>
@@ -6519,7 +6532,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="54" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A54" s="8" t="s">
         <v>557</v>
       </c>
@@ -6546,7 +6559,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A55" s="8" t="s">
         <v>557</v>
       </c>
@@ -6573,7 +6586,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="56" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A56" s="8" t="s">
         <v>559</v>
       </c>
@@ -6609,7 +6622,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="57" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A57" s="8" t="s">
         <v>559</v>
       </c>
@@ -6645,7 +6658,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="58" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A58" s="8" t="s">
         <v>557</v>
       </c>
@@ -6672,7 +6685,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="59" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A59" s="8" t="s">
         <v>558</v>
       </c>
@@ -6702,7 +6715,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="60" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A60" s="8" t="s">
         <v>557</v>
       </c>
@@ -6729,7 +6742,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="61" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B61" s="4" t="s">
         <v>298</v>
       </c>
@@ -6762,7 +6775,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="62" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B62" s="4" t="s">
         <v>294</v>
       </c>
@@ -6795,7 +6808,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="63" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B63" s="4" t="s">
         <v>289</v>
       </c>
@@ -6828,7 +6841,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="64" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A64" s="8" t="s">
         <v>557</v>
       </c>
@@ -6855,7 +6868,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="65" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A65" s="8" t="s">
         <v>557</v>
       </c>
@@ -6882,7 +6895,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="66" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A66" s="8" t="s">
         <v>559</v>
       </c>
@@ -6918,7 +6931,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="67" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A67" s="8" t="s">
         <v>557</v>
       </c>
@@ -6945,7 +6958,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="68" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A68" s="8" t="s">
         <v>558</v>
       </c>
@@ -6975,7 +6988,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="69" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A69" s="8" t="s">
         <v>559</v>
       </c>
@@ -7002,7 +7015,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="70" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A70" s="8" t="s">
         <v>559</v>
       </c>
@@ -7029,7 +7042,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="71" spans="1:12" ht="56" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:12" ht="57" x14ac:dyDescent="0.2">
       <c r="A71" s="8" t="s">
         <v>558</v>
       </c>
@@ -7059,7 +7072,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="72" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A72" s="8" t="s">
         <v>558</v>
       </c>
@@ -7089,7 +7102,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="73" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A73" s="8" t="s">
         <v>558</v>
       </c>
@@ -7119,7 +7132,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="74" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A74" s="8" t="s">
         <v>557</v>
       </c>
@@ -7146,7 +7159,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="75" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A75" s="8" t="s">
         <v>557</v>
       </c>
@@ -7173,7 +7186,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="76" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A76" s="8" t="s">
         <v>558</v>
       </c>
@@ -7206,7 +7219,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="77" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A77" s="8" t="s">
         <v>557</v>
       </c>
@@ -7233,7 +7246,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="78" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A78" s="8" t="s">
         <v>558</v>
       </c>
@@ -7260,7 +7273,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="79" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A79" s="8" t="s">
         <v>557</v>
       </c>
@@ -7287,7 +7300,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="80" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A80" s="8" t="s">
         <v>558</v>
       </c>
@@ -7314,7 +7327,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="81" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A81" s="8" t="s">
         <v>557</v>
       </c>
@@ -7341,7 +7354,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="82" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A82" s="8" t="s">
         <v>557</v>
       </c>
@@ -7368,7 +7381,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="83" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A83" s="8" t="s">
         <v>557</v>
       </c>
@@ -7395,7 +7408,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="84" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A84" s="8" t="s">
         <v>557</v>
       </c>
@@ -7422,7 +7435,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="85" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A85" s="8" t="s">
         <v>558</v>
       </c>
@@ -7449,7 +7462,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="86" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A86" s="8" t="s">
         <v>557</v>
       </c>
@@ -7476,7 +7489,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="87" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A87" s="8" t="s">
         <v>559</v>
       </c>
@@ -7512,7 +7525,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="88" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A88" s="8" t="s">
         <v>559</v>
       </c>
@@ -7548,7 +7561,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="89" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A89" s="8" t="s">
         <v>559</v>
       </c>
@@ -7584,7 +7597,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="90" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A90" s="8" t="s">
         <v>557</v>
       </c>
@@ -7611,7 +7624,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="91" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B91" s="4" t="s">
         <v>151</v>
       </c>
@@ -7644,7 +7657,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="92" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B92" s="4" t="s">
         <v>146</v>
       </c>
@@ -7677,7 +7690,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="93" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B93" s="4" t="s">
         <v>140</v>
       </c>
@@ -7710,7 +7723,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="94" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B94" s="4" t="s">
         <v>135</v>
       </c>
@@ -7743,7 +7756,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="95" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A95" s="8" t="s">
         <v>558</v>
       </c>
@@ -7770,7 +7783,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="96" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B96" s="4" t="s">
         <v>123</v>
       </c>
@@ -7803,7 +7816,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="97" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B97" s="4" t="s">
         <v>118</v>
       </c>
@@ -7836,7 +7849,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="98" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B98" s="4" t="s">
         <v>112</v>
       </c>
@@ -7869,7 +7882,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="99" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B99" s="4" t="s">
         <v>109</v>
       </c>
@@ -7902,7 +7915,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="100" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B100" s="4" t="s">
         <v>104</v>
       </c>
@@ -7935,7 +7948,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="101" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B101" s="4" t="s">
         <v>98</v>
       </c>
@@ -7968,7 +7981,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="102" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B102" s="4" t="s">
         <v>92</v>
       </c>
@@ -8001,7 +8014,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="103" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A103" s="8" t="s">
         <v>559</v>
       </c>
@@ -8037,7 +8050,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="104" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A104" s="8" t="s">
         <v>557</v>
       </c>
@@ -8064,7 +8077,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="105" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A105" s="8" t="s">
         <v>557</v>
       </c>
@@ -8091,7 +8104,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="106" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A106" s="8" t="s">
         <v>557</v>
       </c>
@@ -8118,7 +8131,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="107" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A107" s="8" t="s">
         <v>557</v>
       </c>
@@ -8145,7 +8158,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="108" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A108" s="8" t="s">
         <v>557</v>
       </c>
@@ -8172,7 +8185,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="109" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A109" s="8" t="s">
         <v>559</v>
       </c>
@@ -8208,7 +8221,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A110" s="8" t="s">
         <v>558</v>
       </c>
@@ -8235,7 +8248,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="111" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A111" s="8" t="s">
         <v>557</v>
       </c>
@@ -8262,7 +8275,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A112" s="8" t="s">
         <v>557</v>
       </c>
@@ -8289,7 +8302,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="113" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A113" s="8" t="s">
         <v>557</v>
       </c>
@@ -8316,7 +8329,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A114" s="8" t="s">
         <v>557</v>
       </c>
@@ -8343,7 +8356,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="115" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A115" s="8" t="s">
         <v>557</v>
       </c>
@@ -8370,7 +8383,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="116" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A116" s="8" t="s">
         <v>559</v>
       </c>
@@ -8406,7 +8419,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="117" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A117" s="8" t="s">
         <v>557</v>
       </c>
@@ -8433,7 +8446,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="118" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A118" s="8" t="s">
         <v>558</v>
       </c>
@@ -8463,7 +8476,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="119" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A119" s="8" t="s">
         <v>557</v>
       </c>
@@ -8490,7 +8503,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="120" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A120" s="8" t="s">
         <v>557</v>
       </c>
@@ -8517,7 +8530,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="121" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A121" s="8" t="s">
         <v>597</v>
       </c>
@@ -8544,7 +8557,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="122" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A122" s="8" t="s">
         <v>602</v>
       </c>
@@ -8571,7 +8584,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="123" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A123" s="8" t="s">
         <v>608</v>
       </c>
@@ -8598,7 +8611,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="124" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A124" s="8" t="s">
         <v>611</v>
       </c>
@@ -8625,7 +8638,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="125" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A125" s="8" t="s">
         <v>617</v>
       </c>
@@ -8652,7 +8665,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="126" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A126" s="8" t="s">
         <v>624</v>
       </c>
@@ -8679,7 +8692,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="127" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A127" s="8" t="s">
         <v>557</v>
       </c>
@@ -8706,7 +8719,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="128" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A128" s="8" t="s">
         <v>649</v>
       </c>
@@ -8733,7 +8746,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="129" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A129" s="8" t="s">
         <v>653</v>
       </c>
@@ -8760,7 +8773,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="130" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A130" s="8" t="s">
         <v>659</v>
       </c>
@@ -8787,7 +8800,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="131" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A131" s="8" t="s">
         <v>664</v>
       </c>
@@ -8814,7 +8827,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A132" s="8" t="s">
         <v>557</v>
       </c>
@@ -8841,7 +8854,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="133" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A133" s="8" t="s">
         <v>557</v>
       </c>
@@ -8868,7 +8881,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="134" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A134" s="8" t="s">
         <v>681</v>
       </c>
@@ -8895,7 +8908,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="135" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A135" s="8" t="s">
         <v>687</v>
       </c>
@@ -8922,7 +8935,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="136" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A136" s="8" t="s">
         <v>691</v>
       </c>
@@ -8949,7 +8962,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="137" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A137" s="8" t="s">
         <v>699</v>
       </c>
@@ -8976,7 +8989,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="138" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A138" s="8" t="s">
         <v>704</v>
       </c>
@@ -9003,7 +9016,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="139" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A139" s="8" t="s">
         <v>711</v>
       </c>
@@ -9030,7 +9043,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="140" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A140" s="8" t="s">
         <v>716</v>
       </c>
@@ -9057,7 +9070,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="141" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A141" s="8" t="s">
         <v>724</v>
       </c>
@@ -9084,7 +9097,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="142" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A142" s="8" t="s">
         <v>727</v>
       </c>
@@ -9111,7 +9124,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="143" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A143" s="8" t="s">
         <v>736</v>
       </c>
@@ -9138,7 +9151,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="144" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A144" s="8" t="s">
         <v>740</v>
       </c>
@@ -9165,7 +9178,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="145" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A145" s="8" t="s">
         <v>746</v>
       </c>
@@ -9192,7 +9205,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="146" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A146" s="8" t="s">
         <v>754</v>
       </c>
@@ -9219,7 +9232,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="147" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A147" s="8" t="s">
         <v>759</v>
       </c>
@@ -9246,7 +9259,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="148" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A148" s="8" t="s">
         <v>770</v>
       </c>
@@ -9273,7 +9286,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="149" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A149" s="8" t="s">
         <v>777</v>
       </c>
@@ -9300,7 +9313,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="150" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A150" s="8" t="s">
         <v>782</v>
       </c>
@@ -9327,7 +9340,7 @@
         <v>786</v>
       </c>
     </row>
-    <row r="151" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A151" s="8" t="s">
         <v>557</v>
       </c>
@@ -9354,7 +9367,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="152" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A152" s="8" t="s">
         <v>795</v>
       </c>
@@ -9381,7 +9394,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A153" s="8" t="s">
         <v>800</v>
       </c>
@@ -9408,7 +9421,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A154" s="8" t="s">
         <v>804</v>
       </c>
@@ -9435,7 +9448,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A155" s="8" t="s">
         <v>811</v>
       </c>
@@ -9462,7 +9475,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="156" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A156" s="8" t="s">
         <v>557</v>
       </c>
@@ -9489,7 +9502,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A157" s="8" t="s">
         <v>557</v>
       </c>
@@ -9516,7 +9529,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A158" s="8" t="s">
         <v>827</v>
       </c>
@@ -9543,7 +9556,7 @@
         <v>831</v>
       </c>
     </row>
-    <row r="159" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A159" s="8" t="s">
         <v>557</v>
       </c>
@@ -9570,7 +9583,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A160" s="8" t="s">
         <v>838</v>
       </c>
@@ -9597,7 +9610,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="161" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A161" s="8" t="s">
         <v>557</v>
       </c>
@@ -9624,7 +9637,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A162" s="8" t="s">
         <v>850</v>
       </c>
@@ -9651,7 +9664,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A163" s="8" t="s">
         <v>857</v>
       </c>
@@ -9678,7 +9691,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A164" s="8" t="s">
         <v>557</v>
       </c>
@@ -9705,7 +9718,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="165" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A165" s="8" t="s">
         <v>557</v>
       </c>
@@ -9732,7 +9745,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A166" s="8" t="s">
         <v>557</v>
       </c>
@@ -9759,7 +9772,7 @@
         <v>871</v>
       </c>
     </row>
-    <row r="167" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A167" s="8" t="s">
         <v>557</v>
       </c>
@@ -9786,7 +9799,7 @@
         <v>879</v>
       </c>
     </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A168" s="8" t="s">
         <v>557</v>
       </c>
@@ -9813,7 +9826,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A169" s="8" t="s">
         <v>557</v>
       </c>
@@ -9840,7 +9853,7 @@
         <v>889</v>
       </c>
     </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A170" s="8" t="s">
         <v>557</v>
       </c>
@@ -9867,7 +9880,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A171" s="8" t="s">
         <v>557</v>
       </c>
@@ -9894,7 +9907,7 @@
         <v>897</v>
       </c>
     </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A172" s="8" t="s">
         <v>902</v>
       </c>
@@ -9921,7 +9934,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A173" s="8" t="s">
         <v>902</v>
       </c>
@@ -9948,7 +9961,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A174" s="8" t="s">
         <v>557</v>
       </c>
@@ -9975,7 +9988,7 @@
         <v>915</v>
       </c>
     </row>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A175" s="8" t="s">
         <v>557</v>
       </c>
@@ -10002,7 +10015,7 @@
         <v>919</v>
       </c>
     </row>
-    <row r="176" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A176" s="8" t="s">
         <v>557</v>
       </c>
@@ -10029,7 +10042,7 @@
         <v>925</v>
       </c>
     </row>
-    <row r="177" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A177" s="8" t="s">
         <v>557</v>
       </c>
@@ -10056,7 +10069,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="178" spans="1:13" ht="28" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A178" s="8" t="s">
         <v>557</v>
       </c>
@@ -10083,7 +10096,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="179" spans="1:13" ht="42" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:13" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A179" s="8" t="s">
         <v>938</v>
       </c>
@@ -10110,7 +10123,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="180" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B180" s="4" t="s">
         <v>942</v>
       </c>
@@ -10134,7 +10147,7 @@
         <v>946</v>
       </c>
     </row>
-    <row r="181" spans="1:13" ht="28" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B181" s="4" t="s">
         <v>948</v>
       </c>
@@ -10158,7 +10171,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="182" spans="1:13" ht="28" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B182" s="4" t="s">
         <v>954</v>
       </c>
@@ -10182,7 +10195,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="183" spans="1:13" ht="42" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:13" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B183" s="4" t="s">
         <v>959</v>
       </c>
@@ -10206,7 +10219,7 @@
         <v>960</v>
       </c>
     </row>
-    <row r="184" spans="1:13" ht="28" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B184" s="4" t="s">
         <v>966</v>
       </c>
@@ -10230,7 +10243,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="185" spans="1:13" ht="28" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B185" s="4" t="s">
         <v>971</v>
       </c>
@@ -10254,7 +10267,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="186" spans="1:13" ht="42" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:13" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B186" s="4" t="s">
         <v>976</v>
       </c>
@@ -10278,7 +10291,7 @@
         <v>963</v>
       </c>
     </row>
-    <row r="187" spans="1:13" ht="42" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:13" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B187" s="4" t="s">
         <v>979</v>
       </c>
@@ -10302,7 +10315,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="188" spans="1:13" ht="28" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B188" s="4" t="s">
         <v>985</v>
       </c>
@@ -10329,7 +10342,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="189" spans="1:13" ht="15.5" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:13" ht="15" x14ac:dyDescent="0.2">
       <c r="B189" s="4" t="s">
         <v>988</v>
       </c>
@@ -10354,7 +10367,7 @@
       </c>
       <c r="M189" s="6"/>
     </row>
-    <row r="190" spans="1:13" ht="28" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B190" s="4" t="s">
         <v>992</v>
       </c>
@@ -10378,7 +10391,7 @@
         <v>982</v>
       </c>
     </row>
-    <row r="191" spans="1:13" ht="46.5" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:13" ht="45" x14ac:dyDescent="0.2">
       <c r="B191" s="4" t="s">
         <v>1002</v>
       </c>
@@ -10402,7 +10415,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="192" spans="1:13" ht="28" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B192" s="4" t="s">
         <v>1006</v>
       </c>
@@ -10426,7 +10439,7 @@
         <v>998</v>
       </c>
     </row>
-    <row r="193" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="193" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B193" s="4" t="s">
         <v>1010</v>
       </c>
@@ -10450,7 +10463,7 @@
         <v>1011</v>
       </c>
     </row>
-    <row r="194" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="194" spans="2:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B194" s="4" t="s">
         <v>1015</v>
       </c>
@@ -10477,7 +10490,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="195" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="195" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B195" s="4" t="s">
         <v>1021</v>
       </c>
@@ -10501,7 +10514,7 @@
         <v>1019</v>
       </c>
     </row>
-    <row r="196" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="196" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B196" s="4" t="s">
         <v>1025</v>
       </c>
@@ -10525,7 +10538,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="197" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="197" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B197" s="4" t="s">
         <v>1031</v>
       </c>
@@ -10549,7 +10562,7 @@
         <v>1033</v>
       </c>
     </row>
-    <row r="198" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="198" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B198" s="4" t="s">
         <v>1034</v>
       </c>
@@ -10573,7 +10586,7 @@
         <v>1035</v>
       </c>
     </row>
-    <row r="199" spans="2:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="199" spans="2:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B199" s="4" t="s">
         <v>1040</v>
       </c>
@@ -10597,7 +10610,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="200" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="200" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B200" s="4" t="s">
         <v>1045</v>
       </c>
@@ -10621,7 +10634,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="201" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="201" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B201" s="4" t="s">
         <v>1051</v>
       </c>
@@ -10645,7 +10658,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="202" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="202" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B202" s="4" t="s">
         <v>1058</v>
       </c>
@@ -10669,7 +10682,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="203" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="203" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B203" s="4" t="s">
         <v>1062</v>
       </c>
@@ -10693,7 +10706,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="204" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="204" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B204" s="4" t="s">
         <v>1065</v>
       </c>
@@ -10717,7 +10730,7 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="205" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="205" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B205" s="4" t="s">
         <v>1071</v>
       </c>
@@ -10741,7 +10754,7 @@
         <v>1069</v>
       </c>
     </row>
-    <row r="206" spans="2:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="206" spans="2:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B206" s="4" t="s">
         <v>1074</v>
       </c>
@@ -10765,7 +10778,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="207" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="207" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B207" s="4" t="s">
         <v>1080</v>
       </c>
@@ -10789,7 +10802,7 @@
         <v>1079</v>
       </c>
     </row>
-    <row r="208" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="208" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B208" s="4" t="s">
         <v>1082</v>
       </c>
@@ -10813,7 +10826,7 @@
         <v>1081</v>
       </c>
     </row>
-    <row r="209" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="209" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B209" s="4" t="s">
         <v>1091</v>
       </c>
@@ -10837,7 +10850,7 @@
         <v>1089</v>
       </c>
     </row>
-    <row r="210" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="210" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B210" s="4" t="s">
         <v>1093</v>
       </c>
@@ -10861,7 +10874,7 @@
         <v>1092</v>
       </c>
     </row>
-    <row r="211" spans="2:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="211" spans="2:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B211" s="4" t="s">
         <v>1102</v>
       </c>
@@ -10885,7 +10898,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="212" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="212" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B212" s="4" t="s">
         <v>1105</v>
       </c>
@@ -10909,7 +10922,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="213" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="213" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B213" s="4" t="s">
         <v>1110</v>
       </c>
@@ -10933,7 +10946,7 @@
         <v>1109</v>
       </c>
     </row>
-    <row r="214" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="214" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B214" s="4" t="s">
         <v>1118</v>
       </c>
@@ -10960,7 +10973,7 @@
         <v>1114</v>
       </c>
     </row>
-    <row r="215" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="215" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B215" s="4" t="s">
         <v>1121</v>
       </c>
@@ -10984,7 +10997,7 @@
         <v>1116</v>
       </c>
     </row>
-    <row r="216" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="216" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B216" s="4" t="s">
         <v>1126</v>
       </c>
@@ -11011,7 +11024,7 @@
         <v>1131</v>
       </c>
     </row>
-    <row r="217" spans="2:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="217" spans="2:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B217" s="4" t="s">
         <v>1134</v>
       </c>
@@ -11035,7 +11048,7 @@
         <v>1113</v>
       </c>
     </row>
-    <row r="218" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="218" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B218" s="4" t="s">
         <v>1137</v>
       </c>
@@ -11062,7 +11075,7 @@
         <v>1132</v>
       </c>
     </row>
-    <row r="219" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="219" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B219" s="4" t="s">
         <v>1142</v>
       </c>
@@ -11086,7 +11099,7 @@
         <v>1120</v>
       </c>
     </row>
-    <row r="220" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="220" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B220" s="4" t="s">
         <v>1145</v>
       </c>
@@ -11110,7 +11123,7 @@
         <v>1149</v>
       </c>
     </row>
-    <row r="221" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="221" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B221" s="4" t="s">
         <v>1150</v>
       </c>
@@ -11134,593 +11147,602 @@
         <v>1154</v>
       </c>
     </row>
-    <row r="222" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="222" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B222" s="4" t="s">
         <v>1153</v>
       </c>
+      <c r="C222" s="1" t="s">
+        <v>1158</v>
+      </c>
       <c r="H222" s="1" t="s">
         <v>58</v>
+      </c>
+      <c r="I222" s="4" t="s">
+        <v>1157</v>
       </c>
       <c r="J222" s="5" t="str">
         <f t="shared" si="5"/>
         <v>001127</v>
       </c>
+      <c r="K222" s="3" t="s">
+        <v>1159</v>
+      </c>
       <c r="L222" s="2" t="s">
         <v>1151</v>
       </c>
     </row>
-    <row r="223" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="223" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J223" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="224" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="224" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J224" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="225" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="225" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J225" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="226" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="226" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J226" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="227" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="227" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J227" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="228" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="228" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J228" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="229" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="229" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J229" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="230" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="230" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J230" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="231" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="231" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J231" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="232" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="232" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J232" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="233" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="233" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J233" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="234" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="234" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J234" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="235" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="235" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J235" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="236" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="236" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J236" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="237" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="237" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J237" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="238" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="238" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J238" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="239" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="239" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J239" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="240" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="240" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J240" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="241" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="241" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J241" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="242" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="242" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J242" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="243" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="243" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J243" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="244" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="244" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J244" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="245" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="245" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J245" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="246" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="246" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J246" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="247" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="247" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J247" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="248" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="248" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J248" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="249" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="249" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J249" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="250" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="250" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J250" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="251" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="251" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J251" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="252" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="252" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J252" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="253" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="253" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J253" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="254" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="254" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J254" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="255" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="255" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J255" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="256" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="256" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J256" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="257" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="257" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J257" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="258" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="258" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J258" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="259" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="259" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J259" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="260" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="260" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J260" s="5" t="str">
         <f t="shared" ref="J260:J317" si="7">"00"&amp;B260</f>
         <v>00</v>
       </c>
     </row>
-    <row r="261" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="261" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J261" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="262" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="262" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J262" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="263" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="263" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J263" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="264" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="264" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J264" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="265" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="265" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J265" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="266" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="266" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J266" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="267" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="267" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J267" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="268" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="268" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J268" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="269" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="269" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J269" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="270" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="270" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J270" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="271" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="271" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J271" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="272" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="272" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J272" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="273" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="273" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J273" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="274" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="274" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J274" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="275" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="275" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J275" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="276" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="276" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J276" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="277" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="277" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J277" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="278" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="278" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J278" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="279" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="279" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J279" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="280" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="280" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J280" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="281" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="281" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J281" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="282" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="282" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J282" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="283" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="283" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J283" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="284" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="284" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J284" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="285" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="285" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J285" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="286" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="286" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J286" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="287" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="287" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J287" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="288" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="288" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J288" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="289" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="289" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J289" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="290" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="290" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J290" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="291" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="291" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J291" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="292" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="292" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J292" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="293" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="293" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J293" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="294" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="294" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J294" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="295" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="295" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J295" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="296" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="296" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J296" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="297" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="297" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J297" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="298" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="298" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J298" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="299" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="299" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J299" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="300" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="300" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J300" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="301" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="301" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J301" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="302" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="302" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J302" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="303" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="303" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J303" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="304" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="304" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J304" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="305" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="305" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J305" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="306" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="306" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J306" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="307" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="307" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J307" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="308" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="308" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J308" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="309" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="309" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J309" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="310" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="310" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J310" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="311" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="311" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J311" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="312" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="312" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J312" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="313" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="313" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J313" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="314" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="314" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J314" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="315" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="315" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J315" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="316" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="316" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J316" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
-    <row r="317" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="317" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J317" s="5" t="str">
         <f t="shared" si="7"/>
         <v>00</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:L4"/>
+  <autoFilter ref="A4:L4" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="1">
     <mergeCell ref="A2:L2"/>
   </mergeCells>
@@ -11732,10 +11754,10 @@
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1:E1 D3:E3 D6:E1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1:E1 D3:E3 D6:E1048576" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"是,否"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H1 H3:H1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H1 H3:H1048576" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"VB编程,系统运维,WEB学习,游戏碎片,日常随笔,浥尘伙伴社团"</formula1>
     </dataValidation>
   </dataValidations>
@@ -11745,20 +11767,20 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A2:L34"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="6.33203125" customWidth="1"/>
+    <col min="2" max="2" width="6.375" customWidth="1"/>
     <col min="3" max="3" width="34" style="4" customWidth="1"/>
     <col min="4" max="4" width="4.75" customWidth="1"/>
-    <col min="8" max="8" width="6.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="19" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="7.08203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.08203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:12" ht="22.5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" ht="23.25" x14ac:dyDescent="0.2">
       <c r="A2" s="21" t="s">
         <v>549</v>
       </c>
@@ -11774,7 +11796,7 @@
       <c r="K2" s="21"/>
       <c r="L2" s="21"/>
     </row>
-    <row r="4" spans="1:12" ht="56" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" ht="57" x14ac:dyDescent="0.2">
       <c r="A4" s="7" t="s">
         <v>0</v>
       </c>
@@ -11812,7 +11834,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
         <v>533</v>
       </c>
@@ -11835,7 +11857,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C8" s="15" t="s">
         <v>545</v>
       </c>
@@ -11844,7 +11866,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C9" s="4" t="s">
         <v>539</v>
       </c>
@@ -11852,7 +11874,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C10" t="s">
         <v>537</v>
       </c>
@@ -11860,7 +11882,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C11" t="s">
         <v>538</v>
       </c>
@@ -11868,7 +11890,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="22.5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" ht="23.25" x14ac:dyDescent="0.2">
       <c r="A13" s="21" t="s">
         <v>543</v>
       </c>
@@ -11884,7 +11906,7 @@
       <c r="K13" s="21"/>
       <c r="L13" s="21"/>
     </row>
-    <row r="15" spans="1:12" ht="56" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" ht="57" x14ac:dyDescent="0.2">
       <c r="A15" s="7" t="s">
         <v>0</v>
       </c>
@@ -11922,7 +11944,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
         <v>533</v>
       </c>
@@ -11948,7 +11970,7 @@
         <v>54837657</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C19" s="15" t="s">
         <v>545</v>
       </c>
@@ -11957,7 +11979,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C20" s="4" t="s">
         <v>539</v>
       </c>
@@ -11965,7 +11987,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C21" t="s">
         <v>537</v>
       </c>
@@ -11973,7 +11995,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C22" t="s">
         <v>538</v>
       </c>
@@ -11981,10 +12003,10 @@
         <v>541</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C23"/>
     </row>
-    <row r="25" spans="1:12" ht="22.5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" ht="23.25" x14ac:dyDescent="0.2">
       <c r="A25" s="21" t="s">
         <v>550</v>
       </c>
@@ -12000,7 +12022,7 @@
       <c r="K25" s="21"/>
       <c r="L25" s="21"/>
     </row>
-    <row r="27" spans="1:12" ht="56" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" ht="57" x14ac:dyDescent="0.2">
       <c r="A27" s="7" t="s">
         <v>0</v>
       </c>
@@ -12038,7 +12060,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B28" t="s">
         <v>533</v>
       </c>
@@ -12064,7 +12086,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C31" s="15" t="s">
         <v>545</v>
       </c>
@@ -12073,7 +12095,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C32" s="4" t="s">
         <v>539</v>
       </c>
@@ -12081,7 +12103,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="33" spans="3:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="3:5" x14ac:dyDescent="0.2">
       <c r="C33" t="s">
         <v>537</v>
       </c>
@@ -12089,7 +12111,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="34" spans="3:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="3:5" x14ac:dyDescent="0.2">
       <c r="C34" t="s">
         <v>538</v>
       </c>
@@ -12105,7 +12127,7 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H15 H27 H4">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H15 H27 H4" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"VB编程,系统运维,WEB学习,游戏碎片,日常随笔"</formula1>
     </dataValidation>
   </dataValidations>

--- a/11_付费课程/99.资料/文章信息备忘表.xlsx
+++ b/11_付费课程/99.资料/文章信息备忘表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Writing\11_付费课程\99.资料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{637F0D3D-D8EB-4E92-B101-CD50C1844BEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7F71585-362D-4BA5-9547-B749C7462779}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="870" yWindow="-120" windowWidth="19740" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1590" uniqueCount="1160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1594" uniqueCount="1163">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -4626,6 +4626,18 @@
   </si>
   <si>
     <t>016280</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>49455856</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1128</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cRARk</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -11172,9 +11184,21 @@
       </c>
     </row>
     <row r="223" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B223" s="4" t="s">
+        <v>1161</v>
+      </c>
+      <c r="C223" s="1" t="s">
+        <v>1162</v>
+      </c>
+      <c r="H223" s="1" t="s">
+        <v>654</v>
+      </c>
       <c r="J223" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>00</v>
+        <v>001128</v>
+      </c>
+      <c r="L223" s="2" t="s">
+        <v>1160</v>
       </c>
     </row>
     <row r="224" spans="2:12" x14ac:dyDescent="0.2">

--- a/11_付费课程/99.资料/文章信息备忘表.xlsx
+++ b/11_付费课程/99.资料/文章信息备忘表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Writing\11_付费课程\99.资料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7F71585-362D-4BA5-9547-B749C7462779}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7D153FD-7812-4F13-B724-6296CC20CBF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="870" yWindow="-120" windowWidth="19740" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4637,7 +4637,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>cRARk</t>
+    <t>最近接一私活，破解WinRAR和7-zip密码，还好我有cRARk</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -11183,7 +11183,7 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="223" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="223" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B223" s="4" t="s">
         <v>1161</v>
       </c>

--- a/11_付费课程/99.资料/文章信息备忘表.xlsx
+++ b/11_付费课程/99.资料/文章信息备忘表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Writing\11_付费课程\99.资料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7D153FD-7812-4F13-B724-6296CC20CBF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6EF902D-D89B-4D35-811B-F4FF2F2DD4C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="870" yWindow="-120" windowWidth="19740" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1594" uniqueCount="1163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1596" uniqueCount="1165">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -4638,6 +4638,14 @@
   </si>
   <si>
     <t>最近接一私活，破解WinRAR和7-zip密码，还好我有cRARk</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-02-24 08:44:24</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>424480</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -11193,9 +11201,15 @@
       <c r="H223" s="1" t="s">
         <v>654</v>
       </c>
+      <c r="I223" s="4" t="s">
+        <v>1163</v>
+      </c>
       <c r="J223" s="5" t="str">
         <f t="shared" si="5"/>
         <v>001128</v>
+      </c>
+      <c r="K223" s="3" t="s">
+        <v>1164</v>
       </c>
       <c r="L223" s="2" t="s">
         <v>1160</v>

--- a/11_付费课程/99.资料/文章信息备忘表.xlsx
+++ b/11_付费课程/99.资料/文章信息备忘表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Writing\11_付费课程\99.资料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6EF902D-D89B-4D35-811B-F4FF2F2DD4C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AFF232E-673D-4D7C-8B18-5F0ACFCECDD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="870" yWindow="-120" windowWidth="19740" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1596" uniqueCount="1165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1600" uniqueCount="1168">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -4646,6 +4646,18 @@
   </si>
   <si>
     <t>424480</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1129</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>77846101</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Win11右键菜单</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -11216,9 +11228,21 @@
       </c>
     </row>
     <row r="224" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B224" s="4" t="s">
+        <v>1165</v>
+      </c>
+      <c r="C224" s="1" t="s">
+        <v>1167</v>
+      </c>
+      <c r="H224" s="1" t="s">
+        <v>654</v>
+      </c>
       <c r="J224" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>00</v>
+        <v>001129</v>
+      </c>
+      <c r="L224" s="2" t="s">
+        <v>1166</v>
       </c>
     </row>
     <row r="225" spans="10:10" x14ac:dyDescent="0.2">

--- a/11_付费课程/99.资料/文章信息备忘表.xlsx
+++ b/11_付费课程/99.资料/文章信息备忘表.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Writing\11_付费课程\99.资料\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Disks\E\Writing\11_付费课程\99.资料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AFF232E-673D-4D7C-8B18-5F0ACFCECDD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9949E3A-7DC7-4189-8D49-B3A85E2334F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="870" yWindow="-120" windowWidth="19740" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1600" uniqueCount="1168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1604" uniqueCount="1171">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -4658,6 +4658,18 @@
   </si>
   <si>
     <t>Win11右键菜单</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1130</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>93441623</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Win7老顽固们的春天，跑最新软件就用 VxKex NEXT</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -11227,12 +11239,12 @@
         <v>1160</v>
       </c>
     </row>
-    <row r="224" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="224" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B224" s="4" t="s">
         <v>1165</v>
       </c>
       <c r="C224" s="1" t="s">
-        <v>1167</v>
+        <v>1170</v>
       </c>
       <c r="H224" s="1" t="s">
         <v>654</v>
@@ -11242,100 +11254,112 @@
         <v>001129</v>
       </c>
       <c r="L224" s="2" t="s">
+        <v>1169</v>
+      </c>
+    </row>
+    <row r="225" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B225" s="4" t="s">
+        <v>1168</v>
+      </c>
+      <c r="C225" s="1" t="s">
+        <v>1167</v>
+      </c>
+      <c r="H225" s="1" t="s">
+        <v>654</v>
+      </c>
+      <c r="J225" s="5" t="str">
+        <f t="shared" ref="J225" si="7">"00"&amp;B225</f>
+        <v>001130</v>
+      </c>
+      <c r="L225" s="2" t="s">
         <v>1166</v>
       </c>
     </row>
-    <row r="225" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J225" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>00</v>
-      </c>
-    </row>
-    <row r="226" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="226" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J226" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="227" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="227" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J227" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="228" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="228" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J228" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="229" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="229" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J229" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="230" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="230" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J230" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="231" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="231" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J231" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="232" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="232" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J232" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="233" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="233" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J233" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="234" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="234" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J234" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="235" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="235" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J235" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="236" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="236" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J236" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="237" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="237" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J237" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="238" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="238" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J238" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="239" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="239" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J239" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="240" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="240" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J240" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
@@ -11457,349 +11481,349 @@
     </row>
     <row r="260" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J260" s="5" t="str">
-        <f t="shared" ref="J260:J317" si="7">"00"&amp;B260</f>
+        <f t="shared" ref="J260:J317" si="8">"00"&amp;B260</f>
         <v>00</v>
       </c>
     </row>
     <row r="261" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J261" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
     <row r="262" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J262" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
     <row r="263" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J263" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
     <row r="264" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J264" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
     <row r="265" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J265" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
     <row r="266" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J266" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
     <row r="267" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J267" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
     <row r="268" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J268" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
     <row r="269" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J269" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
     <row r="270" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J270" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
     <row r="271" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J271" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
     <row r="272" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J272" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
     <row r="273" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J273" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
     <row r="274" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J274" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
     <row r="275" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J275" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
     <row r="276" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J276" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
     <row r="277" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J277" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
     <row r="278" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J278" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
     <row r="279" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J279" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
     <row r="280" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J280" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
     <row r="281" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J281" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
     <row r="282" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J282" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
     <row r="283" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J283" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
     <row r="284" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J284" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
     <row r="285" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J285" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
     <row r="286" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J286" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
     <row r="287" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J287" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
     <row r="288" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J288" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
     <row r="289" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J289" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
     <row r="290" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J290" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
     <row r="291" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J291" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
     <row r="292" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J292" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
     <row r="293" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J293" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
     <row r="294" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J294" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
     <row r="295" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J295" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
     <row r="296" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J296" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
     <row r="297" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J297" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
     <row r="298" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J298" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
     <row r="299" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J299" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
     <row r="300" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J300" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
     <row r="301" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J301" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
     <row r="302" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J302" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
     <row r="303" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J303" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
     <row r="304" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J304" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
     <row r="305" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J305" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
     <row r="306" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J306" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
     <row r="307" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J307" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
     <row r="308" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J308" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
     <row r="309" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J309" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
     <row r="310" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J310" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
     <row r="311" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J311" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
     <row r="312" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J312" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
     <row r="313" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J313" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
     <row r="314" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J314" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
     <row r="315" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J315" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
     <row r="316" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J316" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
     <row r="317" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J317" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
@@ -11812,7 +11836,7 @@
   <conditionalFormatting sqref="J219:L219">
     <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J220:L1048576 J1:L218">
+  <conditionalFormatting sqref="J1:L218 J220:L1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <dataValidations count="2">

--- a/11_付费课程/99.资料/文章信息备忘表.xlsx
+++ b/11_付费课程/99.资料/文章信息备忘表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Disks\E\Writing\11_付费课程\99.资料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9949E3A-7DC7-4189-8D49-B3A85E2334F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A77F9D9D-86CA-493E-BF30-B7EF9C8935A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1604" uniqueCount="1171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1606" uniqueCount="1173">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -4670,6 +4670,14 @@
   </si>
   <si>
     <t>Win7老顽固们的春天，跑最新软件就用 VxKex NEXT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-03-10 08:25:37</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>735280</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -11249,9 +11257,15 @@
       <c r="H224" s="1" t="s">
         <v>654</v>
       </c>
+      <c r="I224" s="4" t="s">
+        <v>1171</v>
+      </c>
       <c r="J224" s="5" t="str">
         <f t="shared" si="5"/>
         <v>001129</v>
+      </c>
+      <c r="K224" s="3" t="s">
+        <v>1172</v>
       </c>
       <c r="L224" s="2" t="s">
         <v>1169</v>
@@ -11833,11 +11847,11 @@
     <mergeCell ref="A2:L2"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="J1:L218 J220:L1048576">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="J219:L219">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J1:L218 J220:L1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1:E1 D3:E3 D6:E1048576" xr:uid="{00000000-0002-0000-0000-000000000000}">

--- a/11_付费课程/99.资料/文章信息备忘表.xlsx
+++ b/11_付费课程/99.资料/文章信息备忘表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Disks\E\Writing\11_付费课程\99.资料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A77F9D9D-86CA-493E-BF30-B7EF9C8935A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DCDD42A-0F4A-46C2-9A20-9831A1E5E022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2295" yWindow="2295" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -4657,10 +4657,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Win11右键菜单</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1130</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -4678,6 +4674,10 @@
   </si>
   <si>
     <t>735280</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不改回经典样式，你让我直接改造反人类设计的Win11的右键菜单？</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -11252,31 +11252,31 @@
         <v>1165</v>
       </c>
       <c r="C224" s="1" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="H224" s="1" t="s">
         <v>654</v>
       </c>
       <c r="I224" s="4" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="J224" s="5" t="str">
         <f t="shared" si="5"/>
         <v>001129</v>
       </c>
       <c r="K224" s="3" t="s">
+        <v>1171</v>
+      </c>
+      <c r="L224" s="2" t="s">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="225" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="B225" s="4" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C225" s="1" t="s">
         <v>1172</v>
-      </c>
-      <c r="L224" s="2" t="s">
-        <v>1169</v>
-      </c>
-    </row>
-    <row r="225" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B225" s="4" t="s">
-        <v>1168</v>
-      </c>
-      <c r="C225" s="1" t="s">
-        <v>1167</v>
       </c>
       <c r="H225" s="1" t="s">
         <v>654</v>

--- a/11_付费课程/99.资料/文章信息备忘表.xlsx
+++ b/11_付费课程/99.资料/文章信息备忘表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Disks\E\Writing\11_付费课程\99.资料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DCDD42A-0F4A-46C2-9A20-9831A1E5E022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDA515D2-8359-4BAA-963F-352A0B81929B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2295" yWindow="2295" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1606" uniqueCount="1173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1607" uniqueCount="1173">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -11278,6 +11278,9 @@
       <c r="C225" s="1" t="s">
         <v>1172</v>
       </c>
+      <c r="E225" s="6" t="s">
+        <v>32</v>
+      </c>
       <c r="H225" s="1" t="s">
         <v>654</v>
       </c>

--- a/11_付费课程/99.资料/文章信息备忘表.xlsx
+++ b/11_付费课程/99.资料/文章信息备忘表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Disks\E\Writing\11_付费课程\99.资料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDA515D2-8359-4BAA-963F-352A0B81929B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA60F8F3-6320-4E6B-9E42-0DE1F7742FCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1607" uniqueCount="1173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1611" uniqueCount="1176">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -4678,6 +4678,18 @@
   </si>
   <si>
     <t>不改回经典样式，你让我直接改造反人类设计的Win11的右键菜单？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1131</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>98656011</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>R.saver</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -11293,9 +11305,21 @@
       </c>
     </row>
     <row r="226" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B226" s="4" t="s">
+        <v>1173</v>
+      </c>
+      <c r="C226" s="1" t="s">
+        <v>1175</v>
+      </c>
+      <c r="H226" s="1" t="s">
+        <v>654</v>
+      </c>
       <c r="J226" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>00</v>
+        <v>001131</v>
+      </c>
+      <c r="L226" s="2" t="s">
+        <v>1174</v>
       </c>
     </row>
     <row r="227" spans="2:12" x14ac:dyDescent="0.2">

--- a/11_付费课程/99.资料/文章信息备忘表.xlsx
+++ b/11_付费课程/99.资料/文章信息备忘表.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Disks\E\Writing\11_付费课程\99.资料\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\writing\11_付费课程\99.资料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA60F8F3-6320-4E6B-9E42-0DE1F7742FCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="920" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$L$4</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -40,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1611" uniqueCount="1176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1613" uniqueCount="1178">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -4690,13 +4689,21 @@
   </si>
   <si>
     <t>R.saver</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-03-23 20:22:05</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>502202</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -5188,25 +5195,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A2:M317"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.25" style="8" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="4" customWidth="1"/>
-    <col min="3" max="3" width="30.875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="5.375" style="6" customWidth="1"/>
-    <col min="5" max="6" width="5.125" style="6" customWidth="1"/>
+    <col min="2" max="2" width="5.58203125" style="4" customWidth="1"/>
+    <col min="3" max="3" width="30.83203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="5.33203125" style="6" customWidth="1"/>
+    <col min="5" max="6" width="5.08203125" style="6" customWidth="1"/>
     <col min="7" max="7" width="5.25" style="6" customWidth="1"/>
     <col min="8" max="8" width="13.5" style="1" customWidth="1"/>
     <col min="9" max="9" width="19" style="4" customWidth="1"/>
-    <col min="10" max="10" width="8.625" style="5" customWidth="1"/>
+    <col min="10" max="10" width="8.58203125" style="5" customWidth="1"/>
     <col min="11" max="11" width="7.5" style="3" customWidth="1"/>
     <col min="12" max="12" width="9.25" style="2" customWidth="1"/>
     <col min="13" max="13" width="16.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" ht="25" x14ac:dyDescent="0.3">
       <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
@@ -5222,8 +5229,8 @@
       <c r="K2" s="20"/>
       <c r="L2" s="20"/>
     </row>
-    <row r="3" spans="1:12" ht="6.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="4" spans="1:12" s="7" customFormat="1" ht="57" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12" ht="6.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:12" s="7" customFormat="1" ht="56" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>0</v>
       </c>
@@ -5261,7 +5268,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
         <v>557</v>
       </c>
@@ -5288,7 +5295,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
         <v>559</v>
       </c>
@@ -5324,7 +5331,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
         <v>559</v>
       </c>
@@ -5360,25 +5367,25 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="J8" s="5" t="str">
         <f t="shared" si="0"/>
         <v>000</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="J9" s="5" t="str">
         <f t="shared" si="0"/>
         <v>000</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="J10" s="5" t="str">
         <f t="shared" si="0"/>
         <v>000</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
         <v>522</v>
       </c>
@@ -5411,7 +5418,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
         <v>558</v>
       </c>
@@ -5441,7 +5448,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A13" s="8" t="s">
         <v>558</v>
       </c>
@@ -5471,7 +5478,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A14" s="8" t="s">
         <v>640</v>
       </c>
@@ -5498,7 +5505,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="8" t="s">
         <v>557</v>
       </c>
@@ -5525,7 +5532,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="8" t="s">
         <v>557</v>
       </c>
@@ -5552,7 +5559,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="8" t="s">
         <v>557</v>
       </c>
@@ -5579,7 +5586,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="8" t="s">
         <v>767</v>
       </c>
@@ -5606,7 +5613,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
         <v>557</v>
       </c>
@@ -5633,7 +5640,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A20" s="8" t="s">
         <v>557</v>
       </c>
@@ -5660,7 +5667,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A21" s="8" t="s">
         <v>557</v>
       </c>
@@ -5687,7 +5694,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A22" s="8" t="s">
         <v>559</v>
       </c>
@@ -5723,7 +5730,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" s="8" t="s">
         <v>557</v>
       </c>
@@ -5750,7 +5757,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A24" s="8" t="s">
         <v>558</v>
       </c>
@@ -5780,7 +5787,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A25" s="8" t="s">
         <v>557</v>
       </c>
@@ -5807,7 +5814,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A26" s="8" t="s">
         <v>557</v>
       </c>
@@ -5834,7 +5841,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="27" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A27" s="8" t="s">
         <v>633</v>
       </c>
@@ -5861,7 +5868,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A28" s="8" t="s">
         <v>557</v>
       </c>
@@ -5888,7 +5895,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A29" s="8" t="s">
         <v>559</v>
       </c>
@@ -5924,7 +5931,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A30" s="8" t="s">
         <v>559</v>
       </c>
@@ -5960,7 +5967,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A31" s="8" t="s">
         <v>557</v>
       </c>
@@ -5987,7 +5994,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A32" s="8" t="s">
         <v>557</v>
       </c>
@@ -6014,7 +6021,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A33" s="8" t="s">
         <v>557</v>
       </c>
@@ -6041,7 +6048,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="34" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A34" s="8" t="s">
         <v>557</v>
       </c>
@@ -6068,7 +6075,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="35" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A35" s="8" t="s">
         <v>557</v>
       </c>
@@ -6095,7 +6102,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="36" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A36" s="8" t="s">
         <v>557</v>
       </c>
@@ -6122,7 +6129,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="37" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A37" s="8" t="s">
         <v>559</v>
       </c>
@@ -6158,7 +6165,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="38" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A38" s="8" t="s">
         <v>557</v>
       </c>
@@ -6185,7 +6192,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" s="8" t="s">
         <v>557</v>
       </c>
@@ -6212,7 +6219,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="40" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A40" s="8" t="s">
         <v>557</v>
       </c>
@@ -6239,7 +6246,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="41" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A41" s="8" t="s">
         <v>557</v>
       </c>
@@ -6266,7 +6273,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="42" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A42" s="8" t="s">
         <v>557</v>
       </c>
@@ -6293,7 +6300,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="43" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A43" s="8" t="s">
         <v>559</v>
       </c>
@@ -6326,7 +6333,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="44" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A44" s="8" t="s">
         <v>557</v>
       </c>
@@ -6353,7 +6360,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="45" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A45" s="8" t="s">
         <v>557</v>
       </c>
@@ -6380,7 +6387,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="46" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A46" s="8" t="s">
         <v>557</v>
       </c>
@@ -6407,7 +6414,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" s="8" t="s">
         <v>557</v>
       </c>
@@ -6434,7 +6441,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="48" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A48" s="8" t="s">
         <v>557</v>
       </c>
@@ -6461,7 +6468,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="49" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A49" s="8" t="s">
         <v>557</v>
       </c>
@@ -6488,7 +6495,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="50" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A50" s="8" t="s">
         <v>557</v>
       </c>
@@ -6515,7 +6522,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" s="8" t="s">
         <v>557</v>
       </c>
@@ -6542,7 +6549,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="52" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A52" s="8" t="s">
         <v>557</v>
       </c>
@@ -6569,7 +6576,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" s="8" t="s">
         <v>557</v>
       </c>
@@ -6596,7 +6603,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="54" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A54" s="8" t="s">
         <v>557</v>
       </c>
@@ -6623,7 +6630,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" s="8" t="s">
         <v>557</v>
       </c>
@@ -6650,7 +6657,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="56" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A56" s="8" t="s">
         <v>559</v>
       </c>
@@ -6686,7 +6693,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="57" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A57" s="8" t="s">
         <v>559</v>
       </c>
@@ -6722,7 +6729,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="58" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A58" s="8" t="s">
         <v>557</v>
       </c>
@@ -6749,7 +6756,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="59" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A59" s="8" t="s">
         <v>558</v>
       </c>
@@ -6779,7 +6786,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="60" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A60" s="8" t="s">
         <v>557</v>
       </c>
@@ -6806,7 +6813,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="61" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B61" s="4" t="s">
         <v>298</v>
       </c>
@@ -6839,7 +6846,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="62" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B62" s="4" t="s">
         <v>294</v>
       </c>
@@ -6872,7 +6879,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="63" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B63" s="4" t="s">
         <v>289</v>
       </c>
@@ -6905,7 +6912,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="64" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A64" s="8" t="s">
         <v>557</v>
       </c>
@@ -6932,7 +6939,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="65" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A65" s="8" t="s">
         <v>557</v>
       </c>
@@ -6959,7 +6966,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="66" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A66" s="8" t="s">
         <v>559</v>
       </c>
@@ -6995,7 +7002,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="67" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A67" s="8" t="s">
         <v>557</v>
       </c>
@@ -7022,7 +7029,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="68" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A68" s="8" t="s">
         <v>558</v>
       </c>
@@ -7052,7 +7059,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="69" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A69" s="8" t="s">
         <v>559</v>
       </c>
@@ -7079,7 +7086,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="70" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A70" s="8" t="s">
         <v>559</v>
       </c>
@@ -7106,7 +7113,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="71" spans="1:12" ht="57" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:12" ht="56" x14ac:dyDescent="0.3">
       <c r="A71" s="8" t="s">
         <v>558</v>
       </c>
@@ -7136,7 +7143,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="72" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A72" s="8" t="s">
         <v>558</v>
       </c>
@@ -7166,7 +7173,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="73" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A73" s="8" t="s">
         <v>558</v>
       </c>
@@ -7196,7 +7203,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="74" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A74" s="8" t="s">
         <v>557</v>
       </c>
@@ -7223,7 +7230,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="75" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A75" s="8" t="s">
         <v>557</v>
       </c>
@@ -7250,7 +7257,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="76" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A76" s="8" t="s">
         <v>558</v>
       </c>
@@ -7283,7 +7290,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="77" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A77" s="8" t="s">
         <v>557</v>
       </c>
@@ -7310,7 +7317,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="78" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A78" s="8" t="s">
         <v>558</v>
       </c>
@@ -7337,7 +7344,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="79" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A79" s="8" t="s">
         <v>557</v>
       </c>
@@ -7364,7 +7371,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="80" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A80" s="8" t="s">
         <v>558</v>
       </c>
@@ -7391,7 +7398,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="81" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A81" s="8" t="s">
         <v>557</v>
       </c>
@@ -7418,7 +7425,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="82" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A82" s="8" t="s">
         <v>557</v>
       </c>
@@ -7445,7 +7452,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="83" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A83" s="8" t="s">
         <v>557</v>
       </c>
@@ -7472,7 +7479,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="84" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A84" s="8" t="s">
         <v>557</v>
       </c>
@@ -7499,7 +7506,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="85" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A85" s="8" t="s">
         <v>558</v>
       </c>
@@ -7526,7 +7533,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="86" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A86" s="8" t="s">
         <v>557</v>
       </c>
@@ -7553,7 +7560,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="87" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A87" s="8" t="s">
         <v>559</v>
       </c>
@@ -7589,7 +7596,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="88" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A88" s="8" t="s">
         <v>559</v>
       </c>
@@ -7625,7 +7632,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="89" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A89" s="8" t="s">
         <v>559</v>
       </c>
@@ -7661,7 +7668,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="90" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A90" s="8" t="s">
         <v>557</v>
       </c>
@@ -7688,7 +7695,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="91" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B91" s="4" t="s">
         <v>151</v>
       </c>
@@ -7721,7 +7728,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="92" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B92" s="4" t="s">
         <v>146</v>
       </c>
@@ -7754,7 +7761,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="93" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B93" s="4" t="s">
         <v>140</v>
       </c>
@@ -7787,7 +7794,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="94" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B94" s="4" t="s">
         <v>135</v>
       </c>
@@ -7820,7 +7827,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="95" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A95" s="8" t="s">
         <v>558</v>
       </c>
@@ -7847,7 +7854,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="96" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="B96" s="4" t="s">
         <v>123</v>
       </c>
@@ -7880,7 +7887,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="97" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B97" s="4" t="s">
         <v>118</v>
       </c>
@@ -7913,7 +7920,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="98" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="B98" s="4" t="s">
         <v>112</v>
       </c>
@@ -7946,7 +7953,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="99" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B99" s="4" t="s">
         <v>109</v>
       </c>
@@ -7979,7 +7986,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="100" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B100" s="4" t="s">
         <v>104</v>
       </c>
@@ -8012,7 +8019,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="101" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="B101" s="4" t="s">
         <v>98</v>
       </c>
@@ -8045,7 +8052,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="102" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B102" s="4" t="s">
         <v>92</v>
       </c>
@@ -8078,7 +8085,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="103" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A103" s="8" t="s">
         <v>559</v>
       </c>
@@ -8114,7 +8121,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="104" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A104" s="8" t="s">
         <v>557</v>
       </c>
@@ -8141,7 +8148,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="105" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A105" s="8" t="s">
         <v>557</v>
       </c>
@@ -8168,7 +8175,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="106" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A106" s="8" t="s">
         <v>557</v>
       </c>
@@ -8195,7 +8202,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="107" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A107" s="8" t="s">
         <v>557</v>
       </c>
@@ -8222,7 +8229,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="108" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A108" s="8" t="s">
         <v>557</v>
       </c>
@@ -8249,7 +8256,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="109" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A109" s="8" t="s">
         <v>559</v>
       </c>
@@ -8285,7 +8292,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A110" s="8" t="s">
         <v>558</v>
       </c>
@@ -8312,7 +8319,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="111" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A111" s="8" t="s">
         <v>557</v>
       </c>
@@ -8339,7 +8346,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="112" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A112" s="8" t="s">
         <v>557</v>
       </c>
@@ -8366,7 +8373,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="113" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A113" s="8" t="s">
         <v>557</v>
       </c>
@@ -8393,7 +8400,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A114" s="8" t="s">
         <v>557</v>
       </c>
@@ -8420,7 +8427,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="115" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A115" s="8" t="s">
         <v>557</v>
       </c>
@@ -8447,7 +8454,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="116" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A116" s="8" t="s">
         <v>559</v>
       </c>
@@ -8483,7 +8490,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="117" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A117" s="8" t="s">
         <v>557</v>
       </c>
@@ -8510,7 +8517,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="118" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A118" s="8" t="s">
         <v>558</v>
       </c>
@@ -8540,7 +8547,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="119" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A119" s="8" t="s">
         <v>557</v>
       </c>
@@ -8567,7 +8574,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="120" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A120" s="8" t="s">
         <v>557</v>
       </c>
@@ -8594,7 +8601,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="121" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A121" s="8" t="s">
         <v>597</v>
       </c>
@@ -8621,7 +8628,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="122" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A122" s="8" t="s">
         <v>602</v>
       </c>
@@ -8648,7 +8655,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="123" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A123" s="8" t="s">
         <v>608</v>
       </c>
@@ -8675,7 +8682,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="124" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A124" s="8" t="s">
         <v>611</v>
       </c>
@@ -8702,7 +8709,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="125" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A125" s="8" t="s">
         <v>617</v>
       </c>
@@ -8729,7 +8736,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="126" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A126" s="8" t="s">
         <v>624</v>
       </c>
@@ -8756,7 +8763,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="127" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A127" s="8" t="s">
         <v>557</v>
       </c>
@@ -8783,7 +8790,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="128" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A128" s="8" t="s">
         <v>649</v>
       </c>
@@ -8810,7 +8817,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="129" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A129" s="8" t="s">
         <v>653</v>
       </c>
@@ -8837,7 +8844,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="130" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A130" s="8" t="s">
         <v>659</v>
       </c>
@@ -8864,7 +8871,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="131" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A131" s="8" t="s">
         <v>664</v>
       </c>
@@ -8891,7 +8898,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A132" s="8" t="s">
         <v>557</v>
       </c>
@@ -8918,7 +8925,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="133" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A133" s="8" t="s">
         <v>557</v>
       </c>
@@ -8945,7 +8952,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="134" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A134" s="8" t="s">
         <v>681</v>
       </c>
@@ -8972,7 +8979,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="135" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A135" s="8" t="s">
         <v>687</v>
       </c>
@@ -8999,7 +9006,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="136" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A136" s="8" t="s">
         <v>691</v>
       </c>
@@ -9026,7 +9033,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="137" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A137" s="8" t="s">
         <v>699</v>
       </c>
@@ -9053,7 +9060,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="138" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A138" s="8" t="s">
         <v>704</v>
       </c>
@@ -9080,7 +9087,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="139" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A139" s="8" t="s">
         <v>711</v>
       </c>
@@ -9107,7 +9114,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="140" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A140" s="8" t="s">
         <v>716</v>
       </c>
@@ -9134,7 +9141,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="141" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A141" s="8" t="s">
         <v>724</v>
       </c>
@@ -9161,7 +9168,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="142" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A142" s="8" t="s">
         <v>727</v>
       </c>
@@ -9188,7 +9195,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="143" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A143" s="8" t="s">
         <v>736</v>
       </c>
@@ -9215,7 +9222,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="144" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A144" s="8" t="s">
         <v>740</v>
       </c>
@@ -9242,7 +9249,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="145" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A145" s="8" t="s">
         <v>746</v>
       </c>
@@ -9269,7 +9276,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="146" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A146" s="8" t="s">
         <v>754</v>
       </c>
@@ -9296,7 +9303,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="147" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A147" s="8" t="s">
         <v>759</v>
       </c>
@@ -9323,7 +9330,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="148" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A148" s="8" t="s">
         <v>770</v>
       </c>
@@ -9350,7 +9357,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="149" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A149" s="8" t="s">
         <v>777</v>
       </c>
@@ -9377,7 +9384,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="150" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A150" s="8" t="s">
         <v>782</v>
       </c>
@@ -9404,7 +9411,7 @@
         <v>786</v>
       </c>
     </row>
-    <row r="151" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A151" s="8" t="s">
         <v>557</v>
       </c>
@@ -9431,7 +9438,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="152" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A152" s="8" t="s">
         <v>795</v>
       </c>
@@ -9458,7 +9465,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A153" s="8" t="s">
         <v>800</v>
       </c>
@@ -9485,7 +9492,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A154" s="8" t="s">
         <v>804</v>
       </c>
@@ -9512,7 +9519,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A155" s="8" t="s">
         <v>811</v>
       </c>
@@ -9539,7 +9546,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="156" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A156" s="8" t="s">
         <v>557</v>
       </c>
@@ -9566,7 +9573,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A157" s="8" t="s">
         <v>557</v>
       </c>
@@ -9593,7 +9600,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A158" s="8" t="s">
         <v>827</v>
       </c>
@@ -9620,7 +9627,7 @@
         <v>831</v>
       </c>
     </row>
-    <row r="159" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A159" s="8" t="s">
         <v>557</v>
       </c>
@@ -9647,7 +9654,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A160" s="8" t="s">
         <v>838</v>
       </c>
@@ -9674,7 +9681,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="161" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A161" s="8" t="s">
         <v>557</v>
       </c>
@@ -9701,7 +9708,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A162" s="8" t="s">
         <v>850</v>
       </c>
@@ -9728,7 +9735,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A163" s="8" t="s">
         <v>857</v>
       </c>
@@ -9755,7 +9762,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A164" s="8" t="s">
         <v>557</v>
       </c>
@@ -9782,7 +9789,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="165" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A165" s="8" t="s">
         <v>557</v>
       </c>
@@ -9809,7 +9816,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A166" s="8" t="s">
         <v>557</v>
       </c>
@@ -9836,7 +9843,7 @@
         <v>871</v>
       </c>
     </row>
-    <row r="167" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A167" s="8" t="s">
         <v>557</v>
       </c>
@@ -9863,7 +9870,7 @@
         <v>879</v>
       </c>
     </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A168" s="8" t="s">
         <v>557</v>
       </c>
@@ -9890,7 +9897,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A169" s="8" t="s">
         <v>557</v>
       </c>
@@ -9917,7 +9924,7 @@
         <v>889</v>
       </c>
     </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A170" s="8" t="s">
         <v>557</v>
       </c>
@@ -9944,7 +9951,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A171" s="8" t="s">
         <v>557</v>
       </c>
@@ -9971,7 +9978,7 @@
         <v>897</v>
       </c>
     </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A172" s="8" t="s">
         <v>902</v>
       </c>
@@ -9998,7 +10005,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A173" s="8" t="s">
         <v>902</v>
       </c>
@@ -10025,7 +10032,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A174" s="8" t="s">
         <v>557</v>
       </c>
@@ -10052,7 +10059,7 @@
         <v>915</v>
       </c>
     </row>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A175" s="8" t="s">
         <v>557</v>
       </c>
@@ -10079,7 +10086,7 @@
         <v>919</v>
       </c>
     </row>
-    <row r="176" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A176" s="8" t="s">
         <v>557</v>
       </c>
@@ -10106,7 +10113,7 @@
         <v>925</v>
       </c>
     </row>
-    <row r="177" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A177" s="8" t="s">
         <v>557</v>
       </c>
@@ -10133,7 +10140,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="178" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:13" ht="28" x14ac:dyDescent="0.3">
       <c r="A178" s="8" t="s">
         <v>557</v>
       </c>
@@ -10160,7 +10167,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="179" spans="1:13" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:13" ht="42" x14ac:dyDescent="0.3">
       <c r="A179" s="8" t="s">
         <v>938</v>
       </c>
@@ -10187,7 +10194,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="180" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B180" s="4" t="s">
         <v>942</v>
       </c>
@@ -10211,7 +10218,7 @@
         <v>946</v>
       </c>
     </row>
-    <row r="181" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:13" ht="28" x14ac:dyDescent="0.3">
       <c r="B181" s="4" t="s">
         <v>948</v>
       </c>
@@ -10235,7 +10242,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="182" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:13" ht="28" x14ac:dyDescent="0.3">
       <c r="B182" s="4" t="s">
         <v>954</v>
       </c>
@@ -10259,7 +10266,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="183" spans="1:13" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:13" ht="42" x14ac:dyDescent="0.3">
       <c r="B183" s="4" t="s">
         <v>959</v>
       </c>
@@ -10283,7 +10290,7 @@
         <v>960</v>
       </c>
     </row>
-    <row r="184" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:13" ht="28" x14ac:dyDescent="0.3">
       <c r="B184" s="4" t="s">
         <v>966</v>
       </c>
@@ -10307,7 +10314,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="185" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:13" ht="28" x14ac:dyDescent="0.3">
       <c r="B185" s="4" t="s">
         <v>971</v>
       </c>
@@ -10331,7 +10338,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="186" spans="1:13" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:13" ht="42" x14ac:dyDescent="0.3">
       <c r="B186" s="4" t="s">
         <v>976</v>
       </c>
@@ -10355,7 +10362,7 @@
         <v>963</v>
       </c>
     </row>
-    <row r="187" spans="1:13" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:13" ht="42" x14ac:dyDescent="0.3">
       <c r="B187" s="4" t="s">
         <v>979</v>
       </c>
@@ -10379,7 +10386,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="188" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:13" ht="28" x14ac:dyDescent="0.3">
       <c r="B188" s="4" t="s">
         <v>985</v>
       </c>
@@ -10406,7 +10413,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="189" spans="1:13" ht="15" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:13" ht="15.5" x14ac:dyDescent="0.3">
       <c r="B189" s="4" t="s">
         <v>988</v>
       </c>
@@ -10431,7 +10438,7 @@
       </c>
       <c r="M189" s="6"/>
     </row>
-    <row r="190" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:13" ht="28" x14ac:dyDescent="0.3">
       <c r="B190" s="4" t="s">
         <v>992</v>
       </c>
@@ -10455,7 +10462,7 @@
         <v>982</v>
       </c>
     </row>
-    <row r="191" spans="1:13" ht="45" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:13" ht="46.5" x14ac:dyDescent="0.3">
       <c r="B191" s="4" t="s">
         <v>1002</v>
       </c>
@@ -10479,7 +10486,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="192" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:13" ht="28" x14ac:dyDescent="0.3">
       <c r="B192" s="4" t="s">
         <v>1006</v>
       </c>
@@ -10503,7 +10510,7 @@
         <v>998</v>
       </c>
     </row>
-    <row r="193" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="193" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B193" s="4" t="s">
         <v>1010</v>
       </c>
@@ -10527,7 +10534,7 @@
         <v>1011</v>
       </c>
     </row>
-    <row r="194" spans="2:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="194" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B194" s="4" t="s">
         <v>1015</v>
       </c>
@@ -10554,7 +10561,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="195" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="195" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B195" s="4" t="s">
         <v>1021</v>
       </c>
@@ -10578,7 +10585,7 @@
         <v>1019</v>
       </c>
     </row>
-    <row r="196" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="196" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B196" s="4" t="s">
         <v>1025</v>
       </c>
@@ -10602,7 +10609,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="197" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="197" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B197" s="4" t="s">
         <v>1031</v>
       </c>
@@ -10626,7 +10633,7 @@
         <v>1033</v>
       </c>
     </row>
-    <row r="198" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="198" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B198" s="4" t="s">
         <v>1034</v>
       </c>
@@ -10650,7 +10657,7 @@
         <v>1035</v>
       </c>
     </row>
-    <row r="199" spans="2:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="199" spans="2:12" ht="42" x14ac:dyDescent="0.3">
       <c r="B199" s="4" t="s">
         <v>1040</v>
       </c>
@@ -10674,7 +10681,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="200" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="200" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B200" s="4" t="s">
         <v>1045</v>
       </c>
@@ -10698,7 +10705,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="201" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="201" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B201" s="4" t="s">
         <v>1051</v>
       </c>
@@ -10722,7 +10729,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="202" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="202" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B202" s="4" t="s">
         <v>1058</v>
       </c>
@@ -10746,7 +10753,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="203" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="203" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B203" s="4" t="s">
         <v>1062</v>
       </c>
@@ -10770,7 +10777,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="204" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="204" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B204" s="4" t="s">
         <v>1065</v>
       </c>
@@ -10794,7 +10801,7 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="205" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="205" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B205" s="4" t="s">
         <v>1071</v>
       </c>
@@ -10818,7 +10825,7 @@
         <v>1069</v>
       </c>
     </row>
-    <row r="206" spans="2:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="206" spans="2:12" ht="42" x14ac:dyDescent="0.3">
       <c r="B206" s="4" t="s">
         <v>1074</v>
       </c>
@@ -10842,7 +10849,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="207" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="207" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B207" s="4" t="s">
         <v>1080</v>
       </c>
@@ -10866,7 +10873,7 @@
         <v>1079</v>
       </c>
     </row>
-    <row r="208" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="208" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B208" s="4" t="s">
         <v>1082</v>
       </c>
@@ -10890,7 +10897,7 @@
         <v>1081</v>
       </c>
     </row>
-    <row r="209" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="209" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B209" s="4" t="s">
         <v>1091</v>
       </c>
@@ -10914,7 +10921,7 @@
         <v>1089</v>
       </c>
     </row>
-    <row r="210" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="210" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B210" s="4" t="s">
         <v>1093</v>
       </c>
@@ -10938,7 +10945,7 @@
         <v>1092</v>
       </c>
     </row>
-    <row r="211" spans="2:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="211" spans="2:12" ht="42" x14ac:dyDescent="0.3">
       <c r="B211" s="4" t="s">
         <v>1102</v>
       </c>
@@ -10962,7 +10969,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="212" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="212" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B212" s="4" t="s">
         <v>1105</v>
       </c>
@@ -10986,7 +10993,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="213" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="213" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B213" s="4" t="s">
         <v>1110</v>
       </c>
@@ -11010,7 +11017,7 @@
         <v>1109</v>
       </c>
     </row>
-    <row r="214" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="214" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B214" s="4" t="s">
         <v>1118</v>
       </c>
@@ -11037,7 +11044,7 @@
         <v>1114</v>
       </c>
     </row>
-    <row r="215" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="215" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B215" s="4" t="s">
         <v>1121</v>
       </c>
@@ -11061,7 +11068,7 @@
         <v>1116</v>
       </c>
     </row>
-    <row r="216" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="216" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B216" s="4" t="s">
         <v>1126</v>
       </c>
@@ -11088,7 +11095,7 @@
         <v>1131</v>
       </c>
     </row>
-    <row r="217" spans="2:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="217" spans="2:12" ht="42" x14ac:dyDescent="0.3">
       <c r="B217" s="4" t="s">
         <v>1134</v>
       </c>
@@ -11112,7 +11119,7 @@
         <v>1113</v>
       </c>
     </row>
-    <row r="218" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="218" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B218" s="4" t="s">
         <v>1137</v>
       </c>
@@ -11139,7 +11146,7 @@
         <v>1132</v>
       </c>
     </row>
-    <row r="219" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="219" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B219" s="4" t="s">
         <v>1142</v>
       </c>
@@ -11163,7 +11170,7 @@
         <v>1120</v>
       </c>
     </row>
-    <row r="220" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="220" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B220" s="4" t="s">
         <v>1145</v>
       </c>
@@ -11187,7 +11194,7 @@
         <v>1149</v>
       </c>
     </row>
-    <row r="221" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="221" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B221" s="4" t="s">
         <v>1150</v>
       </c>
@@ -11211,7 +11218,7 @@
         <v>1154</v>
       </c>
     </row>
-    <row r="222" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="222" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B222" s="4" t="s">
         <v>1153</v>
       </c>
@@ -11235,7 +11242,7 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="223" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="223" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B223" s="4" t="s">
         <v>1161</v>
       </c>
@@ -11259,7 +11266,7 @@
         <v>1160</v>
       </c>
     </row>
-    <row r="224" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="224" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B224" s="4" t="s">
         <v>1165</v>
       </c>
@@ -11283,7 +11290,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="225" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="225" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B225" s="4" t="s">
         <v>1167</v>
       </c>
@@ -11295,16 +11302,22 @@
       </c>
       <c r="H225" s="1" t="s">
         <v>654</v>
+      </c>
+      <c r="I225" s="4" t="s">
+        <v>1176</v>
       </c>
       <c r="J225" s="5" t="str">
         <f t="shared" ref="J225" si="7">"00"&amp;B225</f>
         <v>001130</v>
       </c>
+      <c r="K225" s="3" t="s">
+        <v>1177</v>
+      </c>
       <c r="L225" s="2" t="s">
         <v>1166</v>
       </c>
     </row>
-    <row r="226" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="226" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B226" s="4" t="s">
         <v>1173</v>
       </c>
@@ -11322,554 +11335,554 @@
         <v>1174</v>
       </c>
     </row>
-    <row r="227" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="227" spans="2:12" x14ac:dyDescent="0.3">
       <c r="J227" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="228" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="228" spans="2:12" x14ac:dyDescent="0.3">
       <c r="J228" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="229" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="229" spans="2:12" x14ac:dyDescent="0.3">
       <c r="J229" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="230" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="230" spans="2:12" x14ac:dyDescent="0.3">
       <c r="J230" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="231" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="231" spans="2:12" x14ac:dyDescent="0.3">
       <c r="J231" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="232" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="232" spans="2:12" x14ac:dyDescent="0.3">
       <c r="J232" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="233" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="233" spans="2:12" x14ac:dyDescent="0.3">
       <c r="J233" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="234" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="234" spans="2:12" x14ac:dyDescent="0.3">
       <c r="J234" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="235" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="235" spans="2:12" x14ac:dyDescent="0.3">
       <c r="J235" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="236" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="236" spans="2:12" x14ac:dyDescent="0.3">
       <c r="J236" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="237" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="237" spans="2:12" x14ac:dyDescent="0.3">
       <c r="J237" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="238" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="238" spans="2:12" x14ac:dyDescent="0.3">
       <c r="J238" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="239" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="239" spans="2:12" x14ac:dyDescent="0.3">
       <c r="J239" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="240" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="240" spans="2:12" x14ac:dyDescent="0.3">
       <c r="J240" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="241" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="241" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J241" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="242" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="242" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J242" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="243" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="243" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J243" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="244" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="244" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J244" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="245" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="245" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J245" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="246" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="246" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J246" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="247" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="247" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J247" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="248" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="248" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J248" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="249" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="249" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J249" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="250" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="250" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J250" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="251" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="251" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J251" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="252" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="252" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J252" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="253" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="253" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J253" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="254" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="254" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J254" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="255" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="255" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J255" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="256" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="256" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J256" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="257" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="257" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J257" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="258" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="258" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J258" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="259" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="259" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J259" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="260" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="260" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J260" s="5" t="str">
         <f t="shared" ref="J260:J317" si="8">"00"&amp;B260</f>
         <v>00</v>
       </c>
     </row>
-    <row r="261" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="261" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J261" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="262" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="262" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J262" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="263" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="263" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J263" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="264" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="264" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J264" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="265" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="265" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J265" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="266" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="266" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J266" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="267" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="267" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J267" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="268" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="268" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J268" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="269" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="269" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J269" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="270" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="270" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J270" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="271" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="271" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J271" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="272" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="272" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J272" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="273" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="273" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J273" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="274" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="274" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J274" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="275" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="275" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J275" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="276" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="276" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J276" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="277" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="277" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J277" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="278" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="278" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J278" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="279" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="279" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J279" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="280" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="280" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J280" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="281" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="281" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J281" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="282" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="282" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J282" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="283" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="283" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J283" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="284" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="284" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J284" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="285" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="285" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J285" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="286" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="286" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J286" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="287" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="287" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J287" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="288" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="288" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J288" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="289" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="289" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J289" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="290" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="290" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J290" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="291" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="291" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J291" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="292" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="292" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J292" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="293" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="293" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J293" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="294" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="294" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J294" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="295" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="295" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J295" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="296" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="296" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J296" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="297" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="297" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J297" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="298" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="298" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J298" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="299" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="299" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J299" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="300" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="300" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J300" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="301" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="301" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J301" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="302" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="302" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J302" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="303" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="303" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J303" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="304" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="304" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J304" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="305" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="305" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J305" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="306" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="306" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J306" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="307" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="307" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J307" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="308" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="308" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J308" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="309" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="309" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J309" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="310" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="310" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J310" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="311" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="311" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J311" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="312" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="312" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J312" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="313" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="313" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J313" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="314" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="314" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J314" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="315" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="315" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J315" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="316" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="316" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J316" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="317" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="317" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J317" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:L4" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A4:L4"/>
   <mergeCells count="1">
     <mergeCell ref="A2:L2"/>
   </mergeCells>
@@ -11881,10 +11894,10 @@
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1:E1 D3:E3 D6:E1048576" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1:E1 D3:E3 D6:E1048576">
       <formula1>"是,否"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H1 H3:H1048576" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H1 H3:H1048576">
       <formula1>"VB编程,系统运维,WEB学习,游戏碎片,日常随笔,浥尘伙伴社团"</formula1>
     </dataValidation>
   </dataValidations>
@@ -11894,20 +11907,20 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A2:L34"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="6.375" customWidth="1"/>
+    <col min="2" max="2" width="6.33203125" customWidth="1"/>
     <col min="3" max="3" width="34" style="4" customWidth="1"/>
     <col min="4" max="4" width="4.75" customWidth="1"/>
-    <col min="8" max="8" width="6.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.83203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="19" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="7.125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="7.08203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.08203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:12" ht="23.25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
         <v>549</v>
       </c>
@@ -11923,7 +11936,7 @@
       <c r="K2" s="21"/>
       <c r="L2" s="21"/>
     </row>
-    <row r="4" spans="1:12" ht="57" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12" ht="56" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>0</v>
       </c>
@@ -11961,7 +11974,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>533</v>
       </c>
@@ -11984,7 +11997,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C8" s="15" t="s">
         <v>545</v>
       </c>
@@ -11993,7 +12006,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C9" s="4" t="s">
         <v>539</v>
       </c>
@@ -12001,7 +12014,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C10" t="s">
         <v>537</v>
       </c>
@@ -12009,7 +12022,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C11" t="s">
         <v>538</v>
       </c>
@@ -12017,7 +12030,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="23.25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A13" s="21" t="s">
         <v>543</v>
       </c>
@@ -12033,7 +12046,7 @@
       <c r="K13" s="21"/>
       <c r="L13" s="21"/>
     </row>
-    <row r="15" spans="1:12" ht="57" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:12" ht="56" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
         <v>0</v>
       </c>
@@ -12071,7 +12084,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>533</v>
       </c>
@@ -12097,7 +12110,7 @@
         <v>54837657</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C19" s="15" t="s">
         <v>545</v>
       </c>
@@ -12106,7 +12119,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C20" s="4" t="s">
         <v>539</v>
       </c>
@@ -12114,7 +12127,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C21" t="s">
         <v>537</v>
       </c>
@@ -12122,7 +12135,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C22" t="s">
         <v>538</v>
       </c>
@@ -12130,10 +12143,10 @@
         <v>541</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C23"/>
     </row>
-    <row r="25" spans="1:12" ht="23.25" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:12" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A25" s="21" t="s">
         <v>550</v>
       </c>
@@ -12149,7 +12162,7 @@
       <c r="K25" s="21"/>
       <c r="L25" s="21"/>
     </row>
-    <row r="27" spans="1:12" ht="57" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:12" ht="56" x14ac:dyDescent="0.3">
       <c r="A27" s="7" t="s">
         <v>0</v>
       </c>
@@ -12187,7 +12200,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
         <v>533</v>
       </c>
@@ -12213,7 +12226,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C31" s="15" t="s">
         <v>545</v>
       </c>
@@ -12222,7 +12235,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C32" s="4" t="s">
         <v>539</v>
       </c>
@@ -12230,7 +12243,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="33" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="33" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C33" t="s">
         <v>537</v>
       </c>
@@ -12238,7 +12251,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="34" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="34" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C34" t="s">
         <v>538</v>
       </c>
@@ -12254,7 +12267,7 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H15 H27 H4" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H15 H27 H4">
       <formula1>"VB编程,系统运维,WEB学习,游戏碎片,日常随笔"</formula1>
     </dataValidation>
   </dataValidations>

--- a/11_付费课程/99.资料/文章信息备忘表.xlsx
+++ b/11_付费课程/99.资料/文章信息备忘表.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="920" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
+    <workbookView xWindow="1960" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1613" uniqueCount="1178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1615" uniqueCount="1180">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -4688,15 +4688,23 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>R.saver</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>2025-03-23 20:22:05</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>502202</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-04-06 19:58:58</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>858591</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>罗刹国出品的数据恢复神器R.saver</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -11304,14 +11312,14 @@
         <v>654</v>
       </c>
       <c r="I225" s="4" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="J225" s="5" t="str">
         <f t="shared" ref="J225" si="7">"00"&amp;B225</f>
         <v>001130</v>
       </c>
       <c r="K225" s="3" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="L225" s="2" t="s">
         <v>1166</v>
@@ -11322,14 +11330,20 @@
         <v>1173</v>
       </c>
       <c r="C226" s="1" t="s">
-        <v>1175</v>
+        <v>1179</v>
       </c>
       <c r="H226" s="1" t="s">
         <v>654</v>
+      </c>
+      <c r="I226" s="4" t="s">
+        <v>1177</v>
       </c>
       <c r="J226" s="5" t="str">
         <f t="shared" si="5"/>
         <v>001131</v>
+      </c>
+      <c r="K226" s="3" t="s">
+        <v>1178</v>
       </c>
       <c r="L226" s="2" t="s">
         <v>1174</v>

--- a/11_付费课程/99.资料/文章信息备忘表.xlsx
+++ b/11_付费课程/99.资料/文章信息备忘表.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\writing\11_付费课程\99.资料\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Disks\E\Writing\11_付费课程\99.资料\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD1CDA0A-EF48-458A-A86B-26A09F675202}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1960" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,7 +19,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$L$4</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1615" uniqueCount="1180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1619" uniqueCount="1183">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -4705,13 +4706,25 @@
   </si>
   <si>
     <t>罗刹国出品的数据恢复神器R.saver</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>56855281</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1132</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小时候的众多绝版老游戏，想玩就去养老院？</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -5203,25 +5216,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:M317"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.25" style="8" customWidth="1"/>
-    <col min="2" max="2" width="5.58203125" style="4" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="5.33203125" style="6" customWidth="1"/>
-    <col min="5" max="6" width="5.08203125" style="6" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="30.875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="5.375" style="6" customWidth="1"/>
+    <col min="5" max="6" width="5.125" style="6" customWidth="1"/>
     <col min="7" max="7" width="5.25" style="6" customWidth="1"/>
     <col min="8" max="8" width="13.5" style="1" customWidth="1"/>
     <col min="9" max="9" width="19" style="4" customWidth="1"/>
-    <col min="10" max="10" width="8.58203125" style="5" customWidth="1"/>
+    <col min="10" max="10" width="8.625" style="5" customWidth="1"/>
     <col min="11" max="11" width="7.5" style="3" customWidth="1"/>
     <col min="12" max="12" width="9.25" style="2" customWidth="1"/>
     <col min="13" max="13" width="16.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:12" ht="25" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
@@ -5237,8 +5250,8 @@
       <c r="K2" s="20"/>
       <c r="L2" s="20"/>
     </row>
-    <row r="3" spans="1:12" ht="6.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="4" spans="1:12" s="7" customFormat="1" ht="56" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" ht="6.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="4" spans="1:12" s="7" customFormat="1" ht="57" x14ac:dyDescent="0.2">
       <c r="A4" s="7" t="s">
         <v>0</v>
       </c>
@@ -5276,7 +5289,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
         <v>557</v>
       </c>
@@ -5303,7 +5316,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
         <v>559</v>
       </c>
@@ -5339,7 +5352,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="8" t="s">
         <v>559</v>
       </c>
@@ -5375,25 +5388,25 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="J8" s="5" t="str">
         <f t="shared" si="0"/>
         <v>000</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="J9" s="5" t="str">
         <f t="shared" si="0"/>
         <v>000</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="J10" s="5" t="str">
         <f t="shared" si="0"/>
         <v>000</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B11" s="4" t="s">
         <v>522</v>
       </c>
@@ -5426,7 +5439,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A12" s="8" t="s">
         <v>558</v>
       </c>
@@ -5456,7 +5469,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A13" s="8" t="s">
         <v>558</v>
       </c>
@@ -5486,7 +5499,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A14" s="8" t="s">
         <v>640</v>
       </c>
@@ -5513,7 +5526,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" s="8" t="s">
         <v>557</v>
       </c>
@@ -5540,7 +5553,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" s="8" t="s">
         <v>557</v>
       </c>
@@ -5567,7 +5580,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" s="8" t="s">
         <v>557</v>
       </c>
@@ -5594,7 +5607,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" s="8" t="s">
         <v>767</v>
       </c>
@@ -5621,7 +5634,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A19" s="8" t="s">
         <v>557</v>
       </c>
@@ -5648,7 +5661,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A20" s="8" t="s">
         <v>557</v>
       </c>
@@ -5675,7 +5688,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A21" s="8" t="s">
         <v>557</v>
       </c>
@@ -5702,7 +5715,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A22" s="8" t="s">
         <v>559</v>
       </c>
@@ -5738,7 +5751,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23" s="8" t="s">
         <v>557</v>
       </c>
@@ -5765,7 +5778,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A24" s="8" t="s">
         <v>558</v>
       </c>
@@ -5795,7 +5808,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A25" s="8" t="s">
         <v>557</v>
       </c>
@@ -5822,7 +5835,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A26" s="8" t="s">
         <v>557</v>
       </c>
@@ -5849,7 +5862,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="27" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A27" s="8" t="s">
         <v>633</v>
       </c>
@@ -5876,7 +5889,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A28" s="8" t="s">
         <v>557</v>
       </c>
@@ -5903,7 +5916,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A29" s="8" t="s">
         <v>559</v>
       </c>
@@ -5939,7 +5952,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A30" s="8" t="s">
         <v>559</v>
       </c>
@@ -5975,7 +5988,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A31" s="8" t="s">
         <v>557</v>
       </c>
@@ -6002,7 +6015,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A32" s="8" t="s">
         <v>557</v>
       </c>
@@ -6029,7 +6042,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A33" s="8" t="s">
         <v>557</v>
       </c>
@@ -6056,7 +6069,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="34" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A34" s="8" t="s">
         <v>557</v>
       </c>
@@ -6083,7 +6096,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="35" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A35" s="8" t="s">
         <v>557</v>
       </c>
@@ -6110,7 +6123,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="36" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A36" s="8" t="s">
         <v>557</v>
       </c>
@@ -6137,7 +6150,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="37" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A37" s="8" t="s">
         <v>559</v>
       </c>
@@ -6173,7 +6186,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="38" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A38" s="8" t="s">
         <v>557</v>
       </c>
@@ -6200,7 +6213,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A39" s="8" t="s">
         <v>557</v>
       </c>
@@ -6227,7 +6240,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="40" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A40" s="8" t="s">
         <v>557</v>
       </c>
@@ -6254,7 +6267,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="41" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A41" s="8" t="s">
         <v>557</v>
       </c>
@@ -6281,7 +6294,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="42" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A42" s="8" t="s">
         <v>557</v>
       </c>
@@ -6308,7 +6321,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="43" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A43" s="8" t="s">
         <v>559</v>
       </c>
@@ -6341,7 +6354,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="44" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A44" s="8" t="s">
         <v>557</v>
       </c>
@@ -6368,7 +6381,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="45" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A45" s="8" t="s">
         <v>557</v>
       </c>
@@ -6395,7 +6408,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="46" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A46" s="8" t="s">
         <v>557</v>
       </c>
@@ -6422,7 +6435,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A47" s="8" t="s">
         <v>557</v>
       </c>
@@ -6449,7 +6462,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="48" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A48" s="8" t="s">
         <v>557</v>
       </c>
@@ -6476,7 +6489,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="49" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A49" s="8" t="s">
         <v>557</v>
       </c>
@@ -6503,7 +6516,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="50" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A50" s="8" t="s">
         <v>557</v>
       </c>
@@ -6530,7 +6543,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A51" s="8" t="s">
         <v>557</v>
       </c>
@@ -6557,7 +6570,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="52" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A52" s="8" t="s">
         <v>557</v>
       </c>
@@ -6584,7 +6597,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A53" s="8" t="s">
         <v>557</v>
       </c>
@@ -6611,7 +6624,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="54" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A54" s="8" t="s">
         <v>557</v>
       </c>
@@ -6638,7 +6651,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A55" s="8" t="s">
         <v>557</v>
       </c>
@@ -6665,7 +6678,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="56" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A56" s="8" t="s">
         <v>559</v>
       </c>
@@ -6701,7 +6714,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="57" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A57" s="8" t="s">
         <v>559</v>
       </c>
@@ -6737,7 +6750,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="58" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A58" s="8" t="s">
         <v>557</v>
       </c>
@@ -6764,7 +6777,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="59" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A59" s="8" t="s">
         <v>558</v>
       </c>
@@ -6794,7 +6807,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="60" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A60" s="8" t="s">
         <v>557</v>
       </c>
@@ -6821,7 +6834,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="61" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B61" s="4" t="s">
         <v>298</v>
       </c>
@@ -6854,7 +6867,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="62" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B62" s="4" t="s">
         <v>294</v>
       </c>
@@ -6887,7 +6900,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="63" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B63" s="4" t="s">
         <v>289</v>
       </c>
@@ -6920,7 +6933,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="64" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A64" s="8" t="s">
         <v>557</v>
       </c>
@@ -6947,7 +6960,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="65" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A65" s="8" t="s">
         <v>557</v>
       </c>
@@ -6974,7 +6987,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="66" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A66" s="8" t="s">
         <v>559</v>
       </c>
@@ -7010,7 +7023,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="67" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A67" s="8" t="s">
         <v>557</v>
       </c>
@@ -7037,7 +7050,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="68" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A68" s="8" t="s">
         <v>558</v>
       </c>
@@ -7067,7 +7080,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="69" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A69" s="8" t="s">
         <v>559</v>
       </c>
@@ -7094,7 +7107,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="70" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A70" s="8" t="s">
         <v>559</v>
       </c>
@@ -7121,7 +7134,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="71" spans="1:12" ht="56" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:12" ht="57" x14ac:dyDescent="0.2">
       <c r="A71" s="8" t="s">
         <v>558</v>
       </c>
@@ -7151,7 +7164,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="72" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A72" s="8" t="s">
         <v>558</v>
       </c>
@@ -7181,7 +7194,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="73" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A73" s="8" t="s">
         <v>558</v>
       </c>
@@ -7211,7 +7224,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="74" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A74" s="8" t="s">
         <v>557</v>
       </c>
@@ -7238,7 +7251,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="75" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A75" s="8" t="s">
         <v>557</v>
       </c>
@@ -7265,7 +7278,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="76" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A76" s="8" t="s">
         <v>558</v>
       </c>
@@ -7298,7 +7311,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="77" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A77" s="8" t="s">
         <v>557</v>
       </c>
@@ -7325,7 +7338,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="78" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A78" s="8" t="s">
         <v>558</v>
       </c>
@@ -7352,7 +7365,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="79" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A79" s="8" t="s">
         <v>557</v>
       </c>
@@ -7379,7 +7392,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="80" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A80" s="8" t="s">
         <v>558</v>
       </c>
@@ -7406,7 +7419,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="81" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A81" s="8" t="s">
         <v>557</v>
       </c>
@@ -7433,7 +7446,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="82" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A82" s="8" t="s">
         <v>557</v>
       </c>
@@ -7460,7 +7473,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="83" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A83" s="8" t="s">
         <v>557</v>
       </c>
@@ -7487,7 +7500,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="84" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A84" s="8" t="s">
         <v>557</v>
       </c>
@@ -7514,7 +7527,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="85" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A85" s="8" t="s">
         <v>558</v>
       </c>
@@ -7541,7 +7554,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="86" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A86" s="8" t="s">
         <v>557</v>
       </c>
@@ -7568,7 +7581,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="87" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A87" s="8" t="s">
         <v>559</v>
       </c>
@@ -7604,7 +7617,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="88" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A88" s="8" t="s">
         <v>559</v>
       </c>
@@ -7640,7 +7653,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="89" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A89" s="8" t="s">
         <v>559</v>
       </c>
@@ -7676,7 +7689,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="90" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A90" s="8" t="s">
         <v>557</v>
       </c>
@@ -7703,7 +7716,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="91" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B91" s="4" t="s">
         <v>151</v>
       </c>
@@ -7736,7 +7749,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="92" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B92" s="4" t="s">
         <v>146</v>
       </c>
@@ -7769,7 +7782,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="93" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B93" s="4" t="s">
         <v>140</v>
       </c>
@@ -7802,7 +7815,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="94" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B94" s="4" t="s">
         <v>135</v>
       </c>
@@ -7835,7 +7848,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="95" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A95" s="8" t="s">
         <v>558</v>
       </c>
@@ -7862,7 +7875,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="96" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B96" s="4" t="s">
         <v>123</v>
       </c>
@@ -7895,7 +7908,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="97" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B97" s="4" t="s">
         <v>118</v>
       </c>
@@ -7928,7 +7941,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="98" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B98" s="4" t="s">
         <v>112</v>
       </c>
@@ -7961,7 +7974,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="99" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B99" s="4" t="s">
         <v>109</v>
       </c>
@@ -7994,7 +8007,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="100" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B100" s="4" t="s">
         <v>104</v>
       </c>
@@ -8027,7 +8040,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="101" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B101" s="4" t="s">
         <v>98</v>
       </c>
@@ -8060,7 +8073,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="102" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B102" s="4" t="s">
         <v>92</v>
       </c>
@@ -8093,7 +8106,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="103" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A103" s="8" t="s">
         <v>559</v>
       </c>
@@ -8129,7 +8142,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="104" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A104" s="8" t="s">
         <v>557</v>
       </c>
@@ -8156,7 +8169,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="105" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A105" s="8" t="s">
         <v>557</v>
       </c>
@@ -8183,7 +8196,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="106" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A106" s="8" t="s">
         <v>557</v>
       </c>
@@ -8210,7 +8223,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="107" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A107" s="8" t="s">
         <v>557</v>
       </c>
@@ -8237,7 +8250,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="108" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A108" s="8" t="s">
         <v>557</v>
       </c>
@@ -8264,7 +8277,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="109" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A109" s="8" t="s">
         <v>559</v>
       </c>
@@ -8300,7 +8313,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A110" s="8" t="s">
         <v>558</v>
       </c>
@@ -8327,7 +8340,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="111" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A111" s="8" t="s">
         <v>557</v>
       </c>
@@ -8354,7 +8367,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A112" s="8" t="s">
         <v>557</v>
       </c>
@@ -8381,7 +8394,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="113" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A113" s="8" t="s">
         <v>557</v>
       </c>
@@ -8408,7 +8421,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A114" s="8" t="s">
         <v>557</v>
       </c>
@@ -8435,7 +8448,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="115" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A115" s="8" t="s">
         <v>557</v>
       </c>
@@ -8462,7 +8475,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="116" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A116" s="8" t="s">
         <v>559</v>
       </c>
@@ -8498,7 +8511,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="117" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A117" s="8" t="s">
         <v>557</v>
       </c>
@@ -8525,7 +8538,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="118" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A118" s="8" t="s">
         <v>558</v>
       </c>
@@ -8555,7 +8568,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="119" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A119" s="8" t="s">
         <v>557</v>
       </c>
@@ -8582,7 +8595,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="120" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A120" s="8" t="s">
         <v>557</v>
       </c>
@@ -8609,7 +8622,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="121" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A121" s="8" t="s">
         <v>597</v>
       </c>
@@ -8636,7 +8649,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="122" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A122" s="8" t="s">
         <v>602</v>
       </c>
@@ -8663,7 +8676,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="123" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A123" s="8" t="s">
         <v>608</v>
       </c>
@@ -8690,7 +8703,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="124" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A124" s="8" t="s">
         <v>611</v>
       </c>
@@ -8717,7 +8730,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="125" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A125" s="8" t="s">
         <v>617</v>
       </c>
@@ -8744,7 +8757,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="126" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A126" s="8" t="s">
         <v>624</v>
       </c>
@@ -8771,7 +8784,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="127" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A127" s="8" t="s">
         <v>557</v>
       </c>
@@ -8798,7 +8811,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="128" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A128" s="8" t="s">
         <v>649</v>
       </c>
@@ -8825,7 +8838,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="129" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A129" s="8" t="s">
         <v>653</v>
       </c>
@@ -8852,7 +8865,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="130" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A130" s="8" t="s">
         <v>659</v>
       </c>
@@ -8879,7 +8892,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="131" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A131" s="8" t="s">
         <v>664</v>
       </c>
@@ -8906,7 +8919,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A132" s="8" t="s">
         <v>557</v>
       </c>
@@ -8933,7 +8946,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="133" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A133" s="8" t="s">
         <v>557</v>
       </c>
@@ -8960,7 +8973,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="134" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A134" s="8" t="s">
         <v>681</v>
       </c>
@@ -8987,7 +9000,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="135" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A135" s="8" t="s">
         <v>687</v>
       </c>
@@ -9014,7 +9027,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="136" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A136" s="8" t="s">
         <v>691</v>
       </c>
@@ -9041,7 +9054,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="137" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A137" s="8" t="s">
         <v>699</v>
       </c>
@@ -9068,7 +9081,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="138" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A138" s="8" t="s">
         <v>704</v>
       </c>
@@ -9095,7 +9108,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="139" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A139" s="8" t="s">
         <v>711</v>
       </c>
@@ -9122,7 +9135,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="140" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A140" s="8" t="s">
         <v>716</v>
       </c>
@@ -9149,7 +9162,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="141" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A141" s="8" t="s">
         <v>724</v>
       </c>
@@ -9176,7 +9189,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="142" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A142" s="8" t="s">
         <v>727</v>
       </c>
@@ -9203,7 +9216,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="143" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A143" s="8" t="s">
         <v>736</v>
       </c>
@@ -9230,7 +9243,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="144" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A144" s="8" t="s">
         <v>740</v>
       </c>
@@ -9257,7 +9270,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="145" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A145" s="8" t="s">
         <v>746</v>
       </c>
@@ -9284,7 +9297,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="146" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A146" s="8" t="s">
         <v>754</v>
       </c>
@@ -9311,7 +9324,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="147" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A147" s="8" t="s">
         <v>759</v>
       </c>
@@ -9338,7 +9351,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="148" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A148" s="8" t="s">
         <v>770</v>
       </c>
@@ -9365,7 +9378,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="149" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A149" s="8" t="s">
         <v>777</v>
       </c>
@@ -9392,7 +9405,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="150" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A150" s="8" t="s">
         <v>782</v>
       </c>
@@ -9419,7 +9432,7 @@
         <v>786</v>
       </c>
     </row>
-    <row r="151" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A151" s="8" t="s">
         <v>557</v>
       </c>
@@ -9446,7 +9459,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="152" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A152" s="8" t="s">
         <v>795</v>
       </c>
@@ -9473,7 +9486,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A153" s="8" t="s">
         <v>800</v>
       </c>
@@ -9500,7 +9513,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A154" s="8" t="s">
         <v>804</v>
       </c>
@@ -9527,7 +9540,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A155" s="8" t="s">
         <v>811</v>
       </c>
@@ -9554,7 +9567,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="156" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A156" s="8" t="s">
         <v>557</v>
       </c>
@@ -9581,7 +9594,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A157" s="8" t="s">
         <v>557</v>
       </c>
@@ -9608,7 +9621,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A158" s="8" t="s">
         <v>827</v>
       </c>
@@ -9635,7 +9648,7 @@
         <v>831</v>
       </c>
     </row>
-    <row r="159" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A159" s="8" t="s">
         <v>557</v>
       </c>
@@ -9662,7 +9675,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A160" s="8" t="s">
         <v>838</v>
       </c>
@@ -9689,7 +9702,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="161" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A161" s="8" t="s">
         <v>557</v>
       </c>
@@ -9716,7 +9729,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A162" s="8" t="s">
         <v>850</v>
       </c>
@@ -9743,7 +9756,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A163" s="8" t="s">
         <v>857</v>
       </c>
@@ -9770,7 +9783,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A164" s="8" t="s">
         <v>557</v>
       </c>
@@ -9797,7 +9810,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="165" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A165" s="8" t="s">
         <v>557</v>
       </c>
@@ -9824,7 +9837,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A166" s="8" t="s">
         <v>557</v>
       </c>
@@ -9851,7 +9864,7 @@
         <v>871</v>
       </c>
     </row>
-    <row r="167" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A167" s="8" t="s">
         <v>557</v>
       </c>
@@ -9878,7 +9891,7 @@
         <v>879</v>
       </c>
     </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A168" s="8" t="s">
         <v>557</v>
       </c>
@@ -9905,7 +9918,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A169" s="8" t="s">
         <v>557</v>
       </c>
@@ -9932,7 +9945,7 @@
         <v>889</v>
       </c>
     </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A170" s="8" t="s">
         <v>557</v>
       </c>
@@ -9959,7 +9972,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A171" s="8" t="s">
         <v>557</v>
       </c>
@@ -9986,7 +9999,7 @@
         <v>897</v>
       </c>
     </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A172" s="8" t="s">
         <v>902</v>
       </c>
@@ -10013,7 +10026,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A173" s="8" t="s">
         <v>902</v>
       </c>
@@ -10040,7 +10053,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A174" s="8" t="s">
         <v>557</v>
       </c>
@@ -10067,7 +10080,7 @@
         <v>915</v>
       </c>
     </row>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A175" s="8" t="s">
         <v>557</v>
       </c>
@@ -10094,7 +10107,7 @@
         <v>919</v>
       </c>
     </row>
-    <row r="176" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A176" s="8" t="s">
         <v>557</v>
       </c>
@@ -10121,7 +10134,7 @@
         <v>925</v>
       </c>
     </row>
-    <row r="177" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A177" s="8" t="s">
         <v>557</v>
       </c>
@@ -10148,7 +10161,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="178" spans="1:13" ht="28" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A178" s="8" t="s">
         <v>557</v>
       </c>
@@ -10175,7 +10188,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="179" spans="1:13" ht="42" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:13" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A179" s="8" t="s">
         <v>938</v>
       </c>
@@ -10202,7 +10215,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="180" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B180" s="4" t="s">
         <v>942</v>
       </c>
@@ -10226,7 +10239,7 @@
         <v>946</v>
       </c>
     </row>
-    <row r="181" spans="1:13" ht="28" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B181" s="4" t="s">
         <v>948</v>
       </c>
@@ -10250,7 +10263,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="182" spans="1:13" ht="28" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B182" s="4" t="s">
         <v>954</v>
       </c>
@@ -10274,7 +10287,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="183" spans="1:13" ht="42" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:13" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B183" s="4" t="s">
         <v>959</v>
       </c>
@@ -10298,7 +10311,7 @@
         <v>960</v>
       </c>
     </row>
-    <row r="184" spans="1:13" ht="28" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B184" s="4" t="s">
         <v>966</v>
       </c>
@@ -10322,7 +10335,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="185" spans="1:13" ht="28" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B185" s="4" t="s">
         <v>971</v>
       </c>
@@ -10346,7 +10359,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="186" spans="1:13" ht="42" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:13" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B186" s="4" t="s">
         <v>976</v>
       </c>
@@ -10370,7 +10383,7 @@
         <v>963</v>
       </c>
     </row>
-    <row r="187" spans="1:13" ht="42" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:13" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B187" s="4" t="s">
         <v>979</v>
       </c>
@@ -10394,7 +10407,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="188" spans="1:13" ht="28" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B188" s="4" t="s">
         <v>985</v>
       </c>
@@ -10421,7 +10434,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="189" spans="1:13" ht="15.5" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:13" ht="15" x14ac:dyDescent="0.2">
       <c r="B189" s="4" t="s">
         <v>988</v>
       </c>
@@ -10446,7 +10459,7 @@
       </c>
       <c r="M189" s="6"/>
     </row>
-    <row r="190" spans="1:13" ht="28" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B190" s="4" t="s">
         <v>992</v>
       </c>
@@ -10470,7 +10483,7 @@
         <v>982</v>
       </c>
     </row>
-    <row r="191" spans="1:13" ht="46.5" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:13" ht="45" x14ac:dyDescent="0.2">
       <c r="B191" s="4" t="s">
         <v>1002</v>
       </c>
@@ -10494,7 +10507,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="192" spans="1:13" ht="28" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B192" s="4" t="s">
         <v>1006</v>
       </c>
@@ -10518,7 +10531,7 @@
         <v>998</v>
       </c>
     </row>
-    <row r="193" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="193" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B193" s="4" t="s">
         <v>1010</v>
       </c>
@@ -10542,7 +10555,7 @@
         <v>1011</v>
       </c>
     </row>
-    <row r="194" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="194" spans="2:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B194" s="4" t="s">
         <v>1015</v>
       </c>
@@ -10569,7 +10582,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="195" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="195" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B195" s="4" t="s">
         <v>1021</v>
       </c>
@@ -10593,7 +10606,7 @@
         <v>1019</v>
       </c>
     </row>
-    <row r="196" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="196" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B196" s="4" t="s">
         <v>1025</v>
       </c>
@@ -10617,7 +10630,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="197" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="197" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B197" s="4" t="s">
         <v>1031</v>
       </c>
@@ -10641,7 +10654,7 @@
         <v>1033</v>
       </c>
     </row>
-    <row r="198" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="198" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B198" s="4" t="s">
         <v>1034</v>
       </c>
@@ -10665,7 +10678,7 @@
         <v>1035</v>
       </c>
     </row>
-    <row r="199" spans="2:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="199" spans="2:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B199" s="4" t="s">
         <v>1040</v>
       </c>
@@ -10689,7 +10702,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="200" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="200" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B200" s="4" t="s">
         <v>1045</v>
       </c>
@@ -10713,7 +10726,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="201" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="201" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B201" s="4" t="s">
         <v>1051</v>
       </c>
@@ -10737,7 +10750,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="202" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="202" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B202" s="4" t="s">
         <v>1058</v>
       </c>
@@ -10761,7 +10774,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="203" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="203" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B203" s="4" t="s">
         <v>1062</v>
       </c>
@@ -10785,7 +10798,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="204" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="204" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B204" s="4" t="s">
         <v>1065</v>
       </c>
@@ -10809,7 +10822,7 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="205" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="205" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B205" s="4" t="s">
         <v>1071</v>
       </c>
@@ -10833,7 +10846,7 @@
         <v>1069</v>
       </c>
     </row>
-    <row r="206" spans="2:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="206" spans="2:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B206" s="4" t="s">
         <v>1074</v>
       </c>
@@ -10857,7 +10870,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="207" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="207" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B207" s="4" t="s">
         <v>1080</v>
       </c>
@@ -10881,7 +10894,7 @@
         <v>1079</v>
       </c>
     </row>
-    <row r="208" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="208" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B208" s="4" t="s">
         <v>1082</v>
       </c>
@@ -10905,7 +10918,7 @@
         <v>1081</v>
       </c>
     </row>
-    <row r="209" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="209" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B209" s="4" t="s">
         <v>1091</v>
       </c>
@@ -10929,7 +10942,7 @@
         <v>1089</v>
       </c>
     </row>
-    <row r="210" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="210" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B210" s="4" t="s">
         <v>1093</v>
       </c>
@@ -10953,7 +10966,7 @@
         <v>1092</v>
       </c>
     </row>
-    <row r="211" spans="2:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="211" spans="2:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B211" s="4" t="s">
         <v>1102</v>
       </c>
@@ -10977,7 +10990,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="212" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="212" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B212" s="4" t="s">
         <v>1105</v>
       </c>
@@ -11001,7 +11014,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="213" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="213" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B213" s="4" t="s">
         <v>1110</v>
       </c>
@@ -11025,7 +11038,7 @@
         <v>1109</v>
       </c>
     </row>
-    <row r="214" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="214" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B214" s="4" t="s">
         <v>1118</v>
       </c>
@@ -11052,7 +11065,7 @@
         <v>1114</v>
       </c>
     </row>
-    <row r="215" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="215" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B215" s="4" t="s">
         <v>1121</v>
       </c>
@@ -11076,7 +11089,7 @@
         <v>1116</v>
       </c>
     </row>
-    <row r="216" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="216" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B216" s="4" t="s">
         <v>1126</v>
       </c>
@@ -11103,7 +11116,7 @@
         <v>1131</v>
       </c>
     </row>
-    <row r="217" spans="2:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="217" spans="2:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B217" s="4" t="s">
         <v>1134</v>
       </c>
@@ -11127,7 +11140,7 @@
         <v>1113</v>
       </c>
     </row>
-    <row r="218" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="218" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B218" s="4" t="s">
         <v>1137</v>
       </c>
@@ -11154,7 +11167,7 @@
         <v>1132</v>
       </c>
     </row>
-    <row r="219" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="219" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B219" s="4" t="s">
         <v>1142</v>
       </c>
@@ -11178,7 +11191,7 @@
         <v>1120</v>
       </c>
     </row>
-    <row r="220" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="220" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B220" s="4" t="s">
         <v>1145</v>
       </c>
@@ -11202,7 +11215,7 @@
         <v>1149</v>
       </c>
     </row>
-    <row r="221" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="221" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B221" s="4" t="s">
         <v>1150</v>
       </c>
@@ -11226,7 +11239,7 @@
         <v>1154</v>
       </c>
     </row>
-    <row r="222" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="222" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B222" s="4" t="s">
         <v>1153</v>
       </c>
@@ -11250,7 +11263,7 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="223" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="223" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B223" s="4" t="s">
         <v>1161</v>
       </c>
@@ -11274,7 +11287,7 @@
         <v>1160</v>
       </c>
     </row>
-    <row r="224" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="224" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B224" s="4" t="s">
         <v>1165</v>
       </c>
@@ -11298,7 +11311,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="225" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="225" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B225" s="4" t="s">
         <v>1167</v>
       </c>
@@ -11325,7 +11338,7 @@
         <v>1166</v>
       </c>
     </row>
-    <row r="226" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="226" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B226" s="4" t="s">
         <v>1173</v>
       </c>
@@ -11349,554 +11362,566 @@
         <v>1174</v>
       </c>
     </row>
-    <row r="227" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="227" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="B227" s="4" t="s">
+        <v>1181</v>
+      </c>
+      <c r="C227" s="1" t="s">
+        <v>1182</v>
+      </c>
+      <c r="H227" s="1" t="s">
+        <v>58</v>
+      </c>
       <c r="J227" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>00</v>
-      </c>
-    </row>
-    <row r="228" spans="2:12" x14ac:dyDescent="0.3">
+        <v>001132</v>
+      </c>
+      <c r="L227" s="2" t="s">
+        <v>1180</v>
+      </c>
+    </row>
+    <row r="228" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J228" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="229" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="229" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J229" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="230" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="230" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J230" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="231" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="231" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J231" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="232" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="232" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J232" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="233" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="233" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J233" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="234" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="234" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J234" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="235" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="235" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J235" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="236" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="236" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J236" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="237" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="237" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J237" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="238" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="238" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J238" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="239" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="239" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J239" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="240" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="240" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J240" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="241" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="241" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J241" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="242" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="242" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J242" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="243" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="243" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J243" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="244" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="244" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J244" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="245" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="245" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J245" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="246" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="246" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J246" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="247" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="247" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J247" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="248" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="248" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J248" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="249" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="249" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J249" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="250" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="250" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J250" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="251" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="251" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J251" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="252" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="252" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J252" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="253" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="253" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J253" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="254" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="254" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J254" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="255" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="255" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J255" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="256" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="256" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J256" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="257" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="257" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J257" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="258" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="258" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J258" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="259" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="259" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J259" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="260" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="260" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J260" s="5" t="str">
         <f t="shared" ref="J260:J317" si="8">"00"&amp;B260</f>
         <v>00</v>
       </c>
     </row>
-    <row r="261" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="261" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J261" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="262" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="262" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J262" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="263" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="263" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J263" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="264" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="264" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J264" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="265" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="265" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J265" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="266" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="266" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J266" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="267" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="267" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J267" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="268" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="268" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J268" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="269" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="269" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J269" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="270" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="270" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J270" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="271" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="271" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J271" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="272" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="272" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J272" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="273" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="273" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J273" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="274" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="274" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J274" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="275" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="275" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J275" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="276" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="276" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J276" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="277" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="277" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J277" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="278" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="278" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J278" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="279" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="279" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J279" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="280" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="280" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J280" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="281" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="281" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J281" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="282" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="282" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J282" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="283" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="283" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J283" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="284" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="284" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J284" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="285" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="285" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J285" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="286" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="286" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J286" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="287" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="287" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J287" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="288" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="288" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J288" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="289" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="289" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J289" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="290" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="290" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J290" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="291" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="291" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J291" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="292" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="292" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J292" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="293" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="293" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J293" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="294" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="294" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J294" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="295" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="295" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J295" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="296" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="296" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J296" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="297" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="297" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J297" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="298" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="298" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J298" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="299" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="299" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J299" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="300" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="300" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J300" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="301" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="301" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J301" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="302" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="302" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J302" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="303" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="303" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J303" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="304" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="304" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J304" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="305" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="305" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J305" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="306" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="306" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J306" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="307" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="307" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J307" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="308" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="308" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J308" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="309" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="309" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J309" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="310" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="310" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J310" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="311" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="311" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J311" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="312" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="312" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J312" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="313" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="313" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J313" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="314" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="314" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J314" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="315" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="315" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J315" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="316" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="316" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J316" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="317" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="317" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J317" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:L4"/>
+  <autoFilter ref="A4:L4" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="1">
     <mergeCell ref="A2:L2"/>
   </mergeCells>
@@ -11908,10 +11933,10 @@
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1:E1 D3:E3 D6:E1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1:E1 D3:E3 D6:E1048576" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"是,否"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H1 H3:H1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H1 H3:H1048576" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"VB编程,系统运维,WEB学习,游戏碎片,日常随笔,浥尘伙伴社团"</formula1>
     </dataValidation>
   </dataValidations>
@@ -11921,20 +11946,20 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A2:L34"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="6.33203125" customWidth="1"/>
+    <col min="2" max="2" width="6.375" customWidth="1"/>
     <col min="3" max="3" width="34" style="4" customWidth="1"/>
     <col min="4" max="4" width="4.75" customWidth="1"/>
-    <col min="8" max="8" width="6.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="19" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="7.08203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.08203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:12" ht="22.5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" ht="23.25" x14ac:dyDescent="0.2">
       <c r="A2" s="21" t="s">
         <v>549</v>
       </c>
@@ -11950,7 +11975,7 @@
       <c r="K2" s="21"/>
       <c r="L2" s="21"/>
     </row>
-    <row r="4" spans="1:12" ht="56" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" ht="57" x14ac:dyDescent="0.2">
       <c r="A4" s="7" t="s">
         <v>0</v>
       </c>
@@ -11988,7 +12013,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
         <v>533</v>
       </c>
@@ -12011,7 +12036,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C8" s="15" t="s">
         <v>545</v>
       </c>
@@ -12020,7 +12045,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C9" s="4" t="s">
         <v>539</v>
       </c>
@@ -12028,7 +12053,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C10" t="s">
         <v>537</v>
       </c>
@@ -12036,7 +12061,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C11" t="s">
         <v>538</v>
       </c>
@@ -12044,7 +12069,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="22.5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" ht="23.25" x14ac:dyDescent="0.2">
       <c r="A13" s="21" t="s">
         <v>543</v>
       </c>
@@ -12060,7 +12085,7 @@
       <c r="K13" s="21"/>
       <c r="L13" s="21"/>
     </row>
-    <row r="15" spans="1:12" ht="56" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" ht="57" x14ac:dyDescent="0.2">
       <c r="A15" s="7" t="s">
         <v>0</v>
       </c>
@@ -12098,7 +12123,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
         <v>533</v>
       </c>
@@ -12124,7 +12149,7 @@
         <v>54837657</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C19" s="15" t="s">
         <v>545</v>
       </c>
@@ -12133,7 +12158,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C20" s="4" t="s">
         <v>539</v>
       </c>
@@ -12141,7 +12166,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C21" t="s">
         <v>537</v>
       </c>
@@ -12149,7 +12174,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C22" t="s">
         <v>538</v>
       </c>
@@ -12157,10 +12182,10 @@
         <v>541</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C23"/>
     </row>
-    <row r="25" spans="1:12" ht="22.5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" ht="23.25" x14ac:dyDescent="0.2">
       <c r="A25" s="21" t="s">
         <v>550</v>
       </c>
@@ -12176,7 +12201,7 @@
       <c r="K25" s="21"/>
       <c r="L25" s="21"/>
     </row>
-    <row r="27" spans="1:12" ht="56" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" ht="57" x14ac:dyDescent="0.2">
       <c r="A27" s="7" t="s">
         <v>0</v>
       </c>
@@ -12214,7 +12239,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B28" t="s">
         <v>533</v>
       </c>
@@ -12240,7 +12265,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C31" s="15" t="s">
         <v>545</v>
       </c>
@@ -12249,7 +12274,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C32" s="4" t="s">
         <v>539</v>
       </c>
@@ -12257,7 +12282,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="33" spans="3:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="3:5" x14ac:dyDescent="0.2">
       <c r="C33" t="s">
         <v>537</v>
       </c>
@@ -12265,7 +12290,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="34" spans="3:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="3:5" x14ac:dyDescent="0.2">
       <c r="C34" t="s">
         <v>538</v>
       </c>
@@ -12281,7 +12306,7 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H15 H27 H4">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H15 H27 H4" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"VB编程,系统运维,WEB学习,游戏碎片,日常随笔"</formula1>
     </dataValidation>
   </dataValidations>

--- a/11_付费课程/99.资料/文章信息备忘表.xlsx
+++ b/11_付费课程/99.资料/文章信息备忘表.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Disks\E\Writing\11_付费课程\99.资料\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\writing\11_付费课程\99.资料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD1CDA0A-EF48-458A-A86B-26A09F675202}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1960" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$L$4</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -40,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1619" uniqueCount="1183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1621" uniqueCount="1185">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -4718,13 +4717,21 @@
   </si>
   <si>
     <t>小时候的众多绝版老游戏，想玩就去养老院？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-05-18 19:11:16</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>611191</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -5216,25 +5223,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A2:M317"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.25" style="8" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="4" customWidth="1"/>
-    <col min="3" max="3" width="30.875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="5.375" style="6" customWidth="1"/>
-    <col min="5" max="6" width="5.125" style="6" customWidth="1"/>
+    <col min="2" max="2" width="5.58203125" style="4" customWidth="1"/>
+    <col min="3" max="3" width="30.83203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="5.33203125" style="6" customWidth="1"/>
+    <col min="5" max="6" width="5.08203125" style="6" customWidth="1"/>
     <col min="7" max="7" width="5.25" style="6" customWidth="1"/>
     <col min="8" max="8" width="13.5" style="1" customWidth="1"/>
     <col min="9" max="9" width="19" style="4" customWidth="1"/>
-    <col min="10" max="10" width="8.625" style="5" customWidth="1"/>
+    <col min="10" max="10" width="8.58203125" style="5" customWidth="1"/>
     <col min="11" max="11" width="7.5" style="3" customWidth="1"/>
     <col min="12" max="12" width="9.25" style="2" customWidth="1"/>
     <col min="13" max="13" width="16.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" ht="25" x14ac:dyDescent="0.3">
       <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
@@ -5250,8 +5257,8 @@
       <c r="K2" s="20"/>
       <c r="L2" s="20"/>
     </row>
-    <row r="3" spans="1:12" ht="6.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="4" spans="1:12" s="7" customFormat="1" ht="57" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12" ht="6.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:12" s="7" customFormat="1" ht="56" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>0</v>
       </c>
@@ -5289,7 +5296,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
         <v>557</v>
       </c>
@@ -5316,7 +5323,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
         <v>559</v>
       </c>
@@ -5352,7 +5359,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
         <v>559</v>
       </c>
@@ -5388,25 +5395,25 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="J8" s="5" t="str">
         <f t="shared" si="0"/>
         <v>000</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="J9" s="5" t="str">
         <f t="shared" si="0"/>
         <v>000</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="J10" s="5" t="str">
         <f t="shared" si="0"/>
         <v>000</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
         <v>522</v>
       </c>
@@ -5439,7 +5446,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
         <v>558</v>
       </c>
@@ -5469,7 +5476,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A13" s="8" t="s">
         <v>558</v>
       </c>
@@ -5499,7 +5506,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A14" s="8" t="s">
         <v>640</v>
       </c>
@@ -5526,7 +5533,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="8" t="s">
         <v>557</v>
       </c>
@@ -5553,7 +5560,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="8" t="s">
         <v>557</v>
       </c>
@@ -5580,7 +5587,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="8" t="s">
         <v>557</v>
       </c>
@@ -5607,7 +5614,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="8" t="s">
         <v>767</v>
       </c>
@@ -5634,7 +5641,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
         <v>557</v>
       </c>
@@ -5661,7 +5668,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A20" s="8" t="s">
         <v>557</v>
       </c>
@@ -5688,7 +5695,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A21" s="8" t="s">
         <v>557</v>
       </c>
@@ -5715,7 +5722,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A22" s="8" t="s">
         <v>559</v>
       </c>
@@ -5751,7 +5758,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" s="8" t="s">
         <v>557</v>
       </c>
@@ -5778,7 +5785,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A24" s="8" t="s">
         <v>558</v>
       </c>
@@ -5808,7 +5815,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A25" s="8" t="s">
         <v>557</v>
       </c>
@@ -5835,7 +5842,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A26" s="8" t="s">
         <v>557</v>
       </c>
@@ -5862,7 +5869,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="27" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A27" s="8" t="s">
         <v>633</v>
       </c>
@@ -5889,7 +5896,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A28" s="8" t="s">
         <v>557</v>
       </c>
@@ -5916,7 +5923,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A29" s="8" t="s">
         <v>559</v>
       </c>
@@ -5952,7 +5959,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A30" s="8" t="s">
         <v>559</v>
       </c>
@@ -5988,7 +5995,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A31" s="8" t="s">
         <v>557</v>
       </c>
@@ -6015,7 +6022,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A32" s="8" t="s">
         <v>557</v>
       </c>
@@ -6042,7 +6049,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A33" s="8" t="s">
         <v>557</v>
       </c>
@@ -6069,7 +6076,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="34" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A34" s="8" t="s">
         <v>557</v>
       </c>
@@ -6096,7 +6103,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="35" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A35" s="8" t="s">
         <v>557</v>
       </c>
@@ -6123,7 +6130,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="36" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A36" s="8" t="s">
         <v>557</v>
       </c>
@@ -6150,7 +6157,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="37" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A37" s="8" t="s">
         <v>559</v>
       </c>
@@ -6186,7 +6193,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="38" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A38" s="8" t="s">
         <v>557</v>
       </c>
@@ -6213,7 +6220,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" s="8" t="s">
         <v>557</v>
       </c>
@@ -6240,7 +6247,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="40" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A40" s="8" t="s">
         <v>557</v>
       </c>
@@ -6267,7 +6274,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="41" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A41" s="8" t="s">
         <v>557</v>
       </c>
@@ -6294,7 +6301,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="42" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A42" s="8" t="s">
         <v>557</v>
       </c>
@@ -6321,7 +6328,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="43" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A43" s="8" t="s">
         <v>559</v>
       </c>
@@ -6354,7 +6361,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="44" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A44" s="8" t="s">
         <v>557</v>
       </c>
@@ -6381,7 +6388,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="45" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A45" s="8" t="s">
         <v>557</v>
       </c>
@@ -6408,7 +6415,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="46" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A46" s="8" t="s">
         <v>557</v>
       </c>
@@ -6435,7 +6442,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" s="8" t="s">
         <v>557</v>
       </c>
@@ -6462,7 +6469,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="48" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A48" s="8" t="s">
         <v>557</v>
       </c>
@@ -6489,7 +6496,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="49" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A49" s="8" t="s">
         <v>557</v>
       </c>
@@ -6516,7 +6523,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="50" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A50" s="8" t="s">
         <v>557</v>
       </c>
@@ -6543,7 +6550,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" s="8" t="s">
         <v>557</v>
       </c>
@@ -6570,7 +6577,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="52" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A52" s="8" t="s">
         <v>557</v>
       </c>
@@ -6597,7 +6604,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" s="8" t="s">
         <v>557</v>
       </c>
@@ -6624,7 +6631,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="54" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A54" s="8" t="s">
         <v>557</v>
       </c>
@@ -6651,7 +6658,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" s="8" t="s">
         <v>557</v>
       </c>
@@ -6678,7 +6685,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="56" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A56" s="8" t="s">
         <v>559</v>
       </c>
@@ -6714,7 +6721,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="57" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A57" s="8" t="s">
         <v>559</v>
       </c>
@@ -6750,7 +6757,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="58" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A58" s="8" t="s">
         <v>557</v>
       </c>
@@ -6777,7 +6784,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="59" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A59" s="8" t="s">
         <v>558</v>
       </c>
@@ -6807,7 +6814,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="60" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A60" s="8" t="s">
         <v>557</v>
       </c>
@@ -6834,7 +6841,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="61" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B61" s="4" t="s">
         <v>298</v>
       </c>
@@ -6867,7 +6874,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="62" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B62" s="4" t="s">
         <v>294</v>
       </c>
@@ -6900,7 +6907,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="63" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B63" s="4" t="s">
         <v>289</v>
       </c>
@@ -6933,7 +6940,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="64" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A64" s="8" t="s">
         <v>557</v>
       </c>
@@ -6960,7 +6967,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="65" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A65" s="8" t="s">
         <v>557</v>
       </c>
@@ -6987,7 +6994,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="66" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A66" s="8" t="s">
         <v>559</v>
       </c>
@@ -7023,7 +7030,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="67" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A67" s="8" t="s">
         <v>557</v>
       </c>
@@ -7050,7 +7057,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="68" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A68" s="8" t="s">
         <v>558</v>
       </c>
@@ -7080,7 +7087,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="69" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A69" s="8" t="s">
         <v>559</v>
       </c>
@@ -7107,7 +7114,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="70" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A70" s="8" t="s">
         <v>559</v>
       </c>
@@ -7134,7 +7141,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="71" spans="1:12" ht="57" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:12" ht="56" x14ac:dyDescent="0.3">
       <c r="A71" s="8" t="s">
         <v>558</v>
       </c>
@@ -7164,7 +7171,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="72" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A72" s="8" t="s">
         <v>558</v>
       </c>
@@ -7194,7 +7201,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="73" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A73" s="8" t="s">
         <v>558</v>
       </c>
@@ -7224,7 +7231,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="74" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A74" s="8" t="s">
         <v>557</v>
       </c>
@@ -7251,7 +7258,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="75" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A75" s="8" t="s">
         <v>557</v>
       </c>
@@ -7278,7 +7285,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="76" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A76" s="8" t="s">
         <v>558</v>
       </c>
@@ -7311,7 +7318,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="77" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A77" s="8" t="s">
         <v>557</v>
       </c>
@@ -7338,7 +7345,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="78" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A78" s="8" t="s">
         <v>558</v>
       </c>
@@ -7365,7 +7372,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="79" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A79" s="8" t="s">
         <v>557</v>
       </c>
@@ -7392,7 +7399,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="80" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A80" s="8" t="s">
         <v>558</v>
       </c>
@@ -7419,7 +7426,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="81" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A81" s="8" t="s">
         <v>557</v>
       </c>
@@ -7446,7 +7453,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="82" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A82" s="8" t="s">
         <v>557</v>
       </c>
@@ -7473,7 +7480,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="83" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A83" s="8" t="s">
         <v>557</v>
       </c>
@@ -7500,7 +7507,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="84" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A84" s="8" t="s">
         <v>557</v>
       </c>
@@ -7527,7 +7534,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="85" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A85" s="8" t="s">
         <v>558</v>
       </c>
@@ -7554,7 +7561,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="86" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A86" s="8" t="s">
         <v>557</v>
       </c>
@@ -7581,7 +7588,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="87" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A87" s="8" t="s">
         <v>559</v>
       </c>
@@ -7617,7 +7624,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="88" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A88" s="8" t="s">
         <v>559</v>
       </c>
@@ -7653,7 +7660,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="89" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A89" s="8" t="s">
         <v>559</v>
       </c>
@@ -7689,7 +7696,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="90" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A90" s="8" t="s">
         <v>557</v>
       </c>
@@ -7716,7 +7723,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="91" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B91" s="4" t="s">
         <v>151</v>
       </c>
@@ -7749,7 +7756,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="92" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B92" s="4" t="s">
         <v>146</v>
       </c>
@@ -7782,7 +7789,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="93" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B93" s="4" t="s">
         <v>140</v>
       </c>
@@ -7815,7 +7822,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="94" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B94" s="4" t="s">
         <v>135</v>
       </c>
@@ -7848,7 +7855,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="95" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A95" s="8" t="s">
         <v>558</v>
       </c>
@@ -7875,7 +7882,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="96" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="B96" s="4" t="s">
         <v>123</v>
       </c>
@@ -7908,7 +7915,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="97" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B97" s="4" t="s">
         <v>118</v>
       </c>
@@ -7941,7 +7948,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="98" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="B98" s="4" t="s">
         <v>112</v>
       </c>
@@ -7974,7 +7981,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="99" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B99" s="4" t="s">
         <v>109</v>
       </c>
@@ -8007,7 +8014,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="100" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B100" s="4" t="s">
         <v>104</v>
       </c>
@@ -8040,7 +8047,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="101" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="B101" s="4" t="s">
         <v>98</v>
       </c>
@@ -8073,7 +8080,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="102" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B102" s="4" t="s">
         <v>92</v>
       </c>
@@ -8106,7 +8113,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="103" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A103" s="8" t="s">
         <v>559</v>
       </c>
@@ -8142,7 +8149,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="104" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A104" s="8" t="s">
         <v>557</v>
       </c>
@@ -8169,7 +8176,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="105" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A105" s="8" t="s">
         <v>557</v>
       </c>
@@ -8196,7 +8203,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="106" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A106" s="8" t="s">
         <v>557</v>
       </c>
@@ -8223,7 +8230,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="107" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A107" s="8" t="s">
         <v>557</v>
       </c>
@@ -8250,7 +8257,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="108" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A108" s="8" t="s">
         <v>557</v>
       </c>
@@ -8277,7 +8284,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="109" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A109" s="8" t="s">
         <v>559</v>
       </c>
@@ -8313,7 +8320,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A110" s="8" t="s">
         <v>558</v>
       </c>
@@ -8340,7 +8347,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="111" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A111" s="8" t="s">
         <v>557</v>
       </c>
@@ -8367,7 +8374,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="112" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A112" s="8" t="s">
         <v>557</v>
       </c>
@@ -8394,7 +8401,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="113" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A113" s="8" t="s">
         <v>557</v>
       </c>
@@ -8421,7 +8428,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A114" s="8" t="s">
         <v>557</v>
       </c>
@@ -8448,7 +8455,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="115" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A115" s="8" t="s">
         <v>557</v>
       </c>
@@ -8475,7 +8482,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="116" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A116" s="8" t="s">
         <v>559</v>
       </c>
@@ -8511,7 +8518,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="117" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A117" s="8" t="s">
         <v>557</v>
       </c>
@@ -8538,7 +8545,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="118" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A118" s="8" t="s">
         <v>558</v>
       </c>
@@ -8568,7 +8575,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="119" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A119" s="8" t="s">
         <v>557</v>
       </c>
@@ -8595,7 +8602,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="120" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A120" s="8" t="s">
         <v>557</v>
       </c>
@@ -8622,7 +8629,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="121" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A121" s="8" t="s">
         <v>597</v>
       </c>
@@ -8649,7 +8656,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="122" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A122" s="8" t="s">
         <v>602</v>
       </c>
@@ -8676,7 +8683,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="123" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A123" s="8" t="s">
         <v>608</v>
       </c>
@@ -8703,7 +8710,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="124" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A124" s="8" t="s">
         <v>611</v>
       </c>
@@ -8730,7 +8737,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="125" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A125" s="8" t="s">
         <v>617</v>
       </c>
@@ -8757,7 +8764,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="126" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A126" s="8" t="s">
         <v>624</v>
       </c>
@@ -8784,7 +8791,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="127" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A127" s="8" t="s">
         <v>557</v>
       </c>
@@ -8811,7 +8818,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="128" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A128" s="8" t="s">
         <v>649</v>
       </c>
@@ -8838,7 +8845,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="129" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A129" s="8" t="s">
         <v>653</v>
       </c>
@@ -8865,7 +8872,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="130" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A130" s="8" t="s">
         <v>659</v>
       </c>
@@ -8892,7 +8899,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="131" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A131" s="8" t="s">
         <v>664</v>
       </c>
@@ -8919,7 +8926,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A132" s="8" t="s">
         <v>557</v>
       </c>
@@ -8946,7 +8953,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="133" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A133" s="8" t="s">
         <v>557</v>
       </c>
@@ -8973,7 +8980,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="134" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A134" s="8" t="s">
         <v>681</v>
       </c>
@@ -9000,7 +9007,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="135" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A135" s="8" t="s">
         <v>687</v>
       </c>
@@ -9027,7 +9034,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="136" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A136" s="8" t="s">
         <v>691</v>
       </c>
@@ -9054,7 +9061,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="137" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A137" s="8" t="s">
         <v>699</v>
       </c>
@@ -9081,7 +9088,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="138" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A138" s="8" t="s">
         <v>704</v>
       </c>
@@ -9108,7 +9115,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="139" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A139" s="8" t="s">
         <v>711</v>
       </c>
@@ -9135,7 +9142,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="140" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A140" s="8" t="s">
         <v>716</v>
       </c>
@@ -9162,7 +9169,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="141" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A141" s="8" t="s">
         <v>724</v>
       </c>
@@ -9189,7 +9196,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="142" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A142" s="8" t="s">
         <v>727</v>
       </c>
@@ -9216,7 +9223,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="143" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A143" s="8" t="s">
         <v>736</v>
       </c>
@@ -9243,7 +9250,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="144" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A144" s="8" t="s">
         <v>740</v>
       </c>
@@ -9270,7 +9277,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="145" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A145" s="8" t="s">
         <v>746</v>
       </c>
@@ -9297,7 +9304,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="146" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A146" s="8" t="s">
         <v>754</v>
       </c>
@@ -9324,7 +9331,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="147" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A147" s="8" t="s">
         <v>759</v>
       </c>
@@ -9351,7 +9358,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="148" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A148" s="8" t="s">
         <v>770</v>
       </c>
@@ -9378,7 +9385,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="149" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A149" s="8" t="s">
         <v>777</v>
       </c>
@@ -9405,7 +9412,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="150" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A150" s="8" t="s">
         <v>782</v>
       </c>
@@ -9432,7 +9439,7 @@
         <v>786</v>
       </c>
     </row>
-    <row r="151" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A151" s="8" t="s">
         <v>557</v>
       </c>
@@ -9459,7 +9466,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="152" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A152" s="8" t="s">
         <v>795</v>
       </c>
@@ -9486,7 +9493,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A153" s="8" t="s">
         <v>800</v>
       </c>
@@ -9513,7 +9520,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A154" s="8" t="s">
         <v>804</v>
       </c>
@@ -9540,7 +9547,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A155" s="8" t="s">
         <v>811</v>
       </c>
@@ -9567,7 +9574,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="156" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A156" s="8" t="s">
         <v>557</v>
       </c>
@@ -9594,7 +9601,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A157" s="8" t="s">
         <v>557</v>
       </c>
@@ -9621,7 +9628,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A158" s="8" t="s">
         <v>827</v>
       </c>
@@ -9648,7 +9655,7 @@
         <v>831</v>
       </c>
     </row>
-    <row r="159" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A159" s="8" t="s">
         <v>557</v>
       </c>
@@ -9675,7 +9682,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A160" s="8" t="s">
         <v>838</v>
       </c>
@@ -9702,7 +9709,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="161" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A161" s="8" t="s">
         <v>557</v>
       </c>
@@ -9729,7 +9736,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A162" s="8" t="s">
         <v>850</v>
       </c>
@@ -9756,7 +9763,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A163" s="8" t="s">
         <v>857</v>
       </c>
@@ -9783,7 +9790,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A164" s="8" t="s">
         <v>557</v>
       </c>
@@ -9810,7 +9817,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="165" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A165" s="8" t="s">
         <v>557</v>
       </c>
@@ -9837,7 +9844,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A166" s="8" t="s">
         <v>557</v>
       </c>
@@ -9864,7 +9871,7 @@
         <v>871</v>
       </c>
     </row>
-    <row r="167" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A167" s="8" t="s">
         <v>557</v>
       </c>
@@ -9891,7 +9898,7 @@
         <v>879</v>
       </c>
     </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A168" s="8" t="s">
         <v>557</v>
       </c>
@@ -9918,7 +9925,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A169" s="8" t="s">
         <v>557</v>
       </c>
@@ -9945,7 +9952,7 @@
         <v>889</v>
       </c>
     </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A170" s="8" t="s">
         <v>557</v>
       </c>
@@ -9972,7 +9979,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A171" s="8" t="s">
         <v>557</v>
       </c>
@@ -9999,7 +10006,7 @@
         <v>897</v>
       </c>
     </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A172" s="8" t="s">
         <v>902</v>
       </c>
@@ -10026,7 +10033,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A173" s="8" t="s">
         <v>902</v>
       </c>
@@ -10053,7 +10060,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A174" s="8" t="s">
         <v>557</v>
       </c>
@@ -10080,7 +10087,7 @@
         <v>915</v>
       </c>
     </row>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A175" s="8" t="s">
         <v>557</v>
       </c>
@@ -10107,7 +10114,7 @@
         <v>919</v>
       </c>
     </row>
-    <row r="176" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A176" s="8" t="s">
         <v>557</v>
       </c>
@@ -10134,7 +10141,7 @@
         <v>925</v>
       </c>
     </row>
-    <row r="177" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A177" s="8" t="s">
         <v>557</v>
       </c>
@@ -10161,7 +10168,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="178" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:13" ht="28" x14ac:dyDescent="0.3">
       <c r="A178" s="8" t="s">
         <v>557</v>
       </c>
@@ -10188,7 +10195,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="179" spans="1:13" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:13" ht="42" x14ac:dyDescent="0.3">
       <c r="A179" s="8" t="s">
         <v>938</v>
       </c>
@@ -10215,7 +10222,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="180" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B180" s="4" t="s">
         <v>942</v>
       </c>
@@ -10239,7 +10246,7 @@
         <v>946</v>
       </c>
     </row>
-    <row r="181" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:13" ht="28" x14ac:dyDescent="0.3">
       <c r="B181" s="4" t="s">
         <v>948</v>
       </c>
@@ -10263,7 +10270,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="182" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:13" ht="28" x14ac:dyDescent="0.3">
       <c r="B182" s="4" t="s">
         <v>954</v>
       </c>
@@ -10287,7 +10294,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="183" spans="1:13" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:13" ht="42" x14ac:dyDescent="0.3">
       <c r="B183" s="4" t="s">
         <v>959</v>
       </c>
@@ -10311,7 +10318,7 @@
         <v>960</v>
       </c>
     </row>
-    <row r="184" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:13" ht="28" x14ac:dyDescent="0.3">
       <c r="B184" s="4" t="s">
         <v>966</v>
       </c>
@@ -10335,7 +10342,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="185" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:13" ht="28" x14ac:dyDescent="0.3">
       <c r="B185" s="4" t="s">
         <v>971</v>
       </c>
@@ -10359,7 +10366,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="186" spans="1:13" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:13" ht="42" x14ac:dyDescent="0.3">
       <c r="B186" s="4" t="s">
         <v>976</v>
       </c>
@@ -10383,7 +10390,7 @@
         <v>963</v>
       </c>
     </row>
-    <row r="187" spans="1:13" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:13" ht="42" x14ac:dyDescent="0.3">
       <c r="B187" s="4" t="s">
         <v>979</v>
       </c>
@@ -10407,7 +10414,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="188" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:13" ht="28" x14ac:dyDescent="0.3">
       <c r="B188" s="4" t="s">
         <v>985</v>
       </c>
@@ -10434,7 +10441,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="189" spans="1:13" ht="15" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:13" ht="15.5" x14ac:dyDescent="0.3">
       <c r="B189" s="4" t="s">
         <v>988</v>
       </c>
@@ -10459,7 +10466,7 @@
       </c>
       <c r="M189" s="6"/>
     </row>
-    <row r="190" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:13" ht="28" x14ac:dyDescent="0.3">
       <c r="B190" s="4" t="s">
         <v>992</v>
       </c>
@@ -10483,7 +10490,7 @@
         <v>982</v>
       </c>
     </row>
-    <row r="191" spans="1:13" ht="45" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:13" ht="46.5" x14ac:dyDescent="0.3">
       <c r="B191" s="4" t="s">
         <v>1002</v>
       </c>
@@ -10507,7 +10514,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="192" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:13" ht="28" x14ac:dyDescent="0.3">
       <c r="B192" s="4" t="s">
         <v>1006</v>
       </c>
@@ -10531,7 +10538,7 @@
         <v>998</v>
       </c>
     </row>
-    <row r="193" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="193" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B193" s="4" t="s">
         <v>1010</v>
       </c>
@@ -10555,7 +10562,7 @@
         <v>1011</v>
       </c>
     </row>
-    <row r="194" spans="2:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="194" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B194" s="4" t="s">
         <v>1015</v>
       </c>
@@ -10582,7 +10589,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="195" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="195" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B195" s="4" t="s">
         <v>1021</v>
       </c>
@@ -10606,7 +10613,7 @@
         <v>1019</v>
       </c>
     </row>
-    <row r="196" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="196" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B196" s="4" t="s">
         <v>1025</v>
       </c>
@@ -10630,7 +10637,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="197" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="197" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B197" s="4" t="s">
         <v>1031</v>
       </c>
@@ -10654,7 +10661,7 @@
         <v>1033</v>
       </c>
     </row>
-    <row r="198" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="198" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B198" s="4" t="s">
         <v>1034</v>
       </c>
@@ -10678,7 +10685,7 @@
         <v>1035</v>
       </c>
     </row>
-    <row r="199" spans="2:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="199" spans="2:12" ht="42" x14ac:dyDescent="0.3">
       <c r="B199" s="4" t="s">
         <v>1040</v>
       </c>
@@ -10702,7 +10709,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="200" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="200" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B200" s="4" t="s">
         <v>1045</v>
       </c>
@@ -10726,7 +10733,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="201" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="201" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B201" s="4" t="s">
         <v>1051</v>
       </c>
@@ -10750,7 +10757,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="202" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="202" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B202" s="4" t="s">
         <v>1058</v>
       </c>
@@ -10774,7 +10781,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="203" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="203" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B203" s="4" t="s">
         <v>1062</v>
       </c>
@@ -10798,7 +10805,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="204" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="204" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B204" s="4" t="s">
         <v>1065</v>
       </c>
@@ -10822,7 +10829,7 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="205" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="205" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B205" s="4" t="s">
         <v>1071</v>
       </c>
@@ -10846,7 +10853,7 @@
         <v>1069</v>
       </c>
     </row>
-    <row r="206" spans="2:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="206" spans="2:12" ht="42" x14ac:dyDescent="0.3">
       <c r="B206" s="4" t="s">
         <v>1074</v>
       </c>
@@ -10870,7 +10877,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="207" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="207" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B207" s="4" t="s">
         <v>1080</v>
       </c>
@@ -10894,7 +10901,7 @@
         <v>1079</v>
       </c>
     </row>
-    <row r="208" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="208" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B208" s="4" t="s">
         <v>1082</v>
       </c>
@@ -10918,7 +10925,7 @@
         <v>1081</v>
       </c>
     </row>
-    <row r="209" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="209" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B209" s="4" t="s">
         <v>1091</v>
       </c>
@@ -10942,7 +10949,7 @@
         <v>1089</v>
       </c>
     </row>
-    <row r="210" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="210" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B210" s="4" t="s">
         <v>1093</v>
       </c>
@@ -10966,7 +10973,7 @@
         <v>1092</v>
       </c>
     </row>
-    <row r="211" spans="2:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="211" spans="2:12" ht="42" x14ac:dyDescent="0.3">
       <c r="B211" s="4" t="s">
         <v>1102</v>
       </c>
@@ -10990,7 +10997,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="212" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="212" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B212" s="4" t="s">
         <v>1105</v>
       </c>
@@ -11014,7 +11021,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="213" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="213" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B213" s="4" t="s">
         <v>1110</v>
       </c>
@@ -11038,7 +11045,7 @@
         <v>1109</v>
       </c>
     </row>
-    <row r="214" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="214" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B214" s="4" t="s">
         <v>1118</v>
       </c>
@@ -11065,7 +11072,7 @@
         <v>1114</v>
       </c>
     </row>
-    <row r="215" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="215" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B215" s="4" t="s">
         <v>1121</v>
       </c>
@@ -11089,7 +11096,7 @@
         <v>1116</v>
       </c>
     </row>
-    <row r="216" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="216" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B216" s="4" t="s">
         <v>1126</v>
       </c>
@@ -11116,7 +11123,7 @@
         <v>1131</v>
       </c>
     </row>
-    <row r="217" spans="2:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="217" spans="2:12" ht="42" x14ac:dyDescent="0.3">
       <c r="B217" s="4" t="s">
         <v>1134</v>
       </c>
@@ -11140,7 +11147,7 @@
         <v>1113</v>
       </c>
     </row>
-    <row r="218" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="218" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B218" s="4" t="s">
         <v>1137</v>
       </c>
@@ -11167,7 +11174,7 @@
         <v>1132</v>
       </c>
     </row>
-    <row r="219" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="219" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B219" s="4" t="s">
         <v>1142</v>
       </c>
@@ -11191,7 +11198,7 @@
         <v>1120</v>
       </c>
     </row>
-    <row r="220" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="220" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B220" s="4" t="s">
         <v>1145</v>
       </c>
@@ -11215,7 +11222,7 @@
         <v>1149</v>
       </c>
     </row>
-    <row r="221" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="221" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B221" s="4" t="s">
         <v>1150</v>
       </c>
@@ -11239,7 +11246,7 @@
         <v>1154</v>
       </c>
     </row>
-    <row r="222" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="222" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B222" s="4" t="s">
         <v>1153</v>
       </c>
@@ -11263,7 +11270,7 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="223" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="223" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B223" s="4" t="s">
         <v>1161</v>
       </c>
@@ -11287,7 +11294,7 @@
         <v>1160</v>
       </c>
     </row>
-    <row r="224" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="224" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B224" s="4" t="s">
         <v>1165</v>
       </c>
@@ -11311,7 +11318,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="225" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="225" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B225" s="4" t="s">
         <v>1167</v>
       </c>
@@ -11338,7 +11345,7 @@
         <v>1166</v>
       </c>
     </row>
-    <row r="226" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="226" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B226" s="4" t="s">
         <v>1173</v>
       </c>
@@ -11362,7 +11369,7 @@
         <v>1174</v>
       </c>
     </row>
-    <row r="227" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="227" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B227" s="4" t="s">
         <v>1181</v>
       </c>
@@ -11371,557 +11378,563 @@
       </c>
       <c r="H227" s="1" t="s">
         <v>58</v>
+      </c>
+      <c r="I227" s="4" t="s">
+        <v>1183</v>
       </c>
       <c r="J227" s="5" t="str">
         <f t="shared" si="5"/>
         <v>001132</v>
       </c>
+      <c r="K227" s="3" t="s">
+        <v>1184</v>
+      </c>
       <c r="L227" s="2" t="s">
         <v>1180</v>
       </c>
     </row>
-    <row r="228" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="228" spans="2:12" x14ac:dyDescent="0.3">
       <c r="J228" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="229" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="229" spans="2:12" x14ac:dyDescent="0.3">
       <c r="J229" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="230" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="230" spans="2:12" x14ac:dyDescent="0.3">
       <c r="J230" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="231" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="231" spans="2:12" x14ac:dyDescent="0.3">
       <c r="J231" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="232" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="232" spans="2:12" x14ac:dyDescent="0.3">
       <c r="J232" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="233" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="233" spans="2:12" x14ac:dyDescent="0.3">
       <c r="J233" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="234" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="234" spans="2:12" x14ac:dyDescent="0.3">
       <c r="J234" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="235" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="235" spans="2:12" x14ac:dyDescent="0.3">
       <c r="J235" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="236" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="236" spans="2:12" x14ac:dyDescent="0.3">
       <c r="J236" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="237" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="237" spans="2:12" x14ac:dyDescent="0.3">
       <c r="J237" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="238" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="238" spans="2:12" x14ac:dyDescent="0.3">
       <c r="J238" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="239" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="239" spans="2:12" x14ac:dyDescent="0.3">
       <c r="J239" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="240" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="240" spans="2:12" x14ac:dyDescent="0.3">
       <c r="J240" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="241" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="241" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J241" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="242" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="242" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J242" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="243" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="243" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J243" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="244" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="244" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J244" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="245" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="245" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J245" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="246" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="246" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J246" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="247" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="247" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J247" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="248" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="248" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J248" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="249" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="249" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J249" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="250" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="250" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J250" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="251" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="251" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J251" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="252" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="252" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J252" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="253" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="253" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J253" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="254" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="254" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J254" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="255" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="255" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J255" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="256" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="256" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J256" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="257" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="257" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J257" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="258" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="258" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J258" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="259" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="259" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J259" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="260" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="260" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J260" s="5" t="str">
         <f t="shared" ref="J260:J317" si="8">"00"&amp;B260</f>
         <v>00</v>
       </c>
     </row>
-    <row r="261" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="261" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J261" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="262" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="262" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J262" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="263" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="263" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J263" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="264" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="264" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J264" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="265" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="265" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J265" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="266" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="266" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J266" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="267" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="267" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J267" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="268" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="268" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J268" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="269" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="269" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J269" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="270" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="270" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J270" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="271" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="271" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J271" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="272" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="272" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J272" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="273" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="273" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J273" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="274" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="274" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J274" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="275" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="275" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J275" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="276" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="276" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J276" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="277" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="277" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J277" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="278" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="278" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J278" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="279" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="279" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J279" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="280" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="280" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J280" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="281" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="281" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J281" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="282" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="282" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J282" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="283" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="283" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J283" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="284" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="284" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J284" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="285" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="285" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J285" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="286" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="286" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J286" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="287" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="287" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J287" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="288" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="288" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J288" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="289" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="289" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J289" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="290" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="290" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J290" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="291" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="291" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J291" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="292" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="292" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J292" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="293" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="293" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J293" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="294" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="294" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J294" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="295" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="295" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J295" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="296" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="296" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J296" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="297" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="297" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J297" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="298" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="298" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J298" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="299" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="299" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J299" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="300" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="300" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J300" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="301" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="301" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J301" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="302" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="302" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J302" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="303" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="303" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J303" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="304" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="304" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J304" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="305" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="305" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J305" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="306" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="306" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J306" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="307" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="307" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J307" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="308" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="308" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J308" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="309" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="309" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J309" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="310" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="310" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J310" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="311" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="311" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J311" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="312" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="312" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J312" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="313" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="313" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J313" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="314" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="314" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J314" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="315" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="315" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J315" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="316" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="316" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J316" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="317" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="317" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J317" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:L4" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A4:L4"/>
   <mergeCells count="1">
     <mergeCell ref="A2:L2"/>
   </mergeCells>
@@ -11933,10 +11946,10 @@
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1:E1 D3:E3 D6:E1048576" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1:E1 D3:E3 D6:E1048576">
       <formula1>"是,否"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H1 H3:H1048576" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H1 H3:H1048576">
       <formula1>"VB编程,系统运维,WEB学习,游戏碎片,日常随笔,浥尘伙伴社团"</formula1>
     </dataValidation>
   </dataValidations>
@@ -11946,20 +11959,20 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A2:L34"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="6.375" customWidth="1"/>
+    <col min="2" max="2" width="6.33203125" customWidth="1"/>
     <col min="3" max="3" width="34" style="4" customWidth="1"/>
     <col min="4" max="4" width="4.75" customWidth="1"/>
-    <col min="8" max="8" width="6.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.83203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="19" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="7.125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="7.08203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.08203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:12" ht="23.25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
         <v>549</v>
       </c>
@@ -11975,7 +11988,7 @@
       <c r="K2" s="21"/>
       <c r="L2" s="21"/>
     </row>
-    <row r="4" spans="1:12" ht="57" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12" ht="56" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>0</v>
       </c>
@@ -12013,7 +12026,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>533</v>
       </c>
@@ -12036,7 +12049,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C8" s="15" t="s">
         <v>545</v>
       </c>
@@ -12045,7 +12058,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C9" s="4" t="s">
         <v>539</v>
       </c>
@@ -12053,7 +12066,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C10" t="s">
         <v>537</v>
       </c>
@@ -12061,7 +12074,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C11" t="s">
         <v>538</v>
       </c>
@@ -12069,7 +12082,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="23.25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A13" s="21" t="s">
         <v>543</v>
       </c>
@@ -12085,7 +12098,7 @@
       <c r="K13" s="21"/>
       <c r="L13" s="21"/>
     </row>
-    <row r="15" spans="1:12" ht="57" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:12" ht="56" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
         <v>0</v>
       </c>
@@ -12123,7 +12136,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>533</v>
       </c>
@@ -12149,7 +12162,7 @@
         <v>54837657</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C19" s="15" t="s">
         <v>545</v>
       </c>
@@ -12158,7 +12171,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C20" s="4" t="s">
         <v>539</v>
       </c>
@@ -12166,7 +12179,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C21" t="s">
         <v>537</v>
       </c>
@@ -12174,7 +12187,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C22" t="s">
         <v>538</v>
       </c>
@@ -12182,10 +12195,10 @@
         <v>541</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C23"/>
     </row>
-    <row r="25" spans="1:12" ht="23.25" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:12" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A25" s="21" t="s">
         <v>550</v>
       </c>
@@ -12201,7 +12214,7 @@
       <c r="K25" s="21"/>
       <c r="L25" s="21"/>
     </row>
-    <row r="27" spans="1:12" ht="57" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:12" ht="56" x14ac:dyDescent="0.3">
       <c r="A27" s="7" t="s">
         <v>0</v>
       </c>
@@ -12239,7 +12252,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
         <v>533</v>
       </c>
@@ -12265,7 +12278,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C31" s="15" t="s">
         <v>545</v>
       </c>
@@ -12274,7 +12287,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C32" s="4" t="s">
         <v>539</v>
       </c>
@@ -12282,7 +12295,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="33" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="33" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C33" t="s">
         <v>537</v>
       </c>
@@ -12290,7 +12303,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="34" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="34" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C34" t="s">
         <v>538</v>
       </c>
@@ -12306,7 +12319,7 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H15 H27 H4" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H15 H27 H4">
       <formula1>"VB编程,系统运维,WEB学习,游戏碎片,日常随笔"</formula1>
     </dataValidation>
   </dataValidations>

--- a/11_付费课程/99.资料/文章信息备忘表.xlsx
+++ b/11_付费课程/99.资料/文章信息备忘表.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\writing\11_付费课程\99.资料\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Disks\E\Writing\11_付费课程\99.资料\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AB0082A-80F4-4862-B557-331CE2FEA48D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1960" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
+    <workbookView xWindow="6315" yWindow="1410" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,7 +19,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$L$4</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1621" uniqueCount="1185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1627" uniqueCount="1189">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -4725,13 +4726,29 @@
   </si>
   <si>
     <t>611191</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>68285509</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1133</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NULL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>浥尘伙伴社团独家密训课程：孩子成长必备之可视化创意思考课基础篇</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -5223,25 +5240,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:M317"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.25" style="8" customWidth="1"/>
-    <col min="2" max="2" width="5.58203125" style="4" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="5.33203125" style="6" customWidth="1"/>
-    <col min="5" max="6" width="5.08203125" style="6" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="30.875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="5.375" style="6" customWidth="1"/>
+    <col min="5" max="6" width="5.125" style="6" customWidth="1"/>
     <col min="7" max="7" width="5.25" style="6" customWidth="1"/>
     <col min="8" max="8" width="13.5" style="1" customWidth="1"/>
     <col min="9" max="9" width="19" style="4" customWidth="1"/>
-    <col min="10" max="10" width="8.58203125" style="5" customWidth="1"/>
+    <col min="10" max="10" width="8.625" style="5" customWidth="1"/>
     <col min="11" max="11" width="7.5" style="3" customWidth="1"/>
     <col min="12" max="12" width="9.25" style="2" customWidth="1"/>
     <col min="13" max="13" width="16.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:12" ht="25" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
@@ -5257,8 +5274,8 @@
       <c r="K2" s="20"/>
       <c r="L2" s="20"/>
     </row>
-    <row r="3" spans="1:12" ht="6.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="4" spans="1:12" s="7" customFormat="1" ht="56" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" ht="6.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="4" spans="1:12" s="7" customFormat="1" ht="57" x14ac:dyDescent="0.2">
       <c r="A4" s="7" t="s">
         <v>0</v>
       </c>
@@ -5296,7 +5313,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
         <v>557</v>
       </c>
@@ -5323,7 +5340,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
         <v>559</v>
       </c>
@@ -5359,7 +5376,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="8" t="s">
         <v>559</v>
       </c>
@@ -5395,25 +5412,25 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="J8" s="5" t="str">
         <f t="shared" si="0"/>
         <v>000</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="J9" s="5" t="str">
         <f t="shared" si="0"/>
         <v>000</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="J10" s="5" t="str">
         <f t="shared" si="0"/>
         <v>000</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B11" s="4" t="s">
         <v>522</v>
       </c>
@@ -5446,7 +5463,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A12" s="8" t="s">
         <v>558</v>
       </c>
@@ -5476,7 +5493,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A13" s="8" t="s">
         <v>558</v>
       </c>
@@ -5506,7 +5523,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A14" s="8" t="s">
         <v>640</v>
       </c>
@@ -5533,7 +5550,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" s="8" t="s">
         <v>557</v>
       </c>
@@ -5560,7 +5577,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" s="8" t="s">
         <v>557</v>
       </c>
@@ -5587,7 +5604,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" s="8" t="s">
         <v>557</v>
       </c>
@@ -5614,7 +5631,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" s="8" t="s">
         <v>767</v>
       </c>
@@ -5641,7 +5658,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A19" s="8" t="s">
         <v>557</v>
       </c>
@@ -5668,7 +5685,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A20" s="8" t="s">
         <v>557</v>
       </c>
@@ -5695,7 +5712,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A21" s="8" t="s">
         <v>557</v>
       </c>
@@ -5722,7 +5739,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A22" s="8" t="s">
         <v>559</v>
       </c>
@@ -5758,7 +5775,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23" s="8" t="s">
         <v>557</v>
       </c>
@@ -5785,7 +5802,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A24" s="8" t="s">
         <v>558</v>
       </c>
@@ -5815,7 +5832,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A25" s="8" t="s">
         <v>557</v>
       </c>
@@ -5842,7 +5859,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A26" s="8" t="s">
         <v>557</v>
       </c>
@@ -5869,7 +5886,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="27" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A27" s="8" t="s">
         <v>633</v>
       </c>
@@ -5896,7 +5913,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A28" s="8" t="s">
         <v>557</v>
       </c>
@@ -5923,7 +5940,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A29" s="8" t="s">
         <v>559</v>
       </c>
@@ -5959,7 +5976,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A30" s="8" t="s">
         <v>559</v>
       </c>
@@ -5995,7 +6012,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A31" s="8" t="s">
         <v>557</v>
       </c>
@@ -6022,7 +6039,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A32" s="8" t="s">
         <v>557</v>
       </c>
@@ -6049,7 +6066,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A33" s="8" t="s">
         <v>557</v>
       </c>
@@ -6076,7 +6093,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="34" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A34" s="8" t="s">
         <v>557</v>
       </c>
@@ -6103,7 +6120,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="35" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A35" s="8" t="s">
         <v>557</v>
       </c>
@@ -6130,7 +6147,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="36" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A36" s="8" t="s">
         <v>557</v>
       </c>
@@ -6157,7 +6174,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="37" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A37" s="8" t="s">
         <v>559</v>
       </c>
@@ -6193,7 +6210,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="38" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A38" s="8" t="s">
         <v>557</v>
       </c>
@@ -6220,7 +6237,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A39" s="8" t="s">
         <v>557</v>
       </c>
@@ -6247,7 +6264,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="40" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A40" s="8" t="s">
         <v>557</v>
       </c>
@@ -6274,7 +6291,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="41" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A41" s="8" t="s">
         <v>557</v>
       </c>
@@ -6301,7 +6318,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="42" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A42" s="8" t="s">
         <v>557</v>
       </c>
@@ -6328,7 +6345,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="43" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A43" s="8" t="s">
         <v>559</v>
       </c>
@@ -6361,7 +6378,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="44" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A44" s="8" t="s">
         <v>557</v>
       </c>
@@ -6388,7 +6405,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="45" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A45" s="8" t="s">
         <v>557</v>
       </c>
@@ -6415,7 +6432,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="46" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A46" s="8" t="s">
         <v>557</v>
       </c>
@@ -6442,7 +6459,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A47" s="8" t="s">
         <v>557</v>
       </c>
@@ -6469,7 +6486,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="48" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A48" s="8" t="s">
         <v>557</v>
       </c>
@@ -6496,7 +6513,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="49" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A49" s="8" t="s">
         <v>557</v>
       </c>
@@ -6523,7 +6540,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="50" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A50" s="8" t="s">
         <v>557</v>
       </c>
@@ -6550,7 +6567,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A51" s="8" t="s">
         <v>557</v>
       </c>
@@ -6577,7 +6594,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="52" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A52" s="8" t="s">
         <v>557</v>
       </c>
@@ -6604,7 +6621,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A53" s="8" t="s">
         <v>557</v>
       </c>
@@ -6631,7 +6648,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="54" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A54" s="8" t="s">
         <v>557</v>
       </c>
@@ -6658,7 +6675,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A55" s="8" t="s">
         <v>557</v>
       </c>
@@ -6685,7 +6702,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="56" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A56" s="8" t="s">
         <v>559</v>
       </c>
@@ -6721,7 +6738,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="57" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A57" s="8" t="s">
         <v>559</v>
       </c>
@@ -6757,7 +6774,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="58" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A58" s="8" t="s">
         <v>557</v>
       </c>
@@ -6784,7 +6801,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="59" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A59" s="8" t="s">
         <v>558</v>
       </c>
@@ -6814,7 +6831,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="60" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A60" s="8" t="s">
         <v>557</v>
       </c>
@@ -6841,7 +6858,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="61" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B61" s="4" t="s">
         <v>298</v>
       </c>
@@ -6874,7 +6891,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="62" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B62" s="4" t="s">
         <v>294</v>
       </c>
@@ -6907,7 +6924,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="63" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B63" s="4" t="s">
         <v>289</v>
       </c>
@@ -6940,7 +6957,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="64" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A64" s="8" t="s">
         <v>557</v>
       </c>
@@ -6967,7 +6984,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="65" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A65" s="8" t="s">
         <v>557</v>
       </c>
@@ -6994,7 +7011,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="66" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A66" s="8" t="s">
         <v>559</v>
       </c>
@@ -7030,7 +7047,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="67" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A67" s="8" t="s">
         <v>557</v>
       </c>
@@ -7057,7 +7074,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="68" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A68" s="8" t="s">
         <v>558</v>
       </c>
@@ -7087,7 +7104,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="69" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A69" s="8" t="s">
         <v>559</v>
       </c>
@@ -7114,7 +7131,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="70" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A70" s="8" t="s">
         <v>559</v>
       </c>
@@ -7141,7 +7158,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="71" spans="1:12" ht="56" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:12" ht="57" x14ac:dyDescent="0.2">
       <c r="A71" s="8" t="s">
         <v>558</v>
       </c>
@@ -7171,7 +7188,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="72" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A72" s="8" t="s">
         <v>558</v>
       </c>
@@ -7201,7 +7218,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="73" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A73" s="8" t="s">
         <v>558</v>
       </c>
@@ -7231,7 +7248,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="74" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A74" s="8" t="s">
         <v>557</v>
       </c>
@@ -7258,7 +7275,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="75" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A75" s="8" t="s">
         <v>557</v>
       </c>
@@ -7285,7 +7302,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="76" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A76" s="8" t="s">
         <v>558</v>
       </c>
@@ -7318,7 +7335,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="77" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A77" s="8" t="s">
         <v>557</v>
       </c>
@@ -7345,7 +7362,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="78" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A78" s="8" t="s">
         <v>558</v>
       </c>
@@ -7372,7 +7389,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="79" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A79" s="8" t="s">
         <v>557</v>
       </c>
@@ -7399,7 +7416,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="80" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A80" s="8" t="s">
         <v>558</v>
       </c>
@@ -7426,7 +7443,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="81" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A81" s="8" t="s">
         <v>557</v>
       </c>
@@ -7453,7 +7470,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="82" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A82" s="8" t="s">
         <v>557</v>
       </c>
@@ -7480,7 +7497,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="83" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A83" s="8" t="s">
         <v>557</v>
       </c>
@@ -7507,7 +7524,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="84" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A84" s="8" t="s">
         <v>557</v>
       </c>
@@ -7534,7 +7551,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="85" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A85" s="8" t="s">
         <v>558</v>
       </c>
@@ -7561,7 +7578,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="86" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A86" s="8" t="s">
         <v>557</v>
       </c>
@@ -7588,7 +7605,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="87" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A87" s="8" t="s">
         <v>559</v>
       </c>
@@ -7624,7 +7641,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="88" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A88" s="8" t="s">
         <v>559</v>
       </c>
@@ -7660,7 +7677,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="89" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A89" s="8" t="s">
         <v>559</v>
       </c>
@@ -7696,7 +7713,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="90" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A90" s="8" t="s">
         <v>557</v>
       </c>
@@ -7723,7 +7740,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="91" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B91" s="4" t="s">
         <v>151</v>
       </c>
@@ -7756,7 +7773,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="92" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B92" s="4" t="s">
         <v>146</v>
       </c>
@@ -7789,7 +7806,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="93" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B93" s="4" t="s">
         <v>140</v>
       </c>
@@ -7822,7 +7839,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="94" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B94" s="4" t="s">
         <v>135</v>
       </c>
@@ -7855,7 +7872,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="95" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A95" s="8" t="s">
         <v>558</v>
       </c>
@@ -7882,7 +7899,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="96" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B96" s="4" t="s">
         <v>123</v>
       </c>
@@ -7915,7 +7932,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="97" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B97" s="4" t="s">
         <v>118</v>
       </c>
@@ -7948,7 +7965,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="98" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B98" s="4" t="s">
         <v>112</v>
       </c>
@@ -7981,7 +7998,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="99" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B99" s="4" t="s">
         <v>109</v>
       </c>
@@ -8014,7 +8031,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="100" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B100" s="4" t="s">
         <v>104</v>
       </c>
@@ -8047,7 +8064,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="101" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B101" s="4" t="s">
         <v>98</v>
       </c>
@@ -8080,7 +8097,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="102" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B102" s="4" t="s">
         <v>92</v>
       </c>
@@ -8113,7 +8130,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="103" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A103" s="8" t="s">
         <v>559</v>
       </c>
@@ -8149,7 +8166,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="104" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A104" s="8" t="s">
         <v>557</v>
       </c>
@@ -8176,7 +8193,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="105" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A105" s="8" t="s">
         <v>557</v>
       </c>
@@ -8203,7 +8220,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="106" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A106" s="8" t="s">
         <v>557</v>
       </c>
@@ -8230,7 +8247,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="107" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A107" s="8" t="s">
         <v>557</v>
       </c>
@@ -8257,7 +8274,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="108" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A108" s="8" t="s">
         <v>557</v>
       </c>
@@ -8284,7 +8301,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="109" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A109" s="8" t="s">
         <v>559</v>
       </c>
@@ -8320,7 +8337,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A110" s="8" t="s">
         <v>558</v>
       </c>
@@ -8347,7 +8364,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="111" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A111" s="8" t="s">
         <v>557</v>
       </c>
@@ -8374,7 +8391,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A112" s="8" t="s">
         <v>557</v>
       </c>
@@ -8401,7 +8418,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="113" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A113" s="8" t="s">
         <v>557</v>
       </c>
@@ -8428,7 +8445,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A114" s="8" t="s">
         <v>557</v>
       </c>
@@ -8455,7 +8472,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="115" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A115" s="8" t="s">
         <v>557</v>
       </c>
@@ -8482,7 +8499,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="116" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A116" s="8" t="s">
         <v>559</v>
       </c>
@@ -8518,7 +8535,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="117" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A117" s="8" t="s">
         <v>557</v>
       </c>
@@ -8545,7 +8562,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="118" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A118" s="8" t="s">
         <v>558</v>
       </c>
@@ -8575,7 +8592,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="119" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A119" s="8" t="s">
         <v>557</v>
       </c>
@@ -8602,7 +8619,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="120" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A120" s="8" t="s">
         <v>557</v>
       </c>
@@ -8629,7 +8646,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="121" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A121" s="8" t="s">
         <v>597</v>
       </c>
@@ -8656,7 +8673,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="122" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A122" s="8" t="s">
         <v>602</v>
       </c>
@@ -8683,7 +8700,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="123" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A123" s="8" t="s">
         <v>608</v>
       </c>
@@ -8710,7 +8727,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="124" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A124" s="8" t="s">
         <v>611</v>
       </c>
@@ -8737,7 +8754,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="125" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A125" s="8" t="s">
         <v>617</v>
       </c>
@@ -8764,7 +8781,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="126" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A126" s="8" t="s">
         <v>624</v>
       </c>
@@ -8791,7 +8808,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="127" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A127" s="8" t="s">
         <v>557</v>
       </c>
@@ -8818,7 +8835,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="128" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A128" s="8" t="s">
         <v>649</v>
       </c>
@@ -8845,7 +8862,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="129" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A129" s="8" t="s">
         <v>653</v>
       </c>
@@ -8872,7 +8889,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="130" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A130" s="8" t="s">
         <v>659</v>
       </c>
@@ -8899,7 +8916,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="131" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A131" s="8" t="s">
         <v>664</v>
       </c>
@@ -8926,7 +8943,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A132" s="8" t="s">
         <v>557</v>
       </c>
@@ -8953,7 +8970,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="133" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A133" s="8" t="s">
         <v>557</v>
       </c>
@@ -8980,7 +8997,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="134" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A134" s="8" t="s">
         <v>681</v>
       </c>
@@ -9007,7 +9024,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="135" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A135" s="8" t="s">
         <v>687</v>
       </c>
@@ -9034,7 +9051,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="136" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A136" s="8" t="s">
         <v>691</v>
       </c>
@@ -9061,7 +9078,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="137" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A137" s="8" t="s">
         <v>699</v>
       </c>
@@ -9088,7 +9105,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="138" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A138" s="8" t="s">
         <v>704</v>
       </c>
@@ -9115,7 +9132,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="139" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A139" s="8" t="s">
         <v>711</v>
       </c>
@@ -9142,7 +9159,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="140" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A140" s="8" t="s">
         <v>716</v>
       </c>
@@ -9169,7 +9186,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="141" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A141" s="8" t="s">
         <v>724</v>
       </c>
@@ -9196,7 +9213,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="142" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A142" s="8" t="s">
         <v>727</v>
       </c>
@@ -9223,7 +9240,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="143" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A143" s="8" t="s">
         <v>736</v>
       </c>
@@ -9250,7 +9267,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="144" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A144" s="8" t="s">
         <v>740</v>
       </c>
@@ -9277,7 +9294,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="145" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A145" s="8" t="s">
         <v>746</v>
       </c>
@@ -9304,7 +9321,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="146" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A146" s="8" t="s">
         <v>754</v>
       </c>
@@ -9331,7 +9348,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="147" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A147" s="8" t="s">
         <v>759</v>
       </c>
@@ -9358,7 +9375,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="148" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A148" s="8" t="s">
         <v>770</v>
       </c>
@@ -9385,7 +9402,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="149" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A149" s="8" t="s">
         <v>777</v>
       </c>
@@ -9412,7 +9429,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="150" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A150" s="8" t="s">
         <v>782</v>
       </c>
@@ -9439,7 +9456,7 @@
         <v>786</v>
       </c>
     </row>
-    <row r="151" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A151" s="8" t="s">
         <v>557</v>
       </c>
@@ -9466,7 +9483,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="152" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A152" s="8" t="s">
         <v>795</v>
       </c>
@@ -9493,7 +9510,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A153" s="8" t="s">
         <v>800</v>
       </c>
@@ -9520,7 +9537,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A154" s="8" t="s">
         <v>804</v>
       </c>
@@ -9547,7 +9564,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A155" s="8" t="s">
         <v>811</v>
       </c>
@@ -9574,7 +9591,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="156" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A156" s="8" t="s">
         <v>557</v>
       </c>
@@ -9601,7 +9618,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A157" s="8" t="s">
         <v>557</v>
       </c>
@@ -9628,7 +9645,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A158" s="8" t="s">
         <v>827</v>
       </c>
@@ -9655,7 +9672,7 @@
         <v>831</v>
       </c>
     </row>
-    <row r="159" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A159" s="8" t="s">
         <v>557</v>
       </c>
@@ -9682,7 +9699,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A160" s="8" t="s">
         <v>838</v>
       </c>
@@ -9709,7 +9726,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="161" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A161" s="8" t="s">
         <v>557</v>
       </c>
@@ -9736,7 +9753,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A162" s="8" t="s">
         <v>850</v>
       </c>
@@ -9763,7 +9780,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A163" s="8" t="s">
         <v>857</v>
       </c>
@@ -9790,7 +9807,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A164" s="8" t="s">
         <v>557</v>
       </c>
@@ -9817,7 +9834,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="165" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A165" s="8" t="s">
         <v>557</v>
       </c>
@@ -9844,7 +9861,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A166" s="8" t="s">
         <v>557</v>
       </c>
@@ -9871,7 +9888,7 @@
         <v>871</v>
       </c>
     </row>
-    <row r="167" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A167" s="8" t="s">
         <v>557</v>
       </c>
@@ -9898,7 +9915,7 @@
         <v>879</v>
       </c>
     </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A168" s="8" t="s">
         <v>557</v>
       </c>
@@ -9925,7 +9942,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A169" s="8" t="s">
         <v>557</v>
       </c>
@@ -9952,7 +9969,7 @@
         <v>889</v>
       </c>
     </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A170" s="8" t="s">
         <v>557</v>
       </c>
@@ -9979,7 +9996,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A171" s="8" t="s">
         <v>557</v>
       </c>
@@ -10006,7 +10023,7 @@
         <v>897</v>
       </c>
     </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A172" s="8" t="s">
         <v>902</v>
       </c>
@@ -10033,7 +10050,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A173" s="8" t="s">
         <v>902</v>
       </c>
@@ -10060,7 +10077,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A174" s="8" t="s">
         <v>557</v>
       </c>
@@ -10087,7 +10104,7 @@
         <v>915</v>
       </c>
     </row>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A175" s="8" t="s">
         <v>557</v>
       </c>
@@ -10114,7 +10131,7 @@
         <v>919</v>
       </c>
     </row>
-    <row r="176" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A176" s="8" t="s">
         <v>557</v>
       </c>
@@ -10141,7 +10158,7 @@
         <v>925</v>
       </c>
     </row>
-    <row r="177" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A177" s="8" t="s">
         <v>557</v>
       </c>
@@ -10168,7 +10185,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="178" spans="1:13" ht="28" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A178" s="8" t="s">
         <v>557</v>
       </c>
@@ -10195,7 +10212,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="179" spans="1:13" ht="42" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:13" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A179" s="8" t="s">
         <v>938</v>
       </c>
@@ -10222,7 +10239,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="180" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B180" s="4" t="s">
         <v>942</v>
       </c>
@@ -10246,7 +10263,7 @@
         <v>946</v>
       </c>
     </row>
-    <row r="181" spans="1:13" ht="28" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B181" s="4" t="s">
         <v>948</v>
       </c>
@@ -10270,7 +10287,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="182" spans="1:13" ht="28" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B182" s="4" t="s">
         <v>954</v>
       </c>
@@ -10294,7 +10311,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="183" spans="1:13" ht="42" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:13" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B183" s="4" t="s">
         <v>959</v>
       </c>
@@ -10318,7 +10335,7 @@
         <v>960</v>
       </c>
     </row>
-    <row r="184" spans="1:13" ht="28" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B184" s="4" t="s">
         <v>966</v>
       </c>
@@ -10342,7 +10359,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="185" spans="1:13" ht="28" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B185" s="4" t="s">
         <v>971</v>
       </c>
@@ -10366,7 +10383,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="186" spans="1:13" ht="42" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:13" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B186" s="4" t="s">
         <v>976</v>
       </c>
@@ -10390,7 +10407,7 @@
         <v>963</v>
       </c>
     </row>
-    <row r="187" spans="1:13" ht="42" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:13" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B187" s="4" t="s">
         <v>979</v>
       </c>
@@ -10414,7 +10431,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="188" spans="1:13" ht="28" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B188" s="4" t="s">
         <v>985</v>
       </c>
@@ -10441,7 +10458,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="189" spans="1:13" ht="15.5" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:13" ht="15" x14ac:dyDescent="0.2">
       <c r="B189" s="4" t="s">
         <v>988</v>
       </c>
@@ -10466,7 +10483,7 @@
       </c>
       <c r="M189" s="6"/>
     </row>
-    <row r="190" spans="1:13" ht="28" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B190" s="4" t="s">
         <v>992</v>
       </c>
@@ -10490,7 +10507,7 @@
         <v>982</v>
       </c>
     </row>
-    <row r="191" spans="1:13" ht="46.5" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:13" ht="45" x14ac:dyDescent="0.2">
       <c r="B191" s="4" t="s">
         <v>1002</v>
       </c>
@@ -10514,7 +10531,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="192" spans="1:13" ht="28" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B192" s="4" t="s">
         <v>1006</v>
       </c>
@@ -10538,7 +10555,7 @@
         <v>998</v>
       </c>
     </row>
-    <row r="193" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="193" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B193" s="4" t="s">
         <v>1010</v>
       </c>
@@ -10562,7 +10579,7 @@
         <v>1011</v>
       </c>
     </row>
-    <row r="194" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="194" spans="2:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B194" s="4" t="s">
         <v>1015</v>
       </c>
@@ -10589,7 +10606,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="195" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="195" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B195" s="4" t="s">
         <v>1021</v>
       </c>
@@ -10613,7 +10630,7 @@
         <v>1019</v>
       </c>
     </row>
-    <row r="196" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="196" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B196" s="4" t="s">
         <v>1025</v>
       </c>
@@ -10637,7 +10654,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="197" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="197" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B197" s="4" t="s">
         <v>1031</v>
       </c>
@@ -10661,7 +10678,7 @@
         <v>1033</v>
       </c>
     </row>
-    <row r="198" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="198" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B198" s="4" t="s">
         <v>1034</v>
       </c>
@@ -10685,7 +10702,7 @@
         <v>1035</v>
       </c>
     </row>
-    <row r="199" spans="2:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="199" spans="2:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B199" s="4" t="s">
         <v>1040</v>
       </c>
@@ -10709,7 +10726,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="200" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="200" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B200" s="4" t="s">
         <v>1045</v>
       </c>
@@ -10733,7 +10750,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="201" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="201" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B201" s="4" t="s">
         <v>1051</v>
       </c>
@@ -10757,7 +10774,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="202" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="202" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B202" s="4" t="s">
         <v>1058</v>
       </c>
@@ -10781,7 +10798,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="203" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="203" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B203" s="4" t="s">
         <v>1062</v>
       </c>
@@ -10805,7 +10822,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="204" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="204" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B204" s="4" t="s">
         <v>1065</v>
       </c>
@@ -10829,7 +10846,7 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="205" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="205" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B205" s="4" t="s">
         <v>1071</v>
       </c>
@@ -10853,7 +10870,7 @@
         <v>1069</v>
       </c>
     </row>
-    <row r="206" spans="2:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="206" spans="2:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B206" s="4" t="s">
         <v>1074</v>
       </c>
@@ -10877,7 +10894,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="207" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="207" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B207" s="4" t="s">
         <v>1080</v>
       </c>
@@ -10901,7 +10918,7 @@
         <v>1079</v>
       </c>
     </row>
-    <row r="208" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="208" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B208" s="4" t="s">
         <v>1082</v>
       </c>
@@ -10925,7 +10942,7 @@
         <v>1081</v>
       </c>
     </row>
-    <row r="209" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="209" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B209" s="4" t="s">
         <v>1091</v>
       </c>
@@ -10949,7 +10966,7 @@
         <v>1089</v>
       </c>
     </row>
-    <row r="210" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="210" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B210" s="4" t="s">
         <v>1093</v>
       </c>
@@ -10973,7 +10990,7 @@
         <v>1092</v>
       </c>
     </row>
-    <row r="211" spans="2:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="211" spans="2:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B211" s="4" t="s">
         <v>1102</v>
       </c>
@@ -10997,7 +11014,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="212" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="212" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B212" s="4" t="s">
         <v>1105</v>
       </c>
@@ -11021,7 +11038,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="213" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="213" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B213" s="4" t="s">
         <v>1110</v>
       </c>
@@ -11045,7 +11062,7 @@
         <v>1109</v>
       </c>
     </row>
-    <row r="214" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="214" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B214" s="4" t="s">
         <v>1118</v>
       </c>
@@ -11072,7 +11089,7 @@
         <v>1114</v>
       </c>
     </row>
-    <row r="215" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="215" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B215" s="4" t="s">
         <v>1121</v>
       </c>
@@ -11096,7 +11113,7 @@
         <v>1116</v>
       </c>
     </row>
-    <row r="216" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="216" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B216" s="4" t="s">
         <v>1126</v>
       </c>
@@ -11123,7 +11140,7 @@
         <v>1131</v>
       </c>
     </row>
-    <row r="217" spans="2:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="217" spans="2:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B217" s="4" t="s">
         <v>1134</v>
       </c>
@@ -11147,7 +11164,7 @@
         <v>1113</v>
       </c>
     </row>
-    <row r="218" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="218" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B218" s="4" t="s">
         <v>1137</v>
       </c>
@@ -11174,7 +11191,7 @@
         <v>1132</v>
       </c>
     </row>
-    <row r="219" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="219" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B219" s="4" t="s">
         <v>1142</v>
       </c>
@@ -11198,7 +11215,7 @@
         <v>1120</v>
       </c>
     </row>
-    <row r="220" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="220" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B220" s="4" t="s">
         <v>1145</v>
       </c>
@@ -11222,7 +11239,7 @@
         <v>1149</v>
       </c>
     </row>
-    <row r="221" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="221" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B221" s="4" t="s">
         <v>1150</v>
       </c>
@@ -11246,7 +11263,7 @@
         <v>1154</v>
       </c>
     </row>
-    <row r="222" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="222" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B222" s="4" t="s">
         <v>1153</v>
       </c>
@@ -11270,7 +11287,7 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="223" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="223" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B223" s="4" t="s">
         <v>1161</v>
       </c>
@@ -11294,7 +11311,7 @@
         <v>1160</v>
       </c>
     </row>
-    <row r="224" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="224" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B224" s="4" t="s">
         <v>1165</v>
       </c>
@@ -11318,7 +11335,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="225" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="225" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B225" s="4" t="s">
         <v>1167</v>
       </c>
@@ -11345,7 +11362,7 @@
         <v>1166</v>
       </c>
     </row>
-    <row r="226" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="226" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B226" s="4" t="s">
         <v>1173</v>
       </c>
@@ -11369,7 +11386,7 @@
         <v>1174</v>
       </c>
     </row>
-    <row r="227" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="227" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B227" s="4" t="s">
         <v>1181</v>
       </c>
@@ -11393,548 +11410,566 @@
         <v>1180</v>
       </c>
     </row>
-    <row r="228" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="228" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="B228" s="4" t="s">
+        <v>1187</v>
+      </c>
+      <c r="C228" s="1" t="s">
+        <v>1188</v>
+      </c>
+      <c r="E228" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H228" s="1" t="s">
+        <v>1128</v>
+      </c>
       <c r="J228" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>00</v>
-      </c>
-    </row>
-    <row r="229" spans="2:12" x14ac:dyDescent="0.3">
+        <v>00NULL</v>
+      </c>
+      <c r="L228" s="2" t="s">
+        <v>1185</v>
+      </c>
+    </row>
+    <row r="229" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B229" s="4" t="s">
+        <v>1186</v>
+      </c>
       <c r="J229" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>00</v>
-      </c>
-    </row>
-    <row r="230" spans="2:12" x14ac:dyDescent="0.3">
+        <v>001133</v>
+      </c>
+    </row>
+    <row r="230" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J230" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="231" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="231" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J231" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="232" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="232" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J232" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="233" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="233" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J233" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="234" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="234" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J234" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="235" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="235" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J235" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="236" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="236" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J236" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="237" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="237" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J237" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="238" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="238" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J238" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="239" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="239" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J239" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="240" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="240" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J240" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="241" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="241" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J241" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="242" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="242" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J242" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="243" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="243" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J243" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="244" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="244" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J244" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="245" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="245" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J245" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="246" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="246" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J246" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="247" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="247" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J247" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="248" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="248" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J248" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="249" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="249" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J249" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="250" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="250" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J250" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="251" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="251" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J251" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="252" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="252" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J252" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="253" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="253" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J253" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="254" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="254" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J254" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="255" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="255" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J255" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="256" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="256" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J256" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="257" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="257" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J257" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="258" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="258" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J258" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="259" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="259" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J259" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="260" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="260" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J260" s="5" t="str">
         <f t="shared" ref="J260:J317" si="8">"00"&amp;B260</f>
         <v>00</v>
       </c>
     </row>
-    <row r="261" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="261" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J261" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="262" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="262" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J262" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="263" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="263" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J263" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="264" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="264" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J264" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="265" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="265" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J265" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="266" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="266" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J266" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="267" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="267" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J267" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="268" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="268" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J268" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="269" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="269" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J269" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="270" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="270" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J270" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="271" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="271" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J271" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="272" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="272" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J272" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="273" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="273" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J273" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="274" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="274" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J274" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="275" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="275" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J275" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="276" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="276" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J276" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="277" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="277" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J277" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="278" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="278" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J278" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="279" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="279" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J279" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="280" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="280" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J280" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="281" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="281" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J281" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="282" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="282" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J282" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="283" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="283" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J283" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="284" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="284" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J284" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="285" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="285" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J285" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="286" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="286" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J286" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="287" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="287" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J287" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="288" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="288" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J288" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="289" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="289" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J289" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="290" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="290" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J290" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="291" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="291" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J291" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="292" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="292" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J292" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="293" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="293" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J293" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="294" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="294" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J294" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="295" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="295" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J295" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="296" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="296" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J296" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="297" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="297" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J297" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="298" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="298" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J298" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="299" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="299" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J299" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="300" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="300" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J300" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="301" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="301" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J301" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="302" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="302" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J302" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="303" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="303" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J303" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="304" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="304" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J304" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="305" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="305" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J305" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="306" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="306" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J306" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="307" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="307" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J307" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="308" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="308" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J308" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="309" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="309" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J309" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="310" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="310" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J310" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="311" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="311" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J311" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="312" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="312" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J312" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="313" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="313" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J313" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="314" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="314" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J314" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="315" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="315" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J315" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="316" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="316" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J316" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
-    <row r="317" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="317" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J317" s="5" t="str">
         <f t="shared" si="8"/>
         <v>00</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:L4"/>
+  <autoFilter ref="A4:L4" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="1">
     <mergeCell ref="A2:L2"/>
   </mergeCells>
@@ -11946,10 +11981,10 @@
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1:E1 D3:E3 D6:E1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1:E1 D3:E3 D6:E1048576" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"是,否"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H1 H3:H1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H1 H3:H1048576" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"VB编程,系统运维,WEB学习,游戏碎片,日常随笔,浥尘伙伴社团"</formula1>
     </dataValidation>
   </dataValidations>
@@ -11959,20 +11994,20 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A2:L34"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="6.33203125" customWidth="1"/>
+    <col min="2" max="2" width="6.375" customWidth="1"/>
     <col min="3" max="3" width="34" style="4" customWidth="1"/>
     <col min="4" max="4" width="4.75" customWidth="1"/>
-    <col min="8" max="8" width="6.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="19" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="7.08203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.08203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:12" ht="22.5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" ht="23.25" x14ac:dyDescent="0.2">
       <c r="A2" s="21" t="s">
         <v>549</v>
       </c>
@@ -11988,7 +12023,7 @@
       <c r="K2" s="21"/>
       <c r="L2" s="21"/>
     </row>
-    <row r="4" spans="1:12" ht="56" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" ht="57" x14ac:dyDescent="0.2">
       <c r="A4" s="7" t="s">
         <v>0</v>
       </c>
@@ -12026,7 +12061,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
         <v>533</v>
       </c>
@@ -12049,7 +12084,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C8" s="15" t="s">
         <v>545</v>
       </c>
@@ -12058,7 +12093,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C9" s="4" t="s">
         <v>539</v>
       </c>
@@ -12066,7 +12101,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C10" t="s">
         <v>537</v>
       </c>
@@ -12074,7 +12109,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C11" t="s">
         <v>538</v>
       </c>
@@ -12082,7 +12117,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="22.5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" ht="23.25" x14ac:dyDescent="0.2">
       <c r="A13" s="21" t="s">
         <v>543</v>
       </c>
@@ -12098,7 +12133,7 @@
       <c r="K13" s="21"/>
       <c r="L13" s="21"/>
     </row>
-    <row r="15" spans="1:12" ht="56" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" ht="57" x14ac:dyDescent="0.2">
       <c r="A15" s="7" t="s">
         <v>0</v>
       </c>
@@ -12136,7 +12171,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
         <v>533</v>
       </c>
@@ -12162,7 +12197,7 @@
         <v>54837657</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C19" s="15" t="s">
         <v>545</v>
       </c>
@@ -12171,7 +12206,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C20" s="4" t="s">
         <v>539</v>
       </c>
@@ -12179,7 +12214,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C21" t="s">
         <v>537</v>
       </c>
@@ -12187,7 +12222,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C22" t="s">
         <v>538</v>
       </c>
@@ -12195,10 +12230,10 @@
         <v>541</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C23"/>
     </row>
-    <row r="25" spans="1:12" ht="22.5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" ht="23.25" x14ac:dyDescent="0.2">
       <c r="A25" s="21" t="s">
         <v>550</v>
       </c>
@@ -12214,7 +12249,7 @@
       <c r="K25" s="21"/>
       <c r="L25" s="21"/>
     </row>
-    <row r="27" spans="1:12" ht="56" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" ht="57" x14ac:dyDescent="0.2">
       <c r="A27" s="7" t="s">
         <v>0</v>
       </c>
@@ -12252,7 +12287,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B28" t="s">
         <v>533</v>
       </c>
@@ -12278,7 +12313,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C31" s="15" t="s">
         <v>545</v>
       </c>
@@ -12287,7 +12322,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C32" s="4" t="s">
         <v>539</v>
       </c>
@@ -12295,7 +12330,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="33" spans="3:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="3:5" x14ac:dyDescent="0.2">
       <c r="C33" t="s">
         <v>537</v>
       </c>
@@ -12303,7 +12338,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="34" spans="3:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="3:5" x14ac:dyDescent="0.2">
       <c r="C34" t="s">
         <v>538</v>
       </c>
@@ -12319,7 +12354,7 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H15 H27 H4">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H15 H27 H4" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"VB编程,系统运维,WEB学习,游戏碎片,日常随笔"</formula1>
     </dataValidation>
   </dataValidations>

--- a/11_付费课程/99.资料/文章信息备忘表.xlsx
+++ b/11_付费课程/99.资料/文章信息备忘表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Disks\E\Writing\11_付费课程\99.资料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AB0082A-80F4-4862-B557-331CE2FEA48D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B148922-934F-4B29-BD49-C4C34B809DA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6315" yWindow="1410" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1627" uniqueCount="1189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1639" uniqueCount="1198">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -4742,6 +4742,41 @@
   </si>
   <si>
     <t>浥尘伙伴社团独家密训课程：孩子成长必备之可视化创意思考课基础篇</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1134</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>占领岛国后，首长让我在断网的情况下安装日语输入法</t>
+  </si>
+  <si>
+    <t>2025-08-04 08:24:11</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>114280</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>59236932</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>障眼魔法，一行代码即可使网页变为可编辑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-06-22 19:46:03</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>98293716</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>306491</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -11147,6 +11182,9 @@
       <c r="C217" s="1" t="s">
         <v>1133</v>
       </c>
+      <c r="E217" s="6" t="s">
+        <v>32</v>
+      </c>
       <c r="H217" s="1" t="s">
         <v>654</v>
       </c>
@@ -11431,19 +11469,52 @@
         <v>1185</v>
       </c>
     </row>
-    <row r="229" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="229" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B229" s="4" t="s">
         <v>1186</v>
+      </c>
+      <c r="C229" s="1" t="s">
+        <v>1194</v>
+      </c>
+      <c r="H229" s="1" t="s">
+        <v>654</v>
+      </c>
+      <c r="I229" s="4" t="s">
+        <v>1195</v>
       </c>
       <c r="J229" s="5" t="str">
         <f t="shared" si="5"/>
         <v>001133</v>
       </c>
-    </row>
-    <row r="230" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="K229" s="3" t="s">
+        <v>1197</v>
+      </c>
+      <c r="L229" s="2" t="s">
+        <v>1196</v>
+      </c>
+    </row>
+    <row r="230" spans="2:12" ht="30" x14ac:dyDescent="0.2">
+      <c r="B230" s="4" t="s">
+        <v>1189</v>
+      </c>
+      <c r="C230" s="19" t="s">
+        <v>1190</v>
+      </c>
+      <c r="H230" s="1" t="s">
+        <v>654</v>
+      </c>
+      <c r="I230" s="4" t="s">
+        <v>1191</v>
+      </c>
       <c r="J230" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>00</v>
+        <v>001134</v>
+      </c>
+      <c r="K230" s="3" t="s">
+        <v>1192</v>
+      </c>
+      <c r="L230" s="2" t="s">
+        <v>1193</v>
       </c>
     </row>
     <row r="231" spans="2:12" x14ac:dyDescent="0.2">

--- a/11_付费课程/99.资料/文章信息备忘表.xlsx
+++ b/11_付费课程/99.资料/文章信息备忘表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Disks\E\Writing\11_付费课程\99.资料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B148922-934F-4B29-BD49-C4C34B809DA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D96ED7F-C18B-466C-B678-D545CAAAE7F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1639" uniqueCount="1198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1641" uniqueCount="1200">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -4777,6 +4777,14 @@
   </si>
   <si>
     <t>306491</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1135</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>64669853</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -11518,9 +11526,15 @@
       </c>
     </row>
     <row r="231" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B231" s="4" t="s">
+        <v>1198</v>
+      </c>
       <c r="J231" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>00</v>
+        <v>001135</v>
+      </c>
+      <c r="L231" s="2" t="s">
+        <v>1199</v>
       </c>
     </row>
     <row r="232" spans="2:12" x14ac:dyDescent="0.2">

--- a/11_付费课程/99.资料/文章信息备忘表.xlsx
+++ b/11_付费课程/99.资料/文章信息备忘表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Disks\E\Writing\11_付费课程\99.资料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D96ED7F-C18B-466C-B678-D545CAAAE7F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97948EDF-FC37-4039-A1C0-C17F11FAA841}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1641" uniqueCount="1200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1643" uniqueCount="1201">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -4785,6 +4785,10 @@
   </si>
   <si>
     <t>64669853</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>copyparty，仅一个程序文件的文件分享服务，居然还可以引出的卧底？</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -11525,9 +11529,15 @@
         <v>1193</v>
       </c>
     </row>
-    <row r="231" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="231" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B231" s="4" t="s">
         <v>1198</v>
+      </c>
+      <c r="C231" s="1" t="s">
+        <v>1200</v>
+      </c>
+      <c r="H231" s="1" t="s">
+        <v>654</v>
       </c>
       <c r="J231" s="5" t="str">
         <f t="shared" si="5"/>

--- a/11_付费课程/99.资料/文章信息备忘表.xlsx
+++ b/11_付费课程/99.资料/文章信息备忘表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Disks\E\Writing\11_付费课程\99.资料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97948EDF-FC37-4039-A1C0-C17F11FAA841}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9206E051-C34A-40D2-85C7-B7E72541385F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1643" uniqueCount="1201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1645" uniqueCount="1203">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -4789,6 +4789,14 @@
   </si>
   <si>
     <t>copyparty，仅一个程序文件的文件分享服务，居然还可以引出的卧底？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-09-12 09:06:42</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>246090</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -11539,9 +11547,15 @@
       <c r="H231" s="1" t="s">
         <v>654</v>
       </c>
+      <c r="I231" s="4" t="s">
+        <v>1201</v>
+      </c>
       <c r="J231" s="5" t="str">
         <f t="shared" si="5"/>
         <v>001135</v>
+      </c>
+      <c r="K231" s="3" t="s">
+        <v>1202</v>
       </c>
       <c r="L231" s="2" t="s">
         <v>1199</v>

--- a/11_付费课程/99.资料/文章信息备忘表.xlsx
+++ b/11_付费课程/99.资料/文章信息备忘表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Disks\E\Writing\11_付费课程\99.资料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9206E051-C34A-40D2-85C7-B7E72541385F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AE3858C-2D89-4767-A0A7-F3DDA47273F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/11_付费课程/99.资料/文章信息备忘表.xlsx
+++ b/11_付费课程/99.资料/文章信息备忘表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Disks\E\Writing\11_付费课程\99.资料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AE3858C-2D89-4767-A0A7-F3DDA47273F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{048C8C69-6B5C-4B27-8CF9-29DBF822D865}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1645" uniqueCount="1203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1649" uniqueCount="1206">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -4798,6 +4798,17 @@
   <si>
     <t>246090</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>56599184</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1136</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>有个号称 AI 加持的音视频下载工具 Grabcube ，真的好用吗？</t>
   </si>
 </sst>
 </file>
@@ -11561,10 +11572,22 @@
         <v>1199</v>
       </c>
     </row>
-    <row r="232" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="232" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="B232" s="4" t="s">
+        <v>1204</v>
+      </c>
+      <c r="C232" s="1" t="s">
+        <v>1205</v>
+      </c>
+      <c r="H232" s="1" t="s">
+        <v>654</v>
+      </c>
       <c r="J232" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>00</v>
+        <v>001136</v>
+      </c>
+      <c r="L232" s="2" t="s">
+        <v>1203</v>
       </c>
     </row>
     <row r="233" spans="2:12" x14ac:dyDescent="0.2">

--- a/11_付费课程/99.资料/文章信息备忘表.xlsx
+++ b/11_付费课程/99.资料/文章信息备忘表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Disks\E\Writing\11_付费课程\99.资料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{048C8C69-6B5C-4B27-8CF9-29DBF822D865}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A67D77C1-C8A8-4A77-924C-B305ED363044}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1649" uniqueCount="1206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1655" uniqueCount="1211">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -4809,6 +4809,26 @@
   </si>
   <si>
     <t>有个号称 AI 加持的音视频下载工具 Grabcube ，真的好用吗？</t>
+  </si>
+  <si>
+    <t>05243977</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HEVC格式的照片文件是个什么鬼？教你打开它的正确姿势！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1137</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-10-20 07:44:44</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>444470</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -11582,18 +11602,36 @@
       <c r="H232" s="1" t="s">
         <v>654</v>
       </c>
+      <c r="I232" s="4" t="s">
+        <v>1209</v>
+      </c>
       <c r="J232" s="5" t="str">
         <f t="shared" si="5"/>
         <v>001136</v>
       </c>
+      <c r="K232" s="3" t="s">
+        <v>1210</v>
+      </c>
       <c r="L232" s="2" t="s">
         <v>1203</v>
       </c>
     </row>
-    <row r="233" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="233" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="B233" s="4" t="s">
+        <v>1208</v>
+      </c>
+      <c r="C233" s="1" t="s">
+        <v>1207</v>
+      </c>
+      <c r="H233" s="1" t="s">
+        <v>654</v>
+      </c>
       <c r="J233" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>00</v>
+        <v>001137</v>
+      </c>
+      <c r="L233" s="2" t="s">
+        <v>1206</v>
       </c>
     </row>
     <row r="234" spans="2:12" x14ac:dyDescent="0.2">

--- a/11_付费课程/99.资料/文章信息备忘表.xlsx
+++ b/11_付费课程/99.资料/文章信息备忘表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Disks\E\Writing\11_付费课程\99.资料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A67D77C1-C8A8-4A77-924C-B305ED363044}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{539E99B1-E3BC-4E66-A528-3A89B5D674AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1655" uniqueCount="1211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1660" uniqueCount="1214">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -4828,6 +4828,17 @@
   </si>
   <si>
     <t>444470</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>73927536</t>
+  </si>
+  <si>
+    <t>1138</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>restic</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -11635,9 +11646,24 @@
       </c>
     </row>
     <row r="234" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B234" s="4" t="s">
+        <v>1212</v>
+      </c>
+      <c r="C234" s="1" t="s">
+        <v>1213</v>
+      </c>
+      <c r="E234" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H234" s="1" t="s">
+        <v>21</v>
+      </c>
       <c r="J234" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>00</v>
+        <v>001138</v>
+      </c>
+      <c r="L234" s="2" t="s">
+        <v>1211</v>
       </c>
     </row>
     <row r="235" spans="2:12" x14ac:dyDescent="0.2">

--- a/11_付费课程/99.资料/文章信息备忘表.xlsx
+++ b/11_付费课程/99.资料/文章信息备忘表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Disks\E\Writing\11_付费课程\99.资料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{539E99B1-E3BC-4E66-A528-3A89B5D674AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B5E0EA7-EEF9-43E4-A2F8-364E1CFF68D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4831,14 +4831,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>1138</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Restic官方管理手册中文版（网管小贾）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>73927536</t>
-  </si>
-  <si>
-    <t>1138</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>restic</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -5338,7 +5339,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:M317"/>
+  <dimension ref="A2:M316"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.25" style="8" customWidth="1"/>
@@ -10765,7 +10766,7 @@
         <v>1029</v>
       </c>
       <c r="J197" s="5" t="str">
-        <f t="shared" ref="J197:J259" si="5">"00"&amp;B197</f>
+        <f t="shared" ref="J197:J258" si="5">"00"&amp;B197</f>
         <v>001099</v>
       </c>
       <c r="K197" s="3" t="s">
@@ -11632,38 +11633,38 @@
         <v>1208</v>
       </c>
       <c r="C233" s="1" t="s">
-        <v>1207</v>
+        <v>1212</v>
+      </c>
+      <c r="E233" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="H233" s="1" t="s">
-        <v>654</v>
+        <v>21</v>
       </c>
       <c r="J233" s="5" t="str">
         <f t="shared" si="5"/>
         <v>001137</v>
       </c>
       <c r="L233" s="2" t="s">
+        <v>1213</v>
+      </c>
+    </row>
+    <row r="234" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="B234" s="4" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C234" s="1" t="s">
+        <v>1207</v>
+      </c>
+      <c r="H234" s="1" t="s">
+        <v>654</v>
+      </c>
+      <c r="J234" s="5" t="str">
+        <f t="shared" ref="J234" si="8">"00"&amp;B234</f>
+        <v>001138</v>
+      </c>
+      <c r="L234" s="2" t="s">
         <v>1206</v>
-      </c>
-    </row>
-    <row r="234" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B234" s="4" t="s">
-        <v>1212</v>
-      </c>
-      <c r="C234" s="1" t="s">
-        <v>1213</v>
-      </c>
-      <c r="E234" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="H234" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="J234" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>001138</v>
-      </c>
-      <c r="L234" s="2" t="s">
-        <v>1211</v>
       </c>
     </row>
     <row r="235" spans="2:12" x14ac:dyDescent="0.2">
@@ -11812,355 +11813,349 @@
     </row>
     <row r="259" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J259" s="5" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="J259:J316" si="9">"00"&amp;B259</f>
         <v>00</v>
       </c>
     </row>
     <row r="260" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J260" s="5" t="str">
-        <f t="shared" ref="J260:J317" si="8">"00"&amp;B260</f>
+        <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
     <row r="261" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J261" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
     <row r="262" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J262" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
     <row r="263" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J263" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
     <row r="264" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J264" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
     <row r="265" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J265" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
     <row r="266" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J266" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
     <row r="267" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J267" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
     <row r="268" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J268" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
     <row r="269" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J269" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
     <row r="270" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J270" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
     <row r="271" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J271" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
     <row r="272" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J272" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
     <row r="273" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J273" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
     <row r="274" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J274" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
     <row r="275" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J275" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
     <row r="276" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J276" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
     <row r="277" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J277" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
     <row r="278" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J278" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
     <row r="279" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J279" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
     <row r="280" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J280" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
     <row r="281" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J281" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
     <row r="282" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J282" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
     <row r="283" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J283" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
     <row r="284" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J284" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
     <row r="285" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J285" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
     <row r="286" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J286" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
     <row r="287" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J287" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
     <row r="288" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J288" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
     <row r="289" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J289" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
     <row r="290" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J290" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
     <row r="291" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J291" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
     <row r="292" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J292" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
     <row r="293" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J293" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
     <row r="294" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J294" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
     <row r="295" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J295" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
     <row r="296" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J296" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
     <row r="297" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J297" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
     <row r="298" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J298" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
     <row r="299" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J299" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
     <row r="300" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J300" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
     <row r="301" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J301" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
     <row r="302" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J302" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
     <row r="303" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J303" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
     <row r="304" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J304" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
     <row r="305" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J305" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
     <row r="306" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J306" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
     <row r="307" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J307" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
     <row r="308" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J308" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
     <row r="309" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J309" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
     <row r="310" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J310" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
     <row r="311" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J311" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
     <row r="312" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J312" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
     <row r="313" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J313" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
     <row r="314" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J314" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
     <row r="315" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J315" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
     <row r="316" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J316" s="5" t="str">
-        <f t="shared" si="8"/>
-        <v>00</v>
-      </c>
-    </row>
-    <row r="317" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J317" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>

--- a/11_付费课程/99.资料/文章信息备忘表.xlsx
+++ b/11_付费课程/99.资料/文章信息备忘表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Disks\E\Writing\11_付费课程\99.资料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B5E0EA7-EEF9-43E4-A2F8-364E1CFF68D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE336C54-13CA-4659-8AE3-D44BCD985930}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1660" uniqueCount="1214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1664" uniqueCount="1216">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -4840,6 +4840,14 @@
   </si>
   <si>
     <t>73927536</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>浥尘伙伴社团独家密训课程：社会真相与阶层教育高阶课</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>19137672</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -11667,10 +11675,22 @@
         <v>1206</v>
       </c>
     </row>
-    <row r="235" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="235" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="B235" s="4" t="s">
+        <v>1187</v>
+      </c>
+      <c r="C235" s="1" t="s">
+        <v>1214</v>
+      </c>
+      <c r="H235" s="1" t="s">
+        <v>1128</v>
+      </c>
       <c r="J235" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>00</v>
+        <v>00NULL</v>
+      </c>
+      <c r="L235" s="2" t="s">
+        <v>1215</v>
       </c>
     </row>
     <row r="236" spans="2:12" x14ac:dyDescent="0.2">

--- a/11_付费课程/99.资料/文章信息备忘表.xlsx
+++ b/11_付费课程/99.资料/文章信息备忘表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Disks\E\Writing\11_付费课程\99.资料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE336C54-13CA-4659-8AE3-D44BCD985930}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EEE34C3-42EF-4DD4-AB17-425B56874B8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1664" uniqueCount="1216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1666" uniqueCount="1218">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -4848,6 +4848,14 @@
   </si>
   <si>
     <t>19137672</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-11-10 08:48:39</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>938480</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -11667,9 +11675,15 @@
       <c r="H234" s="1" t="s">
         <v>654</v>
       </c>
+      <c r="I234" s="4" t="s">
+        <v>1216</v>
+      </c>
       <c r="J234" s="5" t="str">
         <f t="shared" ref="J234" si="8">"00"&amp;B234</f>
         <v>001138</v>
+      </c>
+      <c r="K234" s="3" t="s">
+        <v>1217</v>
       </c>
       <c r="L234" s="2" t="s">
         <v>1206</v>

--- a/11_付费课程/99.资料/文章信息备忘表.xlsx
+++ b/11_付费课程/99.资料/文章信息备忘表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Disks\E\Writing\11_付费课程\99.资料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EEE34C3-42EF-4DD4-AB17-425B56874B8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C484488-7BD3-4B4B-970A-FCEDEFAA89BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1666" uniqueCount="1218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1670" uniqueCount="1221">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -4856,6 +4856,18 @@
   </si>
   <si>
     <t>938480</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>01787849</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一次特别行动，要从一款从零研发的操作系统 MyraOS 说起……</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1139</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -11707,10 +11719,22 @@
         <v>1215</v>
       </c>
     </row>
-    <row r="236" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="236" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="B236" s="4" t="s">
+        <v>1220</v>
+      </c>
+      <c r="C236" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="H236" s="1" t="s">
+        <v>654</v>
+      </c>
       <c r="J236" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>00</v>
+        <v>001139</v>
+      </c>
+      <c r="L236" s="2" t="s">
+        <v>1218</v>
       </c>
     </row>
     <row r="237" spans="2:12" x14ac:dyDescent="0.2">

--- a/11_付费课程/99.资料/文章信息备忘表.xlsx
+++ b/11_付费课程/99.资料/文章信息备忘表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Disks\E\Writing\11_付费课程\99.资料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C484488-7BD3-4B4B-970A-FCEDEFAA89BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D1BECEE-620A-4DF4-A8ED-6909574F20D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3315" yWindow="4185" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1670" uniqueCount="1221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1674" uniqueCount="1223">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -4868,6 +4868,14 @@
   </si>
   <si>
     <t>1139</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>37259924</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>浥尘伙伴社团：中高考音乐减压心理训练</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -11737,10 +11745,22 @@
         <v>1218</v>
       </c>
     </row>
-    <row r="237" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="237" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="B237" s="4" t="s">
+        <v>1187</v>
+      </c>
+      <c r="C237" s="1" t="s">
+        <v>1222</v>
+      </c>
+      <c r="H237" s="1" t="s">
+        <v>1128</v>
+      </c>
       <c r="J237" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>00</v>
+        <v>00NULL</v>
+      </c>
+      <c r="L237" s="2" t="s">
+        <v>1221</v>
       </c>
     </row>
     <row r="238" spans="2:12" x14ac:dyDescent="0.2">

--- a/11_付费课程/99.资料/文章信息备忘表.xlsx
+++ b/11_付费课程/99.资料/文章信息备忘表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Disks\E\Writing\11_付费课程\99.资料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D1BECEE-620A-4DF4-A8ED-6909574F20D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8B5B526-AEEF-473D-B5D5-9C539308AD9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3315" yWindow="4185" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13110" yWindow="1020" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1674" uniqueCount="1223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1678" uniqueCount="1226">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -4876,6 +4876,18 @@
   </si>
   <si>
     <t>浥尘伙伴社团：中高考音乐减压心理训练</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>07195097</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>难缠的老太太不要Edge的IE模式，非要用IE浏览器，这可如何是好？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1140</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -11763,10 +11775,22 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="238" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="238" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="B238" s="4" t="s">
+        <v>1225</v>
+      </c>
+      <c r="C238" s="1" t="s">
+        <v>1224</v>
+      </c>
+      <c r="H238" s="1" t="s">
+        <v>654</v>
+      </c>
       <c r="J238" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>00</v>
+        <v>001140</v>
+      </c>
+      <c r="L238" s="2" t="s">
+        <v>1223</v>
       </c>
     </row>
     <row r="239" spans="2:12" x14ac:dyDescent="0.2">

--- a/11_付费课程/99.资料/文章信息备忘表.xlsx
+++ b/11_付费课程/99.资料/文章信息备忘表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Disks\E\Writing\11_付费课程\99.资料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8B5B526-AEEF-473D-B5D5-9C539308AD9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{316D747E-CAE1-4703-AB58-ACD7AABD462F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13110" yWindow="1020" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -4887,7 +4887,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1140</t>
+    <t>1141</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -11787,7 +11787,7 @@
       </c>
       <c r="J238" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>001140</v>
+        <v>001141</v>
       </c>
       <c r="L238" s="2" t="s">
         <v>1223</v>

--- a/11_付费课程/99.资料/文章信息备忘表.xlsx
+++ b/11_付费课程/99.资料/文章信息备忘表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Disks\E\Writing\11_付费课程\99.资料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{316D747E-CAE1-4703-AB58-ACD7AABD462F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E336D63-2577-4AFE-AF61-AF86C9C8D281}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5835" yWindow="3030" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1678" uniqueCount="1226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1682" uniqueCount="1229">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -4888,6 +4888,18 @@
   </si>
   <si>
     <t>1141</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>41125500</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1142</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Windows记事本支持Markdown了？我不信！</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -11793,10 +11805,22 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="239" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="239" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="B239" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C239" s="1" t="s">
+        <v>1228</v>
+      </c>
+      <c r="H239" s="1" t="s">
+        <v>654</v>
+      </c>
       <c r="J239" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>00</v>
+        <v>001142</v>
+      </c>
+      <c r="L239" s="2" t="s">
+        <v>1226</v>
       </c>
     </row>
     <row r="240" spans="2:12" x14ac:dyDescent="0.2">

--- a/11_付费课程/99.资料/文章信息备忘表.xlsx
+++ b/11_付费课程/99.资料/文章信息备忘表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Disks\E\Writing\11_付费课程\99.资料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E336D63-2577-4AFE-AF61-AF86C9C8D281}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABD362FC-4639-4CAF-8CFA-E16CED4B3462}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5835" yWindow="3030" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4725" yWindow="4290" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1682" uniqueCount="1229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1686" uniqueCount="1232">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -4900,6 +4900,18 @@
   </si>
   <si>
     <t>Windows记事本支持Markdown了？我不信！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>96650214</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NULL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>浥尘伙伴社团：中高考音乐减压心理训练（含精选独创音乐包）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -11823,10 +11835,22 @@
         <v>1226</v>
       </c>
     </row>
-    <row r="240" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="240" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="B240" s="4" t="s">
+        <v>1230</v>
+      </c>
+      <c r="C240" s="1" t="s">
+        <v>1231</v>
+      </c>
+      <c r="H240" s="1" t="s">
+        <v>1128</v>
+      </c>
       <c r="J240" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>00</v>
+        <v>00NULL</v>
+      </c>
+      <c r="L240" s="2" t="s">
+        <v>1229</v>
       </c>
     </row>
     <row r="241" spans="10:10" x14ac:dyDescent="0.2">

--- a/11_付费课程/99.资料/文章信息备忘表.xlsx
+++ b/11_付费课程/99.资料/文章信息备忘表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Disks\E\Writing\11_付费课程\99.资料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABD362FC-4639-4CAF-8CFA-E16CED4B3462}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53C6D110-E060-4031-94BD-7B517565A133}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4725" yWindow="4290" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6030" yWindow="3930" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1686" uniqueCount="1232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1690" uniqueCount="1234">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -4912,6 +4912,14 @@
   </si>
   <si>
     <t>浥尘伙伴社团：中高考音乐减压心理训练（含精选独创音乐包）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>99129425</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>浥尘伙伴社团原创：情绪释放疗法（EFT）心理训练</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -11853,97 +11861,109 @@
         <v>1229</v>
       </c>
     </row>
-    <row r="241" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="241" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="B241" s="4" t="s">
+        <v>1187</v>
+      </c>
+      <c r="C241" s="1" t="s">
+        <v>1233</v>
+      </c>
+      <c r="H241" s="1" t="s">
+        <v>1128</v>
+      </c>
       <c r="J241" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>00</v>
-      </c>
-    </row>
-    <row r="242" spans="10:10" x14ac:dyDescent="0.2">
+        <v>00NULL</v>
+      </c>
+      <c r="L241" s="2" t="s">
+        <v>1232</v>
+      </c>
+    </row>
+    <row r="242" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J242" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="243" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="243" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J243" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="244" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="244" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J244" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="245" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="245" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J245" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="246" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="246" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J246" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="247" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="247" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J247" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="248" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="248" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J248" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="249" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="249" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J249" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="250" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="250" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J250" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="251" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="251" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J251" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="252" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="252" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J252" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="253" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="253" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J253" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="254" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="254" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J254" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="255" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="255" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J255" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="256" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="256" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J256" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>

--- a/11_付费课程/99.资料/文章信息备忘表.xlsx
+++ b/11_付费课程/99.资料/文章信息备忘表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Disks\E\Writing\11_付费课程\99.资料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53C6D110-E060-4031-94BD-7B517565A133}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE6031F6-E24E-4DA6-9C5B-CACD65878BB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6030" yWindow="3930" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7485" yWindow="5115" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1690" uniqueCount="1234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1694" uniqueCount="1236">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -4920,6 +4920,14 @@
   </si>
   <si>
     <t>浥尘伙伴社团原创：情绪释放疗法（EFT）心理训练</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>45008882</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>浥尘伙伴社团原创课程：从《三只小猪》的故事中寻找育儿真相（共11课）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -11879,10 +11887,22 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="242" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="242" spans="2:12" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="B242" s="4" t="s">
+        <v>1187</v>
+      </c>
+      <c r="C242" s="1" t="s">
+        <v>1235</v>
+      </c>
+      <c r="H242" s="1" t="s">
+        <v>1128</v>
+      </c>
       <c r="J242" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>00</v>
+        <v>00NULL</v>
+      </c>
+      <c r="L242" s="2" t="s">
+        <v>1234</v>
       </c>
     </row>
     <row r="243" spans="2:12" x14ac:dyDescent="0.2">

--- a/11_付费课程/99.资料/文章信息备忘表.xlsx
+++ b/11_付费课程/99.资料/文章信息备忘表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Disks\E\Writing\11_付费课程\99.资料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE6031F6-E24E-4DA6-9C5B-CACD65878BB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2B8F9C1-ED41-4929-B178-1D8124F16A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7485" yWindow="5115" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8325" yWindow="3420" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1694" uniqueCount="1236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1698" uniqueCount="1238">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -4928,6 +4928,14 @@
   </si>
   <si>
     <t>浥尘伙伴社团原创课程：从《三只小猪》的故事中寻找育儿真相（共11课）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>52412016</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>浥尘伙伴社团原创：青少年手机防沉迷认知课堂</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -11905,10 +11913,22 @@
         <v>1234</v>
       </c>
     </row>
-    <row r="243" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="243" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="B243" s="4" t="s">
+        <v>1187</v>
+      </c>
+      <c r="C243" s="1" t="s">
+        <v>1237</v>
+      </c>
+      <c r="H243" s="1" t="s">
+        <v>1128</v>
+      </c>
       <c r="J243" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>00</v>
+        <v>00NULL</v>
+      </c>
+      <c r="L243" s="2" t="s">
+        <v>1236</v>
       </c>
     </row>
     <row r="244" spans="2:12" x14ac:dyDescent="0.2">

--- a/11_付费课程/99.资料/文章信息备忘表.xlsx
+++ b/11_付费课程/99.资料/文章信息备忘表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Disks\E\Writing\11_付费课程\99.资料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2B8F9C1-ED41-4929-B178-1D8124F16A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BF90ED2-7B08-405B-87CC-76D1ED4F879F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8325" yWindow="3420" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1698" uniqueCount="1238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1702" uniqueCount="1241">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -4936,6 +4936,18 @@
   </si>
   <si>
     <t>浥尘伙伴社团原创：青少年手机防沉迷认知课堂</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>48672188</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1143</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bitlocker</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -11932,9 +11944,21 @@
       </c>
     </row>
     <row r="244" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B244" s="4" t="s">
+        <v>1239</v>
+      </c>
+      <c r="C244" s="1" t="s">
+        <v>1240</v>
+      </c>
+      <c r="H244" s="1" t="s">
+        <v>654</v>
+      </c>
       <c r="J244" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>00</v>
+        <v>001143</v>
+      </c>
+      <c r="L244" s="2" t="s">
+        <v>1238</v>
       </c>
     </row>
     <row r="245" spans="2:12" x14ac:dyDescent="0.2">

--- a/11_付费课程/99.资料/文章信息备忘表.xlsx
+++ b/11_付费课程/99.资料/文章信息备忘表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Disks\E\Writing\11_付费课程\99.资料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BF90ED2-7B08-405B-87CC-76D1ED4F879F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7638BE99-CFED-4220-8B2C-BCE33A999907}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6870" yWindow="3150" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -4943,11 +4943,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1143</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Bitlocker</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1144</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -11945,17 +11945,17 @@
     </row>
     <row r="244" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B244" s="4" t="s">
+        <v>1240</v>
+      </c>
+      <c r="C244" s="1" t="s">
         <v>1239</v>
-      </c>
-      <c r="C244" s="1" t="s">
-        <v>1240</v>
       </c>
       <c r="H244" s="1" t="s">
         <v>654</v>
       </c>
       <c r="J244" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>001143</v>
+        <v>001144</v>
       </c>
       <c r="L244" s="2" t="s">
         <v>1238</v>

--- a/11_付费课程/99.资料/文章信息备忘表.xlsx
+++ b/11_付费课程/99.资料/文章信息备忘表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Disks\E\Writing\11_付费课程\99.资料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7638BE99-CFED-4220-8B2C-BCE33A999907}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{983B79EA-38C2-42E4-844C-412E6273BF20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6870" yWindow="3150" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7005" yWindow="5085" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1702" uniqueCount="1241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1711" uniqueCount="1248">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -4948,6 +4948,34 @@
   </si>
   <si>
     <t>1144</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1146</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>14322299</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1145</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1147</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>202603061148_UEFIGame（下）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>202603051505_UEFIGame（上）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26498766</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -11962,21 +11990,48 @@
       </c>
     </row>
     <row r="245" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B245" s="4" t="s">
+        <v>1243</v>
+      </c>
       <c r="J245" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>00</v>
+        <v>001145</v>
       </c>
     </row>
     <row r="246" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B246" s="4" t="s">
+        <v>1241</v>
+      </c>
+      <c r="C246" s="1" t="s">
+        <v>1246</v>
+      </c>
+      <c r="H246" s="1" t="s">
+        <v>58</v>
+      </c>
       <c r="J246" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>00</v>
+        <v>001146</v>
+      </c>
+      <c r="L246" s="2" t="s">
+        <v>1242</v>
       </c>
     </row>
     <row r="247" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B247" s="4" t="s">
+        <v>1244</v>
+      </c>
+      <c r="C247" s="1" t="s">
+        <v>1245</v>
+      </c>
+      <c r="H247" s="1" t="s">
+        <v>58</v>
+      </c>
       <c r="J247" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>00</v>
+        <v>001147</v>
+      </c>
+      <c r="L247" s="2" t="s">
+        <v>1247</v>
       </c>
     </row>
     <row r="248" spans="2:12" x14ac:dyDescent="0.2">

--- a/11_付费课程/99.资料/文章信息备忘表.xlsx
+++ b/11_付费课程/99.资料/文章信息备忘表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Disks\E\Writing\11_付费课程\99.资料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{983B79EA-38C2-42E4-844C-412E6273BF20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97FBE5DB-3FEB-4016-A0FD-C6131CD84DC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7005" yWindow="5085" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5190" yWindow="3375" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -4943,10 +4943,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Bitlocker</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1144</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -4976,6 +4972,10 @@
   </si>
   <si>
     <t>26498766</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>别等电脑挂了后悔，教你现在就查看Bitlocker密钥</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -11971,12 +11971,12 @@
         <v>1236</v>
       </c>
     </row>
-    <row r="244" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="244" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B244" s="4" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="C244" s="1" t="s">
-        <v>1239</v>
+        <v>1247</v>
       </c>
       <c r="H244" s="1" t="s">
         <v>654</v>
@@ -11991,7 +11991,7 @@
     </row>
     <row r="245" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B245" s="4" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="J245" s="5" t="str">
         <f t="shared" si="5"/>
@@ -12000,10 +12000,10 @@
     </row>
     <row r="246" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B246" s="4" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="C246" s="1" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="H246" s="1" t="s">
         <v>58</v>
@@ -12013,15 +12013,15 @@
         <v>001146</v>
       </c>
       <c r="L246" s="2" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="247" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B247" s="4" t="s">
+        <v>1243</v>
+      </c>
+      <c r="C247" s="1" t="s">
         <v>1244</v>
-      </c>
-      <c r="C247" s="1" t="s">
-        <v>1245</v>
       </c>
       <c r="H247" s="1" t="s">
         <v>58</v>
@@ -12031,7 +12031,7 @@
         <v>001147</v>
       </c>
       <c r="L247" s="2" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="248" spans="2:12" x14ac:dyDescent="0.2">

--- a/11_付费课程/99.资料/文章信息备忘表.xlsx
+++ b/11_付费课程/99.资料/文章信息备忘表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Disks\E\Writing\11_付费课程\99.资料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97FBE5DB-3FEB-4016-A0FD-C6131CD84DC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41DE0D5C-22EC-49F2-8BEB-6FEACA0CCC32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5190" yWindow="3375" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1711" uniqueCount="1248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1715" uniqueCount="1251">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -4976,6 +4976,18 @@
   </si>
   <si>
     <t>别等电脑挂了后悔，教你现在就查看Bitlocker密钥</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>46095544</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1148</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Screenbox</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -12035,9 +12047,21 @@
       </c>
     </row>
     <row r="248" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B248" s="4" t="s">
+        <v>1249</v>
+      </c>
+      <c r="C248" s="1" t="s">
+        <v>1250</v>
+      </c>
+      <c r="H248" s="1" t="s">
+        <v>654</v>
+      </c>
       <c r="J248" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>00</v>
+        <v>001148</v>
+      </c>
+      <c r="L248" s="2" t="s">
+        <v>1248</v>
       </c>
     </row>
     <row r="249" spans="2:12" x14ac:dyDescent="0.2">

--- a/11_付费课程/99.资料/文章信息备忘表.xlsx
+++ b/11_付费课程/99.资料/文章信息备忘表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Disks\E\Writing\11_付费课程\99.资料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41DE0D5C-22EC-49F2-8BEB-6FEACA0CCC32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{261038BA-B7AA-4F28-AC5C-D203EE8DF882}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5190" yWindow="3375" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1715" uniqueCount="1251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1718" uniqueCount="1253">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -4988,6 +4988,14 @@
   </si>
   <si>
     <t>Screenbox</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>83320717</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AltSnap</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -12005,9 +12013,18 @@
       <c r="B245" s="4" t="s">
         <v>1242</v>
       </c>
+      <c r="C245" s="1" t="s">
+        <v>1252</v>
+      </c>
+      <c r="H245" s="1" t="s">
+        <v>654</v>
+      </c>
       <c r="J245" s="5" t="str">
         <f t="shared" si="5"/>
         <v>001145</v>
+      </c>
+      <c r="L245" s="2" t="s">
+        <v>1251</v>
       </c>
     </row>
     <row r="246" spans="2:12" x14ac:dyDescent="0.2">

--- a/11_付费课程/99.资料/文章信息备忘表.xlsx
+++ b/11_付费课程/99.资料/文章信息备忘表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Disks\E\Writing\11_付费课程\99.资料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{261038BA-B7AA-4F28-AC5C-D203EE8DF882}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C76E368-B0B3-4979-8032-425E1E5BB564}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5190" yWindow="3375" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5355" yWindow="3870" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -4995,7 +4995,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>AltSnap</t>
+    <t>一个兼职打工的介绍起了AltSanp，能有什么坏心思？</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -12009,7 +12009,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="245" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="245" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B245" s="4" t="s">
         <v>1242</v>
       </c>

--- a/11_付费课程/99.资料/文章信息备忘表.xlsx
+++ b/11_付费课程/99.资料/文章信息备忘表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Disks\E\Writing\11_付费课程\99.资料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C76E368-B0B3-4979-8032-425E1E5BB564}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25456D62-BF3D-4A50-89C2-484BEE8E9594}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5355" yWindow="3870" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5115" yWindow="3675" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/11_付费课程/99.资料/文章信息备忘表.xlsx
+++ b/11_付费课程/99.资料/文章信息备忘表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Disks\E\Writing\11_付费课程\99.资料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25456D62-BF3D-4A50-89C2-484BEE8E9594}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD6BAA6D-E440-43D7-BFBD-2BB5F4D300DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5115" yWindow="3675" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1718" uniqueCount="1253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1724" uniqueCount="1256">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -4996,6 +4996,18 @@
   </si>
   <si>
     <t>一个兼职打工的介绍起了AltSanp，能有什么坏心思？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>01741118</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>【浥尘伙伴社团独家密训】儿童青少年心理养育宝鉴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>许可口令：yichenhuoban</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -11592,7 +11604,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="225" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="225" spans="2:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B225" s="4" t="s">
         <v>1167</v>
       </c>
@@ -11619,7 +11631,7 @@
         <v>1166</v>
       </c>
     </row>
-    <row r="226" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="226" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B226" s="4" t="s">
         <v>1173</v>
       </c>
@@ -11643,7 +11655,7 @@
         <v>1174</v>
       </c>
     </row>
-    <row r="227" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="227" spans="2:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B227" s="4" t="s">
         <v>1181</v>
       </c>
@@ -11667,7 +11679,7 @@
         <v>1180</v>
       </c>
     </row>
-    <row r="228" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="228" spans="2:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B228" s="4" t="s">
         <v>1187</v>
       </c>
@@ -11688,7 +11700,7 @@
         <v>1185</v>
       </c>
     </row>
-    <row r="229" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="229" spans="2:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B229" s="4" t="s">
         <v>1186</v>
       </c>
@@ -11712,7 +11724,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="230" spans="2:12" ht="30" x14ac:dyDescent="0.2">
+    <row r="230" spans="2:13" ht="30" x14ac:dyDescent="0.2">
       <c r="B230" s="4" t="s">
         <v>1189</v>
       </c>
@@ -11736,7 +11748,7 @@
         <v>1193</v>
       </c>
     </row>
-    <row r="231" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="231" spans="2:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B231" s="4" t="s">
         <v>1198</v>
       </c>
@@ -11760,7 +11772,7 @@
         <v>1199</v>
       </c>
     </row>
-    <row r="232" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="232" spans="2:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B232" s="4" t="s">
         <v>1204</v>
       </c>
@@ -11784,7 +11796,7 @@
         <v>1203</v>
       </c>
     </row>
-    <row r="233" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="233" spans="2:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B233" s="4" t="s">
         <v>1208</v>
       </c>
@@ -11805,7 +11817,7 @@
         <v>1213</v>
       </c>
     </row>
-    <row r="234" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="234" spans="2:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B234" s="4" t="s">
         <v>1211</v>
       </c>
@@ -11829,7 +11841,7 @@
         <v>1206</v>
       </c>
     </row>
-    <row r="235" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="235" spans="2:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B235" s="4" t="s">
         <v>1187</v>
       </c>
@@ -11846,8 +11858,11 @@
       <c r="L235" s="2" t="s">
         <v>1215</v>
       </c>
-    </row>
-    <row r="236" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="M235" t="s">
+        <v>1255</v>
+      </c>
+    </row>
+    <row r="236" spans="2:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B236" s="4" t="s">
         <v>1220</v>
       </c>
@@ -11865,7 +11880,7 @@
         <v>1218</v>
       </c>
     </row>
-    <row r="237" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="237" spans="2:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B237" s="4" t="s">
         <v>1187</v>
       </c>
@@ -11883,7 +11898,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="238" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="238" spans="2:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B238" s="4" t="s">
         <v>1225</v>
       </c>
@@ -11901,7 +11916,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="239" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="239" spans="2:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B239" s="4" t="s">
         <v>1227</v>
       </c>
@@ -11919,7 +11934,7 @@
         <v>1226</v>
       </c>
     </row>
-    <row r="240" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="240" spans="2:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B240" s="4" t="s">
         <v>1230</v>
       </c>
@@ -11937,7 +11952,7 @@
         <v>1229</v>
       </c>
     </row>
-    <row r="241" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="241" spans="2:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B241" s="4" t="s">
         <v>1187</v>
       </c>
@@ -11955,7 +11970,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="242" spans="2:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="242" spans="2:13" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B242" s="4" t="s">
         <v>1187</v>
       </c>
@@ -11973,7 +11988,7 @@
         <v>1234</v>
       </c>
     </row>
-    <row r="243" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="243" spans="2:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B243" s="4" t="s">
         <v>1187</v>
       </c>
@@ -11991,7 +12006,7 @@
         <v>1236</v>
       </c>
     </row>
-    <row r="244" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="244" spans="2:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B244" s="4" t="s">
         <v>1239</v>
       </c>
@@ -12009,7 +12024,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="245" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="245" spans="2:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B245" s="4" t="s">
         <v>1242</v>
       </c>
@@ -12027,7 +12042,7 @@
         <v>1251</v>
       </c>
     </row>
-    <row r="246" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="246" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B246" s="4" t="s">
         <v>1240</v>
       </c>
@@ -12045,7 +12060,7 @@
         <v>1241</v>
       </c>
     </row>
-    <row r="247" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="247" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B247" s="4" t="s">
         <v>1243</v>
       </c>
@@ -12063,7 +12078,7 @@
         <v>1246</v>
       </c>
     </row>
-    <row r="248" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="248" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B248" s="4" t="s">
         <v>1249</v>
       </c>
@@ -12081,49 +12096,64 @@
         <v>1248</v>
       </c>
     </row>
-    <row r="249" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="249" spans="2:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="B249" s="4" t="s">
+        <v>1187</v>
+      </c>
+      <c r="C249" s="1" t="s">
+        <v>1254</v>
+      </c>
+      <c r="H249" s="1" t="s">
+        <v>1128</v>
+      </c>
       <c r="J249" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>00</v>
-      </c>
-    </row>
-    <row r="250" spans="2:12" x14ac:dyDescent="0.2">
+        <v>00NULL</v>
+      </c>
+      <c r="L249" s="2" t="s">
+        <v>1253</v>
+      </c>
+      <c r="M249" t="s">
+        <v>1255</v>
+      </c>
+    </row>
+    <row r="250" spans="2:13" x14ac:dyDescent="0.2">
       <c r="J250" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="251" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="251" spans="2:13" x14ac:dyDescent="0.2">
       <c r="J251" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="252" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="252" spans="2:13" x14ac:dyDescent="0.2">
       <c r="J252" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="253" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="253" spans="2:13" x14ac:dyDescent="0.2">
       <c r="J253" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="254" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="254" spans="2:13" x14ac:dyDescent="0.2">
       <c r="J254" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="255" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="255" spans="2:13" x14ac:dyDescent="0.2">
       <c r="J255" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="256" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="256" spans="2:13" x14ac:dyDescent="0.2">
       <c r="J256" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>

--- a/11_付费课程/99.资料/文章信息备忘表.xlsx
+++ b/11_付费课程/99.资料/文章信息备忘表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Disks\E\Writing\11_付费课程\99.资料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD6BAA6D-E440-43D7-BFBD-2BB5F4D300DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{258342D4-AA87-4428-957F-936496D560EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/11_付费课程/99.资料/文章信息备忘表.xlsx
+++ b/11_付费课程/99.资料/文章信息备忘表.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Disks\E\Writing\11_付费课程\99.资料\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\writing\11_付费课程\99.资料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{258342D4-AA87-4428-957F-936496D560EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2660" yWindow="1560" windowWidth="21600" windowHeight="11300"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$L$4</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -4963,14 +4962,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>202603061148_UEFIGame（下）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>202603051505_UEFIGame（上）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>26498766</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -4987,10 +4978,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Screenbox</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>83320717</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -5008,13 +4995,25 @@
   </si>
   <si>
     <t>许可口令：yichenhuoban</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>现代媒体播放器Screenbox，轻量颜值高，香！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>游戏不过关不让开机？UEFIGame（上）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>游戏不过关不让开机？UEFIGame（下）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -5506,25 +5505,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A2:M316"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.25" style="8" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="4" customWidth="1"/>
-    <col min="3" max="3" width="30.875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="5.375" style="6" customWidth="1"/>
-    <col min="5" max="6" width="5.125" style="6" customWidth="1"/>
+    <col min="2" max="2" width="5.58203125" style="4" customWidth="1"/>
+    <col min="3" max="3" width="30.83203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="5.33203125" style="6" customWidth="1"/>
+    <col min="5" max="6" width="5.08203125" style="6" customWidth="1"/>
     <col min="7" max="7" width="5.25" style="6" customWidth="1"/>
     <col min="8" max="8" width="13.5" style="1" customWidth="1"/>
     <col min="9" max="9" width="19" style="4" customWidth="1"/>
-    <col min="10" max="10" width="8.625" style="5" customWidth="1"/>
+    <col min="10" max="10" width="8.58203125" style="5" customWidth="1"/>
     <col min="11" max="11" width="7.5" style="3" customWidth="1"/>
     <col min="12" max="12" width="9.25" style="2" customWidth="1"/>
     <col min="13" max="13" width="16.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" ht="25" x14ac:dyDescent="0.3">
       <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
@@ -5540,8 +5539,8 @@
       <c r="K2" s="20"/>
       <c r="L2" s="20"/>
     </row>
-    <row r="3" spans="1:12" ht="6.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="4" spans="1:12" s="7" customFormat="1" ht="57" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12" ht="6.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:12" s="7" customFormat="1" ht="56" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>0</v>
       </c>
@@ -5579,7 +5578,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
         <v>557</v>
       </c>
@@ -5606,7 +5605,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
         <v>559</v>
       </c>
@@ -5642,7 +5641,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
         <v>559</v>
       </c>
@@ -5678,25 +5677,25 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="J8" s="5" t="str">
         <f t="shared" si="0"/>
         <v>000</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="J9" s="5" t="str">
         <f t="shared" si="0"/>
         <v>000</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="J10" s="5" t="str">
         <f t="shared" si="0"/>
         <v>000</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
         <v>522</v>
       </c>
@@ -5729,7 +5728,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
         <v>558</v>
       </c>
@@ -5759,7 +5758,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A13" s="8" t="s">
         <v>558</v>
       </c>
@@ -5789,7 +5788,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A14" s="8" t="s">
         <v>640</v>
       </c>
@@ -5816,7 +5815,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="8" t="s">
         <v>557</v>
       </c>
@@ -5843,7 +5842,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="8" t="s">
         <v>557</v>
       </c>
@@ -5870,7 +5869,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="8" t="s">
         <v>557</v>
       </c>
@@ -5897,7 +5896,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="8" t="s">
         <v>767</v>
       </c>
@@ -5924,7 +5923,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
         <v>557</v>
       </c>
@@ -5951,7 +5950,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A20" s="8" t="s">
         <v>557</v>
       </c>
@@ -5978,7 +5977,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A21" s="8" t="s">
         <v>557</v>
       </c>
@@ -6005,7 +6004,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A22" s="8" t="s">
         <v>559</v>
       </c>
@@ -6041,7 +6040,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" s="8" t="s">
         <v>557</v>
       </c>
@@ -6068,7 +6067,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A24" s="8" t="s">
         <v>558</v>
       </c>
@@ -6098,7 +6097,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A25" s="8" t="s">
         <v>557</v>
       </c>
@@ -6125,7 +6124,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A26" s="8" t="s">
         <v>557</v>
       </c>
@@ -6152,7 +6151,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="27" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A27" s="8" t="s">
         <v>633</v>
       </c>
@@ -6179,7 +6178,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A28" s="8" t="s">
         <v>557</v>
       </c>
@@ -6206,7 +6205,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A29" s="8" t="s">
         <v>559</v>
       </c>
@@ -6242,7 +6241,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A30" s="8" t="s">
         <v>559</v>
       </c>
@@ -6278,7 +6277,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A31" s="8" t="s">
         <v>557</v>
       </c>
@@ -6305,7 +6304,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A32" s="8" t="s">
         <v>557</v>
       </c>
@@ -6332,7 +6331,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A33" s="8" t="s">
         <v>557</v>
       </c>
@@ -6359,7 +6358,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="34" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A34" s="8" t="s">
         <v>557</v>
       </c>
@@ -6386,7 +6385,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="35" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A35" s="8" t="s">
         <v>557</v>
       </c>
@@ -6413,7 +6412,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="36" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A36" s="8" t="s">
         <v>557</v>
       </c>
@@ -6440,7 +6439,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="37" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A37" s="8" t="s">
         <v>559</v>
       </c>
@@ -6476,7 +6475,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="38" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A38" s="8" t="s">
         <v>557</v>
       </c>
@@ -6503,7 +6502,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" s="8" t="s">
         <v>557</v>
       </c>
@@ -6530,7 +6529,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="40" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A40" s="8" t="s">
         <v>557</v>
       </c>
@@ -6557,7 +6556,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="41" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A41" s="8" t="s">
         <v>557</v>
       </c>
@@ -6584,7 +6583,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="42" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A42" s="8" t="s">
         <v>557</v>
       </c>
@@ -6611,7 +6610,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="43" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A43" s="8" t="s">
         <v>559</v>
       </c>
@@ -6644,7 +6643,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="44" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A44" s="8" t="s">
         <v>557</v>
       </c>
@@ -6671,7 +6670,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="45" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A45" s="8" t="s">
         <v>557</v>
       </c>
@@ -6698,7 +6697,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="46" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A46" s="8" t="s">
         <v>557</v>
       </c>
@@ -6725,7 +6724,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" s="8" t="s">
         <v>557</v>
       </c>
@@ -6752,7 +6751,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="48" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A48" s="8" t="s">
         <v>557</v>
       </c>
@@ -6779,7 +6778,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="49" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A49" s="8" t="s">
         <v>557</v>
       </c>
@@ -6806,7 +6805,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="50" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A50" s="8" t="s">
         <v>557</v>
       </c>
@@ -6833,7 +6832,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" s="8" t="s">
         <v>557</v>
       </c>
@@ -6860,7 +6859,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="52" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A52" s="8" t="s">
         <v>557</v>
       </c>
@@ -6887,7 +6886,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" s="8" t="s">
         <v>557</v>
       </c>
@@ -6914,7 +6913,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="54" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A54" s="8" t="s">
         <v>557</v>
       </c>
@@ -6941,7 +6940,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" s="8" t="s">
         <v>557</v>
       </c>
@@ -6968,7 +6967,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="56" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A56" s="8" t="s">
         <v>559</v>
       </c>
@@ -7004,7 +7003,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="57" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A57" s="8" t="s">
         <v>559</v>
       </c>
@@ -7040,7 +7039,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="58" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A58" s="8" t="s">
         <v>557</v>
       </c>
@@ -7067,7 +7066,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="59" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A59" s="8" t="s">
         <v>558</v>
       </c>
@@ -7097,7 +7096,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="60" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A60" s="8" t="s">
         <v>557</v>
       </c>
@@ -7124,7 +7123,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="61" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B61" s="4" t="s">
         <v>298</v>
       </c>
@@ -7157,7 +7156,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="62" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B62" s="4" t="s">
         <v>294</v>
       </c>
@@ -7190,7 +7189,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="63" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B63" s="4" t="s">
         <v>289</v>
       </c>
@@ -7223,7 +7222,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="64" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A64" s="8" t="s">
         <v>557</v>
       </c>
@@ -7250,7 +7249,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="65" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A65" s="8" t="s">
         <v>557</v>
       </c>
@@ -7277,7 +7276,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="66" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A66" s="8" t="s">
         <v>559</v>
       </c>
@@ -7313,7 +7312,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="67" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A67" s="8" t="s">
         <v>557</v>
       </c>
@@ -7340,7 +7339,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="68" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A68" s="8" t="s">
         <v>558</v>
       </c>
@@ -7370,7 +7369,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="69" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A69" s="8" t="s">
         <v>559</v>
       </c>
@@ -7397,7 +7396,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="70" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A70" s="8" t="s">
         <v>559</v>
       </c>
@@ -7424,7 +7423,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="71" spans="1:12" ht="57" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:12" ht="56" x14ac:dyDescent="0.3">
       <c r="A71" s="8" t="s">
         <v>558</v>
       </c>
@@ -7454,7 +7453,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="72" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A72" s="8" t="s">
         <v>558</v>
       </c>
@@ -7484,7 +7483,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="73" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A73" s="8" t="s">
         <v>558</v>
       </c>
@@ -7514,7 +7513,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="74" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A74" s="8" t="s">
         <v>557</v>
       </c>
@@ -7541,7 +7540,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="75" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A75" s="8" t="s">
         <v>557</v>
       </c>
@@ -7568,7 +7567,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="76" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A76" s="8" t="s">
         <v>558</v>
       </c>
@@ -7601,7 +7600,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="77" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A77" s="8" t="s">
         <v>557</v>
       </c>
@@ -7628,7 +7627,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="78" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A78" s="8" t="s">
         <v>558</v>
       </c>
@@ -7655,7 +7654,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="79" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A79" s="8" t="s">
         <v>557</v>
       </c>
@@ -7682,7 +7681,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="80" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A80" s="8" t="s">
         <v>558</v>
       </c>
@@ -7709,7 +7708,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="81" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A81" s="8" t="s">
         <v>557</v>
       </c>
@@ -7736,7 +7735,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="82" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A82" s="8" t="s">
         <v>557</v>
       </c>
@@ -7763,7 +7762,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="83" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A83" s="8" t="s">
         <v>557</v>
       </c>
@@ -7790,7 +7789,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="84" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A84" s="8" t="s">
         <v>557</v>
       </c>
@@ -7817,7 +7816,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="85" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A85" s="8" t="s">
         <v>558</v>
       </c>
@@ -7844,7 +7843,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="86" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A86" s="8" t="s">
         <v>557</v>
       </c>
@@ -7871,7 +7870,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="87" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A87" s="8" t="s">
         <v>559</v>
       </c>
@@ -7907,7 +7906,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="88" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A88" s="8" t="s">
         <v>559</v>
       </c>
@@ -7943,7 +7942,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="89" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A89" s="8" t="s">
         <v>559</v>
       </c>
@@ -7979,7 +7978,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="90" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A90" s="8" t="s">
         <v>557</v>
       </c>
@@ -8006,7 +8005,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="91" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B91" s="4" t="s">
         <v>151</v>
       </c>
@@ -8039,7 +8038,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="92" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B92" s="4" t="s">
         <v>146</v>
       </c>
@@ -8072,7 +8071,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="93" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B93" s="4" t="s">
         <v>140</v>
       </c>
@@ -8105,7 +8104,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="94" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B94" s="4" t="s">
         <v>135</v>
       </c>
@@ -8138,7 +8137,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="95" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A95" s="8" t="s">
         <v>558</v>
       </c>
@@ -8165,7 +8164,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="96" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="B96" s="4" t="s">
         <v>123</v>
       </c>
@@ -8198,7 +8197,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="97" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B97" s="4" t="s">
         <v>118</v>
       </c>
@@ -8231,7 +8230,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="98" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="B98" s="4" t="s">
         <v>112</v>
       </c>
@@ -8264,7 +8263,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="99" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B99" s="4" t="s">
         <v>109</v>
       </c>
@@ -8297,7 +8296,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="100" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B100" s="4" t="s">
         <v>104</v>
       </c>
@@ -8330,7 +8329,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="101" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="B101" s="4" t="s">
         <v>98</v>
       </c>
@@ -8363,7 +8362,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="102" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B102" s="4" t="s">
         <v>92</v>
       </c>
@@ -8396,7 +8395,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="103" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A103" s="8" t="s">
         <v>559</v>
       </c>
@@ -8432,7 +8431,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="104" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A104" s="8" t="s">
         <v>557</v>
       </c>
@@ -8459,7 +8458,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="105" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A105" s="8" t="s">
         <v>557</v>
       </c>
@@ -8486,7 +8485,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="106" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A106" s="8" t="s">
         <v>557</v>
       </c>
@@ -8513,7 +8512,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="107" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A107" s="8" t="s">
         <v>557</v>
       </c>
@@ -8540,7 +8539,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="108" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A108" s="8" t="s">
         <v>557</v>
       </c>
@@ -8567,7 +8566,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="109" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A109" s="8" t="s">
         <v>559</v>
       </c>
@@ -8603,7 +8602,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A110" s="8" t="s">
         <v>558</v>
       </c>
@@ -8630,7 +8629,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="111" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A111" s="8" t="s">
         <v>557</v>
       </c>
@@ -8657,7 +8656,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="112" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A112" s="8" t="s">
         <v>557</v>
       </c>
@@ -8684,7 +8683,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="113" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A113" s="8" t="s">
         <v>557</v>
       </c>
@@ -8711,7 +8710,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A114" s="8" t="s">
         <v>557</v>
       </c>
@@ -8738,7 +8737,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="115" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A115" s="8" t="s">
         <v>557</v>
       </c>
@@ -8765,7 +8764,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="116" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A116" s="8" t="s">
         <v>559</v>
       </c>
@@ -8801,7 +8800,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="117" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A117" s="8" t="s">
         <v>557</v>
       </c>
@@ -8828,7 +8827,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="118" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A118" s="8" t="s">
         <v>558</v>
       </c>
@@ -8858,7 +8857,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="119" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A119" s="8" t="s">
         <v>557</v>
       </c>
@@ -8885,7 +8884,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="120" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A120" s="8" t="s">
         <v>557</v>
       </c>
@@ -8912,7 +8911,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="121" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A121" s="8" t="s">
         <v>597</v>
       </c>
@@ -8939,7 +8938,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="122" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A122" s="8" t="s">
         <v>602</v>
       </c>
@@ -8966,7 +8965,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="123" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A123" s="8" t="s">
         <v>608</v>
       </c>
@@ -8993,7 +8992,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="124" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A124" s="8" t="s">
         <v>611</v>
       </c>
@@ -9020,7 +9019,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="125" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A125" s="8" t="s">
         <v>617</v>
       </c>
@@ -9047,7 +9046,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="126" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A126" s="8" t="s">
         <v>624</v>
       </c>
@@ -9074,7 +9073,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="127" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A127" s="8" t="s">
         <v>557</v>
       </c>
@@ -9101,7 +9100,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="128" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A128" s="8" t="s">
         <v>649</v>
       </c>
@@ -9128,7 +9127,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="129" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A129" s="8" t="s">
         <v>653</v>
       </c>
@@ -9155,7 +9154,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="130" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A130" s="8" t="s">
         <v>659</v>
       </c>
@@ -9182,7 +9181,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="131" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A131" s="8" t="s">
         <v>664</v>
       </c>
@@ -9209,7 +9208,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A132" s="8" t="s">
         <v>557</v>
       </c>
@@ -9236,7 +9235,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="133" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A133" s="8" t="s">
         <v>557</v>
       </c>
@@ -9263,7 +9262,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="134" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A134" s="8" t="s">
         <v>681</v>
       </c>
@@ -9290,7 +9289,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="135" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A135" s="8" t="s">
         <v>687</v>
       </c>
@@ -9317,7 +9316,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="136" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A136" s="8" t="s">
         <v>691</v>
       </c>
@@ -9344,7 +9343,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="137" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A137" s="8" t="s">
         <v>699</v>
       </c>
@@ -9371,7 +9370,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="138" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A138" s="8" t="s">
         <v>704</v>
       </c>
@@ -9398,7 +9397,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="139" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A139" s="8" t="s">
         <v>711</v>
       </c>
@@ -9425,7 +9424,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="140" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A140" s="8" t="s">
         <v>716</v>
       </c>
@@ -9452,7 +9451,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="141" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A141" s="8" t="s">
         <v>724</v>
       </c>
@@ -9479,7 +9478,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="142" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A142" s="8" t="s">
         <v>727</v>
       </c>
@@ -9506,7 +9505,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="143" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A143" s="8" t="s">
         <v>736</v>
       </c>
@@ -9533,7 +9532,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="144" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A144" s="8" t="s">
         <v>740</v>
       </c>
@@ -9560,7 +9559,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="145" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A145" s="8" t="s">
         <v>746</v>
       </c>
@@ -9587,7 +9586,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="146" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A146" s="8" t="s">
         <v>754</v>
       </c>
@@ -9614,7 +9613,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="147" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A147" s="8" t="s">
         <v>759</v>
       </c>
@@ -9641,7 +9640,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="148" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A148" s="8" t="s">
         <v>770</v>
       </c>
@@ -9668,7 +9667,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="149" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A149" s="8" t="s">
         <v>777</v>
       </c>
@@ -9695,7 +9694,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="150" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="A150" s="8" t="s">
         <v>782</v>
       </c>
@@ -9722,7 +9721,7 @@
         <v>786</v>
       </c>
     </row>
-    <row r="151" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A151" s="8" t="s">
         <v>557</v>
       </c>
@@ -9749,7 +9748,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="152" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A152" s="8" t="s">
         <v>795</v>
       </c>
@@ -9776,7 +9775,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A153" s="8" t="s">
         <v>800</v>
       </c>
@@ -9803,7 +9802,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A154" s="8" t="s">
         <v>804</v>
       </c>
@@ -9830,7 +9829,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A155" s="8" t="s">
         <v>811</v>
       </c>
@@ -9857,7 +9856,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="156" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A156" s="8" t="s">
         <v>557</v>
       </c>
@@ -9884,7 +9883,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A157" s="8" t="s">
         <v>557</v>
       </c>
@@ -9911,7 +9910,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A158" s="8" t="s">
         <v>827</v>
       </c>
@@ -9938,7 +9937,7 @@
         <v>831</v>
       </c>
     </row>
-    <row r="159" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A159" s="8" t="s">
         <v>557</v>
       </c>
@@ -9965,7 +9964,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A160" s="8" t="s">
         <v>838</v>
       </c>
@@ -9992,7 +9991,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="161" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A161" s="8" t="s">
         <v>557</v>
       </c>
@@ -10019,7 +10018,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A162" s="8" t="s">
         <v>850</v>
       </c>
@@ -10046,7 +10045,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A163" s="8" t="s">
         <v>857</v>
       </c>
@@ -10073,7 +10072,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A164" s="8" t="s">
         <v>557</v>
       </c>
@@ -10100,7 +10099,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="165" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A165" s="8" t="s">
         <v>557</v>
       </c>
@@ -10127,7 +10126,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A166" s="8" t="s">
         <v>557</v>
       </c>
@@ -10154,7 +10153,7 @@
         <v>871</v>
       </c>
     </row>
-    <row r="167" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A167" s="8" t="s">
         <v>557</v>
       </c>
@@ -10181,7 +10180,7 @@
         <v>879</v>
       </c>
     </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A168" s="8" t="s">
         <v>557</v>
       </c>
@@ -10208,7 +10207,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A169" s="8" t="s">
         <v>557</v>
       </c>
@@ -10235,7 +10234,7 @@
         <v>889</v>
       </c>
     </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A170" s="8" t="s">
         <v>557</v>
       </c>
@@ -10262,7 +10261,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A171" s="8" t="s">
         <v>557</v>
       </c>
@@ -10289,7 +10288,7 @@
         <v>897</v>
       </c>
     </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A172" s="8" t="s">
         <v>902</v>
       </c>
@@ -10316,7 +10315,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A173" s="8" t="s">
         <v>902</v>
       </c>
@@ -10343,7 +10342,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A174" s="8" t="s">
         <v>557</v>
       </c>
@@ -10370,7 +10369,7 @@
         <v>915</v>
       </c>
     </row>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A175" s="8" t="s">
         <v>557</v>
       </c>
@@ -10397,7 +10396,7 @@
         <v>919</v>
       </c>
     </row>
-    <row r="176" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A176" s="8" t="s">
         <v>557</v>
       </c>
@@ -10424,7 +10423,7 @@
         <v>925</v>
       </c>
     </row>
-    <row r="177" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A177" s="8" t="s">
         <v>557</v>
       </c>
@@ -10451,7 +10450,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="178" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:13" ht="28" x14ac:dyDescent="0.3">
       <c r="A178" s="8" t="s">
         <v>557</v>
       </c>
@@ -10478,7 +10477,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="179" spans="1:13" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:13" ht="42" x14ac:dyDescent="0.3">
       <c r="A179" s="8" t="s">
         <v>938</v>
       </c>
@@ -10505,7 +10504,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="180" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B180" s="4" t="s">
         <v>942</v>
       </c>
@@ -10529,7 +10528,7 @@
         <v>946</v>
       </c>
     </row>
-    <row r="181" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:13" ht="28" x14ac:dyDescent="0.3">
       <c r="B181" s="4" t="s">
         <v>948</v>
       </c>
@@ -10553,7 +10552,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="182" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:13" ht="28" x14ac:dyDescent="0.3">
       <c r="B182" s="4" t="s">
         <v>954</v>
       </c>
@@ -10577,7 +10576,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="183" spans="1:13" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:13" ht="42" x14ac:dyDescent="0.3">
       <c r="B183" s="4" t="s">
         <v>959</v>
       </c>
@@ -10601,7 +10600,7 @@
         <v>960</v>
       </c>
     </row>
-    <row r="184" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:13" ht="28" x14ac:dyDescent="0.3">
       <c r="B184" s="4" t="s">
         <v>966</v>
       </c>
@@ -10625,7 +10624,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="185" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:13" ht="28" x14ac:dyDescent="0.3">
       <c r="B185" s="4" t="s">
         <v>971</v>
       </c>
@@ -10649,7 +10648,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="186" spans="1:13" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:13" ht="42" x14ac:dyDescent="0.3">
       <c r="B186" s="4" t="s">
         <v>976</v>
       </c>
@@ -10673,7 +10672,7 @@
         <v>963</v>
       </c>
     </row>
-    <row r="187" spans="1:13" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:13" ht="42" x14ac:dyDescent="0.3">
       <c r="B187" s="4" t="s">
         <v>979</v>
       </c>
@@ -10697,7 +10696,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="188" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:13" ht="28" x14ac:dyDescent="0.3">
       <c r="B188" s="4" t="s">
         <v>985</v>
       </c>
@@ -10724,7 +10723,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="189" spans="1:13" ht="15" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:13" ht="15.5" x14ac:dyDescent="0.3">
       <c r="B189" s="4" t="s">
         <v>988</v>
       </c>
@@ -10749,7 +10748,7 @@
       </c>
       <c r="M189" s="6"/>
     </row>
-    <row r="190" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:13" ht="28" x14ac:dyDescent="0.3">
       <c r="B190" s="4" t="s">
         <v>992</v>
       </c>
@@ -10773,7 +10772,7 @@
         <v>982</v>
       </c>
     </row>
-    <row r="191" spans="1:13" ht="45" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:13" ht="46.5" x14ac:dyDescent="0.3">
       <c r="B191" s="4" t="s">
         <v>1002</v>
       </c>
@@ -10797,7 +10796,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="192" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:13" ht="28" x14ac:dyDescent="0.3">
       <c r="B192" s="4" t="s">
         <v>1006</v>
       </c>
@@ -10821,7 +10820,7 @@
         <v>998</v>
       </c>
     </row>
-    <row r="193" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="193" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B193" s="4" t="s">
         <v>1010</v>
       </c>
@@ -10845,7 +10844,7 @@
         <v>1011</v>
       </c>
     </row>
-    <row r="194" spans="2:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="194" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B194" s="4" t="s">
         <v>1015</v>
       </c>
@@ -10872,7 +10871,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="195" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="195" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B195" s="4" t="s">
         <v>1021</v>
       </c>
@@ -10896,7 +10895,7 @@
         <v>1019</v>
       </c>
     </row>
-    <row r="196" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="196" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B196" s="4" t="s">
         <v>1025</v>
       </c>
@@ -10920,7 +10919,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="197" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="197" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B197" s="4" t="s">
         <v>1031</v>
       </c>
@@ -10944,7 +10943,7 @@
         <v>1033</v>
       </c>
     </row>
-    <row r="198" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="198" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B198" s="4" t="s">
         <v>1034</v>
       </c>
@@ -10968,7 +10967,7 @@
         <v>1035</v>
       </c>
     </row>
-    <row r="199" spans="2:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="199" spans="2:12" ht="42" x14ac:dyDescent="0.3">
       <c r="B199" s="4" t="s">
         <v>1040</v>
       </c>
@@ -10992,7 +10991,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="200" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="200" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B200" s="4" t="s">
         <v>1045</v>
       </c>
@@ -11016,7 +11015,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="201" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="201" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B201" s="4" t="s">
         <v>1051</v>
       </c>
@@ -11040,7 +11039,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="202" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="202" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B202" s="4" t="s">
         <v>1058</v>
       </c>
@@ -11064,7 +11063,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="203" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="203" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B203" s="4" t="s">
         <v>1062</v>
       </c>
@@ -11088,7 +11087,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="204" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="204" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B204" s="4" t="s">
         <v>1065</v>
       </c>
@@ -11112,7 +11111,7 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="205" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="205" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B205" s="4" t="s">
         <v>1071</v>
       </c>
@@ -11136,7 +11135,7 @@
         <v>1069</v>
       </c>
     </row>
-    <row r="206" spans="2:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="206" spans="2:12" ht="42" x14ac:dyDescent="0.3">
       <c r="B206" s="4" t="s">
         <v>1074</v>
       </c>
@@ -11160,7 +11159,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="207" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="207" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B207" s="4" t="s">
         <v>1080</v>
       </c>
@@ -11184,7 +11183,7 @@
         <v>1079</v>
       </c>
     </row>
-    <row r="208" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="208" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B208" s="4" t="s">
         <v>1082</v>
       </c>
@@ -11208,7 +11207,7 @@
         <v>1081</v>
       </c>
     </row>
-    <row r="209" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="209" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B209" s="4" t="s">
         <v>1091</v>
       </c>
@@ -11232,7 +11231,7 @@
         <v>1089</v>
       </c>
     </row>
-    <row r="210" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="210" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B210" s="4" t="s">
         <v>1093</v>
       </c>
@@ -11256,7 +11255,7 @@
         <v>1092</v>
       </c>
     </row>
-    <row r="211" spans="2:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="211" spans="2:12" ht="42" x14ac:dyDescent="0.3">
       <c r="B211" s="4" t="s">
         <v>1102</v>
       </c>
@@ -11280,7 +11279,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="212" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="212" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B212" s="4" t="s">
         <v>1105</v>
       </c>
@@ -11304,7 +11303,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="213" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="213" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B213" s="4" t="s">
         <v>1110</v>
       </c>
@@ -11328,7 +11327,7 @@
         <v>1109</v>
       </c>
     </row>
-    <row r="214" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="214" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B214" s="4" t="s">
         <v>1118</v>
       </c>
@@ -11355,7 +11354,7 @@
         <v>1114</v>
       </c>
     </row>
-    <row r="215" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="215" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B215" s="4" t="s">
         <v>1121</v>
       </c>
@@ -11379,7 +11378,7 @@
         <v>1116</v>
       </c>
     </row>
-    <row r="216" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="216" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B216" s="4" t="s">
         <v>1126</v>
       </c>
@@ -11406,7 +11405,7 @@
         <v>1131</v>
       </c>
     </row>
-    <row r="217" spans="2:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="217" spans="2:12" ht="42" x14ac:dyDescent="0.3">
       <c r="B217" s="4" t="s">
         <v>1134</v>
       </c>
@@ -11433,7 +11432,7 @@
         <v>1113</v>
       </c>
     </row>
-    <row r="218" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="218" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B218" s="4" t="s">
         <v>1137</v>
       </c>
@@ -11460,7 +11459,7 @@
         <v>1132</v>
       </c>
     </row>
-    <row r="219" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="219" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B219" s="4" t="s">
         <v>1142</v>
       </c>
@@ -11484,7 +11483,7 @@
         <v>1120</v>
       </c>
     </row>
-    <row r="220" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="220" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B220" s="4" t="s">
         <v>1145</v>
       </c>
@@ -11508,7 +11507,7 @@
         <v>1149</v>
       </c>
     </row>
-    <row r="221" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="221" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B221" s="4" t="s">
         <v>1150</v>
       </c>
@@ -11532,7 +11531,7 @@
         <v>1154</v>
       </c>
     </row>
-    <row r="222" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="222" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B222" s="4" t="s">
         <v>1153</v>
       </c>
@@ -11556,7 +11555,7 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="223" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="223" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B223" s="4" t="s">
         <v>1161</v>
       </c>
@@ -11580,7 +11579,7 @@
         <v>1160</v>
       </c>
     </row>
-    <row r="224" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="224" spans="2:12" ht="28" x14ac:dyDescent="0.3">
       <c r="B224" s="4" t="s">
         <v>1165</v>
       </c>
@@ -11604,7 +11603,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="225" spans="2:13" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="225" spans="2:13" ht="28" x14ac:dyDescent="0.3">
       <c r="B225" s="4" t="s">
         <v>1167</v>
       </c>
@@ -11631,7 +11630,7 @@
         <v>1166</v>
       </c>
     </row>
-    <row r="226" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="226" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B226" s="4" t="s">
         <v>1173</v>
       </c>
@@ -11655,7 +11654,7 @@
         <v>1174</v>
       </c>
     </row>
-    <row r="227" spans="2:13" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="227" spans="2:13" ht="28" x14ac:dyDescent="0.3">
       <c r="B227" s="4" t="s">
         <v>1181</v>
       </c>
@@ -11679,7 +11678,7 @@
         <v>1180</v>
       </c>
     </row>
-    <row r="228" spans="2:13" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="228" spans="2:13" ht="28" x14ac:dyDescent="0.3">
       <c r="B228" s="4" t="s">
         <v>1187</v>
       </c>
@@ -11700,7 +11699,7 @@
         <v>1185</v>
       </c>
     </row>
-    <row r="229" spans="2:13" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="229" spans="2:13" ht="28" x14ac:dyDescent="0.3">
       <c r="B229" s="4" t="s">
         <v>1186</v>
       </c>
@@ -11724,7 +11723,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="230" spans="2:13" ht="30" x14ac:dyDescent="0.2">
+    <row r="230" spans="2:13" ht="31" x14ac:dyDescent="0.3">
       <c r="B230" s="4" t="s">
         <v>1189</v>
       </c>
@@ -11748,7 +11747,7 @@
         <v>1193</v>
       </c>
     </row>
-    <row r="231" spans="2:13" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="231" spans="2:13" ht="28" x14ac:dyDescent="0.3">
       <c r="B231" s="4" t="s">
         <v>1198</v>
       </c>
@@ -11772,7 +11771,7 @@
         <v>1199</v>
       </c>
     </row>
-    <row r="232" spans="2:13" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="232" spans="2:13" ht="28" x14ac:dyDescent="0.3">
       <c r="B232" s="4" t="s">
         <v>1204</v>
       </c>
@@ -11796,7 +11795,7 @@
         <v>1203</v>
       </c>
     </row>
-    <row r="233" spans="2:13" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="233" spans="2:13" ht="28" x14ac:dyDescent="0.3">
       <c r="B233" s="4" t="s">
         <v>1208</v>
       </c>
@@ -11817,7 +11816,7 @@
         <v>1213</v>
       </c>
     </row>
-    <row r="234" spans="2:13" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="234" spans="2:13" ht="28" x14ac:dyDescent="0.3">
       <c r="B234" s="4" t="s">
         <v>1211</v>
       </c>
@@ -11841,7 +11840,7 @@
         <v>1206</v>
       </c>
     </row>
-    <row r="235" spans="2:13" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="235" spans="2:13" ht="28" x14ac:dyDescent="0.3">
       <c r="B235" s="4" t="s">
         <v>1187</v>
       </c>
@@ -11859,10 +11858,10 @@
         <v>1215</v>
       </c>
       <c r="M235" t="s">
-        <v>1255</v>
-      </c>
-    </row>
-    <row r="236" spans="2:13" ht="28.5" x14ac:dyDescent="0.2">
+        <v>1252</v>
+      </c>
+    </row>
+    <row r="236" spans="2:13" ht="28" x14ac:dyDescent="0.3">
       <c r="B236" s="4" t="s">
         <v>1220</v>
       </c>
@@ -11880,7 +11879,7 @@
         <v>1218</v>
       </c>
     </row>
-    <row r="237" spans="2:13" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="237" spans="2:13" ht="28" x14ac:dyDescent="0.3">
       <c r="B237" s="4" t="s">
         <v>1187</v>
       </c>
@@ -11898,7 +11897,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="238" spans="2:13" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="238" spans="2:13" ht="28" x14ac:dyDescent="0.3">
       <c r="B238" s="4" t="s">
         <v>1225</v>
       </c>
@@ -11916,7 +11915,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="239" spans="2:13" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="239" spans="2:13" ht="28" x14ac:dyDescent="0.3">
       <c r="B239" s="4" t="s">
         <v>1227</v>
       </c>
@@ -11934,7 +11933,7 @@
         <v>1226</v>
       </c>
     </row>
-    <row r="240" spans="2:13" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="240" spans="2:13" ht="28" x14ac:dyDescent="0.3">
       <c r="B240" s="4" t="s">
         <v>1230</v>
       </c>
@@ -11952,7 +11951,7 @@
         <v>1229</v>
       </c>
     </row>
-    <row r="241" spans="2:13" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="241" spans="2:13" ht="28" x14ac:dyDescent="0.3">
       <c r="B241" s="4" t="s">
         <v>1187</v>
       </c>
@@ -11970,7 +11969,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="242" spans="2:13" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="242" spans="2:13" ht="42" x14ac:dyDescent="0.3">
       <c r="B242" s="4" t="s">
         <v>1187</v>
       </c>
@@ -11988,7 +11987,7 @@
         <v>1234</v>
       </c>
     </row>
-    <row r="243" spans="2:13" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="243" spans="2:13" ht="28" x14ac:dyDescent="0.3">
       <c r="B243" s="4" t="s">
         <v>1187</v>
       </c>
@@ -12006,12 +12005,12 @@
         <v>1236</v>
       </c>
     </row>
-    <row r="244" spans="2:13" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="244" spans="2:13" ht="28" x14ac:dyDescent="0.3">
       <c r="B244" s="4" t="s">
         <v>1239</v>
       </c>
       <c r="C244" s="1" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="H244" s="1" t="s">
         <v>654</v>
@@ -12024,12 +12023,12 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="245" spans="2:13" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="245" spans="2:13" ht="28" x14ac:dyDescent="0.3">
       <c r="B245" s="4" t="s">
         <v>1242</v>
       </c>
       <c r="C245" s="1" t="s">
-        <v>1252</v>
+        <v>1249</v>
       </c>
       <c r="H245" s="1" t="s">
         <v>654</v>
@@ -12039,15 +12038,15 @@
         <v>001145</v>
       </c>
       <c r="L245" s="2" t="s">
-        <v>1251</v>
-      </c>
-    </row>
-    <row r="246" spans="2:13" x14ac:dyDescent="0.2">
+        <v>1248</v>
+      </c>
+    </row>
+    <row r="246" spans="2:13" ht="28" x14ac:dyDescent="0.3">
       <c r="B246" s="4" t="s">
         <v>1240</v>
       </c>
       <c r="C246" s="1" t="s">
-        <v>1245</v>
+        <v>1254</v>
       </c>
       <c r="H246" s="1" t="s">
         <v>58</v>
@@ -12060,12 +12059,12 @@
         <v>1241</v>
       </c>
     </row>
-    <row r="247" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="247" spans="2:13" ht="28" x14ac:dyDescent="0.3">
       <c r="B247" s="4" t="s">
         <v>1243</v>
       </c>
       <c r="C247" s="1" t="s">
-        <v>1244</v>
+        <v>1255</v>
       </c>
       <c r="H247" s="1" t="s">
         <v>58</v>
@@ -12075,15 +12074,15 @@
         <v>001147</v>
       </c>
       <c r="L247" s="2" t="s">
-        <v>1246</v>
-      </c>
-    </row>
-    <row r="248" spans="2:13" x14ac:dyDescent="0.2">
+        <v>1244</v>
+      </c>
+    </row>
+    <row r="248" spans="2:13" ht="28" x14ac:dyDescent="0.3">
       <c r="B248" s="4" t="s">
-        <v>1249</v>
+        <v>1247</v>
       </c>
       <c r="C248" s="1" t="s">
-        <v>1250</v>
+        <v>1253</v>
       </c>
       <c r="H248" s="1" t="s">
         <v>654</v>
@@ -12093,15 +12092,15 @@
         <v>001148</v>
       </c>
       <c r="L248" s="2" t="s">
-        <v>1248</v>
-      </c>
-    </row>
-    <row r="249" spans="2:13" ht="28.5" x14ac:dyDescent="0.2">
+        <v>1246</v>
+      </c>
+    </row>
+    <row r="249" spans="2:13" ht="28" x14ac:dyDescent="0.3">
       <c r="B249" s="4" t="s">
         <v>1187</v>
       </c>
       <c r="C249" s="1" t="s">
-        <v>1254</v>
+        <v>1251</v>
       </c>
       <c r="H249" s="1" t="s">
         <v>1128</v>
@@ -12111,416 +12110,416 @@
         <v>00NULL</v>
       </c>
       <c r="L249" s="2" t="s">
-        <v>1253</v>
+        <v>1250</v>
       </c>
       <c r="M249" t="s">
-        <v>1255</v>
-      </c>
-    </row>
-    <row r="250" spans="2:13" x14ac:dyDescent="0.2">
+        <v>1252</v>
+      </c>
+    </row>
+    <row r="250" spans="2:13" x14ac:dyDescent="0.3">
       <c r="J250" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="251" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="251" spans="2:13" x14ac:dyDescent="0.3">
       <c r="J251" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="252" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="252" spans="2:13" x14ac:dyDescent="0.3">
       <c r="J252" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="253" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="253" spans="2:13" x14ac:dyDescent="0.3">
       <c r="J253" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="254" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="254" spans="2:13" x14ac:dyDescent="0.3">
       <c r="J254" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="255" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="255" spans="2:13" x14ac:dyDescent="0.3">
       <c r="J255" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="256" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="256" spans="2:13" x14ac:dyDescent="0.3">
       <c r="J256" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="257" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="257" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J257" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="258" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="258" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J258" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="259" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="259" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J259" s="5" t="str">
         <f t="shared" ref="J259:J316" si="9">"00"&amp;B259</f>
         <v>00</v>
       </c>
     </row>
-    <row r="260" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="260" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J260" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="261" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="261" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J261" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="262" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="262" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J262" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="263" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="263" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J263" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="264" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="264" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J264" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="265" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="265" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J265" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="266" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="266" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J266" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="267" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="267" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J267" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="268" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="268" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J268" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="269" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="269" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J269" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="270" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="270" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J270" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="271" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="271" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J271" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="272" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="272" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J272" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="273" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="273" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J273" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="274" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="274" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J274" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="275" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="275" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J275" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="276" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="276" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J276" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="277" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="277" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J277" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="278" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="278" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J278" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="279" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="279" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J279" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="280" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="280" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J280" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="281" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="281" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J281" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="282" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="282" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J282" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="283" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="283" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J283" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="284" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="284" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J284" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="285" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="285" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J285" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="286" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="286" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J286" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="287" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="287" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J287" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="288" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="288" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J288" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="289" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="289" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J289" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="290" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="290" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J290" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="291" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="291" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J291" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="292" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="292" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J292" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="293" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="293" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J293" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="294" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="294" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J294" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="295" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="295" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J295" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="296" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="296" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J296" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="297" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="297" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J297" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="298" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="298" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J298" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="299" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="299" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J299" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="300" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="300" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J300" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="301" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="301" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J301" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="302" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="302" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J302" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="303" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="303" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J303" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="304" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="304" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J304" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="305" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="305" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J305" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="306" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="306" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J306" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="307" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="307" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J307" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="308" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="308" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J308" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="309" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="309" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J309" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="310" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="310" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J310" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="311" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="311" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J311" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="312" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="312" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J312" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="313" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="313" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J313" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="314" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="314" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J314" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="315" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="315" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J315" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="316" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="316" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J316" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:L4" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A4:L4"/>
   <mergeCells count="1">
     <mergeCell ref="A2:L2"/>
   </mergeCells>
@@ -12532,10 +12531,10 @@
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1:E1 D3:E3 D6:E1048576" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1:E1 D3:E3 D6:E1048576">
       <formula1>"是,否"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H1 H3:H1048576" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H1 H3:H1048576">
       <formula1>"VB编程,系统运维,WEB学习,游戏碎片,日常随笔,浥尘伙伴社团"</formula1>
     </dataValidation>
   </dataValidations>
@@ -12545,20 +12544,20 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A2:L34"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="6.375" customWidth="1"/>
+    <col min="2" max="2" width="6.33203125" customWidth="1"/>
     <col min="3" max="3" width="34" style="4" customWidth="1"/>
     <col min="4" max="4" width="4.75" customWidth="1"/>
-    <col min="8" max="8" width="6.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.83203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="19" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="7.125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="7.08203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.08203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:12" ht="23.25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
         <v>549</v>
       </c>
@@ -12574,7 +12573,7 @@
       <c r="K2" s="21"/>
       <c r="L2" s="21"/>
     </row>
-    <row r="4" spans="1:12" ht="57" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12" ht="56" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>0</v>
       </c>
@@ -12612,7 +12611,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>533</v>
       </c>
@@ -12635,7 +12634,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C8" s="15" t="s">
         <v>545</v>
       </c>
@@ -12644,7 +12643,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C9" s="4" t="s">
         <v>539</v>
       </c>
@@ -12652,7 +12651,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C10" t="s">
         <v>537</v>
       </c>
@@ -12660,7 +12659,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C11" t="s">
         <v>538</v>
       </c>
@@ -12668,7 +12667,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="23.25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A13" s="21" t="s">
         <v>543</v>
       </c>
@@ -12684,7 +12683,7 @@
       <c r="K13" s="21"/>
       <c r="L13" s="21"/>
     </row>
-    <row r="15" spans="1:12" ht="57" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:12" ht="56" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
         <v>0</v>
       </c>
@@ -12722,7 +12721,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>533</v>
       </c>
@@ -12748,7 +12747,7 @@
         <v>54837657</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C19" s="15" t="s">
         <v>545</v>
       </c>
@@ -12757,7 +12756,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C20" s="4" t="s">
         <v>539</v>
       </c>
@@ -12765,7 +12764,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C21" t="s">
         <v>537</v>
       </c>
@@ -12773,7 +12772,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C22" t="s">
         <v>538</v>
       </c>
@@ -12781,10 +12780,10 @@
         <v>541</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C23"/>
     </row>
-    <row r="25" spans="1:12" ht="23.25" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:12" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A25" s="21" t="s">
         <v>550</v>
       </c>
@@ -12800,7 +12799,7 @@
       <c r="K25" s="21"/>
       <c r="L25" s="21"/>
     </row>
-    <row r="27" spans="1:12" ht="57" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:12" ht="56" x14ac:dyDescent="0.3">
       <c r="A27" s="7" t="s">
         <v>0</v>
       </c>
@@ -12838,7 +12837,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:12" ht="42" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
         <v>533</v>
       </c>
@@ -12864,7 +12863,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C31" s="15" t="s">
         <v>545</v>
       </c>
@@ -12873,7 +12872,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C32" s="4" t="s">
         <v>539</v>
       </c>
@@ -12881,7 +12880,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="33" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="33" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C33" t="s">
         <v>537</v>
       </c>
@@ -12889,7 +12888,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="34" spans="3:5" x14ac:dyDescent="0.2">
+    <row r="34" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C34" t="s">
         <v>538</v>
       </c>
@@ -12905,7 +12904,7 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H15 H27 H4" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H15 H27 H4">
       <formula1>"VB编程,系统运维,WEB学习,游戏碎片,日常随笔"</formula1>
     </dataValidation>
   </dataValidations>

--- a/11_付费课程/99.资料/文章信息备忘表.xlsx
+++ b/11_付费课程/99.资料/文章信息备忘表.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\writing\11_付费课程\99.资料\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Disks\E\Writing\11_付费课程\99.资料\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFAB88E0-B7E9-44C5-9E52-EB98D37CB5C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2660" yWindow="1560" windowWidth="21600" windowHeight="11300"/>
+    <workbookView xWindow="3450" yWindow="4020" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,7 +19,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$L$4</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1724" uniqueCount="1256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1728" uniqueCount="1259">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -5007,13 +5008,25 @@
   </si>
   <si>
     <t>游戏不过关不让开机？UEFIGame（下）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>67853590</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1149</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SuperTux</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -5505,25 +5518,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:M316"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.25" style="8" customWidth="1"/>
-    <col min="2" max="2" width="5.58203125" style="4" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="5.33203125" style="6" customWidth="1"/>
-    <col min="5" max="6" width="5.08203125" style="6" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="30.875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="5.375" style="6" customWidth="1"/>
+    <col min="5" max="6" width="5.125" style="6" customWidth="1"/>
     <col min="7" max="7" width="5.25" style="6" customWidth="1"/>
     <col min="8" max="8" width="13.5" style="1" customWidth="1"/>
     <col min="9" max="9" width="19" style="4" customWidth="1"/>
-    <col min="10" max="10" width="8.58203125" style="5" customWidth="1"/>
+    <col min="10" max="10" width="8.625" style="5" customWidth="1"/>
     <col min="11" max="11" width="7.5" style="3" customWidth="1"/>
     <col min="12" max="12" width="9.25" style="2" customWidth="1"/>
     <col min="13" max="13" width="16.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:12" ht="25" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
@@ -5539,8 +5552,8 @@
       <c r="K2" s="20"/>
       <c r="L2" s="20"/>
     </row>
-    <row r="3" spans="1:12" ht="6.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="4" spans="1:12" s="7" customFormat="1" ht="56" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" ht="6.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="4" spans="1:12" s="7" customFormat="1" ht="57" x14ac:dyDescent="0.2">
       <c r="A4" s="7" t="s">
         <v>0</v>
       </c>
@@ -5578,7 +5591,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
         <v>557</v>
       </c>
@@ -5605,7 +5618,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
         <v>559</v>
       </c>
@@ -5641,7 +5654,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="8" t="s">
         <v>559</v>
       </c>
@@ -5677,25 +5690,25 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="J8" s="5" t="str">
         <f t="shared" si="0"/>
         <v>000</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="J9" s="5" t="str">
         <f t="shared" si="0"/>
         <v>000</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="J10" s="5" t="str">
         <f t="shared" si="0"/>
         <v>000</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B11" s="4" t="s">
         <v>522</v>
       </c>
@@ -5728,7 +5741,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A12" s="8" t="s">
         <v>558</v>
       </c>
@@ -5758,7 +5771,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A13" s="8" t="s">
         <v>558</v>
       </c>
@@ -5788,7 +5801,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A14" s="8" t="s">
         <v>640</v>
       </c>
@@ -5815,7 +5828,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" s="8" t="s">
         <v>557</v>
       </c>
@@ -5842,7 +5855,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" s="8" t="s">
         <v>557</v>
       </c>
@@ -5869,7 +5882,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" s="8" t="s">
         <v>557</v>
       </c>
@@ -5896,7 +5909,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" s="8" t="s">
         <v>767</v>
       </c>
@@ -5923,7 +5936,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A19" s="8" t="s">
         <v>557</v>
       </c>
@@ -5950,7 +5963,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A20" s="8" t="s">
         <v>557</v>
       </c>
@@ -5977,7 +5990,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A21" s="8" t="s">
         <v>557</v>
       </c>
@@ -6004,7 +6017,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A22" s="8" t="s">
         <v>559</v>
       </c>
@@ -6040,7 +6053,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23" s="8" t="s">
         <v>557</v>
       </c>
@@ -6067,7 +6080,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A24" s="8" t="s">
         <v>558</v>
       </c>
@@ -6097,7 +6110,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A25" s="8" t="s">
         <v>557</v>
       </c>
@@ -6124,7 +6137,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A26" s="8" t="s">
         <v>557</v>
       </c>
@@ -6151,7 +6164,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="27" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A27" s="8" t="s">
         <v>633</v>
       </c>
@@ -6178,7 +6191,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A28" s="8" t="s">
         <v>557</v>
       </c>
@@ -6205,7 +6218,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A29" s="8" t="s">
         <v>559</v>
       </c>
@@ -6241,7 +6254,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A30" s="8" t="s">
         <v>559</v>
       </c>
@@ -6277,7 +6290,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A31" s="8" t="s">
         <v>557</v>
       </c>
@@ -6304,7 +6317,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A32" s="8" t="s">
         <v>557</v>
       </c>
@@ -6331,7 +6344,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A33" s="8" t="s">
         <v>557</v>
       </c>
@@ -6358,7 +6371,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="34" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A34" s="8" t="s">
         <v>557</v>
       </c>
@@ -6385,7 +6398,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="35" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A35" s="8" t="s">
         <v>557</v>
       </c>
@@ -6412,7 +6425,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="36" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A36" s="8" t="s">
         <v>557</v>
       </c>
@@ -6439,7 +6452,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="37" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A37" s="8" t="s">
         <v>559</v>
       </c>
@@ -6475,7 +6488,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="38" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A38" s="8" t="s">
         <v>557</v>
       </c>
@@ -6502,7 +6515,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A39" s="8" t="s">
         <v>557</v>
       </c>
@@ -6529,7 +6542,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="40" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A40" s="8" t="s">
         <v>557</v>
       </c>
@@ -6556,7 +6569,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="41" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A41" s="8" t="s">
         <v>557</v>
       </c>
@@ -6583,7 +6596,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="42" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A42" s="8" t="s">
         <v>557</v>
       </c>
@@ -6610,7 +6623,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="43" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A43" s="8" t="s">
         <v>559</v>
       </c>
@@ -6643,7 +6656,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="44" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A44" s="8" t="s">
         <v>557</v>
       </c>
@@ -6670,7 +6683,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="45" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A45" s="8" t="s">
         <v>557</v>
       </c>
@@ -6697,7 +6710,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="46" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A46" s="8" t="s">
         <v>557</v>
       </c>
@@ -6724,7 +6737,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A47" s="8" t="s">
         <v>557</v>
       </c>
@@ -6751,7 +6764,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="48" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A48" s="8" t="s">
         <v>557</v>
       </c>
@@ -6778,7 +6791,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="49" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A49" s="8" t="s">
         <v>557</v>
       </c>
@@ -6805,7 +6818,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="50" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A50" s="8" t="s">
         <v>557</v>
       </c>
@@ -6832,7 +6845,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A51" s="8" t="s">
         <v>557</v>
       </c>
@@ -6859,7 +6872,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="52" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A52" s="8" t="s">
         <v>557</v>
       </c>
@@ -6886,7 +6899,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A53" s="8" t="s">
         <v>557</v>
       </c>
@@ -6913,7 +6926,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="54" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A54" s="8" t="s">
         <v>557</v>
       </c>
@@ -6940,7 +6953,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A55" s="8" t="s">
         <v>557</v>
       </c>
@@ -6967,7 +6980,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="56" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A56" s="8" t="s">
         <v>559</v>
       </c>
@@ -7003,7 +7016,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="57" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A57" s="8" t="s">
         <v>559</v>
       </c>
@@ -7039,7 +7052,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="58" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A58" s="8" t="s">
         <v>557</v>
       </c>
@@ -7066,7 +7079,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="59" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A59" s="8" t="s">
         <v>558</v>
       </c>
@@ -7096,7 +7109,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="60" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A60" s="8" t="s">
         <v>557</v>
       </c>
@@ -7123,7 +7136,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="61" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B61" s="4" t="s">
         <v>298</v>
       </c>
@@ -7156,7 +7169,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="62" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B62" s="4" t="s">
         <v>294</v>
       </c>
@@ -7189,7 +7202,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="63" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B63" s="4" t="s">
         <v>289</v>
       </c>
@@ -7222,7 +7235,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="64" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A64" s="8" t="s">
         <v>557</v>
       </c>
@@ -7249,7 +7262,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="65" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A65" s="8" t="s">
         <v>557</v>
       </c>
@@ -7276,7 +7289,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="66" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A66" s="8" t="s">
         <v>559</v>
       </c>
@@ -7312,7 +7325,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="67" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A67" s="8" t="s">
         <v>557</v>
       </c>
@@ -7339,7 +7352,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="68" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A68" s="8" t="s">
         <v>558</v>
       </c>
@@ -7369,7 +7382,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="69" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A69" s="8" t="s">
         <v>559</v>
       </c>
@@ -7396,7 +7409,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="70" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A70" s="8" t="s">
         <v>559</v>
       </c>
@@ -7423,7 +7436,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="71" spans="1:12" ht="56" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:12" ht="57" x14ac:dyDescent="0.2">
       <c r="A71" s="8" t="s">
         <v>558</v>
       </c>
@@ -7453,7 +7466,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="72" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A72" s="8" t="s">
         <v>558</v>
       </c>
@@ -7483,7 +7496,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="73" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A73" s="8" t="s">
         <v>558</v>
       </c>
@@ -7513,7 +7526,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="74" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A74" s="8" t="s">
         <v>557</v>
       </c>
@@ -7540,7 +7553,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="75" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A75" s="8" t="s">
         <v>557</v>
       </c>
@@ -7567,7 +7580,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="76" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A76" s="8" t="s">
         <v>558</v>
       </c>
@@ -7600,7 +7613,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="77" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A77" s="8" t="s">
         <v>557</v>
       </c>
@@ -7627,7 +7640,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="78" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A78" s="8" t="s">
         <v>558</v>
       </c>
@@ -7654,7 +7667,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="79" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A79" s="8" t="s">
         <v>557</v>
       </c>
@@ -7681,7 +7694,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="80" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A80" s="8" t="s">
         <v>558</v>
       </c>
@@ -7708,7 +7721,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="81" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A81" s="8" t="s">
         <v>557</v>
       </c>
@@ -7735,7 +7748,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="82" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A82" s="8" t="s">
         <v>557</v>
       </c>
@@ -7762,7 +7775,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="83" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A83" s="8" t="s">
         <v>557</v>
       </c>
@@ -7789,7 +7802,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="84" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A84" s="8" t="s">
         <v>557</v>
       </c>
@@ -7816,7 +7829,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="85" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A85" s="8" t="s">
         <v>558</v>
       </c>
@@ -7843,7 +7856,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="86" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A86" s="8" t="s">
         <v>557</v>
       </c>
@@ -7870,7 +7883,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="87" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A87" s="8" t="s">
         <v>559</v>
       </c>
@@ -7906,7 +7919,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="88" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A88" s="8" t="s">
         <v>559</v>
       </c>
@@ -7942,7 +7955,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="89" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A89" s="8" t="s">
         <v>559</v>
       </c>
@@ -7978,7 +7991,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="90" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A90" s="8" t="s">
         <v>557</v>
       </c>
@@ -8005,7 +8018,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="91" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B91" s="4" t="s">
         <v>151</v>
       </c>
@@ -8038,7 +8051,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="92" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B92" s="4" t="s">
         <v>146</v>
       </c>
@@ -8071,7 +8084,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="93" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B93" s="4" t="s">
         <v>140</v>
       </c>
@@ -8104,7 +8117,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="94" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B94" s="4" t="s">
         <v>135</v>
       </c>
@@ -8137,7 +8150,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="95" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A95" s="8" t="s">
         <v>558</v>
       </c>
@@ -8164,7 +8177,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="96" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B96" s="4" t="s">
         <v>123</v>
       </c>
@@ -8197,7 +8210,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="97" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B97" s="4" t="s">
         <v>118</v>
       </c>
@@ -8230,7 +8243,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="98" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B98" s="4" t="s">
         <v>112</v>
       </c>
@@ -8263,7 +8276,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="99" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B99" s="4" t="s">
         <v>109</v>
       </c>
@@ -8296,7 +8309,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="100" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B100" s="4" t="s">
         <v>104</v>
       </c>
@@ -8329,7 +8342,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="101" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B101" s="4" t="s">
         <v>98</v>
       </c>
@@ -8362,7 +8375,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="102" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B102" s="4" t="s">
         <v>92</v>
       </c>
@@ -8395,7 +8408,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="103" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A103" s="8" t="s">
         <v>559</v>
       </c>
@@ -8431,7 +8444,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="104" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A104" s="8" t="s">
         <v>557</v>
       </c>
@@ -8458,7 +8471,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="105" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A105" s="8" t="s">
         <v>557</v>
       </c>
@@ -8485,7 +8498,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="106" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A106" s="8" t="s">
         <v>557</v>
       </c>
@@ -8512,7 +8525,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="107" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A107" s="8" t="s">
         <v>557</v>
       </c>
@@ -8539,7 +8552,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="108" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A108" s="8" t="s">
         <v>557</v>
       </c>
@@ -8566,7 +8579,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="109" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A109" s="8" t="s">
         <v>559</v>
       </c>
@@ -8602,7 +8615,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A110" s="8" t="s">
         <v>558</v>
       </c>
@@ -8629,7 +8642,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="111" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A111" s="8" t="s">
         <v>557</v>
       </c>
@@ -8656,7 +8669,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A112" s="8" t="s">
         <v>557</v>
       </c>
@@ -8683,7 +8696,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="113" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A113" s="8" t="s">
         <v>557</v>
       </c>
@@ -8710,7 +8723,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A114" s="8" t="s">
         <v>557</v>
       </c>
@@ -8737,7 +8750,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="115" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A115" s="8" t="s">
         <v>557</v>
       </c>
@@ -8764,7 +8777,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="116" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A116" s="8" t="s">
         <v>559</v>
       </c>
@@ -8800,7 +8813,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="117" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A117" s="8" t="s">
         <v>557</v>
       </c>
@@ -8827,7 +8840,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="118" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A118" s="8" t="s">
         <v>558</v>
       </c>
@@ -8857,7 +8870,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="119" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A119" s="8" t="s">
         <v>557</v>
       </c>
@@ -8884,7 +8897,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="120" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A120" s="8" t="s">
         <v>557</v>
       </c>
@@ -8911,7 +8924,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="121" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A121" s="8" t="s">
         <v>597</v>
       </c>
@@ -8938,7 +8951,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="122" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A122" s="8" t="s">
         <v>602</v>
       </c>
@@ -8965,7 +8978,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="123" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A123" s="8" t="s">
         <v>608</v>
       </c>
@@ -8992,7 +9005,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="124" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A124" s="8" t="s">
         <v>611</v>
       </c>
@@ -9019,7 +9032,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="125" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A125" s="8" t="s">
         <v>617</v>
       </c>
@@ -9046,7 +9059,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="126" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A126" s="8" t="s">
         <v>624</v>
       </c>
@@ -9073,7 +9086,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="127" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A127" s="8" t="s">
         <v>557</v>
       </c>
@@ -9100,7 +9113,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="128" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A128" s="8" t="s">
         <v>649</v>
       </c>
@@ -9127,7 +9140,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="129" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A129" s="8" t="s">
         <v>653</v>
       </c>
@@ -9154,7 +9167,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="130" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A130" s="8" t="s">
         <v>659</v>
       </c>
@@ -9181,7 +9194,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="131" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A131" s="8" t="s">
         <v>664</v>
       </c>
@@ -9208,7 +9221,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A132" s="8" t="s">
         <v>557</v>
       </c>
@@ -9235,7 +9248,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="133" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A133" s="8" t="s">
         <v>557</v>
       </c>
@@ -9262,7 +9275,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="134" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A134" s="8" t="s">
         <v>681</v>
       </c>
@@ -9289,7 +9302,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="135" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A135" s="8" t="s">
         <v>687</v>
       </c>
@@ -9316,7 +9329,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="136" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A136" s="8" t="s">
         <v>691</v>
       </c>
@@ -9343,7 +9356,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="137" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A137" s="8" t="s">
         <v>699</v>
       </c>
@@ -9370,7 +9383,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="138" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A138" s="8" t="s">
         <v>704</v>
       </c>
@@ -9397,7 +9410,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="139" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A139" s="8" t="s">
         <v>711</v>
       </c>
@@ -9424,7 +9437,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="140" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A140" s="8" t="s">
         <v>716</v>
       </c>
@@ -9451,7 +9464,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="141" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A141" s="8" t="s">
         <v>724</v>
       </c>
@@ -9478,7 +9491,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="142" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A142" s="8" t="s">
         <v>727</v>
       </c>
@@ -9505,7 +9518,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="143" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A143" s="8" t="s">
         <v>736</v>
       </c>
@@ -9532,7 +9545,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="144" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A144" s="8" t="s">
         <v>740</v>
       </c>
@@ -9559,7 +9572,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="145" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A145" s="8" t="s">
         <v>746</v>
       </c>
@@ -9586,7 +9599,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="146" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A146" s="8" t="s">
         <v>754</v>
       </c>
@@ -9613,7 +9626,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="147" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A147" s="8" t="s">
         <v>759</v>
       </c>
@@ -9640,7 +9653,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="148" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A148" s="8" t="s">
         <v>770</v>
       </c>
@@ -9667,7 +9680,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="149" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A149" s="8" t="s">
         <v>777</v>
       </c>
@@ -9694,7 +9707,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="150" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A150" s="8" t="s">
         <v>782</v>
       </c>
@@ -9721,7 +9734,7 @@
         <v>786</v>
       </c>
     </row>
-    <row r="151" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A151" s="8" t="s">
         <v>557</v>
       </c>
@@ -9748,7 +9761,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="152" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A152" s="8" t="s">
         <v>795</v>
       </c>
@@ -9775,7 +9788,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A153" s="8" t="s">
         <v>800</v>
       </c>
@@ -9802,7 +9815,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A154" s="8" t="s">
         <v>804</v>
       </c>
@@ -9829,7 +9842,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A155" s="8" t="s">
         <v>811</v>
       </c>
@@ -9856,7 +9869,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="156" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A156" s="8" t="s">
         <v>557</v>
       </c>
@@ -9883,7 +9896,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A157" s="8" t="s">
         <v>557</v>
       </c>
@@ -9910,7 +9923,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A158" s="8" t="s">
         <v>827</v>
       </c>
@@ -9937,7 +9950,7 @@
         <v>831</v>
       </c>
     </row>
-    <row r="159" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A159" s="8" t="s">
         <v>557</v>
       </c>
@@ -9964,7 +9977,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A160" s="8" t="s">
         <v>838</v>
       </c>
@@ -9991,7 +10004,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="161" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A161" s="8" t="s">
         <v>557</v>
       </c>
@@ -10018,7 +10031,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A162" s="8" t="s">
         <v>850</v>
       </c>
@@ -10045,7 +10058,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A163" s="8" t="s">
         <v>857</v>
       </c>
@@ -10072,7 +10085,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A164" s="8" t="s">
         <v>557</v>
       </c>
@@ -10099,7 +10112,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="165" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A165" s="8" t="s">
         <v>557</v>
       </c>
@@ -10126,7 +10139,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A166" s="8" t="s">
         <v>557</v>
       </c>
@@ -10153,7 +10166,7 @@
         <v>871</v>
       </c>
     </row>
-    <row r="167" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A167" s="8" t="s">
         <v>557</v>
       </c>
@@ -10180,7 +10193,7 @@
         <v>879</v>
       </c>
     </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A168" s="8" t="s">
         <v>557</v>
       </c>
@@ -10207,7 +10220,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A169" s="8" t="s">
         <v>557</v>
       </c>
@@ -10234,7 +10247,7 @@
         <v>889</v>
       </c>
     </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A170" s="8" t="s">
         <v>557</v>
       </c>
@@ -10261,7 +10274,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A171" s="8" t="s">
         <v>557</v>
       </c>
@@ -10288,7 +10301,7 @@
         <v>897</v>
       </c>
     </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A172" s="8" t="s">
         <v>902</v>
       </c>
@@ -10315,7 +10328,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A173" s="8" t="s">
         <v>902</v>
       </c>
@@ -10342,7 +10355,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A174" s="8" t="s">
         <v>557</v>
       </c>
@@ -10369,7 +10382,7 @@
         <v>915</v>
       </c>
     </row>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A175" s="8" t="s">
         <v>557</v>
       </c>
@@ -10396,7 +10409,7 @@
         <v>919</v>
       </c>
     </row>
-    <row r="176" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A176" s="8" t="s">
         <v>557</v>
       </c>
@@ -10423,7 +10436,7 @@
         <v>925</v>
       </c>
     </row>
-    <row r="177" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A177" s="8" t="s">
         <v>557</v>
       </c>
@@ -10450,7 +10463,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="178" spans="1:13" ht="28" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A178" s="8" t="s">
         <v>557</v>
       </c>
@@ -10477,7 +10490,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="179" spans="1:13" ht="42" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:13" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A179" s="8" t="s">
         <v>938</v>
       </c>
@@ -10504,7 +10517,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="180" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B180" s="4" t="s">
         <v>942</v>
       </c>
@@ -10528,7 +10541,7 @@
         <v>946</v>
       </c>
     </row>
-    <row r="181" spans="1:13" ht="28" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B181" s="4" t="s">
         <v>948</v>
       </c>
@@ -10552,7 +10565,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="182" spans="1:13" ht="28" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B182" s="4" t="s">
         <v>954</v>
       </c>
@@ -10576,7 +10589,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="183" spans="1:13" ht="42" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:13" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B183" s="4" t="s">
         <v>959</v>
       </c>
@@ -10600,7 +10613,7 @@
         <v>960</v>
       </c>
     </row>
-    <row r="184" spans="1:13" ht="28" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B184" s="4" t="s">
         <v>966</v>
       </c>
@@ -10624,7 +10637,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="185" spans="1:13" ht="28" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B185" s="4" t="s">
         <v>971</v>
       </c>
@@ -10648,7 +10661,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="186" spans="1:13" ht="42" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:13" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B186" s="4" t="s">
         <v>976</v>
       </c>
@@ -10672,7 +10685,7 @@
         <v>963</v>
       </c>
     </row>
-    <row r="187" spans="1:13" ht="42" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:13" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B187" s="4" t="s">
         <v>979</v>
       </c>
@@ -10696,7 +10709,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="188" spans="1:13" ht="28" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B188" s="4" t="s">
         <v>985</v>
       </c>
@@ -10723,7 +10736,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="189" spans="1:13" ht="15.5" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:13" ht="15" x14ac:dyDescent="0.2">
       <c r="B189" s="4" t="s">
         <v>988</v>
       </c>
@@ -10748,7 +10761,7 @@
       </c>
       <c r="M189" s="6"/>
     </row>
-    <row r="190" spans="1:13" ht="28" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B190" s="4" t="s">
         <v>992</v>
       </c>
@@ -10772,7 +10785,7 @@
         <v>982</v>
       </c>
     </row>
-    <row r="191" spans="1:13" ht="46.5" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:13" ht="45" x14ac:dyDescent="0.2">
       <c r="B191" s="4" t="s">
         <v>1002</v>
       </c>
@@ -10796,7 +10809,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="192" spans="1:13" ht="28" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B192" s="4" t="s">
         <v>1006</v>
       </c>
@@ -10820,7 +10833,7 @@
         <v>998</v>
       </c>
     </row>
-    <row r="193" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="193" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B193" s="4" t="s">
         <v>1010</v>
       </c>
@@ -10844,7 +10857,7 @@
         <v>1011</v>
       </c>
     </row>
-    <row r="194" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="194" spans="2:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B194" s="4" t="s">
         <v>1015</v>
       </c>
@@ -10871,7 +10884,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="195" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="195" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B195" s="4" t="s">
         <v>1021</v>
       </c>
@@ -10895,7 +10908,7 @@
         <v>1019</v>
       </c>
     </row>
-    <row r="196" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="196" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B196" s="4" t="s">
         <v>1025</v>
       </c>
@@ -10919,7 +10932,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="197" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="197" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B197" s="4" t="s">
         <v>1031</v>
       </c>
@@ -10943,7 +10956,7 @@
         <v>1033</v>
       </c>
     </row>
-    <row r="198" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="198" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B198" s="4" t="s">
         <v>1034</v>
       </c>
@@ -10967,7 +10980,7 @@
         <v>1035</v>
       </c>
     </row>
-    <row r="199" spans="2:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="199" spans="2:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B199" s="4" t="s">
         <v>1040</v>
       </c>
@@ -10991,7 +11004,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="200" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="200" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B200" s="4" t="s">
         <v>1045</v>
       </c>
@@ -11015,7 +11028,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="201" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="201" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B201" s="4" t="s">
         <v>1051</v>
       </c>
@@ -11039,7 +11052,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="202" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="202" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B202" s="4" t="s">
         <v>1058</v>
       </c>
@@ -11063,7 +11076,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="203" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="203" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B203" s="4" t="s">
         <v>1062</v>
       </c>
@@ -11087,7 +11100,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="204" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="204" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B204" s="4" t="s">
         <v>1065</v>
       </c>
@@ -11111,7 +11124,7 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="205" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="205" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B205" s="4" t="s">
         <v>1071</v>
       </c>
@@ -11135,7 +11148,7 @@
         <v>1069</v>
       </c>
     </row>
-    <row r="206" spans="2:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="206" spans="2:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B206" s="4" t="s">
         <v>1074</v>
       </c>
@@ -11159,7 +11172,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="207" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="207" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B207" s="4" t="s">
         <v>1080</v>
       </c>
@@ -11183,7 +11196,7 @@
         <v>1079</v>
       </c>
     </row>
-    <row r="208" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="208" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B208" s="4" t="s">
         <v>1082</v>
       </c>
@@ -11207,7 +11220,7 @@
         <v>1081</v>
       </c>
     </row>
-    <row r="209" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="209" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B209" s="4" t="s">
         <v>1091</v>
       </c>
@@ -11231,7 +11244,7 @@
         <v>1089</v>
       </c>
     </row>
-    <row r="210" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="210" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B210" s="4" t="s">
         <v>1093</v>
       </c>
@@ -11255,7 +11268,7 @@
         <v>1092</v>
       </c>
     </row>
-    <row r="211" spans="2:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="211" spans="2:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B211" s="4" t="s">
         <v>1102</v>
       </c>
@@ -11279,7 +11292,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="212" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="212" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B212" s="4" t="s">
         <v>1105</v>
       </c>
@@ -11303,7 +11316,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="213" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="213" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B213" s="4" t="s">
         <v>1110</v>
       </c>
@@ -11327,7 +11340,7 @@
         <v>1109</v>
       </c>
     </row>
-    <row r="214" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="214" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B214" s="4" t="s">
         <v>1118</v>
       </c>
@@ -11354,7 +11367,7 @@
         <v>1114</v>
       </c>
     </row>
-    <row r="215" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="215" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B215" s="4" t="s">
         <v>1121</v>
       </c>
@@ -11378,7 +11391,7 @@
         <v>1116</v>
       </c>
     </row>
-    <row r="216" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="216" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B216" s="4" t="s">
         <v>1126</v>
       </c>
@@ -11405,7 +11418,7 @@
         <v>1131</v>
       </c>
     </row>
-    <row r="217" spans="2:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="217" spans="2:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B217" s="4" t="s">
         <v>1134</v>
       </c>
@@ -11432,7 +11445,7 @@
         <v>1113</v>
       </c>
     </row>
-    <row r="218" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="218" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B218" s="4" t="s">
         <v>1137</v>
       </c>
@@ -11459,7 +11472,7 @@
         <v>1132</v>
       </c>
     </row>
-    <row r="219" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="219" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B219" s="4" t="s">
         <v>1142</v>
       </c>
@@ -11483,7 +11496,7 @@
         <v>1120</v>
       </c>
     </row>
-    <row r="220" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="220" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B220" s="4" t="s">
         <v>1145</v>
       </c>
@@ -11507,7 +11520,7 @@
         <v>1149</v>
       </c>
     </row>
-    <row r="221" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="221" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B221" s="4" t="s">
         <v>1150</v>
       </c>
@@ -11531,7 +11544,7 @@
         <v>1154</v>
       </c>
     </row>
-    <row r="222" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="222" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B222" s="4" t="s">
         <v>1153</v>
       </c>
@@ -11555,7 +11568,7 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="223" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="223" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B223" s="4" t="s">
         <v>1161</v>
       </c>
@@ -11579,7 +11592,7 @@
         <v>1160</v>
       </c>
     </row>
-    <row r="224" spans="2:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="224" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B224" s="4" t="s">
         <v>1165</v>
       </c>
@@ -11603,7 +11616,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="225" spans="2:13" ht="28" x14ac:dyDescent="0.3">
+    <row r="225" spans="2:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B225" s="4" t="s">
         <v>1167</v>
       </c>
@@ -11630,7 +11643,7 @@
         <v>1166</v>
       </c>
     </row>
-    <row r="226" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="226" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B226" s="4" t="s">
         <v>1173</v>
       </c>
@@ -11654,7 +11667,7 @@
         <v>1174</v>
       </c>
     </row>
-    <row r="227" spans="2:13" ht="28" x14ac:dyDescent="0.3">
+    <row r="227" spans="2:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B227" s="4" t="s">
         <v>1181</v>
       </c>
@@ -11678,7 +11691,7 @@
         <v>1180</v>
       </c>
     </row>
-    <row r="228" spans="2:13" ht="28" x14ac:dyDescent="0.3">
+    <row r="228" spans="2:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B228" s="4" t="s">
         <v>1187</v>
       </c>
@@ -11699,7 +11712,7 @@
         <v>1185</v>
       </c>
     </row>
-    <row r="229" spans="2:13" ht="28" x14ac:dyDescent="0.3">
+    <row r="229" spans="2:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B229" s="4" t="s">
         <v>1186</v>
       </c>
@@ -11723,7 +11736,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="230" spans="2:13" ht="31" x14ac:dyDescent="0.3">
+    <row r="230" spans="2:13" ht="30" x14ac:dyDescent="0.2">
       <c r="B230" s="4" t="s">
         <v>1189</v>
       </c>
@@ -11747,7 +11760,7 @@
         <v>1193</v>
       </c>
     </row>
-    <row r="231" spans="2:13" ht="28" x14ac:dyDescent="0.3">
+    <row r="231" spans="2:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B231" s="4" t="s">
         <v>1198</v>
       </c>
@@ -11771,7 +11784,7 @@
         <v>1199</v>
       </c>
     </row>
-    <row r="232" spans="2:13" ht="28" x14ac:dyDescent="0.3">
+    <row r="232" spans="2:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B232" s="4" t="s">
         <v>1204</v>
       </c>
@@ -11795,7 +11808,7 @@
         <v>1203</v>
       </c>
     </row>
-    <row r="233" spans="2:13" ht="28" x14ac:dyDescent="0.3">
+    <row r="233" spans="2:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B233" s="4" t="s">
         <v>1208</v>
       </c>
@@ -11816,7 +11829,7 @@
         <v>1213</v>
       </c>
     </row>
-    <row r="234" spans="2:13" ht="28" x14ac:dyDescent="0.3">
+    <row r="234" spans="2:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B234" s="4" t="s">
         <v>1211</v>
       </c>
@@ -11840,7 +11853,7 @@
         <v>1206</v>
       </c>
     </row>
-    <row r="235" spans="2:13" ht="28" x14ac:dyDescent="0.3">
+    <row r="235" spans="2:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B235" s="4" t="s">
         <v>1187</v>
       </c>
@@ -11861,7 +11874,7 @@
         <v>1252</v>
       </c>
     </row>
-    <row r="236" spans="2:13" ht="28" x14ac:dyDescent="0.3">
+    <row r="236" spans="2:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B236" s="4" t="s">
         <v>1220</v>
       </c>
@@ -11879,7 +11892,7 @@
         <v>1218</v>
       </c>
     </row>
-    <row r="237" spans="2:13" ht="28" x14ac:dyDescent="0.3">
+    <row r="237" spans="2:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B237" s="4" t="s">
         <v>1187</v>
       </c>
@@ -11897,7 +11910,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="238" spans="2:13" ht="28" x14ac:dyDescent="0.3">
+    <row r="238" spans="2:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B238" s="4" t="s">
         <v>1225</v>
       </c>
@@ -11915,7 +11928,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="239" spans="2:13" ht="28" x14ac:dyDescent="0.3">
+    <row r="239" spans="2:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B239" s="4" t="s">
         <v>1227</v>
       </c>
@@ -11933,7 +11946,7 @@
         <v>1226</v>
       </c>
     </row>
-    <row r="240" spans="2:13" ht="28" x14ac:dyDescent="0.3">
+    <row r="240" spans="2:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B240" s="4" t="s">
         <v>1230</v>
       </c>
@@ -11951,7 +11964,7 @@
         <v>1229</v>
       </c>
     </row>
-    <row r="241" spans="2:13" ht="28" x14ac:dyDescent="0.3">
+    <row r="241" spans="2:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B241" s="4" t="s">
         <v>1187</v>
       </c>
@@ -11969,7 +11982,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="242" spans="2:13" ht="42" x14ac:dyDescent="0.3">
+    <row r="242" spans="2:13" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B242" s="4" t="s">
         <v>1187</v>
       </c>
@@ -11987,7 +12000,7 @@
         <v>1234</v>
       </c>
     </row>
-    <row r="243" spans="2:13" ht="28" x14ac:dyDescent="0.3">
+    <row r="243" spans="2:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B243" s="4" t="s">
         <v>1187</v>
       </c>
@@ -12005,7 +12018,7 @@
         <v>1236</v>
       </c>
     </row>
-    <row r="244" spans="2:13" ht="28" x14ac:dyDescent="0.3">
+    <row r="244" spans="2:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B244" s="4" t="s">
         <v>1239</v>
       </c>
@@ -12023,7 +12036,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="245" spans="2:13" ht="28" x14ac:dyDescent="0.3">
+    <row r="245" spans="2:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B245" s="4" t="s">
         <v>1242</v>
       </c>
@@ -12041,7 +12054,7 @@
         <v>1248</v>
       </c>
     </row>
-    <row r="246" spans="2:13" ht="28" x14ac:dyDescent="0.3">
+    <row r="246" spans="2:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B246" s="4" t="s">
         <v>1240</v>
       </c>
@@ -12059,7 +12072,7 @@
         <v>1241</v>
       </c>
     </row>
-    <row r="247" spans="2:13" ht="28" x14ac:dyDescent="0.3">
+    <row r="247" spans="2:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B247" s="4" t="s">
         <v>1243</v>
       </c>
@@ -12077,7 +12090,7 @@
         <v>1244</v>
       </c>
     </row>
-    <row r="248" spans="2:13" ht="28" x14ac:dyDescent="0.3">
+    <row r="248" spans="2:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B248" s="4" t="s">
         <v>1247</v>
       </c>
@@ -12095,7 +12108,7 @@
         <v>1246</v>
       </c>
     </row>
-    <row r="249" spans="2:13" ht="28" x14ac:dyDescent="0.3">
+    <row r="249" spans="2:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B249" s="4" t="s">
         <v>1187</v>
       </c>
@@ -12116,410 +12129,422 @@
         <v>1252</v>
       </c>
     </row>
-    <row r="250" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="250" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B250" s="4" t="s">
+        <v>1257</v>
+      </c>
+      <c r="C250" s="1" t="s">
+        <v>1258</v>
+      </c>
+      <c r="H250" s="1" t="s">
+        <v>58</v>
+      </c>
       <c r="J250" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>00</v>
-      </c>
-    </row>
-    <row r="251" spans="2:13" x14ac:dyDescent="0.3">
+        <v>001149</v>
+      </c>
+      <c r="L250" s="2" t="s">
+        <v>1256</v>
+      </c>
+    </row>
+    <row r="251" spans="2:13" x14ac:dyDescent="0.2">
       <c r="J251" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="252" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="252" spans="2:13" x14ac:dyDescent="0.2">
       <c r="J252" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="253" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="253" spans="2:13" x14ac:dyDescent="0.2">
       <c r="J253" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="254" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="254" spans="2:13" x14ac:dyDescent="0.2">
       <c r="J254" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="255" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="255" spans="2:13" x14ac:dyDescent="0.2">
       <c r="J255" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="256" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="256" spans="2:13" x14ac:dyDescent="0.2">
       <c r="J256" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="257" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="257" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J257" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="258" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="258" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J258" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
       </c>
     </row>
-    <row r="259" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="259" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J259" s="5" t="str">
         <f t="shared" ref="J259:J316" si="9">"00"&amp;B259</f>
         <v>00</v>
       </c>
     </row>
-    <row r="260" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="260" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J260" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="261" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="261" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J261" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="262" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="262" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J262" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="263" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="263" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J263" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="264" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="264" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J264" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="265" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="265" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J265" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="266" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="266" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J266" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="267" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="267" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J267" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="268" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="268" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J268" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="269" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="269" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J269" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="270" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="270" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J270" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="271" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="271" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J271" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="272" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="272" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J272" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="273" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="273" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J273" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="274" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="274" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J274" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="275" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="275" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J275" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="276" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="276" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J276" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="277" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="277" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J277" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="278" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="278" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J278" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="279" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="279" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J279" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="280" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="280" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J280" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="281" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="281" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J281" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="282" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="282" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J282" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="283" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="283" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J283" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="284" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="284" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J284" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="285" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="285" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J285" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="286" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="286" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J286" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="287" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="287" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J287" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="288" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="288" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J288" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="289" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="289" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J289" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="290" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="290" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J290" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="291" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="291" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J291" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="292" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="292" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J292" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="293" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="293" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J293" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="294" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="294" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J294" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="295" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="295" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J295" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="296" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="296" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J296" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="297" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="297" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J297" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="298" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="298" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J298" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="299" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="299" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J299" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="300" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="300" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J300" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="301" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="301" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J301" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="302" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="302" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J302" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="303" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="303" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J303" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="304" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="304" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J304" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="305" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="305" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J305" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="306" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="306" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J306" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="307" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="307" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J307" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="308" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="308" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J308" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="309" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="309" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J309" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="310" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="310" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J310" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="311" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="311" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J311" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="312" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="312" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J312" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="313" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="313" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J313" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="314" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="314" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J314" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="315" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="315" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J315" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="316" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="316" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J316" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:L4"/>
+  <autoFilter ref="A4:L4" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="1">
     <mergeCell ref="A2:L2"/>
   </mergeCells>
@@ -12531,10 +12556,10 @@
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1:E1 D3:E3 D6:E1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1:E1 D3:E3 D6:E1048576" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"是,否"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H1 H3:H1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H1 H3:H1048576" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"VB编程,系统运维,WEB学习,游戏碎片,日常随笔,浥尘伙伴社团"</formula1>
     </dataValidation>
   </dataValidations>
@@ -12544,20 +12569,20 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A2:L34"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="6.33203125" customWidth="1"/>
+    <col min="2" max="2" width="6.375" customWidth="1"/>
     <col min="3" max="3" width="34" style="4" customWidth="1"/>
     <col min="4" max="4" width="4.75" customWidth="1"/>
-    <col min="8" max="8" width="6.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="19" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="7.08203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.08203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:12" ht="22.5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" ht="23.25" x14ac:dyDescent="0.2">
       <c r="A2" s="21" t="s">
         <v>549</v>
       </c>
@@ -12573,7 +12598,7 @@
       <c r="K2" s="21"/>
       <c r="L2" s="21"/>
     </row>
-    <row r="4" spans="1:12" ht="56" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" ht="57" x14ac:dyDescent="0.2">
       <c r="A4" s="7" t="s">
         <v>0</v>
       </c>
@@ -12611,7 +12636,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
         <v>533</v>
       </c>
@@ -12634,7 +12659,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C8" s="15" t="s">
         <v>545</v>
       </c>
@@ -12643,7 +12668,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C9" s="4" t="s">
         <v>539</v>
       </c>
@@ -12651,7 +12676,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C10" t="s">
         <v>537</v>
       </c>
@@ -12659,7 +12684,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C11" t="s">
         <v>538</v>
       </c>
@@ -12667,7 +12692,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="22.5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" ht="23.25" x14ac:dyDescent="0.2">
       <c r="A13" s="21" t="s">
         <v>543</v>
       </c>
@@ -12683,7 +12708,7 @@
       <c r="K13" s="21"/>
       <c r="L13" s="21"/>
     </row>
-    <row r="15" spans="1:12" ht="56" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" ht="57" x14ac:dyDescent="0.2">
       <c r="A15" s="7" t="s">
         <v>0</v>
       </c>
@@ -12721,7 +12746,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
         <v>533</v>
       </c>
@@ -12747,7 +12772,7 @@
         <v>54837657</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C19" s="15" t="s">
         <v>545</v>
       </c>
@@ -12756,7 +12781,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C20" s="4" t="s">
         <v>539</v>
       </c>
@@ -12764,7 +12789,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C21" t="s">
         <v>537</v>
       </c>
@@ -12772,7 +12797,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C22" t="s">
         <v>538</v>
       </c>
@@ -12780,10 +12805,10 @@
         <v>541</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C23"/>
     </row>
-    <row r="25" spans="1:12" ht="22.5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" ht="23.25" x14ac:dyDescent="0.2">
       <c r="A25" s="21" t="s">
         <v>550</v>
       </c>
@@ -12799,7 +12824,7 @@
       <c r="K25" s="21"/>
       <c r="L25" s="21"/>
     </row>
-    <row r="27" spans="1:12" ht="56" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" ht="57" x14ac:dyDescent="0.2">
       <c r="A27" s="7" t="s">
         <v>0</v>
       </c>
@@ -12837,7 +12862,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B28" t="s">
         <v>533</v>
       </c>
@@ -12863,7 +12888,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C31" s="15" t="s">
         <v>545</v>
       </c>
@@ -12872,7 +12897,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C32" s="4" t="s">
         <v>539</v>
       </c>
@@ -12880,7 +12905,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="33" spans="3:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="3:5" x14ac:dyDescent="0.2">
       <c r="C33" t="s">
         <v>537</v>
       </c>
@@ -12888,7 +12913,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="34" spans="3:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="3:5" x14ac:dyDescent="0.2">
       <c r="C34" t="s">
         <v>538</v>
       </c>
@@ -12904,7 +12929,7 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H15 H27 H4">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H15 H27 H4" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"VB编程,系统运维,WEB学习,游戏碎片,日常随笔"</formula1>
     </dataValidation>
   </dataValidations>

--- a/11_付费课程/99.资料/文章信息备忘表.xlsx
+++ b/11_付费课程/99.资料/文章信息备忘表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Disks\E\Writing\11_付费课程\99.资料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFAB88E0-B7E9-44C5-9E52-EB98D37CB5C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D1EA08A-ADBD-4F1B-9C95-4E9BB4E02C6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3450" yWindow="4020" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5019,7 +5019,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>SuperTux</t>
+    <t>喜欢聊游戏的不一定是送快递的，也可能是保安（SuperTux）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -12129,7 +12129,7 @@
         <v>1252</v>
       </c>
     </row>
-    <row r="250" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="250" spans="2:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B250" s="4" t="s">
         <v>1257</v>
       </c>

--- a/11_付费课程/99.资料/文章信息备忘表.xlsx
+++ b/11_付费课程/99.资料/文章信息备忘表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Disks\E\Writing\11_付费课程\99.资料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D1EA08A-ADBD-4F1B-9C95-4E9BB4E02C6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9648987-72C1-4EF3-9854-B0D2818FB6BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3450" yWindow="4020" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5985" yWindow="4350" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1728" uniqueCount="1259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1730" uniqueCount="1261">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -5020,6 +5020,14 @@
   </si>
   <si>
     <t>喜欢聊游戏的不一定是送快递的，也可能是保安（SuperTux）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>34587372</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>绕过Bitlocker的神奇黄钥匙YellowKey</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -12160,9 +12168,15 @@
       </c>
     </row>
     <row r="253" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="C253" s="1" t="s">
+        <v>1260</v>
+      </c>
       <c r="J253" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
+      </c>
+      <c r="L253" s="2" t="s">
+        <v>1259</v>
       </c>
     </row>
     <row r="254" spans="2:13" x14ac:dyDescent="0.2">

--- a/11_付费课程/99.资料/文章信息备忘表.xlsx
+++ b/11_付费课程/99.资料/文章信息备忘表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Disks\E\Writing\11_付费课程\99.资料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9648987-72C1-4EF3-9854-B0D2818FB6BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3D1CEC2-E13E-4521-8208-F5C6FA6D9B50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5985" yWindow="4350" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3450" yWindow="4020" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1730" uniqueCount="1261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1731" uniqueCount="1262">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -5028,6 +5028,10 @@
   </si>
   <si>
     <t>绕过Bitlocker的神奇黄钥匙YellowKey</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1150</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -5527,7 +5531,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:M316"/>
+  <dimension ref="A2:M314"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.25" style="8" customWidth="1"/>
@@ -10954,7 +10958,7 @@
         <v>1029</v>
       </c>
       <c r="J197" s="5" t="str">
-        <f t="shared" ref="J197:J258" si="5">"00"&amp;B197</f>
+        <f t="shared" ref="J197:J256" si="5">"00"&amp;B197</f>
         <v>001099</v>
       </c>
       <c r="K197" s="3" t="s">
@@ -12156,9 +12160,18 @@
       </c>
     </row>
     <row r="251" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B251" s="4" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C251" s="1" t="s">
+        <v>1260</v>
+      </c>
       <c r="J251" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>00</v>
+        <v>001150</v>
+      </c>
+      <c r="L251" s="2" t="s">
+        <v>1259</v>
       </c>
     </row>
     <row r="252" spans="2:13" x14ac:dyDescent="0.2">
@@ -12168,15 +12181,9 @@
       </c>
     </row>
     <row r="253" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="C253" s="1" t="s">
-        <v>1260</v>
-      </c>
       <c r="J253" s="5" t="str">
         <f t="shared" si="5"/>
         <v>00</v>
-      </c>
-      <c r="L253" s="2" t="s">
-        <v>1259</v>
       </c>
     </row>
     <row r="254" spans="2:13" x14ac:dyDescent="0.2">
@@ -12199,19 +12206,19 @@
     </row>
     <row r="257" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J257" s="5" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="J257:J314" si="9">"00"&amp;B257</f>
         <v>00</v>
       </c>
     </row>
     <row r="258" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J258" s="5" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
     <row r="259" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J259" s="5" t="str">
-        <f t="shared" ref="J259:J316" si="9">"00"&amp;B259</f>
+        <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
@@ -12541,18 +12548,6 @@
     </row>
     <row r="314" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J314" s="5" t="str">
-        <f t="shared" si="9"/>
-        <v>00</v>
-      </c>
-    </row>
-    <row r="315" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J315" s="5" t="str">
-        <f t="shared" si="9"/>
-        <v>00</v>
-      </c>
-    </row>
-    <row r="316" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J316" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>

--- a/11_付费课程/99.资料/文章信息备忘表.xlsx
+++ b/11_付费课程/99.资料/文章信息备忘表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Disks\E\Writing\11_付费课程\99.资料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3D1CEC2-E13E-4521-8208-F5C6FA6D9B50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B59E2FEB-9DD5-4F8E-8365-F3D41AED2878}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3450" yWindow="4020" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1731" uniqueCount="1262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1732" uniqueCount="1262">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -12166,6 +12166,9 @@
       <c r="C251" s="1" t="s">
         <v>1260</v>
       </c>
+      <c r="H251" s="1" t="s">
+        <v>654</v>
+      </c>
       <c r="J251" s="5" t="str">
         <f t="shared" si="5"/>
         <v>001150</v>

--- a/11_付费课程/99.资料/文章信息备忘表.xlsx
+++ b/11_付费课程/99.资料/文章信息备忘表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Disks\E\Writing\11_付费课程\99.资料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B59E2FEB-9DD5-4F8E-8365-F3D41AED2878}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03968F26-8762-4425-853A-113C0D3B0BAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1732" uniqueCount="1262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1736" uniqueCount="1265">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -5032,6 +5032,18 @@
   </si>
   <si>
     <t>1150</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1151</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>“阅后即焚”的PrivateBin与乌龙事件</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>65829459</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -12178,9 +12190,21 @@
       </c>
     </row>
     <row r="252" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B252" s="4" t="s">
+        <v>1262</v>
+      </c>
+      <c r="C252" s="1" t="s">
+        <v>1263</v>
+      </c>
+      <c r="H252" s="1" t="s">
+        <v>654</v>
+      </c>
       <c r="J252" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>00</v>
+        <v>001151</v>
+      </c>
+      <c r="L252" s="2" t="s">
+        <v>1264</v>
       </c>
     </row>
     <row r="253" spans="2:13" x14ac:dyDescent="0.2">

--- a/11_付费课程/99.资料/文章信息备忘表.xlsx
+++ b/11_付费课程/99.资料/文章信息备忘表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Disks\E\Writing\11_付费课程\99.资料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03968F26-8762-4425-853A-113C0D3B0BAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FB05A78-3B8E-44BC-905B-414A5E5EBB7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4455" yWindow="855" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1736" uniqueCount="1265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1740" uniqueCount="1268">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -5044,6 +5044,18 @@
   </si>
   <si>
     <t>65829459</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1152</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>89216918</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>躺平工作、睡后收入？难道我被骗了？</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -5548,7 +5560,7 @@
   <cols>
     <col min="1" max="1" width="4.25" style="8" customWidth="1"/>
     <col min="2" max="2" width="5.625" style="4" customWidth="1"/>
-    <col min="3" max="3" width="30.875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="32.5" style="1" customWidth="1"/>
     <col min="4" max="4" width="5.375" style="6" customWidth="1"/>
     <col min="5" max="6" width="5.125" style="6" customWidth="1"/>
     <col min="7" max="7" width="5.25" style="6" customWidth="1"/>
@@ -12208,9 +12220,21 @@
       </c>
     </row>
     <row r="253" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B253" s="4" t="s">
+        <v>1265</v>
+      </c>
+      <c r="C253" s="1" t="s">
+        <v>1267</v>
+      </c>
+      <c r="H253" s="1" t="s">
+        <v>654</v>
+      </c>
       <c r="J253" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>00</v>
+        <v>001152</v>
+      </c>
+      <c r="L253" s="2" t="s">
+        <v>1266</v>
       </c>
     </row>
     <row r="254" spans="2:13" x14ac:dyDescent="0.2">

--- a/11_付费课程/99.资料/文章信息备忘表.xlsx
+++ b/11_付费课程/99.资料/文章信息备忘表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Disks\E\Writing\11_付费课程\99.资料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FB05A78-3B8E-44BC-905B-414A5E5EBB7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42C111CE-BE12-4440-A45D-FA09A96465F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4455" yWindow="855" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1740" uniqueCount="1268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1745" uniqueCount="1272">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -5056,6 +5056,22 @@
   </si>
   <si>
     <t>躺平工作、睡后收入？难道我被骗了？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1154</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1155</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>74383446</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mykonos-island-voxels-汉化版</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -5777,7 +5793,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="8" t="s">
         <v>558</v>
       </c>
@@ -5999,7 +6015,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20" s="8" t="s">
         <v>557</v>
       </c>
@@ -6227,7 +6243,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A28" s="8" t="s">
         <v>557</v>
       </c>
@@ -7052,7 +7068,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="57" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A57" s="8" t="s">
         <v>559</v>
       </c>
@@ -7388,7 +7404,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="68" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A68" s="8" t="s">
         <v>558</v>
       </c>
@@ -7418,7 +7434,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="69" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A69" s="8" t="s">
         <v>559</v>
       </c>
@@ -7445,7 +7461,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="70" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A70" s="8" t="s">
         <v>559</v>
       </c>
@@ -7955,7 +7971,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="88" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A88" s="8" t="s">
         <v>559</v>
       </c>
@@ -7991,7 +8007,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="89" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A89" s="8" t="s">
         <v>559</v>
       </c>
@@ -8186,7 +8202,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="95" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A95" s="8" t="s">
         <v>558</v>
       </c>
@@ -8246,7 +8262,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="97" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B97" s="4" t="s">
         <v>118</v>
       </c>
@@ -8345,7 +8361,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="100" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B100" s="4" t="s">
         <v>104</v>
       </c>
@@ -8378,7 +8394,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="101" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B101" s="4" t="s">
         <v>98</v>
       </c>
@@ -8705,7 +8721,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="112" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A112" s="8" t="s">
         <v>557</v>
       </c>
@@ -9608,7 +9624,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="145" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A145" s="8" t="s">
         <v>746</v>
       </c>
@@ -9662,7 +9678,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="147" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A147" s="8" t="s">
         <v>759</v>
       </c>
@@ -9716,7 +9732,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="149" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A149" s="8" t="s">
         <v>777</v>
       </c>
@@ -9743,7 +9759,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="150" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A150" s="8" t="s">
         <v>782</v>
       </c>
@@ -10893,7 +10909,7 @@
         <v>1011</v>
       </c>
     </row>
-    <row r="194" spans="2:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="194" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B194" s="4" t="s">
         <v>1015</v>
       </c>
@@ -11016,7 +11032,7 @@
         <v>1035</v>
       </c>
     </row>
-    <row r="199" spans="2:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="199" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B199" s="4" t="s">
         <v>1040</v>
       </c>
@@ -11112,7 +11128,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="203" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="203" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B203" s="4" t="s">
         <v>1062</v>
       </c>
@@ -11304,7 +11320,7 @@
         <v>1092</v>
       </c>
     </row>
-    <row r="211" spans="2:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="211" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B211" s="4" t="s">
         <v>1102</v>
       </c>
@@ -11454,7 +11470,7 @@
         <v>1131</v>
       </c>
     </row>
-    <row r="217" spans="2:12" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="217" spans="2:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B217" s="4" t="s">
         <v>1134</v>
       </c>
@@ -12018,7 +12034,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="242" spans="2:13" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="242" spans="2:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B242" s="4" t="s">
         <v>1187</v>
       </c>
@@ -12244,15 +12260,30 @@
       </c>
     </row>
     <row r="255" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B255" s="4" t="s">
+        <v>1268</v>
+      </c>
       <c r="J255" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>00</v>
+        <v>001154</v>
       </c>
     </row>
     <row r="256" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B256" s="4" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C256" s="1" t="s">
+        <v>1271</v>
+      </c>
+      <c r="H256" s="1" t="s">
+        <v>58</v>
+      </c>
       <c r="J256" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>00</v>
+        <v>001155</v>
+      </c>
+      <c r="L256" s="2" t="s">
+        <v>1270</v>
       </c>
     </row>
     <row r="257" spans="10:10" x14ac:dyDescent="0.2">

--- a/11_付费课程/99.资料/文章信息备忘表.xlsx
+++ b/11_付费课程/99.资料/文章信息备忘表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Disks\E\Writing\11_付费课程\99.资料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42C111CE-BE12-4440-A45D-FA09A96465F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD241B41-E3E9-430F-A59C-8BE35740238C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1745" uniqueCount="1272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1750" uniqueCount="1275">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -5072,6 +5072,18 @@
   </si>
   <si>
     <t>mykonos-island-voxels-汉化版</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>06591233</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>【浥尘伙伴社团独家密训】AI时代颠覆式高阶学习法</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NULL</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -12286,97 +12298,112 @@
         <v>1270</v>
       </c>
     </row>
-    <row r="257" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="257" spans="2:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="B257" s="4" t="s">
+        <v>1274</v>
+      </c>
+      <c r="C257" s="1" t="s">
+        <v>1273</v>
+      </c>
+      <c r="H257" s="1" t="s">
+        <v>1128</v>
+      </c>
       <c r="J257" s="5" t="str">
         <f t="shared" ref="J257:J314" si="9">"00"&amp;B257</f>
-        <v>00</v>
-      </c>
-    </row>
-    <row r="258" spans="10:10" x14ac:dyDescent="0.2">
+        <v>00NULL</v>
+      </c>
+      <c r="L257" s="2" t="s">
+        <v>1272</v>
+      </c>
+      <c r="M257" t="s">
+        <v>1252</v>
+      </c>
+    </row>
+    <row r="258" spans="2:13" x14ac:dyDescent="0.2">
       <c r="J258" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="259" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="259" spans="2:13" x14ac:dyDescent="0.2">
       <c r="J259" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="260" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="260" spans="2:13" x14ac:dyDescent="0.2">
       <c r="J260" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="261" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="261" spans="2:13" x14ac:dyDescent="0.2">
       <c r="J261" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="262" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="262" spans="2:13" x14ac:dyDescent="0.2">
       <c r="J262" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="263" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="263" spans="2:13" x14ac:dyDescent="0.2">
       <c r="J263" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="264" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="264" spans="2:13" x14ac:dyDescent="0.2">
       <c r="J264" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="265" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="265" spans="2:13" x14ac:dyDescent="0.2">
       <c r="J265" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="266" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="266" spans="2:13" x14ac:dyDescent="0.2">
       <c r="J266" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="267" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="267" spans="2:13" x14ac:dyDescent="0.2">
       <c r="J267" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="268" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="268" spans="2:13" x14ac:dyDescent="0.2">
       <c r="J268" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="269" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="269" spans="2:13" x14ac:dyDescent="0.2">
       <c r="J269" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="270" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="270" spans="2:13" x14ac:dyDescent="0.2">
       <c r="J270" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="271" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="271" spans="2:13" x14ac:dyDescent="0.2">
       <c r="J271" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="272" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="272" spans="2:13" x14ac:dyDescent="0.2">
       <c r="J272" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>

--- a/11_付费课程/99.资料/文章信息备忘表.xlsx
+++ b/11_付费课程/99.资料/文章信息备忘表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Disks\E\Writing\11_付费课程\99.资料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD241B41-E3E9-430F-A59C-8BE35740238C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79B934A6-039C-4523-B966-476422FCB644}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1750" uniqueCount="1275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1753" uniqueCount="1277">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -5084,6 +5084,14 @@
   </si>
   <si>
     <t>NULL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>65794308</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>男房东面对女租客一定要把握好分寸，特别是碰上Windows截图工具没有录屏功能时</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -5583,7 +5591,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:M314"/>
+  <dimension ref="A2:M313"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.25" style="8" customWidth="1"/>
@@ -11010,7 +11018,7 @@
         <v>1029</v>
       </c>
       <c r="J197" s="5" t="str">
-        <f t="shared" ref="J197:J256" si="5">"00"&amp;B197</f>
+        <f t="shared" ref="J197:J255" si="5">"00"&amp;B197</f>
         <v>001099</v>
       </c>
       <c r="K197" s="3" t="s">
@@ -12265,145 +12273,154 @@
         <v>1266</v>
       </c>
     </row>
-    <row r="254" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="254" spans="2:13" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="B254" s="4" t="s">
+        <v>1268</v>
+      </c>
+      <c r="C254" s="1" t="s">
+        <v>1276</v>
+      </c>
+      <c r="H254" s="1" t="s">
+        <v>654</v>
+      </c>
       <c r="J254" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>00</v>
+        <v>001154</v>
+      </c>
+      <c r="L254" s="2" t="s">
+        <v>1275</v>
       </c>
     </row>
     <row r="255" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B255" s="4" t="s">
-        <v>1268</v>
+        <v>1269</v>
+      </c>
+      <c r="C255" s="1" t="s">
+        <v>1271</v>
+      </c>
+      <c r="H255" s="1" t="s">
+        <v>58</v>
       </c>
       <c r="J255" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>001154</v>
-      </c>
-    </row>
-    <row r="256" spans="2:13" x14ac:dyDescent="0.2">
+        <v>001155</v>
+      </c>
+      <c r="L255" s="2" t="s">
+        <v>1270</v>
+      </c>
+    </row>
+    <row r="256" spans="2:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B256" s="4" t="s">
-        <v>1269</v>
+        <v>1274</v>
       </c>
       <c r="C256" s="1" t="s">
-        <v>1271</v>
+        <v>1273</v>
       </c>
       <c r="H256" s="1" t="s">
-        <v>58</v>
+        <v>1128</v>
       </c>
       <c r="J256" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>001155</v>
+        <f t="shared" ref="J256:J313" si="9">"00"&amp;B256</f>
+        <v>00NULL</v>
       </c>
       <c r="L256" s="2" t="s">
-        <v>1270</v>
-      </c>
-    </row>
-    <row r="257" spans="2:13" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="B257" s="4" t="s">
-        <v>1274</v>
-      </c>
-      <c r="C257" s="1" t="s">
-        <v>1273</v>
-      </c>
-      <c r="H257" s="1" t="s">
-        <v>1128</v>
-      </c>
+        <v>1272</v>
+      </c>
+      <c r="M256" t="s">
+        <v>1252</v>
+      </c>
+    </row>
+    <row r="257" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J257" s="5" t="str">
-        <f t="shared" ref="J257:J314" si="9">"00"&amp;B257</f>
-        <v>00NULL</v>
-      </c>
-      <c r="L257" s="2" t="s">
-        <v>1272</v>
-      </c>
-      <c r="M257" t="s">
-        <v>1252</v>
-      </c>
-    </row>
-    <row r="258" spans="2:13" x14ac:dyDescent="0.2">
+        <f t="shared" si="9"/>
+        <v>00</v>
+      </c>
+    </row>
+    <row r="258" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J258" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="259" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="259" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J259" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="260" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="260" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J260" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="261" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="261" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J261" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="262" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="262" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J262" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="263" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="263" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J263" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="264" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="264" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J264" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="265" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="265" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J265" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="266" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="266" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J266" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="267" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="267" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J267" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="268" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="268" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J268" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="269" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="269" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J269" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="270" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="270" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J270" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="271" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="271" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J271" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
     </row>
-    <row r="272" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="272" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J272" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
@@ -12651,12 +12668,6 @@
     </row>
     <row r="313" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J313" s="5" t="str">
-        <f t="shared" si="9"/>
-        <v>00</v>
-      </c>
-    </row>
-    <row r="314" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J314" s="5" t="str">
         <f t="shared" si="9"/>
         <v>00</v>
       </c>
